--- a/RSL/cribado/revision/REVISION_TEXTO_COMPLETO.xlsx
+++ b/RSL/cribado/revision/REVISION_TEXTO_COMPLETO.xlsx
@@ -3,19 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0_Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_TextoCompleto" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_Observaciones" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_TextoCompleto" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Extraccion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Calidad" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Extraccion" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Calidad" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1_TextoCompleto'!$A$1:$H$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2_Extraccion'!$A$1:$X$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3_Calidad'!$A$1:$U$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1_TextoCompleto'!$A$1:$H$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_Extraccion'!$A$1:$X$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_Calidad'!$A$1:$U$105</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +42,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +62,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -107,11 +116,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -200,7 +215,7 @@
     <comment ref="F6" authorId="0" shapeId="0">
       <text>
         <t>Texto original:
-—</t>
+No aplica: cumple los criterios de inclusión por ser un artículo original de conferencia ACM publicado en 2026, con texto completo disponible, aplicación a conducción vehicular real, modelos de Deep Learning y evaluación cuantitativa de comportamientos de riesgo. Se incluye como clasificación supervisada de conducción normal, agresiva y somnolienta, no como detección no supervisada de anomalías desconocidas.</t>
       </text>
     </comment>
     <comment ref="F7" authorId="0" shapeId="0">
@@ -287,16 +302,16 @@
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F42" authorId="0" shapeId="0">
-      <text>
-        <t>Texto original:
-No aplica</t>
+    <comment ref="F42" authorId="1" shapeId="0">
+      <text>
+        <t>Antes: CE-3
+Motivo: Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
       </text>
     </comment>
     <comment ref="F43" authorId="0" shapeId="0">
       <text>
         <t>Texto original:
-No aplica</t>
+No aplica: cumple los criterios de inclusión por ser un artículo original revisado por pares, publicado en 2025 y disponible en acceso abierto, que desarrolla y evalúa cuantitativamente un modelo de Deep Learning para anticipación de accidentes vehiculares. La tarea se considera detección anticipada de situaciones anormales de riesgo, no detección retrospectiva de accidentes.</t>
       </text>
     </comment>
     <comment ref="F44" authorId="0" shapeId="0">
@@ -654,3497 +669,3545 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>Revisión</author>
     <author>Normalización</author>
-    <author>Revisión</author>
   </authors>
   <commentList>
     <comment ref="E6" authorId="0" shapeId="0">
       <text>
-        <t>Texto original:
-EXCLUIDO</t>
-      </text>
-    </comment>
-    <comment ref="E9" authorId="0" shapeId="0">
+        <t>Antes: Trayectorias GPS
+Motivo: Acelerómetro, giroscopio y GPS del teléfono (UAH-DriveSet).</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Conducción real en autopistas y carreteras secundarias, según la descripción explícita de UAH-DriveSet. No se presenta una evaluación separada por tipo de vía ni se identifica en el artículo una ciudad concreta para cada recorrido. El análisis se centra en comportamiento individual de conducción y no en congestión de redes urbanas, intersecciones o accidentes registrados. Página 3, sección 3.1.</t>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Etiquetas supervisadas de tres estilos de conducción del conjunto UAH-DriveSet: normal, sleepy/drowsy y aggressive. Son categorías preexistentes del benchmark y no anomalías sintéticas inyectadas. El artículo no describe cómo se establecieron originalmente las etiquetas, si hubo anotadores independientes, qué criterios definieron la somnolencia o la agresividad ni si se verificaron nuevamente las etiquetas. Se utiliza SMOTE para crear ejemplos sintéticos de la clase minoritaria durante el procesamiento, pero estos son ejemplos de entrenamiento artificiales y no nuevas anomalías reales observadas. Páginas 1 y 3, sección 3.1.</t>
+      </text>
+    </comment>
+    <comment ref="J6" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Aprendizaje supervisado multiclase con tres categorías de conducción. Se entrenan clasificadores tradicionales y profundos, y se optimizan pesos de combinación mediante Particle Swarm Optimization. El balanceo de clases utiliza SMOTE y la selección de características emplea información mutua. No se presenta aprendizaje no supervisado, auto-supervisado, modelado de normalidad exclusivamente ni identificación abierta de anomalías desconocidas. Páginas 3–4, secciones 3.1–3.3 y Figura 1.</t>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+CNN unidimensional, red convolucional temporal TCN, red recurrente bidireccional BiLSTM y LSTM con mecanismo de atención. El ensamble final combina modelos seleccionados de Machine Learning y Deep Learning mediante pesos optimizados por PSO. PSO es un método metaheurístico de optimización y no una familia de Deep Learning. No se describen autoencoders, VAE, GAN, GNN, Transformers completos ni difusión. Páginas 1, 3–5.</t>
+      </text>
+    </comment>
+    <comment ref="M6" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Sí, con precisión conceptual: el sistema final es un ensamble heterogéneo que combina un modelo de aprendizaje automático tradicional, CatBoost, con arquitecturas profundas de familias diferentes, CNN 1D y TCN según la descripción de resultados. CNN 1D y TCN son ambas convolucionales, por lo que, bajo el criterio estricto de combinación de dos familias distintas de Deep Learning, la evidencia no permite afirmar que el ensamble final sea híbrido entre familias profundas. Se registra como ensamble híbrido ML + DL optimizado por PSO, pero no como híbrido DL multfamilia confirmado. La inclusión de Attention-LSTM como modelo comparado no demuestra que forme parte de la fusión final. Página 4, Figura 1; página 4, sección 4.3.</t>
+      </text>
+    </comment>
+    <comment ref="N6" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Conducción agresiva y conducción somnolienta como comportamientos potencialmente peligrosos, frente a conducción normal. El artículo menciona ejemplos generales de conducción rápida, frenado brusco, aceleración agresiva y cambios frecuentes de carril, pero el experimento no proporciona resultados independientes para cada maniobra. No se detectan accidentes reales, congestión anómala, errores de sensores ni eventos inesperados de tráfico sin etiqueta previa. Páginas 1–3.</t>
+      </text>
+    </comment>
+    <comment ref="S6" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Se informa partición estratificada de 70% entrenamiento, 15% validación y 15% prueba, preservando proporciones de clase. No se indica separación por conductor, trayecto, fecha o secuencia de origen; por ello, observaciones correlacionadas de los seis participantes podrían encontrarse en diferentes particiones. Los autores describen agrupación de datos y aplicación de SMOTE, imputación, selección de características y estandarización sin precisar si cada transformador se ajustó solo con entrenamiento. Esto constituye un riesgo de fuga de información no confirmado, pero metodológicamente relevante. La sección 4.2 advierte explícitamente posibles problemas de particionamiento relacionados con la representación de la clase minoritaria. Páginas 3–4.</t>
+      </text>
+    </comment>
+    <comment ref="U6" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Sí. Se comparan directamente cuatro métodos no profundos: CatBoost, XGBoost, KNN y ExtraTrees. CatBoost obtiene accuracy 94.47%, XGBoost 72.65%, ExtraTrees 76.20% y KNN 60.11%. Estos baselines permiten contrastar el ensamble con técnicas tradicionales, aunque no aíslan completamente el aporte de PSO frente a una fusión sin optimización. Página 5, Tabla 1.</t>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 GPS/trayectorias</t>
       </text>
     </comment>
-    <comment ref="H9" authorId="0" shapeId="0">
+    <comment ref="H9" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales con anomalías sintéticas</t>
       </text>
     </comment>
-    <comment ref="K9" authorId="0" shapeId="0">
+    <comment ref="K9" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autoencoder (VAE)</t>
       </text>
     </comment>
-    <comment ref="N9" authorId="0" shapeId="0">
+    <comment ref="N9" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Conducción anómala (velocidad, aceleración y dirección)</t>
       </text>
     </comment>
-    <comment ref="S9" authorId="0" shapeId="0">
+    <comment ref="S9" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No especificada claramente</t>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Imágenes/CCTV</t>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
+    <comment ref="F10" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano, rural y autopistas</t>
       </text>
     </comment>
-    <comment ref="H10" authorId="0" shapeId="0">
+    <comment ref="H10" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales; aumentación sintética mediante rotación, desenfoque gaussiano y ruido</t>
       </text>
     </comment>
-    <comment ref="K10" authorId="0" shapeId="0">
+    <comment ref="K10" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CNN (YOLO)</t>
       </text>
     </comment>
-    <comment ref="N10" authorId="0" shapeId="0">
+    <comment ref="N10" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes de tránsito/colisiones vehiculares</t>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 411 entrenamiento; 35 validación; 148 prueba</t>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0">
+    <comment ref="E11" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Videos/CCTV</t>
       </text>
     </comment>
-    <comment ref="F11" authorId="1" shapeId="0">
+    <comment ref="F11" authorId="0" shapeId="0">
       <text>
         <t>Antes: Autopista
 Motivo: Intersecciones y rampas/puentes de carretera.</t>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0">
+    <comment ref="H11" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales; videos de vigilancia vehicular; no se informa generación sintética</t>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0">
+    <comment ref="K11" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 DNN (red neuronal profunda)</t>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+    <comment ref="N11" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes vehiculares y patrones anómalos de movimiento/conducción</t>
       </text>
     </comment>
-    <comment ref="S11" authorId="0" shapeId="0">
+    <comment ref="S11" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No especificado; no se informa separación de entrenamiento, validación y prueba</t>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
+    <comment ref="E12" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal: sensores de tráfico, series temporales, video/imágenes y variables ambientales</t>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0">
+    <comment ref="F12" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopistas de Los Ángeles y área de la Bahía de San Francisco, Estados Unidos</t>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0">
+    <comment ref="H12" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales; conjuntos públicos de monitoreo vehicular; pruebas adicionales con ruido gaussiano simulado</t>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0">
+    <comment ref="K12" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 HGNN / GNN</t>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0">
+    <comment ref="N12" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes vehiculares, congestión, alteraciones meteorológicas y patrones anómalos del tráfico</t>
       </text>
     </comment>
-    <comment ref="S12" authorId="0" shapeId="0">
+    <comment ref="S12" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Partición 80:20; evaluación de generalización entrenando con METR-LA y probando con PEMS-BAY; pruebas con ruido y ablación</t>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0">
+    <comment ref="E13" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores de tráfico; series temporales numéricas de detectores de bucle inductivo</t>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0">
+    <comment ref="F13" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopista I-880, Estados Unidos</t>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0">
+    <comment ref="H13" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales; registros de sensores de autopista; muestras sintéticas de incidentes generadas mediante SMOTE para balancear entrenamiento</t>
       </text>
     </comment>
-    <comment ref="K13" authorId="0" shapeId="0">
+    <comment ref="K13" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 LSTM</t>
       </text>
     </comment>
-    <comment ref="N13" authorId="0" shapeId="0">
+    <comment ref="N13" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Incidentes de tráfico en autopistas, incluyendo accidentes, averías y otros eventos que interrumpen el flujo; clasificación binaria incidente/no incidente</t>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Separación por incidentes: 23 entrenamiento y 22 prueba; validación cruzada de 5 particiones para entrenar LSTM; evaluación en conjunto de prueba de la autopista I-880</t>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0">
+    <comment ref="E14" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Videos de conducción; cámaras vehiculares dashcam; flujo óptico y trayectorias de objetos</t>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0">
+    <comment ref="F14" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Escenarios reales de conducción vial; múltiples condiciones meteorológicas y de iluminación; ubicación geográfica específica no reportada</t>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Datos reales; videos capturados desde vehículos en movimiento, con anotaciones de anomalías; entrenamiento utilizando exclusivamente fotogramas normales previos al incidente</t>
       </text>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0">
+    <comment ref="K14" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Transformer; GRU; redes convolucionales; memoria neuronal con mecanismos de atención</t>
       </text>
     </comment>
-    <comment ref="M14" authorId="0" shapeId="0">
+    <comment ref="M14" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; atención multi-cabeza tipo Transformer para integrar movimiento global y local</t>
       </text>
     </comment>
-    <comment ref="N14" authorId="0" shapeId="0">
+    <comment ref="N14" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes, colisiones vehículo-vehículo, colisiones vehículo-peatón, colisiones con obstáculos, pérdida de control y otros eventos anómalos; anomalías ego-involved y non-ego</t>
       </text>
     </comment>
-    <comment ref="S14" authorId="0" shapeId="0">
+    <comment ref="S14" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 División estándar de DoTA y DADA-2000 siguiendo trabajos previos; entrenamiento con fotogramas precursores normales; evaluación por AUC a nivel de fotograma y por categorías; ablaciones de tareas, memoria y capas</t>
       </text>
     </comment>
-    <comment ref="E15" authorId="0" shapeId="0">
+    <comment ref="E15" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Datos multimodales de tráfico vehicular: imágenes de cámaras, nubes de puntos LiDAR, sonido, temperatura, velocidad, flujo y densidad vehicular</t>
       </text>
     </comment>
-    <comment ref="F15" authorId="0" shapeId="0">
+    <comment ref="F15" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopistas y túneles; redes viales de Los Ángeles y Bahía de San Francisco, California, Estados Unidos</t>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0">
+    <comment ref="H15" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Datos reales de sensores vehiculares complementados con experimentos y simulaciones; no se documenta completamente la procedencia y alineación de las cuatro modalidades propuestas</t>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0">
+    <comment ref="J15" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aprendizaje supervisado con optimización CPLE</t>
       </text>
     </comment>
-    <comment ref="K15" authorId="0" shapeId="0">
+    <comment ref="K15" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Heterogeneous Graph Neural Network (HGNN); Graph Convolutional Network (GCN); LSTM; mecanismos de atención; optimización Contrastive Pessimistic Likelihood Estimation (CPLE)</t>
       </text>
     </comment>
-    <comment ref="M15" authorId="0" shapeId="0">
+    <comment ref="M15" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; mecanismo de atención para ponderar dinámicamente la contribución de cada modalidad</t>
       </text>
     </comment>
-    <comment ref="N15" authorId="0" shapeId="0">
+    <comment ref="N15" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes de tránsito, congestión vehicular, anomalías relacionadas con condiciones meteorológicas y alteraciones del flujo vehicular</t>
       </text>
     </comment>
-    <comment ref="S15" authorId="0" shapeId="0">
+    <comment ref="S15" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 División 80:20; entrenamiento con 100 épocas, Adam, learning rate=0.001, batch size=64, dropout=0.5; evaluación en escenarios estáticos y dinámicos; prueba METR-LA a PEMS-BAY; ruido gaussiano de 5%, 10%, 15% y 20%; ablaciones</t>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
+    <comment ref="E17" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Videos RGB de cámaras de vigilancia vial instaladas en unidades de carretera (RSU); características espaciales CNN y movimiento mediante flujo óptico</t>
       </text>
     </comment>
-    <comment ref="F17" authorId="1" shapeId="0">
+    <comment ref="F17" authorId="0" shapeId="0">
       <text>
         <t>Antes: Autopista
 Motivo: Intersecciones y autopistas.</t>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0">
+    <comment ref="H17" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Dataset de videos de escenas viales descritas como realistas; procedencia, nombre y repositorio no especificados; datos disponibles mediante solicitud a los autores</t>
       </text>
     </comment>
-    <comment ref="J17" authorId="0" shapeId="0">
+    <comment ref="J17" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aprendizaje supervisado con función de pérdida binary cross-entropy</t>
       </text>
     </comment>
-    <comment ref="K17" authorId="0" shapeId="0">
+    <comment ref="K17" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolutional Neural Network (CNN) ligera; análisis de flujo óptico; fusión espacial-temporal; clasificación mediante capa completamente conectada y función sigmoide</t>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0">
+    <comment ref="M17" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No se describe un mecanismo de atención; utiliza fusión de características CNN y flujo óptico</t>
       </text>
     </comment>
-    <comment ref="N17" authorId="0" shapeId="0">
+    <comment ref="N17" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes individuales, colisiones entre múltiples vehículos, maniobras anómalas y eventos sin accidente como vehículos detenidos e interferencia de peatones</t>
       </text>
     </comment>
-    <comment ref="S17" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Partición estratificada entrenamiento/validación/prueba sin porcentajes especificados; entrenamiento supervisado con binary cross-entropy; selección del umbral mediante ROC en validación; evaluación en conjunto de prueba; análisis de latencia y sensibilidad de ventana temporal K</t>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0">
+    <comment ref="E18" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Videos CCTV de tráfico vehicular y peatonal; trayectorias GPS derivadas de visión artificial; velocidades, aceleraciones, volumen vehicular, indicadores MTTC y DRAC</t>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0">
+    <comment ref="F18" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Dos cruces peatonales de mitad de cuadra equipados con RRFB en Florida, Estados Unidos: Marion County (29.04662, -82.46389) y Brevard County (28.32562, -80.60923); límite de velocidad de 35 mph</t>
       </text>
     </comment>
-    <comment ref="H18" authorId="0" shapeId="0">
+    <comment ref="H18" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Conjunto de datos propio obtenido mediante cámaras CCTV portátiles; validación complementaria mediante 20 minutos de video UAV por ubicación; datos disponibles mediante solicitud a los autores</t>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0">
+    <comment ref="J18" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aprendizaje supervisado de clasificación binaria; optimizador Adam; ajuste de hiperparámetros; función de pérdida no especificada explícitamente</t>
       </text>
     </comment>
-    <comment ref="K18" authorId="0" shapeId="0">
+    <comment ref="K18" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Time-Embedded Transformer basado en inTformer, con Time2Vec, atención multicabezal y codificación Transformer; ensemble mediante voting classifier</t>
       </text>
     </comment>
-    <comment ref="M18" authorId="0" shapeId="0">
+    <comment ref="M18" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; codificación temporal Time2Vec, mecanismo Multi-Head Self-Attention, conexiones residuales, normalización y dropout; red CNN de kernel 1 en la capa feed-forward</t>
       </text>
     </comment>
-    <comment ref="N18" authorId="0" shapeId="0">
+    <comment ref="N18" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Conflictos vehículo-vehículo por alcance; riesgo de colisión asociado con frenado brusco, variación de velocidad y actividad peatonal en cruces RRFB</t>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 División 80% entrenamiento y 20% prueba; SMOTE para equilibrar clases de entrenamiento; ajuste de learning rate, batch size, épocas, cabezas de atención y capas encoder; Adam; evaluación mediante Recall y FAR; validación de extracción de trayectorias mediante video UAV e Intersection over Union</t>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0">
+    <comment ref="E21" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Telemetría vehicular y secuencias espaciotemporales; GPS, velocidad, aceleración, orientación y relaciones entre segmentos viales; datos simulados CARLA y subconjuntos reales Comma.ai</t>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
+    <comment ref="F21" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Tráfico urbano de alta densidad, intersecciones y rutas de autopista/suburbanas; escenarios simulados CARLA y registros reales de conducción Comma.ai; no se especifica ubicación geográfica concreta de los datos reales</t>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0">
+    <comment ref="H21" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CARLA Autonomous Driving Simulator y Comma.ai; CARLA genera trayectorias y eventos simulados; Comma.ai proporciona registros reales de GPS, velocidad y orientación; no se identifican versiones, subconjuntos exactos ni enlaces directos a los datos utilizados</t>
       </text>
     </comment>
-    <comment ref="J21" authorId="0" shapeId="0">
+    <comment ref="J21" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aprendizaje profundo espaciotemporal federado; entrenamiento distribuido entre 3 clientes con 50 rondas federadas; personalización basada en divergencia entre modelos locales y global; poda dinámica de parámetros</t>
       </text>
     </comment>
-    <comment ref="K21" authorId="0" shapeId="0">
+    <comment ref="K21" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 MGTGCN (Multi-component Graph Temporal Graph Convolutional Network), integración de Temporal Convolutional Networks (TCN), Graph Convolutional Networks (GCN) y Graph Attention Networks (GAT)</t>
       </text>
     </comment>
-    <comment ref="M21" authorId="0" shapeId="0">
+    <comment ref="M21" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; tres bloques TCN con dilataciones 1, 2 y 4, kernel 3 y ReLU; GCN de dos capas y GAT de una cabeza; espacio latente de 64 dimensiones; conexiones residuales, normalización, dropout y fusión ponderada de características</t>
       </text>
     </comment>
-    <comment ref="N21" authorId="0" shapeId="0">
+    <comment ref="N21" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Conducción anómala en vehículos autónomos: frenadas repentinas, paradas bruscas, cambios ilegales de carril, desviaciones de trayectoria, aceleraciones irregulares y comportamientos relacionados con incidentes; análisis forense posterior al evento</t>
       </text>
     </comment>
-    <comment ref="S21" authorId="1" shapeId="0">
+    <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <t>Antes: Aleatoria
 Motivo: «No se detallan particiones».</t>
       </text>
     </comment>
-    <comment ref="E22" authorId="0" shapeId="0">
+    <comment ref="E22" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Imágenes RGB extraídas de videos de accidentes y conducción normal; fotogramas de cámaras vehiculares y cámaras de vigilancia de tráfico; resolución de entrada 224 × 224 píxeles</t>
       </text>
     </comment>
-    <comment ref="F22" authorId="1" shapeId="0">
+    <comment ref="F22" authorId="0" shapeId="0">
       <text>
         <t>Antes: Autopista
 Motivo: No especifica el tipo de vía.</t>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0">
+    <comment ref="H22" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CarCrash Dataset (CCD), repositorio https://github.com/Cogito2012/CarCrashDataset; CADP (CCTV Traffic Camera Accident Dataset), https://ankitshah009.github.io/accident_forecasting_traffic_camera; ambos identificados como públicos en la declaración de disponibilidad de datos</t>
       </text>
     </comment>
-    <comment ref="J22" authorId="0" shapeId="0">
+    <comment ref="J22" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Deep Learning supervisado basado en visión por computadora; combinación de redes neuronales convolucionales y Vision Transformers; inferencia local en vehículos y validación de alertas mediante arquitectura IoV de tres capas</t>
       </text>
     </comment>
-    <comment ref="K22" authorId="0" shapeId="0">
+    <comment ref="K22" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ensamble híbrido de Vision Transformer ViT-B/16 y EfficientNet-B0; ViT basado en mecanismos de autoatención y EfficientNet basado en redes neuronales convolucionales</t>
       </text>
     </comment>
-    <comment ref="M22" authorId="0" shapeId="0">
+    <comment ref="M22" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; ViT-B/16 con aproximadamente 86 millones de parámetros y 17.6 GFLOPs; EfficientNet-B0 con aproximadamente 5.3 millones de parámetros y 0.39 GFLOPs; ambos inicializados con pesos preentrenados ImageNet-1K y adaptados a dos clases; combinación mediante regla lógica AND</t>
       </text>
     </comment>
-    <comment ref="N22" authorId="0" shapeId="0">
+    <comment ref="N22" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes de tránsito y colisiones vehiculares identificados visualmente; clasificación de fotogramas Accident frente a No Accident; no se evalúa detección general de anomalías de trayectoria, velocidad o flujo vehicular ni predicción anticipada del accidente</t>
       </text>
     </comment>
-    <comment ref="S22" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Entrenamiento supervisado con AdamW, pesos ImageNet-1K y partición 80/20 con semilla 42; ViT CarCrash entrenado 8 épocas más 10 de ajuste fino, EfficientNet CarCrash 8 épocas, ViT CADP 8 épocas y EfficientNet CADP 5 épocas; tasas de aprendizaje de 5e-5 y 1e-4; evaluación mediante métricas de clasificación, matrices de confusión, latencia y ablación; experimentos en workstation</t>
       </text>
     </comment>
-    <comment ref="E23" authorId="0" shapeId="0">
+    <comment ref="E23" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias vehiculares reales; velocidad, distancia lateral y longitudinal entre vehículos, valor de riesgo y posición relativa; datos capturados mediante cámaras HD, INS, GNSS y radar de ondas milimétricas</t>
       </text>
     </comment>
-    <comment ref="F23" authorId="0" shapeId="0">
+    <comment ref="F23" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Seis túneles de montaña en Chongqing, China: Zengjiayan, Liujiatai, Nancheng, Nanping, Zhongliangshan Huafu y Xianghuang; escenarios de seguimiento vehicular y cambio de carril</t>
       </text>
     </comment>
-    <comment ref="H23" authorId="0" shapeId="0">
+    <comment ref="H23" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Datos experimentales propios recolectados en seis túneles de Chongqing mediante vehículo instrumentado; no se proporciona repositorio público ni enlace de descarga del dataset</t>
       </text>
     </comment>
-    <comment ref="J23" authorId="0" shapeId="0">
+    <comment ref="J23" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Deep Learning supervisado con modelado espaciotemporal de interacciones multivehiculares; integración de indicadores de seguridad vial y mecanismos de atención</t>
       </text>
     </comment>
-    <comment ref="K23" authorId="0" shapeId="0">
+    <comment ref="K23" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CNN-LSTM-Attention; red neuronal convolucional unidimensional, Long Short-Term Memory y mecanismo Multi-Head Attention</t>
       </text>
     </comment>
-    <comment ref="M23" authorId="0" shapeId="0">
+    <comment ref="M23" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; Conv1D para extracción espacial, LSTM para evolución temporal por celda, Multi-Head Attention para dependencias entre celdas y capa totalmente conectada para clasificación; entrada (64,2,9,5) y salida (64,8,4) según Tabla 1</t>
       </text>
     </comment>
-    <comment ref="N23" authorId="0" shapeId="0">
+    <comment ref="N23" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Estados anómalos de conducción y riesgo de colisión derivados de interacciones entre múltiples vehículos; riesgo bajo, moderado y alto; escenarios de seguimiento y cambio de carril; no detecta accidentes ocurridos directamente</t>
       </text>
     </comment>
-    <comment ref="S23" authorId="1" shapeId="0">
+    <comment ref="S23" authorId="0" shapeId="0">
       <text>
         <t>Antes: Prueba independiente
 Motivo: No describe la partición.</t>
       </text>
     </comment>
-    <comment ref="E25" authorId="0" shapeId="0">
+    <comment ref="E25" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Detección de anomalías y disrupciones del tráfico urbano a nivel de red y zonas locales</t>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F25" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anomalías de flujo vehicular asociadas a eventos meteorológicos extremos</t>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Deep Learning multitarea; encoder-decoder LSTM con atención y autoencoder</t>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J25" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Datos reales históricos de tráfico urbano de Nueva York</t>
       </text>
     </comment>
-    <comment ref="K25" authorId="0" shapeId="0">
+    <comment ref="K25" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 NYC Traffic Estimates 2010-2013; aproximadamente 700 millones de viajes de taxi</t>
       </text>
     </comment>
-    <comment ref="M25" authorId="0" shapeId="0">
+    <comment ref="M25" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 46 zonas urbanas; datos horarios de tiempos de viaje y pace</t>
       </text>
     </comment>
-    <comment ref="N25" authorId="0" shapeId="0">
+    <comment ref="N25" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Entrenamiento con tráfico normal; división cronológica con 20% para validación; ventanas de 24 horas; 25% de observaciones eliminadas artificialmente durante entrenamiento</t>
       </text>
     </comment>
-    <comment ref="S25" authorId="0" shapeId="0">
+    <comment ref="S25" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Detecta disrupciones del huracán Sandy del 30/10 al 02/11/2012 y anomalías durante la tormenta del 26-27/12/2010 y el periodo posterior</t>
       </text>
     </comment>
-    <comment ref="U25" authorId="0" shapeId="0">
+    <comment ref="U25" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 El modelo supera los métodos de referencia en imputación para porcentajes de datos faltantes de 10% a 50%; inferencia aproximada de 55 ms por secuencia</t>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 GPS/trayectorias</t>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0">
+    <comment ref="H27" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Etiquetado de validación; procedimiento no detallado</t>
       </text>
     </comment>
-    <comment ref="M27" authorId="0" shapeId="0">
+    <comment ref="M27" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí, VAE + LSTM</t>
       </text>
     </comment>
-    <comment ref="N27" authorId="0" shapeId="0">
+    <comment ref="N27" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias anómalas</t>
       </text>
     </comment>
-    <comment ref="S27" authorId="0" shapeId="0">
+    <comment ref="S27" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 2000 entrenamiento; 500 validación</t>
       </text>
     </comment>
-    <comment ref="E28" authorId="0" shapeId="0">
+    <comment ref="E28" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video/CCTV</t>
       </text>
     </comment>
-    <comment ref="F28" authorId="0" shapeId="0">
+    <comment ref="F28" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano y vial; múltiples escenarios</t>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0">
+    <comment ref="H28" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Etiquetas binarias de datasets; validación manual de imágenes</t>
       </text>
     </comment>
-    <comment ref="K28" authorId="0" shapeId="0">
+    <comment ref="K28" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CNN + RNN/ConvLSTM</t>
       </text>
     </comment>
-    <comment ref="M28" authorId="0" shapeId="0">
+    <comment ref="M28" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí, CNN + ConvLSTM</t>
       </text>
     </comment>
-    <comment ref="N28" authorId="0" shapeId="0">
+    <comment ref="N28" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/colisiones vehiculares</t>
       </text>
     </comment>
-    <comment ref="S28" authorId="0" shapeId="0">
+    <comment ref="S28" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Entrenamiento y validación; proporciones no reportadas</t>
       </text>
     </comment>
-    <comment ref="U28" authorId="0" shapeId="0">
+    <comment ref="U28" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí, solo segmentación SSIM/similitud de píxeles; no detector externo</t>
       </text>
     </comment>
-    <comment ref="E29" authorId="0" shapeId="0">
+    <comment ref="E29" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores/series temporales multivariadas</t>
       </text>
     </comment>
-    <comment ref="F29" authorId="0" shapeId="0">
+    <comment ref="F29" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano; red vial de Pekín, China</t>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0">
+    <comment ref="H29" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Registros de incidentes; procedimiento de etiquetado no detallado</t>
       </text>
     </comment>
-    <comment ref="J29" authorId="0" shapeId="0">
+    <comment ref="J29" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado; inconsistencia terminológica con sección 3.1</t>
       </text>
     </comment>
-    <comment ref="K29" authorId="0" shapeId="0">
+    <comment ref="K29" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 GNN / Graph Attention Network</t>
       </text>
     </comment>
-    <comment ref="M29" authorId="0" shapeId="0">
+    <comment ref="M29" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí, aprendizaje de grafos + atención + detección estadística</t>
       </text>
     </comment>
-    <comment ref="N29" authorId="0" shapeId="0">
+    <comment ref="N29" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Congestiones, accidentes, obras viales y cierres de carriles</t>
       </text>
     </comment>
-    <comment ref="S29" authorId="0" shapeId="0">
+    <comment ref="S29" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 80% entrenamiento; 20% validación; prueba independiente no reportada</t>
       </text>
     </comment>
-    <comment ref="U29" authorId="0" shapeId="0">
+    <comment ref="U29" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí, LOF, IFOREST, OCSVM, HBOS y COPOD</t>
       </text>
     </comment>
-    <comment ref="E39" authorId="0" shapeId="0">
+    <comment ref="E39" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias GPS; datos de posición y movimiento vehicular obtenidos originalmente mediante radares viales, transformados a coordenadas geográficas WGS84/GCJ02; características: velocidad, aceleración, cambios de carril, necesidad de cambio de carril, longitud y latitud (secciones 3.1, 4.1 y Tabla 1).</t>
       </text>
     </comment>
-    <comment ref="F39" authorId="0" shapeId="0">
+    <comment ref="F39" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano; análisis de vías urbanas y comportamiento a nivel de carril en Hangzhou y Chengdu, China.</t>
       </text>
     </comment>
-    <comment ref="H39" authorId="0" shapeId="0">
+    <comment ref="H39" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No reportado; se utilizan etiquetas de referencia Aggressive, Distracted y Normal (sección 3.1, p. 6; sección 4.3.1, p. 14), pero no se explica suficientemente quién realizó el etiquetado, cómo se verificó ni si procede de anotación manual o registros reales.</t>
       </text>
     </comment>
-    <comment ref="J39" authorId="0" shapeId="0">
+    <comment ref="J39" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; entrenamiento de clasificación multiclase con etiquetas verdaderas codificadas y función de pérdida de entropía cruzada, tres clases de conducción (p. 14, ecuación 16).</t>
       </text>
     </comment>
-    <comment ref="K39" authorId="0" shapeId="0">
+    <comment ref="K39" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM/GRU); variante modificada de GRU con interacción iterativa entre entrada y estado oculto.</t>
       </text>
     </comment>
-    <comment ref="M39" authorId="0" shapeId="0">
+    <comment ref="M39" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; la arquitectura profunda propuesta pertenece a la familia recurrente GRU. Se complementa con CRF y entropía de trayectorias, pero estos componentes no constituyen una segunda familia Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="N39" authorId="0" shapeId="0">
+    <comment ref="N39" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción; conducción agresiva y distraída identificadas como anomalías, frente a conducción normal, mediante análisis de trayectorias y cambios de carril a nivel de vía.</t>
       </text>
     </comment>
-    <comment ref="S39" authorId="0" shapeId="0">
+    <comment ref="S39" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No reportada; no se describe una partición explícita entrenamiento/prueba para la evaluación principal de detección ni separación temporal o por ubicación. La sección 5.5 utiliza 100 segmentos temporales densos para evaluar reconocimiento temprano, pero no demuestra que la partición del entrenamiento y prueba sea temporal.</t>
       </text>
     </comment>
-    <comment ref="U39" authorId="0" shapeId="0">
+    <comment ref="U39" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; los cinco baselines principales son modelos de redes neuronales profundas o arquitecturas con atención. No se presenta comparación cuantitativa con un detector tradicional no Deep Learning para la misma tarea.</t>
       </text>
     </comment>
-    <comment ref="E40" authorId="0" shapeId="0">
+    <comment ref="E40" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias vehiculares espaciotemporales extraídas de simulación microscópica y videovigilancia aérea; variables por vehículo: posición longitudinal, posición lateral, identificador de carril, velocidad longitudinal y aceleración longitudinal. Se representan como nodos de grafos dinámicos y sus relaciones de proximidad como aristas (secciones 3.1–3.2, p. 3).</t>
       </text>
     </comment>
-    <comment ref="F40" authorId="0" shapeId="0">
+    <comment ref="F40" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopistas; carreteras de múltiples carriles, incluyendo un tramo simulado de 5 millas con cuatro carriles y tramos reales de autopistas alemanas de tres carriles.</t>
       </text>
     </comment>
-    <comment ref="H40" authorId="0" shapeId="0">
+    <comment ref="H40" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 En simulación se dispone de etiquetas de referencia generadas a partir de escenarios controlados de comportamiento anómalo: speeding, slow, tailgating y stalled. Los vehículos se etiquetan como anómalos únicamente cuando manifiestan efectivamente el comportamiento anormal, no solo por su velocidad deseada (Apéndice A, p. 11). En highD no existen etiquetas de referencia de anomalías; se inspeccionan cualitativamente los casos con mayores puntuaciones (sección 4.1.2, p. 5).</t>
       </text>
     </comment>
-    <comment ref="J40" authorId="0" shapeId="0">
+    <comment ref="J40" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado; el autoencoder aprende patrones habituales de conducción mediante reconstrucción probabilística sin utilizar etiquetas de anomalía como objetivo de entrenamiento. Las etiquetas simuladas se utilizan para evaluación cuantitativa. El entrenamiento normal incluye una pequeña proporción de comportamientos anómalos (secciones 1.2 y 4.1).</t>
       </text>
     </comment>
-    <comment ref="K40" authorId="0" shapeId="0">
+    <comment ref="K40" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 GNN y recurrente (GRU); arquitectura híbrida de Graph Attention Networks, redes recurrentes y autoencoder profundo.</t>
       </text>
     </comment>
-    <comment ref="M40" authorId="0" shapeId="0">
+    <comment ref="M40" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; combina explícitamente dos familias de Deep Learning, redes neuronales recurrentes GRU y Graph Attention Networks, dentro de un autoencoder espaciotemporal.</t>
       </text>
     </comment>
-    <comment ref="N40" authorId="0" shapeId="0">
+    <comment ref="N40" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción anómalo en autopistas; exceso de velocidad respecto al contexto, circulación excesivamente lenta, seguimiento a distancia insegura (tailgating) y vehículos detenidos. También identifica anomalías sociales que dependen de las interacciones con otros conductores y del carril utilizado.</t>
       </text>
     </comment>
-    <comment ref="S40" authorId="0" shapeId="0">
+    <comment ref="S40" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; el estudio utiliza conjuntos separados de entrenamiento y prueba. En simulación se entrena con 180 minutos de tráfico normal y se prueba con cinco escenarios anómalos de 10 minutos cada uno. En highD se entrena con aproximadamente 350 minutos y se evalúa sobre una grabación no vista de 15 minutos (sección 4.1, p. 5). No se documenta una validación cruzada temporal sistemática ni separación por localización.</t>
       </text>
     </comment>
-    <comment ref="U40" authorId="0" shapeId="0">
+    <comment ref="U40" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; se compara con métodos tradicionales y no Deep Learning: interpolación temporal lineal (LTI), modelo de velocidad constante (CVM) y recuperación robusta de tensores (RTR). También se compara con modelos profundos Seq2Seq y STGAE (sección 4.2.1, pp. 5–6).</t>
       </text>
     </comment>
-    <comment ref="E41" authorId="0" shapeId="0">
+    <comment ref="E41" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Datos espaciotemporales de monitoreo vehicular obtenidos mediante la API de Amap; incluyen fecha, hora de muestreo, ubicación o segmento vial, velocidad del tráfico, longitud y latitud. Los registros de puntos de trayectoria y condiciones de circulación se transforman en imágenes de condiciones de tráfico (Traffic Condition Images, TCI), utilizando velocidades relativas normalizadas en valores de píxel entre 0 y 255 (sección 3.1, pp. 5–6; ecuaciones 1–3).</t>
       </text>
     </comment>
-    <comment ref="F41" authorId="0" shapeId="0">
+    <comment ref="F41" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Red vial urbana de Wuhan, China; comprende vías principales, carreteras urbanas, intersecciones, accesos a autopistas y corredores metropolitanos. El análisis considera tres escalas espaciales: carretera, región y ciudad, con evaluación cuantitativa en carretera y ciudad (secciones 1 y 4).</t>
       </text>
     </comment>
-    <comment ref="H41" authorId="0" shapeId="0">
+    <comment ref="H41" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 El entrenamiento es no supervisado y no requiere etiquetas de anomalías. Para la evaluación se identifican eventos anómalos mediante análisis de información procedente de plataformas de internet, noticias y publicaciones de la autoridad de tráfico de Wuhan (sección 3.1, p. 6). Los eventos examinados incluyen festividades y acontecimientos deportivos. El artículo no proporciona una descripción exhaustiva de un conjunto público de etiquetas por observación ni del procedimiento independiente de anotación.</t>
       </text>
     </comment>
-    <comment ref="J41" authorId="0" shapeId="0">
+    <comment ref="J41" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado; Traffic-ConvLSTM aprende las características espaciotemporales del tráfico habitual y posteriormente identifica desviaciones mediante comparación entre las condiciones observadas y las predicciones del modelo, utilizando diferencias del índice SSIM (secciones 2 y 3.2, pp. 3–8).</t>
       </text>
     </comment>
-    <comment ref="K41" authorId="0" shapeId="0">
+    <comment ref="K41" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CNN y redes recurrentes ConvLSTM; arquitectura híbrida espaciotemporal multiescala con componentes convolucionales y memoria de largo y corto plazo.</t>
       </text>
     </comment>
-    <comment ref="M41" authorId="0" shapeId="0">
+    <comment ref="M41" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; integra convoluciones espaciales multiescala y unidades recurrentes ConvLSTM para modelar conjuntamente dependencias espaciales y temporales. Se trata de una arquitectura híbrida dentro de Deep Learning, no de una combinación documentada con un clasificador tradicional independiente.</t>
       </text>
     </comment>
-    <comment ref="N41" authorId="0" shapeId="0">
+    <comment ref="N41" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anomalías espaciotemporales del flujo vehicular urbano, principalmente congestión no recurrente y alteraciones inusuales de la circulación respecto a patrones periódicos normales. Considera anomalías en escala de carretera, región y ciudad; analiza alteraciones vinculadas con el Día Nacional de China, Día del Trabajo, Festival del Bote del Dragón y Juegos Municipales de Wuhan (sección 4.2, pp. 10–12).</t>
       </text>
     </comment>
-    <comment ref="S41" authorId="0" shapeId="0">
+    <comment ref="S41" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Se realiza evaluación experimental sobre datos históricos reales de nueve meses y comparación con cinco arquitecturas de referencia (sección 4.1, pp. 8–10). Sin embargo, no se documentan de manera suficientemente explícita las proporciones de entrenamiento, validación y prueba, la separación cronológica exacta ni una validación cruzada temporal. Por tanto, no puede confirmarse una estrategia estricta de separación temporal sin fuga de información.</t>
       </text>
     </comment>
-    <comment ref="U41" authorId="0" shapeId="0">
+    <comment ref="U41" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí, se comparan cinco arquitecturas de Deep Learning: SAE, CNN-LSTM, Bi-LSTM, GAN y Transformer (Tabla 2, p. 10). No se presenta una comparación experimental directa con modelos tradicionales como ARIMA, STARIMA o descomposición tensorial, aunque se discuten en los trabajos relacionados.</t>
       </text>
     </comment>
-    <comment ref="E42" authorId="0" shapeId="0">
+    <comment ref="E42" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Datos espaciotemporales de monitoreo vehicular obtenidos mediante la API de Amap; incluyen fecha, hora de muestreo, ubicación o segmento vial, velocidad del tráfico, longitud y latitud. Los registros de puntos de trayectoria y condiciones de circulación se transforman en imágenes de condiciones de tráfico (Traffic Condition Images, TCI), utilizando velocidades relativas normalizadas en valores de píxel entre 0 y 255 (sección 3.1, pp. 5–6; ecuaciones 1–3).</t>
       </text>
     </comment>
-    <comment ref="F42" authorId="0" shapeId="0">
+    <comment ref="F42" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Red vial urbana de Wuhan, China; comprende vías principales, carreteras urbanas, intersecciones, accesos a autopistas y corredores metropolitanos. El análisis considera tres escalas espaciales: carretera, región y ciudad, con evaluación cuantitativa en carretera y ciudad (secciones 1 y 4).</t>
       </text>
     </comment>
-    <comment ref="H42" authorId="0" shapeId="0">
+    <comment ref="H42" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 El entrenamiento es no supervisado y no requiere etiquetas de anomalías. Para la evaluación se identifican eventos anómalos mediante análisis de información procedente de plataformas de internet, noticias y publicaciones de la autoridad de tráfico de Wuhan (sección 3.1, p. 6). Los eventos examinados incluyen festividades y acontecimientos deportivos. El artículo no proporciona una descripción exhaustiva de un conjunto público de etiquetas por observación ni del procedimiento independiente de anotación.</t>
       </text>
     </comment>
-    <comment ref="J42" authorId="0" shapeId="0">
+    <comment ref="J42" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado; Traffic-ConvLSTM aprende las características espaciotemporales del tráfico habitual y posteriormente identifica desviaciones mediante comparación entre las condiciones observadas y las predicciones del modelo, utilizando diferencias del índice SSIM (secciones 2 y 3.2, pp. 3–8).</t>
       </text>
     </comment>
-    <comment ref="K42" authorId="0" shapeId="0">
+    <comment ref="K42" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CNN y redes recurrentes ConvLSTM; arquitectura híbrida espaciotemporal multiescala con componentes convolucionales y memoria de largo y corto plazo.</t>
       </text>
     </comment>
-    <comment ref="M42" authorId="0" shapeId="0">
+    <comment ref="M42" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; integra convoluciones espaciales multiescala y unidades recurrentes ConvLSTM para modelar conjuntamente dependencias espaciales y temporales. Se trata de una arquitectura híbrida dentro de Deep Learning, no de una combinación documentada con un clasificador tradicional independiente.</t>
       </text>
     </comment>
-    <comment ref="N42" authorId="0" shapeId="0">
+    <comment ref="N42" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anomalías espaciotemporales del flujo vehicular urbano, principalmente congestión no recurrente y alteraciones inusuales de la circulación respecto a patrones periódicos normales. Considera anomalías en escala de carretera, región y ciudad; analiza alteraciones vinculadas con el Día Nacional de China, Día del Trabajo, Festival del Bote del Dragón y Juegos Municipales de Wuhan (sección 4.2, pp. 10–12).</t>
       </text>
     </comment>
-    <comment ref="S42" authorId="0" shapeId="0">
+    <comment ref="S42" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Se realiza evaluación experimental sobre datos históricos reales de nueve meses y comparación con cinco arquitecturas de referencia (sección 4.1, pp. 8–10). Sin embargo, no se documentan de manera suficientemente explícita las proporciones de entrenamiento, validación y prueba, la separación cronológica exacta ni una validación cruzada temporal. Por tanto, no puede confirmarse una estrategia estricta de separación temporal sin fuga de información.</t>
       </text>
     </comment>
-    <comment ref="U42" authorId="0" shapeId="0">
+    <comment ref="U42" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí, se comparan cinco arquitecturas de Deep Learning: SAE, CNN-LSTM, Bi-LSTM, GAN y Transformer (Tabla 2, p. 10). No se presenta una comparación experimental directa con modelos tradicionales como ARIMA, STARIMA o descomposición tensorial, aunque se discuten en los trabajos relacionados.</t>
       </text>
     </comment>
-    <comment ref="E43" authorId="0" shapeId="0">
-      <text>
-        <t>Texto original:
-Movilidad agregada; registros espaciotemporales de monitoreo vehicular obtenidos mediante Amap API, incluyendo velocidad, coordenadas geográficas, segmentos viales y tiempo de observación. Los datos se transforman en imágenes de condiciones de tráfico (Traffic Condition Images, TCI) para el procesamiento mediante redes neuronales (sección 3.1, pp. 5–6).</t>
-      </text>
-    </comment>
-    <comment ref="F43" authorId="0" shapeId="0">
-      <text>
-        <t>Texto original:
-Urbano; red vial de Wuhan, China, con análisis en escalas de carretera, región y ciudad.</t>
-      </text>
-    </comment>
-    <comment ref="H43" authorId="0" shapeId="0">
-      <text>
-        <t>Texto original:
-El entrenamiento no utiliza etiquetas de anomalía. Para la evaluación se emplea información contextual de eventos obtenida de plataformas de internet, noticias y publicaciones de autoridades de tráfico de Wuhan (sección 3.1, p. 6). No se documenta un conjunto exhaustivo de etiquetas verificadas por observación ni un protocolo independiente de anotación.</t>
-      </text>
-    </comment>
-    <comment ref="J43" authorId="0" shapeId="0">
-      <text>
-        <t>Texto original:
-No supervisado; el modelo aprende regularidades espaciotemporales del tráfico y detecta desviaciones comparando condiciones observadas y estimadas mediante SSIM (secciones 2 y 3.2).</t>
-      </text>
-    </comment>
-    <comment ref="K43" authorId="0" shapeId="0">
-      <text>
-        <t>Texto original:
-Convolucional (CNN) y Recurrente (ConvLSTM); arquitectura profunda espaciotemporal con convoluciones multiescala y memoria recurrente.</t>
-      </text>
-    </comment>
-    <comment ref="M43" authorId="0" shapeId="0">
-      <text>
-        <t>Texto original:
-Sí; integra explícitamente componentes convolucionales y recurrentes ConvLSTM para aprender relaciones espaciales y temporales.</t>
-      </text>
-    </comment>
-    <comment ref="N43" authorId="0" shapeId="0">
-      <text>
-        <t>Texto original:
-Congestión atípica y alteraciones espaciotemporales anormales de circulación urbana. Incluye anomalías asociadas con festividades, eventos deportivos y cambios inesperados de las condiciones del tráfico, evaluadas en escalas de carretera y ciudad (sección 4.2, pp. 10–12).</t>
+    <comment ref="E43" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Video de cámaras vehiculares dashcam con secuencias RGB; representaciones visuales extraídas por red neuronal; texto estructurado procedente de informes de accidentes; conocimiento contextual sobre condiciones de conducción, factores de riesgo y situaciones sin colisión. El modelo combina características visuales y textuales, mientras GPT-4o genera explicaciones y recomendaciones a partir de predicciones y contexto. No se describe una entrada operativa principal basada en sensores inductivos, GPS de trayectorias o series de velocidad agregada. Páginas 1–7, Figuras 1–4.</t>
+      </text>
+    </comment>
+    <comment ref="F43" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Escenarios viales reales observados desde vehículos en movimiento, con interacciones entre automóviles y otros usuarios de la vía. DAD reúne videos de seis ciudades de Taiwán; A3D contiene escenarios urbanos de Asia oriental; CCD combina videos de accidentes de YouTube y conducción normal de BDD100K. Los resultados no se desagregan sistemáticamente en urbano frente a autopista. No corresponde afirmar validación específica en autopistas sin evidencia adicional. Página 8, sección 4.1.</t>
+      </text>
+    </comment>
+    <comment ref="H43" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Los videos positivos y negativos proceden de benchmarks publicados con anotaciones de accidentes y momentos de ocurrencia; CCD también aporta anotaciones generales sobre condiciones y factores asociados. DAD alinea el accidente en el fotograma 90, mientras CCD lo sitúa en los últimos 2 s. A3D contiene videos positivos y genera segmentos negativos de la misma colección, por lo que la independencia de estos negativos requiere cautela. Para enriquecer el conocimiento de dominio se utilizan informes reales del DMV y 500 informes sintéticos de situaciones sin colisión generados mediante prompts. No se reporta una nueva anotación manual independiente de todos los videos de prueba. Páginas 4–5 y 8, Tabla 2.</t>
+      </text>
+    </comment>
+    <comment ref="J43" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Aprendizaje supervisado para anticipación binaria de accidentes mediante etiquetas de accidente/no accidente y supervisión temporal asociada a la proximidad del evento. Emplea características de modelos previamente entrenados, alineamiento multimodal y optimización de pérdidas con un umbral de decisión aprendible. Los informes sintéticos amplían las representaciones de situaciones seguras, pero no convierten el detector principal en un método no supervisado. La generación de recomendaciones con GPT-4o es posterior a la predicción de riesgo. Páginas 3–8.</t>
+      </text>
+    </comment>
+    <comment ref="K43" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Arquitectura profunda multimodal de dos ramas: CNN VGG-16 para características visuales, modelo visión-lenguaje Long-CLIP para representaciones textuales, mecanismo de atención multi-head para agregación y alineamiento, módulo temporal de anticipación y componente de lenguaje GPT-4o para retroalimentación. Se considera híbrido por integrar familias distintas de DL, principalmente CNN y Transformer/atención, no simplemente por combinar estadística y red neuronal. Páginas 3–8, Figura 2.</t>
+      </text>
+    </comment>
+    <comment ref="M43" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Sí. Se integran una CNN visual VGG-16 y representaciones basadas en Transformer de Long-CLIP, con atención multi-head y aprendizaje conjunto de la decisión de riesgo. GPT-4o añade generación de explicaciones, pero debe distinguirse del núcleo que produce AP y mTTA. La combinación CNN más Transformer satisface el criterio de dos familias DL diferentes. No se debe registrar como una combinación CNN–LSTM o GNN–GRU, pues no es la arquitectura propuesta.</t>
+      </text>
+    </comment>
+    <comment ref="N43" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+Anticipación de colisiones y accidentes de tráfico, incluidos riesgos derivados de interacciones entre vehículos, cambios de carril y maniobras próximas a la colisión. El sistema distingue videos positivos y negativos y estima riesgo temporal antes del accidente. Los factores meteorológicos, iluminación, carretera y tipo de colisión aportan contexto y permiten análisis por escenarios, pero no equivalen a categorías independientes de anomalía con F1 individual reportado. No se estudia principalmente fallo de sensor, anomalía de GPS o congestión atípica. Páginas 1–3 y 8–11.</t>
       </text>
     </comment>
     <comment ref="S43" authorId="0" shapeId="0">
       <text>
-        <t>Texto original:
-No reportada; aunque el estudio utiliza nueve meses de datos históricos y realiza evaluación experimental, no especifica de forma suficientemente clara las proporciones ni los periodos exactos de entrenamiento, validación y prueba. Tampoco documenta una partición temporal rigurosa que permita descartar fuga de información.</t>
-      </text>
-    </comment>
-    <comment ref="U43" authorId="0" shapeId="0">
-      <text>
-        <t>Texto original:
-No; los cinco modelos de referencia evaluados cuantitativamente son arquitecturas Deep Learning. No se presenta comparación experimental directa con modelos tradicionales no profundos.</t>
-      </text>
-    </comment>
-    <comment ref="E44" authorId="0" shapeId="0">
+        <t>Antes: Aleatoria
+Motivo: Particiones oficiales de DAD y CCD.</t>
+      </text>
+    </comment>
+    <comment ref="U43" authorId="1" shapeId="0">
+      <text>
+        <t>Texto original:
+No se identifica una comparación experimental claramente configurada contra un detector clásico no profundo como Random Forest, SVM, Isolation Forest o reglas estadísticas independientes. Los baselines principales son métodos de aprendizaje profundo de anticipación de accidentes y arquitecturas de video. El umbral fijo 0,5 es un comparador de decisión dentro del modelo, no un baseline completo no-DL. Las ablaciones tampoco constituyen métodos clásicos independientes. Páginas 8–11, Tablas 3, 4 y 7.</t>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal; señales de sensores inerciales de teléfonos inteligentes y GPS, incluyendo aceleración longitudinal y lateral, velocidad angular, velocidad lineal, jerk, posición lateral respecto al centro del carril y ángulo respecto a la curvatura vial. Los sensores inerciales operan a 10 Hz y el GPS a 1 Hz; las señales se sincronizan a 1 Hz mediante una capa de fusión (secciones 4.1–4.2, pp. 5–7).</t>
       </text>
     </comment>
-    <comment ref="F44" authorId="0" shapeId="0">
+    <comment ref="F44" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ambos; carretera secundaria convencional M-100, de aproximadamente 16 km y un carril por sentido, y autovía A-2, con recorrido de aproximadamente 25 km y entre dos y cuatro carriles por sentido, ambas situadas en la región de Madrid, España (p. 6).</t>
       </text>
     </comment>
-    <comment ref="H44" authorId="0" shapeId="0">
+    <comment ref="H44" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Pseudo-etiquetas; aunque los recorridos se realizaron bajo perfiles de conducción preestablecidos, las etiquetas utilizadas por los modelos se derivan de reglas sobre variables medidas. La ecuación 7, p. 8, distingue normal/anómalo mediante aceleración longitudinal y aceleración lateral percibida respecto a sus medias; la ecuación 8 diferencia conducción agresiva/inatenta mediante jerk longitudinal respecto a su media. No se documenta validación independiente de todas las etiquetas generadas.</t>
       </text>
     </comment>
-    <comment ref="J44" authorId="0" shapeId="0">
+    <comment ref="J44" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; los clasificadores se entrenan con muestras etiquetadas como conducción normal/anómala y, en la segunda etapa, agresiva/inatenta. Las etiquetas proceden de reglas de aceleración y jerk y de los perfiles de conducción del dataset (ecuaciones 7–8, p. 8; sección 4.3, p. 9).</t>
       </text>
     </comment>
-    <comment ref="K44" authorId="0" shapeId="0">
+    <comment ref="K44" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM/GRU) como familia principal; también Convolucional (CNN) en una configuración alternativa. La configuración con mejor desempeño combina una red profunda LSTM con un clasificador estadístico basado en la transformada de Hotelling.</t>
       </text>
     </comment>
-    <comment ref="M44" authorId="0" shapeId="0">
+    <comment ref="M44" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No para la configuración principal LSTM-HT según la definición de combinación de familias Deep Learning, porque integra una red LSTM con una técnica estadística tradicional de Hotelling/PCA. Sí existe una configuración alternativa LSTM-CNN que combina dos familias profundas diferentes, pero no es la arquitectura de mejor rendimiento.</t>
       </text>
     </comment>
-    <comment ref="N44" authorId="0" shapeId="0">
+    <comment ref="N44" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción; identificación de maniobras anómalas, agresivas, imprudentes, distraídas o inatentas frente a conducción normal o segura. El sistema reconoce anomalías asociadas con aceleraciones bruscas, variaciones de velocidad, maniobras laterales y comportamiento riesgoso considerando indirectamente la geometría vial.</t>
       </text>
     </comment>
-    <comment ref="S44" authorId="0" shapeId="0">
+    <comment ref="S44" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Prueba independiente por conductor y evaluación aleatoria complementaria. La estrategia principal entrena con el conductor D1 y evalúa separadamente con D2–D6, evitando compartir el mismo conductor entre entrenamiento y prueba (secciones 4.3 y 5.1, pp. 9 y 13–14). También se describe una partición aleatoria inicial 50% entrenamiento y 50% prueba y una evaluación denominada 5-fold con todos los perfiles. El artículo no documenta separación temporal cronológica ni una partición por ubicación.</t>
       </text>
     </comment>
-    <comment ref="U44" authorId="0" shapeId="0">
+    <comment ref="U44" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; el sistema LSTM-HT utiliza un clasificador no profundo basado en Hotelling/PCA como componente de segunda etapa y lo compara con CNN y LSTM. No se evalúa un baseline completamente no profundo para la tarea binaria inicial normal/anómala.</t>
       </text>
     </comment>
-    <comment ref="E45" authorId="0" shapeId="0">
+    <comment ref="E45" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video; específicamente imágenes estáticas de accidentes de tránsito recopiladas de fuentes públicas en línea. No se utilizan secuencias temporales de video ni datos de sensores de tráfico; la entrada es una imagen RGB redimensionada a 640 × 640 píxeles (secciones 3.1 y 4.1, pp. 3–4 y 9).</t>
       </text>
     </comment>
-    <comment ref="F45" authorId="0" shapeId="0">
+    <comment ref="F45" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ambos; el conjunto incluye escenas de accidentes en entornos urbanos y autopistas, con predominio de imágenes urbanas. No se indican ciudades, carreteras concretas ni distribución numérica por entorno (sección 3.1, p. 3).</t>
       </text>
     </comment>
-    <comment ref="H45" authorId="0" shapeId="0">
+    <comment ref="H45" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación manual; los autores indican que cada imagen fue anotada para identificar la presencia de accidentes y recibió una etiqueta de gravedad moderada o severa basada en daño vehicular, intensidad del impacto y contexto visual. No se especifican número de anotadores, acuerdo interevaluador ni validación independiente de etiquetas (sección 3.1, p. 3).</t>
       </text>
     </comment>
-    <comment ref="J45" authorId="0" shapeId="0">
+    <comment ref="J45" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; el detector se entrena con imágenes anotadas de accidentes, regiones de interés y clases de gravedad moderada o severa. La función de entrenamiento optimiza pérdidas de localización, clasificación y distribución, como muestra la Figura 4, p. 11.</t>
       </text>
     </comment>
-    <comment ref="K45" authorId="0" shapeId="0">
+    <comment ref="K45" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN), con mecanismos de Atención/Transformer en forma de atención espacial y de canales. La base arquitectónica es YOLOv13n, con bloques convolucionales DS-C3K2 y FasterNet y módulo G-CSA de atención; no se presenta un Transformer completo como familia independiente (sección 3.2, pp. 4–7).</t>
       </text>
     </comment>
-    <comment ref="M45" authorId="0" shapeId="0">
+    <comment ref="M45" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; DSGF-YOLO integra convoluciones y módulos de atención dentro de una arquitectura YOLO, pero el artículo no demuestra una combinación de dos familias profundas autónomas, como CNN y Transformer completo, o CNN y LSTM. Los componentes G-CSA y FasterNet son mejoras internas del detector convolucional.</t>
       </text>
     </comment>
-    <comment ref="N45" authorId="0" shapeId="0">
+    <comment ref="N45" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes; detección visual y localización de accidentes de tráfico y clasificación de gravedad moderada o severa. Incluye colisiones de varios vehículos, vuelcos, choques frontales y accidentes en condiciones de baja iluminación (sección 4.2, pp. 10–12; Figura 5, p. 12).</t>
       </text>
     </comment>
-    <comment ref="S45" authorId="0" shapeId="0">
+    <comment ref="S45" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria; el conjunto de 2265 imágenes se dividió aleatoriamente en 1892 de entrenamiento, 262 de validación y 111 de prueba, aproximadamente 8:1:1 según la descripción de la sección 4.1, p. 9. No se documenta separación temporal, por ciudad, por fuente original ni por evento de accidente; tampoco se demuestra ausencia de imágenes relacionadas entre particiones.</t>
       </text>
     </comment>
-    <comment ref="U45" authorId="0" shapeId="0">
+    <comment ref="U45" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; todos los baselines experimentales reportados son detectores de Deep Learning: DETR, Faster R-CNN y variantes YOLO. No se incluye un clasificador tradicional de visión por computadora, SVM, Random Forest u otro método completamente no profundo.</t>
       </text>
     </comment>
-    <comment ref="E46" authorId="0" shapeId="0">
+    <comment ref="E46" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores/detectores; series de tiempo multivariadas de sensores radar instalados en autopista. Cada nodo registra velocidad, ocupación y volumen de tráfico en intervalos de 30 segundos. Los datos se representan como grafos espaciales por instante temporal; no se utilizan imágenes, video ni trayectorias GPS individuales (secciones V.A–V.B, pp. 7–9).</t>
       </text>
     </comment>
-    <comment ref="F46" authorId="0" shapeId="0">
+    <comment ref="F46" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopista; corredor oeste de Interstate 24, cerca de Nashville, Tennessee, Estados Unidos. Comprende aproximadamente 18 millas, cuatro carriles y 49 posiciones de sensores radar, equivalentes a 196 nodos carril–posición (sección V.A, pp. 7–8).</t>
       </text>
     </comment>
-    <comment ref="H46" authorId="0" shapeId="0">
+    <comment ref="H46" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales/registros; los accidentes utilizados como verdad de referencia proceden de registros oficiales del Nashville Traffic Management Center. El dataset también contiene anomalías identificadas por expertos mediante inspección visual de perfiles espacio-temporales de velocidad, pero estas etiquetas se utilizan para retirar periodos anómalos del entrenamiento y no como objetivos de evaluación (sección V.A, p. 8).</t>
       </text>
     </comment>
-    <comment ref="J46" authorId="0" shapeId="0">
+    <comment ref="J46" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado; aprendizaje de una sola clase mediante entrenamiento exclusivamente con patrones de tráfico normal, después de eliminar periodos afectados por accidentes y otras anomalías conocidas. Las etiquetas oficiales se emplean para depurar el entrenamiento y evaluar la detección, no para entrenar un clasificador supervisado de accidentes (secciones IV.C y V.B, pp. 6–9).</t>
       </text>
     </comment>
-    <comment ref="K46" authorId="0" shapeId="0">
+    <comment ref="K46" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Generativo (GAN/difusión) y Grafos (GNN); utiliza un Bidirectional GAN con redes Graph Attention Network en generador, codificador y discriminador. La detección se basa en reconstrucción de características, similar a un autoencoder, pero el entrenamiento principal es adversario con consistencia cíclica (sección IV.B, pp. 5–6).</t>
       </text>
     </comment>
-    <comment ref="M46" authorId="0" shapeId="0">
+    <comment ref="M46" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; integra dos familias profundas diferenciadas: un modelo generativo adversario bidireccional (BiGAN) y redes neuronales de grafos con atención (GAT). Los tres componentes adversarios utilizan capas GAT, mientras las pérdidas de consistencia cíclica permiten reconstrucción de datos y representaciones latentes (sección IV.B, pp. 5–6).</t>
       </text>
     </comment>
-    <comment ref="N46" authorId="0" shapeId="0">
+    <comment ref="N46" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes; detección temprana de accidentes registrados oficialmente y perturbaciones anómalas de velocidad, ocupación y volumen asociadas con incidentes en autopista. El modelo puede señalar nodos con comportamiento atípico, pero la evaluación cuantitativa principal utiliza accidentes reportados; no demuestra desempeño separado para vehículos detenidos, cierres de carril o eventos meteorológicos (secciones V.A y V.D, pp. 8–11; sección VI, p. 12).</t>
       </text>
     </comment>
-    <comment ref="S46" authorId="0" shapeId="0">
+    <comment ref="S46" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Temporal; los autores separan días completos: 14 días de entrenamiento, cinco de prueba y un día excluido por anomalías excesivas. El entrenamiento elimina periodos potencialmente contaminados por incidentes, considerando hasta 30 minutos previos y dos horas posteriores a accidentes reportados y dos horas posteriores a anomalías identificadas manualmente. No se especifica que la separación respete estrictamente el orden cronológico entre todos los días; sí existe separación por días, sin mezcla de observaciones del mismo día entre entrenamiento y prueba (sección V.B, p. 9).</t>
       </text>
     </comment>
-    <comment ref="U46" authorId="0" shapeId="0">
+    <comment ref="U46" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; los cinco baselines de la Tabla 1 son modelos profundos basados en grafos, autoencoders, LSTM o Transformer. El artículo menciona métodos tradicionales en trabajos relacionados, pero no los incluye en la comparación experimental de resultados (secciones II y V.D, pp. 2–3 y 9–10).</t>
       </text>
     </comment>
-    <comment ref="E47" authorId="0" shapeId="0">
+    <comment ref="E47" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores/detectores; series temporales de mediciones de radar vehicular con velocidad, ocupación de carril y volumen de tráfico, complementadas con variables derivadas de fecha y hora (secciones 3.1 y 4.1, pp. 3 y 5).</t>
       </text>
     </comment>
-    <comment ref="F47" authorId="0" shapeId="0">
+    <comment ref="F47" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopista; tramo de aproximadamente 18 millas de Interstate 24, Estados Unidos, con mediciones de tráfico distribuidas entre cuatro carriles (secciones 3.1 y 4.1, pp. 3 y 5).</t>
       </text>
     </comment>
-    <comment ref="H47" authorId="0" shapeId="0">
+    <comment ref="H47" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales/registros y anotación manual; el dataset contiene accidentes oficialmente reportados e indicadores de anomalías etiquetados por humanos. El modelo utiliza etiquetas binarias para distinguir tráfico normal de anomalías; adicionalmente, SMOTE genera ejemplos sintéticos de la clase minoritaria durante el balanceo, pero estos no constituyen la fuente original de las etiquetas (secciones 3.1, 3.2 y 4.3, pp. 3 y 6).</t>
       </text>
     </comment>
-    <comment ref="J47" authorId="0" shapeId="0">
+    <comment ref="J47" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; clasificador binario entrenado con etiquetas explícitas de tráfico normal y anomalías mediante pérdida binary cross-entropy. El remuestreo RUS+SMOTE se utiliza para equilibrar las clases durante el aprendizaje (secciones 2, 3.2, 3.4 y 4.3, pp. 2–4 y 6).</t>
       </text>
     </comment>
-    <comment ref="K47" authorId="0" shapeId="0">
+    <comment ref="K47" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM/GRU); arquitectura formada por una capa LSTM bidireccional seguida de dos capas LSTM convencionales y capas densas para clasificación binaria (sección 3.3, pp. 3–4; Figura 1, p. 4).</t>
       </text>
     </comment>
-    <comment ref="M47" authorId="0" shapeId="0">
+    <comment ref="M47" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; combina variantes bidireccional y unidireccional de una misma familia recurrente LSTM. RUS y SMOTE son técnicas de remuestreo de datos, no familias adicionales de Deep Learning; por tanto, el método de balanceo híbrido no convierte la arquitectura neuronal en un modelo híbrido de familias profundas.</t>
       </text>
     </comment>
-    <comment ref="N47" authorId="0" shapeId="0">
+    <comment ref="N47" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes y perturbaciones anómalas del flujo vehicular; el estudio describe accidentes y congestión como eventos de interés, pero la clasificación supervisada se presenta principalmente como detección de tráfico normal frente a eventos anómalos o accidentes. No ofrece resultados cuantitativos desagregados por congestión, tipo de accidente u otras categorías (resumen, p. 1; secciones 3.1 y 4.3, pp. 3 y 6).</t>
       </text>
     </comment>
-    <comment ref="S47" authorId="0" shapeId="0">
+    <comment ref="S47" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria; partición estratificada 80% entrenamiento y 20% prueba después de describir normalización y balanceo mediante RUS+SMOTE (sección 4.1, p. 5). Se menciona validación y early stopping, pero no se proporciona proporción separada de validación ni procedimiento de agrupación por día, sensor o secuencia. La redacción genera riesgo potencial de fuga de información por remuestreo previo a la partición, sin evidencia suficiente para confirmar que se produjo.</t>
       </text>
     </comment>
-    <comment ref="U47" authorId="0" shapeId="0">
+    <comment ref="U47" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; los seis modelos de referencia son arquitecturas de Deep Learning basadas en autoencoders, redes de grafos, LSTM, Transformer o perceptrones multicapa. No se presenta una comparación experimental con un método clásico no profundo (Tabla 2, p. 6).</t>
       </text>
     </comment>
-    <comment ref="E49" authorId="0" shapeId="0">
+    <comment ref="E49" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video (fotogramas estáticos extraídos de grabaciones de conducción y accidentes); la clasificación utiliza una sola imagen por predicción, sin modelado temporal explícito</t>
       </text>
     </comment>
-    <comment ref="F49" authorId="1" shapeId="0">
+    <comment ref="F49" authorId="0" shapeId="0">
       <text>
         <t>Antes: Autopista
 Motivo: Vías urbanas e interurbanas.</t>
       </text>
     </comment>
-    <comment ref="H49" authorId="0" shapeId="0">
+    <comment ref="H49" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Etiquetas heredadas de anotaciones temporales originales del CCD, no verificadas manualmente fotograma por fotograma; los videos normales aportan etiquetas negativas. ECVD: anotación manual de fotogramas según evidencia visual, con guía predefinida y segunda revisión. La etiqueta positiva representa accidente, aunque existe una contradicción en la codificación numérica entre las secciones 3.2 y 3.3.</t>
       </text>
     </comment>
-    <comment ref="J49" authorId="0" shapeId="0">
+    <comment ref="J49" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; aprendizaje por transferencia desde pesos preentrenados en ImageNet, seguido de ajuste para clasificación binaria accidente/no accidente</t>
       </text>
     </comment>
-    <comment ref="K49" authorId="0" shapeId="0">
+    <comment ref="K49" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Atención/Transformer y Convolucional (CNN), evaluados como arquitecturas alternativas</t>
       </text>
     </comment>
-    <comment ref="M49" authorId="0" shapeId="0">
+    <comment ref="M49" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; ViT, Swin Transformer y ResNet-50 se entrenan y comparan por separado. No se presenta una arquitectura que fusione dos familias distintas de Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="N49" authorId="0" shapeId="0">
+    <comment ref="N49" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes; detección visual de colisiones vehiculares, impactos laterales, choques por alcance, colisiones múltiples y accidentes de un solo vehículo; no se evalúa como objetivo principal la congestión anómala ni las trayectorias anómalas</t>
       </text>
     </comment>
-    <comment ref="S49" authorId="1" shapeId="0">
+    <comment ref="S49" authorId="0" shapeId="0">
       <text>
         <t>Antes: Aleatoria
 Motivo: Conjunto externo ECVD solo para prueba.</t>
       </text>
     </comment>
-    <comment ref="U49" authorId="0" shapeId="0">
+    <comment ref="U49" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; todos los modelos comparativos experimentales son Deep Learning. Los métodos clásicos aparecen en trabajos relacionados, pero no como baselines cuantitativos del experimento.</t>
       </text>
     </comment>
-    <comment ref="E52" authorId="0" shapeId="0">
+    <comment ref="E52" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal: trayectorias GPS y sensores vehiculares; combina latitud, longitud, velocidad, aceleración, desaceleración, ángulo de dirección, rumbo, uso de frenos, RPM, consumo de combustible, desviación de carril, geofencing y condiciones ambientales. La Tabla 2 (p. 8) documenta 23 atributos del conjunto de datos.</t>
       </text>
     </comment>
-    <comment ref="F52" authorId="0" shapeId="0">
+    <comment ref="F52" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ambos; incluye conducción urbana, suburbana y en autopistas dentro de una misma región logística (Dataset description, p. 6). No se reportan resultados de detección desagregados por cada entorno vial.</t>
       </text>
     </comment>
-    <comment ref="H52" authorId="0" shapeId="0">
+    <comment ref="H52" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Etiquetas existentes en el dataset; la Tabla 2 (p. 8) identifica Anomalous Event y Route Anomaly como variables de referencia para eventos anómalos y desviaciones de ruta. El entrenamiento utiliza etiquetas verdaderas y pérdida de entropía cruzada (ecuación 20, p. 14). No se documenta si las etiquetas originales fueron obtenidas mediante registros operativos, anotación humana, reglas automáticas o una combinación de procedimientos; tampoco se informa una validación independiente de su exactitud.</t>
       </text>
     </comment>
-    <comment ref="J52" authorId="0" shapeId="0">
+    <comment ref="J52" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; GNN-RMNet utiliza etiquetas de clase, una capa de clasificación softmax y pérdida categorical cross-entropy para aprender a distinguir comportamiento normal y anómalo (ecuaciones 19-20, p. 14; Algoritmo 3, p. 15). La estrategia TER se aplica para mitigar el desequilibrio de clases.</t>
       </text>
     </comment>
-    <comment ref="K52" authorId="0" shapeId="0">
+    <comment ref="K52" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Grafos (GNN) y Convolucional (CNN); combina aprendizaje relacional mediante Graph Neural Networks con redes profundas residuales ResNet y convoluciones separables MobileNet. Los componentes ResNet y MobileNet pertenecen a la familia convolucional, mientras que GNN representa una familia distinta de Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="M52" authorId="0" shapeId="0">
+    <comment ref="M52" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; combina dos familias diferentes de Deep Learning: redes de grafos (GNN) y redes convolucionales (ResNet y MobileNet). La combinación es explícita y constituye el núcleo de la arquitectura propuesta, no solamente un procesamiento estadístico añadido a un modelo profundo.</t>
       </text>
     </comment>
-    <comment ref="N52" authorId="0" shapeId="0">
+    <comment ref="N52" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción y trayectoria anómala; detecta frenadas bruscas, aceleraciones agresivas, cambios repentinos de carril, patrones de conducción peligrosos, desviaciones de rutas planificadas y violaciones de geofencing. Se evalúan tanto anomalías conductuales como desviaciones de rutas logísticas, sin centrarse exclusivamente en accidentes o congestión atípica.</t>
       </text>
     </comment>
-    <comment ref="S52" authorId="1" shapeId="0">
+    <comment ref="S52" authorId="0" shapeId="0">
       <text>
         <t>Antes: Prueba independiente
 Motivo: Sin proporciones ni protocolo de separación.</t>
       </text>
     </comment>
-    <comment ref="U52" authorId="0" shapeId="0">
+    <comment ref="U52" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; la Tabla 4 (p. 22) incluye comparadores no Deep Learning: SVM, AdaBoost, Random Forest, DBSCAN, K-means y Genetic Algorithm. El mejor baseline no profundo por accuracy es SVM, con 92%, y por AUC-ROC también SVM, con 0,93.</t>
       </text>
     </comment>
-    <comment ref="E53" authorId="0" shapeId="0">
+    <comment ref="E53" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Movilidad agregada y sensores/detectores; el conjunto NYC representa viajes de taxi mediante registros de origen, destino y tiempo, agregados en matrices horarias de movilidad entre zonas; PEMS-BAY contiene mediciones de velocidad y flujo vehicular de sensores instalados en autopistas. Los datos se representan como grafos dirigidos ponderados con nodos, aristas y pesos asociados a las relaciones de movilidad (pp. 3-4 y 8).</t>
       </text>
     </comment>
-    <comment ref="F53" authorId="0" shapeId="0">
+    <comment ref="F53" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ambos; NYC corresponde a movilidad urbana de taxis en Nueva York, mientras que PEMS-BAY procede de sensores de autopistas del área de la bahía de California. La evaluación principal de clasificación de anomalías mediante AUC se realiza en NYC; PEMS-BAY se utiliza para ablaciones con métricas de error (p. 8; Tablas 1-3, pp. 10-11).</t>
       </text>
     </comment>
-    <comment ref="H53" authorId="0" shapeId="0">
+    <comment ref="H53" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Inyectadas/sintéticas para la evaluación principal NYC: el dataset carece de etiquetas de anomalía y los autores introducen perturbaciones espaciales y temporales en intervalos seleccionados aleatoriamente (pp. 8-9). Las anomalías espaciales modifican tiempos de viaje de pares origen-destino y las temporales desplazan horarios 12 horas. En PEMS-BAY se mencionan incidentes de California Highway Patrol, pero el artículo no presenta para ese conjunto una evaluación independiente de clasificación con métricas AUC, precision o recall.</t>
       </text>
     </comment>
-    <comment ref="J53" authorId="0" shapeId="0">
+    <comment ref="J53" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado; el autoencoder aprende relaciones normales de tráfico mediante reconstrucción de grafos y utiliza errores elevados como evidencia de anomalía. El artículo especifica que el modelo se entrena con condiciones normales (p. 3) y utiliza MSE como función de pérdida y puntuación de anomalía durante la prueba (p. 8). Las etiquetas sintéticas se emplean para evaluar discriminación, no para definir una clasificación supervisada del modelo principal.</t>
       </text>
     </comment>
-    <comment ref="K53" authorId="0" shapeId="0">
+    <comment ref="K53" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autoencoder/VAE, Grafos (GNN), Convolucional (CNN/TCN) y Recurrente (GRU); la arquitectura combina autoencoder de grafos, convoluciones temporales dilatadas con transformación espejo, capas de convolución de grafos y mecanismos recurrentes inspirados en GRU (pp. 3-7).</t>
       </text>
     </comment>
-    <comment ref="M53" authorId="0" shapeId="0">
+    <comment ref="M53" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; combina familias distintas de Deep Learning: autoencoder de grafos, GNN/GCN, convoluciones temporales TCN y mecanismos recurrentes GRU. La integración ocurre dentro de una arquitectura única de codificación y reconstrucción espaciotemporal, no como un posprocesamiento estadístico aislado.</t>
       </text>
     </comment>
-    <comment ref="N53" authorId="0" shapeId="0">
+    <comment ref="N53" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anomalías espaciales y temporales de movilidad vehicular: cambios atípicos en relaciones de tráfico entre pares origen-destino, tiempos de viaje perturbados, patrones de flujo incompatibles con condiciones habituales y patrones de movilidad desplazados respecto de su horario normal. Pueden representar situaciones compatibles con congestión atípica o eventos de tráfico, pero las anomalías inyectadas en NYC no se corresponden con accidentes reales individualmente verificados (pp. 3 y 9).</t>
       </text>
     </comment>
-    <comment ref="S53" authorId="0" shapeId="0">
+    <comment ref="S53" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Separación temporal documentada, pero no cronológica prospectiva: entrenamiento NYC del 8 de enero al 31 de marzo de 2019, con 10% reservado para validación; prueba del 1 al 7 de enero de 2019 y una porción de Uber Movement. Los autores declaran exclusividad de registros entre entrenamiento y prueba y muestreo aleatorio uniforme (p. 9). La prueba corresponde a fechas anteriores a las utilizadas para entrenar, por lo que existe separación temporal de observaciones, pero no una evaluación prospectiva entrenando en el pasado y probando en el futuro.</t>
       </text>
     </comment>
-    <comment ref="U53" authorId="0" shapeId="0">
+    <comment ref="U53" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; la Tabla 1 (p. 10) incluye HA (Historical Average) y RTC como comparadores no basados en arquitecturas profundas, además de múltiples redes neuronales profundas. HA presenta AUC de 0,728, 0,687 y 0,711 para γ = 5%, 10% y 20%, respectivamente; RTC obtiene 0,736, 0,765 y 0,790.</t>
       </text>
     </comment>
-    <comment ref="E54" authorId="0" shapeId="0">
+    <comment ref="E54" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias GPS; datos reales de taxis y trayectorias sintéticas de movilidad vehicular, transformadas en secuencias de identificadores de segmentos viales mediante map matching. Cada segmento incorpora atributos de OpenStreetMap como longitud, tipo de vía, número de carriles, velocidad máxima, grado de entrada y salida y frecuencia histórica de uso (pp. 3-7).</t>
       </text>
     </comment>
-    <comment ref="F54" authorId="0" shapeId="0">
+    <comment ref="F54" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano; se evalúan recorridos de taxis en Porto, Portugal, y desplazamientos simulados sobre la red vial de San Francisco, Estados Unidos. El modelo representa las vías como un grafo dirigido, pero no presenta una evaluación específica de incidentes en autopistas (pp. 6-7).</t>
       </text>
     </comment>
-    <comment ref="H54" authorId="0" shapeId="0">
+    <comment ref="H54" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Inyectadas/sintéticas; los autores explican que no disponen de etiquetas públicas de anomalías y generan desvíos sobre trayectorias normales. Eliminan temporalmente uno o varios segmentos consecutivos de la red y recalculan una ruta alternativa mediante un algoritmo de camino mínimo. Crean anomalías restringidas, cuyo desvío no supera el 20% de la longitud de la trayectoria original, y no restringidas, sin ese límite. La Figura 2, página 8, ilustra ambos tipos sobre trayectorias de Porto. No existe validación de las etiquetas mediante incidentes reales o anotación humana (p. 7).</t>
       </text>
     </comment>
-    <comment ref="J54" authorId="0" shapeId="0">
+    <comment ref="J54" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Auto-supervisado para el aprendizaje principal de trayectorias mediante predicción autorregresiva del siguiente segmento vial; incorpora una tarea auxiliar supervisada de predicción de enlaces con etiquetas binarias derivadas de la conectividad y transiciones de la red. La detección final no requiere etiquetas de anomalías para entrenar el clasificador, por lo que también puede describirse como detección no supervisada de anomalías basada en un modelo auto-supervisado (pp. 5-6).</t>
       </text>
     </comment>
-    <comment ref="K54" authorId="0" shapeId="0">
+    <comment ref="K54" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Grafos (GNN/GAT) y Atención/Transformer; combina una Graph Attention Network de múltiples cabezas para codificar segmentos viales con un Transformer Decoder autorregresivo para modelar secuencias de movimiento. Incorpora Graph Positional Embedding, derivado de distancias de caminos mínimos, y una función de puntuación probabilística CW-NLL (pp. 4-6).</t>
       </text>
     </comment>
-    <comment ref="M54" authorId="0" shapeId="0">
+    <comment ref="M54" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; integra dos familias diferentes de Deep Learning: GNN mediante Graph Attention Network y arquitectura de atención secuencial mediante Transformer Decoder. Ambos componentes forman parte del modelo entrenado conjuntamente; Graph Positional Embedding y CW-NLL complementan la arquitectura, pero no constituyen familias profundas independientes.</t>
       </text>
     </comment>
-    <comment ref="N54" authorId="0" shapeId="0">
+    <comment ref="N54" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectoria anómala; específicamente desvíos de rutas vehiculares respecto de patrones habituales sobre una red vial. Se consideran dos variantes experimentales: desvíos restringidos, de longitud limitada, y no restringidos. Aunque los autores mencionan fraude, conducción errática y desviaciones temporales como aplicaciones potenciales, aclaran que sus experimentos se restringen a anomalías de desvío espacial (p. 4 y conclusión, p. 10).</t>
       </text>
     </comment>
-    <comment ref="S54" authorId="0" shapeId="0">
+    <comment ref="S54" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No reportada de forma suficiente; el artículo distingue trayectorias históricas de entrenamiento y conjuntos de prueba con anomalías generadas artificialmente, y especifica que el vocabulario se construye a partir de segmentos presentes en las trayectorias de entrenamiento (sección 5.1.4, p. 7). Sin embargo, no documenta porcentajes exactos de entrenamiento, validación y prueba, fechas de corte, separación por vehículo o agente, ni un protocolo temporal independiente para evaluar detección.</t>
       </text>
     </comment>
-    <comment ref="U54" authorId="0" shapeId="0">
+    <comment ref="U54" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; los cuatro baselines principales de la Tabla 2 son modelos de Deep Learning basados en autoencoders, modelos generativos profundos o Transformer. NLL y perplexity son estrategias de puntuación aplicadas al mismo modelo entrenado, no modelos independientes no profundos. El trabajo menciona métodos heurísticos como iBOAT en los antecedentes, pero no los incorpora en la comparación experimental principal.</t>
       </text>
     </comment>
-    <comment ref="E55" authorId="0" shapeId="0">
+    <comment ref="E55" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores/detectores simulados; series temporales de cinco atributos de tráfico por carril generadas mediante el simulador microscópico VISSIM: número de vehículos que pasan, velocidad media armónica, velocidad media aritmética, tiempo total de demora y porcentaje de ocupación. Las mediciones se registran cada 5 minutos; no se emplean trayectorias GPS ni video como entradas del modelo (sección IV.A, p. 6; Tabla 4, p. 7).</t>
       </text>
     </comment>
-    <comment ref="F55" authorId="0" shapeId="0">
+    <comment ref="F55" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano; red vial de la zona de demostración de conducción autónoma de Pangyo, Corea del Sur, con intersecciones, enlaces y carriles, simulando circulación mixta de vehículos autónomos y convencionales (Figura 2, p. 6).</t>
       </text>
     </comment>
-    <comment ref="H55" authorId="0" shapeId="0">
+    <comment ref="H55" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Inyectadas/sintéticas; las etiquetas de anomalía proceden de intervenciones controladas en VISSIM. AN1, AN2 y AN3 representan distintos grados de bloqueo de carriles; AN4 simula condiciones meteorológicas adversas mediante reducción de velocidad. Los eventos se programan en enlaces seleccionados y momentos conocidos, por lo que su presencia y duración son conocidas por construcción. Las estadísticas de incidentes reales de Gyeonggi-do sirven para diseñar escenarios, pero no constituyen etiquetas observadas en datos reales (sección IV.A y Tabla 2, p. 6; Tabla 3, p. 7).</t>
       </text>
     </comment>
-    <comment ref="J55" authorId="0" shapeId="0">
+    <comment ref="J55" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado; GMRT se entrena y valida exclusivamente con datos de tráfico normal para reconstruir las series temporales. Las etiquetas de anomalías sintéticas se utilizan posteriormente en la prueba, no como clases objetivo durante el entrenamiento (sección III.C, p. 5; sección IV.B, p. 6).</t>
       </text>
     </comment>
-    <comment ref="K55" authorId="0" shapeId="0">
+    <comment ref="K55" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Atención/Transformer; arquitectura profunda de encoders Transformer con atención multicabeza y aprendizaje temporal multirresolución. La información espacial se incorpora mediante una matriz de adyacencia de la red vial, no mediante capas GCN, GAT o un modelo GNN entrenable explícitamente descrito. Por ello, no corresponde clasificarla automáticamente como híbrido GNN-Transformer (sección III.B, pp. 4-5).</t>
       </text>
     </comment>
-    <comment ref="M55" authorId="0" shapeId="0">
+    <comment ref="M55" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; el modelo utiliza una familia profunda principal, Transformer. Aunque combina conectividad espacial, codificación temporal y procesamiento multirresolución, la transformación mediante matriz de adyacencia es una operación matemática fija y no una segunda familia neuronal profunda entrenada. Por tanto, no cumple el criterio de modelo híbrido entre dos familias diferentes de Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="N55" authorId="0" shapeId="0">
+    <comment ref="N55" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes y congestión atípica; la evaluación simula bloqueos de carriles de distinta severidad, asociados a interrupciones viales, y reducciones anormales de velocidad que representan condiciones meteorológicas adversas. AN1-AN3 son bloqueos de carriles y AN4 es una desaceleración generalizada. No se evalúan trayectorias individuales anómalas ni comportamientos de conducción etiquetados por vehículo (sección IV.A, p. 6; Tabla 2).</t>
       </text>
     </comment>
-    <comment ref="S55" authorId="0" shapeId="0">
+    <comment ref="S55" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Temporal; separación cronológica de los 14 días simulados: días 1-5 para entrenamiento con tráfico normal, días 6-7 para validación normal y días 8-14 para prueba con anomalías sintéticas. La validación determina el umbral y permite aplicar parada temprana. El conjunto de prueba es posterior y continuo respecto de la validación, sin mezcla temporal explícita de observaciones entre las tres fases (sección IV.B, p. 6).</t>
       </text>
     </comment>
-    <comment ref="U55" authorId="0" shapeId="0">
+    <comment ref="U55" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; todos los modelos de referencia incluidos en los experimentos son arquitecturas de Deep Learning. Aunque el artículo menciona GMM, PCA, SVM, Random Forest, k-NN y métodos de agrupamiento en trabajos relacionados, no presenta resultados experimentales comparativos de estos métodos frente a GMRT (sección II.A, pp. 2-3; sección IV.C, p. 6).</t>
       </text>
     </comment>
-    <comment ref="E56" authorId="0" shapeId="0">
+    <comment ref="E56" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores/detectores; registros reales de lazos inductivos que capturan el paso de vehículos, su velocidad y longitud. Los registros individuales se agregan temporalmente en intervalos de 3, 5, 10 y 15 minutos. Se prueban dos configuraciones de atributos: únicamente velocidad y velocidad más longitud del vehículo (sección 3.1, p. 3).</t>
       </text>
     </comment>
-    <comment ref="F56" authorId="0" shapeId="0">
+    <comment ref="F56" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopista; principales autopistas y vías de circunvalación alrededor de Amberes, Bélgica. La Figura 1, página 3, muestra la distribución geográfica de los sensores y la conectividad de la red vial.</t>
       </text>
     </comment>
-    <comment ref="H56" authorId="0" shapeId="0">
+    <comment ref="H56" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Inyectadas/sintéticas; aunque inicialmente se dispone de registros reales de eventos de tráfico, los autores descartan utilizarlos para la evaluación principal debido a la presencia de congestión habitual etiquetada y a la escasez de incidentes relevantes. En su lugar, inyectan anomalías contextuales en los datos reales mediante la biblioteca PyGod, siguiendo el procedimiento asociado a DOMINANT (sección 3.2.2, p. 4). Existe un estudio de caso adicional con un atasco real registrado, pero no constituye el conjunto principal de etiquetas de la evaluación ROC-AUC.</t>
       </text>
     </comment>
-    <comment ref="J56" authorId="0" shapeId="0">
+    <comment ref="J56" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado para la etapa de detección de anomalías en grafos, utilizando detectores profundos que identifican valores atípicos sin requerir etiquetas reales de incidentes durante su ajuste. La etapa previa de predicción de velocidad utiliza aprendizaje supervisado de series temporales, optimizando el error de predicción MAE. Por tanto, el sistema completo combina predicción supervisada y detección no supervisada (sección 3.2, pp. 3-4).</t>
       </text>
     </comment>
-    <comment ref="K56" authorId="0" shapeId="0">
+    <comment ref="K56" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Grafos (GNN) y Autoencoder; se evalúan Graph WaveNet y MTGNN para predicción espacio-temporal basada en grafos, además de STID como predictor profundo alternativo. La detección emplea DONE, AdOne, AnomalyDAE y DOMINANT, arquitecturas profundas de detección de valores atípicos en grafos, con mecanismos de representación y reconstrucción (secciones 3.2.1 y 3.2.2, pp. 3-4).</t>
       </text>
     </comment>
-    <comment ref="M56" authorId="0" shapeId="0">
+    <comment ref="M56" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; el sistema integra modelos profundos de predicción de series temporales, particularmente modelos espacio-temporales basados en grafos como MTGNN, con una segunda etapa independiente de detección profunda de anomalías en grafos, como DONE. Se trata de una arquitectura híbrida secuencial de predicción y detección, aunque ambas etapas pertenecen principalmente al ámbito de aprendizaje profundo sobre grafos. No se presenta como una única red entrenada conjuntamente de extremo a extremo.</t>
       </text>
     </comment>
-    <comment ref="N56" authorId="0" shapeId="0">
+    <comment ref="N56" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes y congestión atípica; el objetivo es detectar desviaciones significativas de velocidad asociadas con accidentes y atascos no habituales. El caso real corresponde a una congestión de causa desconocida en la carretera R2 de Amberes, el 13 de enero de 2021. Los autores distinguen estas anomalías de la congestión periódica de hora punta, considerada comportamiento normal (introducción, pp. 1-2; sección 5, p. 6).</t>
       </text>
     </comment>
-    <comment ref="S56" authorId="0" shapeId="0">
+    <comment ref="S56" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No reportada de forma suficiente; se menciona que los modelos entrenados se evalúan sobre un conjunto de prueba común para cada resolución temporal, pero no se describen porcentajes, fechas exactas de separación, estrategia temporal o aleatoria, ni prevención de solapamiento entre entrenamiento y prueba. La evaluación de detección utiliza anomalías inyectadas y múltiples ejecuciones, pero no detalla una partición independiente específica para dichas anomalías (secciones 3.2 y 4, pp. 3-5).</t>
       </text>
     </comment>
-    <comment ref="U56" authorId="0" shapeId="0">
+    <comment ref="U56" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; todos los detectores evaluados experimentalmente son métodos de Deep Learning sobre grafos. No se presenta un baseline tradicional de detección como Isolation Forest, LOF, One-Class SVM, PCA o un detector estadístico de umbral fijo. La mención de métodos convencionales en la revisión de literatura no equivale a una comparación experimental.</t>
       </text>
     </comment>
-    <comment ref="E59" authorId="0" shapeId="0">
+    <comment ref="E59" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores/detectores de tráfico urbano; registros agregados de flujo vehicular obtenidos mediante observaciones de automóviles y motocicletas en ubicaciones específicas. Los autores mencionan variables como número de vehículos y velocidad, pero no detallan exhaustivamente las características de entrada de cada dataset (secciones 1 y 4, pp. 1 y 4).</t>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0">
+    <comment ref="F59" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano; se estudian redes y observaciones de tráfico urbano en Odense, Dinamarca, y Pekín, China.</t>
       </text>
     </comment>
-    <comment ref="H59" authorId="0" shapeId="0">
+    <comment ref="H59" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No reportado con suficiente detalle; el Algoritmo 1 y la sección 3.4 indican que los conjuntos de entrenamiento y prueba disponen de ground truth binario que identifica cada flujo como normal o anómalo. Sin embargo, no se explica si esas etiquetas proceden de registros oficiales de incidentes, anotación manual, reglas automáticas, anomalías sintéticas o algún procedimiento de validación. No es correcto asumir que las etiquetas son reales y verificadas únicamente porque las mediciones de tráfico proceden de fuentes reales (sección 3.4, p. 4).</t>
       </text>
     </comment>
-    <comment ref="J59" authorId="0" shapeId="0">
+    <comment ref="J59" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; el entrenamiento utiliza ejemplos acompañados de ground truth binario normal/anómalo y el modelo aprende a clasificarlos. Se aplican transferencia de aprendizaje y minería de negativos difíciles, pero no se documenta un procedimiento de aprendizaje no supervisado para determinar las etiquetas finales (secciones 3.2-3.4, pp. 3-4).</t>
       </text>
     </comment>
-    <comment ref="K59" authorId="0" shapeId="0">
+    <comment ref="K59" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN); específicamente una adaptación de Faster R-CNN con propuestas de regiones, concatenación de características multiescala y minería de negativos difíciles. El agrupamiento k-means y la votación son componentes auxiliares no profundos (secciones 3.1-3.3, pp. 2-3).</t>
       </text>
     </comment>
-    <comment ref="M59" authorId="0" shapeId="0">
+    <comment ref="M59" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; aunque DCNN-TFO combina k-means, CNN y votación, no fusiona dos familias diferentes de Deep Learning. Los múltiples clasificadores pertenecen a la misma familia convolucional; el agrupamiento y la votación son técnicas auxiliares de aprendizaje automático y agregación (sección 3, pp. 2-4).</t>
       </text>
     </comment>
-    <comment ref="N59" authorId="0" shapeId="0">
+    <comment ref="N59" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Congestión atípica y patrones anormales de flujo vehicular urbano; el objetivo declarado es identificar outliers o comportamientos inesperados del flujo de tráfico. No se especifica una taxonomía de accidentes, incidentes, congestión recurrente, fallas de sensores o comportamientos de conducción, por lo que la categoría más precisa es anomalía de flujo vehicular urbano no desagregada por causa (introducción y secciones 3-4).</t>
       </text>
     </comment>
-    <comment ref="S59" authorId="1" shapeId="0">
+    <comment ref="S59" authorId="0" shapeId="0">
       <text>
         <t>Antes: Prueba independiente
 Motivo: Partición insuficientemente reportada.</t>
       </text>
     </comment>
-    <comment ref="U59" authorId="0" shapeId="0">
+    <comment ref="U59" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; se incluye una referencia basada en Support Vector Machine (SVM), aunque el artículo señala que el método comparado incorpora transferencia de aprendizaje. También se compara con CNN, que es un baseline profundo. La naturaleza exacta de la transferencia del baseline SVM no se desarrolla suficientemente en el artículo (sección 4, p. 4).</t>
       </text>
     </comment>
-    <comment ref="E60" authorId="0" shapeId="0">
+    <comment ref="E60" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal; fusión de señales de sensores vehiculares: acelerómetro triaxial (Acc_X, Acc_Y, Acc_Z), giroscopio triaxial (Gyro_X, Gyro_Y, Gyro_Z) y velocidad GPS. La adquisición se realiza mediante cámaras inteligentes Raven+ instaladas en vehículos; el modelo utiliza señales numéricas y no imágenes de video (secciones 3.1-3.2, pp. 5-7).</t>
       </text>
     </comment>
-    <comment ref="F60" authorId="1" shapeId="0">
+    <comment ref="F60" authorId="0" shapeId="0">
       <text>
         <t>Antes: Autopista
 Motivo: Pista de pruebas; no es urbano ni autopista.</t>
       </text>
     </comment>
-    <comment ref="H60" authorId="0" shapeId="0">
+    <comment ref="H60" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Pseudo-etiquetas; los eventos experimentales se segmentan mediante recorridos conocidos e intervalos de inactividad, pero sus instantes anómalos precisos se identifican automáticamente con dos autoencoders LSTM entrenados exclusivamente sobre conducción normal. Las anomalías se etiquetan cuando el error de reconstrucción supera un umbral y se distinguen giros izquierda/derecha o frenada/aceleración mediante el signo de las señales seleccionadas. No se documenta una validación independiente de todas las pseudoetiquetas por expertos o registros externos (secciones 4.1 y 5, pp. 10 y 13-16).</t>
       </text>
     </comment>
-    <comment ref="J60" authorId="0" shapeId="0">
+    <comment ref="J60" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado con pseudoetiquetado no supervisado previo; primero se utilizan autoencoders LSTM no supervisados para asignar etiquetas a señales de conducción y luego se entrenan dos clasificadores híbridos supervisados para distinguir conducción normal y dos tipos de anomalías por grupo (secciones 5-6, pp. 13-18).</t>
       </text>
     </comment>
-    <comment ref="K60" authorId="0" shapeId="0">
+    <comment ref="K60" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN), Recurrente (LSTM), Atención y Autoencoder; la etapa de etiquetado emplea autoencoders LSTM, mientras que la clasificación final combina 1D-CNN, LSTM, mecanismo de atención y capas completamente conectadas profundas FCDNN (Figuras 15 y 20, pp. 14 y 18).</t>
       </text>
     </comment>
-    <comment ref="M60" authorId="0" shapeId="0">
+    <comment ref="M60" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; integra diferentes familias de Deep Learning en una misma arquitectura de clasificación: CNN, LSTM y atención, además de capas FCDNN. Los autoencoders LSTM constituyen una etapa profunda adicional de generación de etiquetas (secciones 5-6, pp. 13-18).</t>
       </text>
     </comment>
-    <comment ref="N60" authorId="0" shapeId="0">
+    <comment ref="N60" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción; cuatro anomalías específicas: giro brusco a la izquierda (harsh left cornering), giro brusco a la derecha (harsh right cornering), frenada brusca (harsh braking) y aceleración rápida (rapid acceleration). La conducción normal constituye la clase de referencia. No se evalúa detección directa de accidentes o congestión vial (sección 3.1, p. 5; sección 6.3, p. 18).</t>
       </text>
     </comment>
-    <comment ref="S60" authorId="0" shapeId="0">
+    <comment ref="S60" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Prueba independiente por vehículo; Mazda, Toyota y BMW se destinan a entrenamiento, mientras que Malibu y Hyundai se reservan para evaluación (sección 5, p. 16). Esta separación reduce la superposición directa entre vehículos de entrenamiento y prueba. No se describe validación temporal independiente, evaluación en una instalación distinta ni múltiples particiones repetidas.</t>
       </text>
     </comment>
-    <comment ref="U60" authorId="0" shapeId="0">
+    <comment ref="U60" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; Random Forest y XGBoost son dos baselines de aprendizaje automático no profundo. También se incluyen FCDNN, 1D-CNN y LSTM como referencias de Deep Learning (Tabla 4, p. 21).</t>
       </text>
     </comment>
-    <comment ref="E61" authorId="0" shapeId="0">
+    <comment ref="E61" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video; secuencias de imágenes captadas por cámaras de tablero de vehículos (dashcam). Cada video se representa mediante 50 fotogramas consecutivos convertidos a escala de grises, redimensionados a 144 × 256 píxeles y aplanados en vectores de 36864 intensidades por instante (sección 5.3 y Tabla 3, p. 5).</t>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0">
+    <comment ref="F61" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No reportado como categoría vial única; el CCD contiene escenas de conducción vehicular y accidentes registrados desde cámaras frontales de automóviles. El artículo propone aplicaciones en carreteras urbanas y autopistas, pero no presenta una clasificación verificable de todos los videos por entorno urbano o autopista (secciones 5.1 y 8, pp. 4 y 9).</t>
       </text>
     </comment>
-    <comment ref="H61" authorId="0" shapeId="0">
+    <comment ref="H61" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales/registros; el CCD proporciona etiquetas originales de accidente y conducción normal asociadas a videos de tráfico. Los videos positivos también incluyen una secuencia binaria de 50 anotaciones temporales para localizar fotogramas del accidente, pero el estudio utiliza exclusivamente la etiqueta binaria a nivel de clip como objetivo de clasificación (Tabla 1 y sección 5.1, p. 4). El artículo no detalla un nuevo proceso independiente de auditoría de estas etiquetas.</t>
       </text>
     </comment>
-    <comment ref="J61" authorId="0" shapeId="0">
+    <comment ref="J61" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; clasificación binaria entrenada con etiquetas de video previamente disponibles, accidente frente a conducción normal. Utiliza entropía cruzada categórica y optimizador Adam (secciones 5.3-5.5, p. 5).</t>
       </text>
     </comment>
-    <comment ref="K61" authorId="0" shapeId="0">
+    <comment ref="K61" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM); utiliza exclusivamente capas LSTM como arquitectura profunda principal. No integra CNN, autoencoder, GNN ni Transformer en el detector propuesto. CNN y CNN-LSTM aparecen únicamente como modelos comparativos (secciones 5.4 y 5.6, pp. 5-6).</t>
       </text>
     </comment>
-    <comment ref="M61" authorId="0" shapeId="0">
+    <comment ref="M61" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; el modelo propuesto combina capas de una misma familia recurrente LSTM con una capa de clasificación densa, sin integrar dos familias diferenciadas de Deep Learning. CNN-LSTM es un baseline, no la arquitectura propuesta (secciones 5.4 y 5.6, pp. 5-6).</t>
       </text>
     </comment>
-    <comment ref="N61" authorId="0" shapeId="0">
+    <comment ref="N61" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes; detección binaria de presencia o ausencia de accidente de tráfico dentro de un clip de video. No se evalúan por separado congestión atípica, conducción peligrosa sin colisión, trayectorias anómalas ni fallos de sensores (secciones 5.1 y 6, pp. 4 y 6-8).</t>
       </text>
     </comment>
-    <comment ref="S61" authorId="0" shapeId="0">
+    <comment ref="S61" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria estratificada por video; validación cruzada de cinco folds, cada uno con 3600 clips para desarrollo y 900 para prueba, manteniendo 300 accidentes y 600 normales en cada fold de prueba. Los 50 fotogramas de cada clip permanecen juntos y la validación interna se obtiene de los folds de entrenamiento (sección 5.2 y Tabla 2, p. 4). No se documenta partición temporal, por ciudad ni por cámara independiente. La sección 6.7 aclara que los resultados de clasificación publicados proceden de resimulación con semilla, por lo que la aplicación efectiva del protocolo a predicciones reales queda sin confirmar.</t>
       </text>
     </comment>
-    <comment ref="U61" authorId="0" shapeId="0">
+    <comment ref="U61" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; Support Vector Machine (SVM) es un baseline tradicional no basado en Deep Learning. Además, CNN-only y CNN-LSTM constituyen baselines profundos (Tabla 5, p. 6; Tabla 9, p. 9).</t>
       </text>
     </comment>
-    <comment ref="F62" authorId="0" shapeId="0">
+    <comment ref="F62" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Vías urbanas, autopistas, carreteras rurales e intersecciones; el estudio comprende distintos entornos viales.</t>
       </text>
     </comment>
-    <comment ref="H62" authorId="0" shapeId="0">
+    <comment ref="H62" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación manual validada. En 4M-TAD, los fotogramas se etiquetan como normales (0) o anómalos (1), con revisión por especialistas, cribado y doble verificación (sección 3.1, p. 4). El modelo se entrena únicamente con segmentos normales; las etiquetas de anomalías se emplean para validación y evaluación. En AI City Challenge se utilizan las anotaciones de los eventos anómalos del conjunto de referencia.</t>
       </text>
     </comment>
-    <comment ref="J62" authorId="0" shapeId="0">
+    <comment ref="J62" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado; entrenamiento con segmentos normales y detección de desviaciones respecto al comportamiento aprendido, aunque se utilizan etiquetas de anomalías para calibración y evaluación.</t>
       </text>
     </comment>
-    <comment ref="K62" authorId="0" shapeId="0">
+    <comment ref="K62" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN) + recurrente/convolución temporal (ConvLSTM) + autoencoder variacional (VAE) + mecanismos de atención y fusión adaptativa.</t>
       </text>
     </comment>
-    <comment ref="M62" authorId="0" shapeId="0">
+    <comment ref="M62" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí. Combina extracción convolucional espacial, modelado temporal profundo y representación variacional en una arquitectura de doble flujo, con atención y fusión adaptativa.</t>
       </text>
     </comment>
-    <comment ref="N62" authorId="0" shapeId="0">
+    <comment ref="N62" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes de tránsito: colisiones entre vehículos, accidentes con bicicletas eléctricas, impactos contra objetos, vuelcos, vehículos detenidos y otros eventos anómalos captados por cámaras viales.</t>
       </text>
     </comment>
-    <comment ref="S62" authorId="0" shapeId="0">
+    <comment ref="S62" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Particiones independientes de entrenamiento, validación y prueba, con segmentos temporalmente continuos y entrenamiento exclusivo con comportamiento normal. AI City Challenge dispone originalmente de 100 videos de entrenamiento y 150 de prueba; se selecciona además validación independiente. No se identifica una evaluación cronológica estricta por fechas ni se detallan todas las cantidades finales de cada partición de 4M-TAD (sección 3.3, p. 5).</t>
       </text>
     </comment>
-    <comment ref="U62" authorId="0" shapeId="0">
+    <comment ref="U62" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No. Los métodos comparativos identificados son arquitecturas de aprendizaje profundo; no se presenta una comparación cuantitativa de detección con métodos tradicionales no Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="F63" authorId="0" shapeId="0">
+    <comment ref="F63" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Transporte de carga por carretera; cabina de camión en operación. El artículo no especifica una ciudad, carretera o tipo de vía para la evaluación del modelo.</t>
       </text>
     </comment>
-    <comment ref="H63" authorId="0" shapeId="0">
+    <comment ref="H63" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación de imágenes. Los autores indican que las 6000 imágenes están etiquetadas, pero no describen quién realizó la anotación, el procedimiento de validación ni la concordancia entre anotadores.</t>
       </text>
     </comment>
-    <comment ref="J63" authorId="0" shapeId="0">
+    <comment ref="J63" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado. YOLOv8n se entrena con imágenes etiquetadas de las seis clases de comportamiento y estado facial.</t>
       </text>
     </comment>
-    <comment ref="K63" authorId="0" shapeId="0">
+    <comment ref="K63" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN), mediante la arquitectura de detección de objetos YOLOv8n.</t>
       </text>
     </comment>
-    <comment ref="M63" authorId="0" shapeId="0">
+    <comment ref="M63" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No. Se utiliza una familia principal de Deep Learning, YOLOv8n (CNN). La combinación con sensores, filtrado de Kalman, reglas de negocio y componentes de hardware constituye integración de sistemas, pero no una arquitectura híbrida de distintas familias de redes profundas.</t>
       </text>
     </comment>
-    <comment ref="N63" authorId="0" shapeId="0">
+    <comment ref="N63" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción anómalo: fatiga, bostezo, cierre de ojos, uso del teléfono y tabaquismo. También contempla riesgo de vuelco, pero este se detecta mediante una regla basada en el sensor MPU6050, no mediante el modelo Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="S63" authorId="0" shapeId="0">
+    <comment ref="S63" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria/no especificada. Se documenta una división entrenamiento/prueba de 10:1 de las 6000 imágenes, pero no el método de asignación, separación por conductor o vehículo, independencia temporal ni un conjunto de validación diferenciado (sección 3, p. 289).</t>
       </text>
     </comment>
-    <comment ref="U63" authorId="0" shapeId="0">
+    <comment ref="U63" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No. No se comparan experimentalmente métodos tradicionales de detección de comportamiento peligroso con el modelo YOLOv8n.</t>
       </text>
     </comment>
-    <comment ref="E65" authorId="0" shapeId="0">
+    <comment ref="E65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores/detectores de tráfico vehicular; series temporales de flujo, velocidad, densidad y ocupación, con características derivadas de detectores aguas arriba y aguas abajo; adicionalmente, datos geométricos de curvas y características de carreteras para el componente de clasificación estructural.</t>
       </text>
     </comment>
-    <comment ref="F65" authorId="0" shapeId="0">
+    <comment ref="F65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Carreteras montañosas y tramos de carreteras nacionales y provinciales de Ningxia, China; no se evalúa específicamente una red urbana. La sección 3.1 (p. 192) enumera tramos de las rutas G109, G110, G211, G244, G307, G309, G312, G327, G338, G341, G344 y G566, entre otras.</t>
       </text>
     </comment>
-    <comment ref="H65" authorId="0" shapeId="0">
+    <comment ref="H65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales/registros, con procedencia y validación incompletamente documentadas. Los autores describen conjuntos de datos de incidentes de carreteras montañosas y etiquetas binarias de incidente (1) y no incidente (0), pero no identifican el registro oficial de referencia para cada incidente, el procedimiento de anotación, la sincronización con sensores ni una validación independiente de las etiquetas (sección 4.1, p. 199; ecuación 11, p. 198). No se afirma que las anomalías sean inyectadas o sintéticas.</t>
       </text>
     </comment>
-    <comment ref="J65" authorId="0" shapeId="0">
+    <comment ref="J65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado. El LSTM se entrena para clasificar observaciones etiquetadas como incidente (1) o ausencia de incidente (0), mediante una función de pérdida de entropía cruzada; el conjunto de entrenamiento se equilibra mediante técnicas de sobremuestreo y submuestreo (sección 3.3, pp. 196–198).</t>
       </text>
     </comment>
-    <comment ref="K65" authorId="0" shapeId="0">
+    <comment ref="K65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM/GRU). La familia profunda utilizada es LSTM; Improved Random Forest, eliminación recursiva de características, optimización bayesiana y técnicas de remuestreo son componentes de aprendizaje automático convencional o de optimización, no familias adicionales de Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="M65" authorId="0" shapeId="0">
+    <comment ref="M65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No. El sistema combina una sola familia de Deep Learning, LSTM, con Random Forest, eliminación recursiva, optimización bayesiana y remuestreo. Aunque constituye un procedimiento combinado de técnicas, no integra dos familias profundas distintas; 3D-CNN se utiliza como comparador, no como componente de la arquitectura propuesta.</t>
       </text>
     </comment>
-    <comment ref="N65" authorId="0" shapeId="0">
+    <comment ref="N65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes de tráfico en carreteras montañosas. La variable objetivo principal distingue presencia frente a ausencia de incidente; la aplicación geográfica adicional identifica tramos con comportamiento anormal mediante residuos estandarizados, pero no debe confundirse con una segunda evaluación cuantitativa independiente de detección de accidentes (Figura 6, p. 197; Figura 11 y Tabla 7, p. 203).</t>
       </text>
     </comment>
-    <comment ref="S65" authorId="0" shapeId="0">
+    <comment ref="S65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria, con descripción ambigua. El texto declara una partición de datos de incidente en entrenamiento y prueba de 1:1, balanceo del entrenamiento hasta 5600 muestras y posteriormente otra división 1:1; la sección 3.3 también indica una partición 5:5 (pp. 198–199). Se mencionan cinco validaciones cruzadas y una división aleatoria en K subconjuntos (pp. 201–202). No se informa separación temporal, por carretera o por incidente independiente ni se aclara suficientemente la relación entre las sucesivas particiones.</t>
       </text>
     </comment>
-    <comment ref="U65" authorId="0" shapeId="0">
+    <comment ref="U65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí. Wavelet Analysis (WA) constituye una línea base no profunda; VRT se identifica como tecnología de reconocimiento de video, aunque el artículo no detalla suficientemente su arquitectura para determinar de forma inequívoca si utiliza redes profundas. También se incluyen comparadores profundos 3D-CNN y LSTM estándar.</t>
       </text>
     </comment>
-    <comment ref="E70" authorId="0" shapeId="0">
+    <comment ref="E70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores/detectores y trayectorias GPS; series temporales de vehículos conectados que contienen velocidad, aceleración longitudinal y lateral, posición geográfica, dirección, acelerador, freno y otras variables del estado del vehículo. No se utilizan imágenes como entrada del modelo.</t>
       </text>
     </comment>
-    <comment ref="F70" authorId="0" shapeId="0">
+    <comment ref="F70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Tráfico vehicular terrestre en recorridos reales; el artículo no especifica una clasificación exclusiva como urbano o autopista, ni presenta resultados separados por tipo de vía.</t>
       </text>
     </comment>
-    <comment ref="H70" authorId="0" shapeId="0">
+    <comment ref="H70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación manual por consenso, asistida por reglas estadísticas. Primero se identifican puntos extremos de aceleración y desaceleración mediante un criterio del 15 % para cada extremo; posteriormente diez personas familiarizadas con series temporales de conducción revisan los fragmentos. Un fragmento se incorpora a una categoría cuando más de ocho evaluadores coinciden. No se informa validación independiente de los anotadores ni concordancia interevaluador. Secciones 3.2 y 3.4, páginas 308–309.</t>
       </text>
     </comment>
-    <comment ref="J70" authorId="0" shapeId="0">
+    <comment ref="J70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; clasificación multiclase de cinco comportamientos vehiculares a partir de fragmentos etiquetados manualmente.</t>
       </text>
     </comment>
-    <comment ref="K70" authorId="0" shapeId="0">
+    <comment ref="K70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM) y Convolucional (CNN).</t>
       </text>
     </comment>
-    <comment ref="M70" authorId="0" shapeId="0">
+    <comment ref="M70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; combina dos familias distintas de Deep Learning: red recurrente LSTM y red convolucional CNN. El procedimiento estadístico para identificar aceleraciones extremas es un preprocesamiento complementario y no se contabiliza como una tercera familia de Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="N70" authorId="0" shapeId="0">
+    <comment ref="N70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción: aceleración brusca, frenado de emergencia, cambio rápido al carril derecho y cambio rápido al carril izquierdo. Incluye una quinta clase de conducción normal. No evalúa directamente accidentes ocurridos ni congestión atípica.</t>
       </text>
     </comment>
-    <comment ref="S70" authorId="0" shapeId="0">
+    <comment ref="S70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria/no especificada: el artículo declara que 70 % de los 1141 fragmentos se utiliza para entrenamiento y 30 % para verificación, sin explicar el procedimiento de asignación. Se presentan cinco ensayos, pero no se aclara si corresponden a nuevas particiones, semillas o ejecuciones del entrenamiento. No se documenta separación temporal ni por vehículo, conductor o trayecto. Sección 5.1, página 310, y Tabla 3, página 311.</t>
       </text>
     </comment>
-    <comment ref="U70" authorId="0" shapeId="0">
+    <comment ref="U70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; el comparador experimental reportado es LSTM, que también pertenece a Deep Learning. Aunque se emplean reglas estadísticas para seleccionar fragmentos, no se evalúan como un clasificador independiente frente a LSTM-CNN.</t>
       </text>
     </comment>
-    <comment ref="E72" authorId="0" shapeId="0">
+    <comment ref="E72" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal; videos RGB de vigilancia aérea mediante drones y videos CCTV, combinados con descripciones textuales generadas automáticamente a partir de los fotogramas.</t>
       </text>
     </comment>
-    <comment ref="F72" authorId="0" shapeId="0">
+    <comment ref="F72" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano y mixto; UIT-ADrone corresponde a rotondas urbanas de Ciudad Ho Chi Minh; Drone-Anomaly contiene autopistas, cruces y rotondas, además de entornos no viales; UCF-Crime y XD-Violence son vigilancia general.</t>
       </text>
     </comment>
-    <comment ref="H72" authorId="0" shapeId="0">
+    <comment ref="H72" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotaciones de conjuntos de referencia existentes: UIT-ADrone dispone de etiquetas de anomalía a nivel de fotograma y entrenamiento únicamente con videos normales; Drone-Anomaly dispone de etiquetas por video para entrenamiento débilmente supervisado; UCF-Crime y XD-Violence contienen etiquetas de video para entrenamiento y anotaciones temporales utilizadas en la evaluación. No se describe una validación independiente de las etiquetas por los autores de MMVAD.</t>
       </text>
     </comment>
-    <comment ref="J72" authorId="0" shapeId="0">
+    <comment ref="J72" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Débilmente supervisado mediante Multiple Instance Learning (MIL), aprendizaje contrastivo con ejemplos normales/anómalos y etiquetas de video; particularidad: UIT-ADrone se describe con entrenamiento de videos normales y anotaciones a nivel de fotograma, por lo que la configuración de supervisión no es homogénea entre conjuntos.</t>
       </text>
     </comment>
-    <comment ref="K72" authorId="0" shapeId="0">
+    <comment ref="K72" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN) y Atención/Transformer; extractor visual I3D/C3D con backbone CSPDarkNet53, generación de descripciones con SwinBERT y módulo de fusión multimodal basado en atención cruzada; aprendizaje contrastivo como estrategia de entrenamiento.</t>
       </text>
     </comment>
-    <comment ref="M72" authorId="0" shapeId="0">
+    <comment ref="M72" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; combina familias distintas de Deep Learning, específicamente redes convolucionales para representación visual y mecanismos Transformer/atención para subtítulos y fusión multimodal. La incorporación de una pérdida tipo SVM no es por sí sola el fundamento de la clasificación híbrida.</t>
       </text>
     </comment>
-    <comment ref="N72" authorId="0" shapeId="0">
+    <comment ref="N72" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción y evento/otro; en UIT-ADrone aparecen conducción en sentido contrario, estacionamiento ilegal y otras actividades anómalas en rotondas, incluidas situaciones de peatones. En Drone-Anomaly existen eventos anómalos de carreteras y escenarios no viales; UCF-Crime y XD-Violence corresponden principalmente a anomalías generales de seguridad y violencia.</t>
       </text>
     </comment>
-    <comment ref="S72" authorId="0" shapeId="0">
+    <comment ref="S72" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Prueba independiente predefinida por cada conjunto de datos: UIT-ADrone 592 videos de entrenamiento y 905 de prueba; Drone-Anomaly 37/22; UCF-Crime 1610/290; XD-Violence 3954/800. No se documenta separación temporal estricta ni separación por rotonda, ciudad o cámara. Se reutilizan las particiones de los benchmarks y no se demuestra validación externa independiente del protocolo original.</t>
       </text>
     </comment>
-    <comment ref="U72" authorId="0" shapeId="0">
+    <comment ref="U72" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; los comparadores principales son modelos de detección de anomalías basados en Deep Learning. La pérdida SVM incorporada en MMVAD no constituye una evaluación independiente de un modelo tradicional sin Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="E73" authorId="0" shapeId="0">
+    <comment ref="E73" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal; videos RGB de cámaras de vigilancia vial y texto estructurado en forma de instrucciones, preguntas y respuestas. El modelo integra representaciones visuales y lingüísticas; no se reporta uso experimental de sensores físicos, GPS o LiDAR como entradas.</t>
       </text>
     </comment>
-    <comment ref="F73" authorId="0" shapeId="0">
+    <comment ref="F73" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ambos; intersecciones urbanas de Tianjin y autopistas de la provincia de Shandong, China. El conjunto urbano se orienta a comprensión de escenas y el de autopistas a clasificación de eventos viales.</t>
       </text>
     </comment>
-    <comment ref="H73" authorId="0" shapeId="0">
+    <comment ref="H73" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales/registros con anotación estructurada semiautomática y revisión manual parcial. Los videos proceden de cámaras de vigilancia reales. La sección 3.3 (p. 5) describe generación de anotaciones mediante extracción CNN, clasificación multietiqueta, reglas probabilísticas y pares de preguntas-respuestas; la sección 4.2.3 (p. 10) menciona inspección manual y filtrado de fotogramas clave para la evaluación. No se detallan el número de anotadores humanos, la concordancia interevaluador ni la validación independiente de todas las etiquetas de incidentes.</t>
       </text>
     </comment>
-    <comment ref="J73" authorId="0" shapeId="0">
+    <comment ref="J73" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; ajuste fino de un modelo fundacional previamente entrenado mediante videos, anotaciones estructuradas, pares pregunta-respuesta y etiquetas de eventos. Utiliza LoRA y ajuste mediante prompts, con pérdidas contrastivas de alineación visual-textual y entropía cruzada autorregresiva. La preformación del modelo fundacional es previa al estudio.</t>
       </text>
     </comment>
-    <comment ref="K73" authorId="0" shapeId="0">
+    <comment ref="K73" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Atención/Transformer y Convolucional (CNN); el núcleo utiliza LLaMA3 basado en Transformer y Video Q-Former para alineación temporal y multimodal, mientras que el proceso de anotación visual incorpora una CNN compacta.</t>
       </text>
     </comment>
-    <comment ref="M73" authorId="0" shapeId="0">
+    <comment ref="M73" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; el procedimiento completo combina una CNN para anotación y extracción visual de elementos viales con una arquitectura de atención/Transformer para comprensión y generación multimodal. Debe precisarse que la CNN se describe principalmente dentro de la preparación de anotaciones, mientras que el núcleo de inferencia MoTIF se centra en Video Q-Former y LLaMA3.</t>
       </text>
     </comment>
-    <comment ref="N73" authorId="0" shapeId="0">
+    <comment ref="N73" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes y congestión atípica; clasificación explícita de Accident, Congestion y Construction frente a Normal. El conjunto Shandong también contiene estacionamiento anómalo, aunque la evaluación multiclase principal no lo presenta como categoría independiente. Construction corresponde a un evento especial de infraestructura y no necesariamente a una anomalía vial.</t>
       </text>
     </comment>
-    <comment ref="S73" authorId="0" shapeId="0">
+    <comment ref="S73" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Prueba independiente por particiones de video: Tianjin 400 entrenamiento y 62 prueba; Shandong 160 entrenamiento y 30 prueba (sección 4.1, pp. 7–8). Los autores indican entrenamiento conjunto con datos urbanos y de autopista, y ajuste de comparadores bajo condiciones equivalentes (p. 10). No se especifica partición temporal estricta, independencia por cámara o carretera, ni una prueba en una ciudad o autopista completamente excluida del entrenamiento.</t>
       </text>
     </comment>
-    <comment ref="U73" authorId="0" shapeId="0">
+    <comment ref="U73" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; los comparadores cuantitativos principales son modelos fundacionales de visión y lenguaje basados en redes profundas. No se presenta una línea base independiente de reglas, SVM tradicional, Random Forest u otro método sin Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="E74" authorId="0" shapeId="0">
+    <comment ref="E74" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video; imágenes de cámaras de vigilancia de autopistas y trayectorias vehiculares derivadas de detecciones y seguimiento. Las posiciones en píxeles se transforman a coordenadas del mundo real; se calculan dirección, velocidad, desplazamiento y pendiente.</t>
       </text>
     </comment>
-    <comment ref="F74" authorId="0" shapeId="0">
+    <comment ref="F74" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopista; escenario principal de vigilancia multicámara en vías de alta velocidad y tramos extensos con zonas ciegas entre cámaras. Se mencionan la carretera del puente Hong Kong-Zhuhai-Macao como escenario de investigación y la autopista de circunvalación de Xi’an, provincia de Shaanxi, como entorno experimental de reidentificación y reconstrucción.</t>
       </text>
     </comment>
-    <comment ref="H74" authorId="0" shapeId="0">
+    <comment ref="H74" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación manual para detección de vehículos mediante LabelImg, incluyendo tipo, ubicación y tamaño de cajas delimitadoras (Figura 8, p. 12). Para anomalías, los autores utilizan reglas y conteos de comportamientos presentes en videos reales, pero no detallan cómo se obtuvieron ni verificaron las etiquetas de referencia de conducción en sentido contrario, velocidad anómala, estacionamiento o cambio de carril peligroso. En sentido contrario se simula la condición inversa usando trayectorias normales por escasez de datos reales (p. 11).</t>
       </text>
     </comment>
-    <comment ref="J74" authorId="0" shapeId="0">
+    <comment ref="J74" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado para detección y reidentificación vehicular y para predicción BiLSTM de segmentos ocultos mediante trayectorias de referencia. La etapa de decisión de anomalías es basada en reglas deterministas, no un clasificador profundo supervisado ni un detector profundo no supervisado.</t>
       </text>
     </comment>
-    <comment ref="K74" authorId="0" shapeId="0">
+    <comment ref="K74" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN) y Recurrente (RNN/LSTM/GRU); YOLOv5s y la red de atributos de reidentificación procesan imágenes mediante convoluciones, mientras que BiLSTM predice posiciones de trayectorias en zonas sin cobertura. La red de reidentificación incorpora módulos de atención.</t>
       </text>
     </comment>
-    <comment ref="M74" authorId="0" shapeId="0">
+    <comment ref="M74" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; la arquitectura global integra familias profundas distintas, CNN para detección y reidentificación visual y BiLSTM para predicción secuencial. No obstante, la etapa final que clasifica anomalías es de reglas, no una fusión profunda CNN-BiLSTM entrenada directamente para clasificar anomalías.</t>
       </text>
     </comment>
-    <comment ref="N74" authorId="0" shapeId="0">
+    <comment ref="N74" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción y trayectoria anómala; circulación en sentido contrario, exceso de velocidad, velocidad excesivamente baja, estacionamiento anómalo en autopista y cambios de carril peligrosos. No evalúa detección de accidentes consumados ni congestión atípica.</t>
       </text>
     </comment>
-    <comment ref="S74" authorId="1" shapeId="0">
+    <comment ref="S74" authorId="0" shapeId="0">
       <text>
         <t>Antes: Prueba independiente
 Motivo: No detalla la partición.</t>
       </text>
     </comment>
-    <comment ref="U74" authorId="0" shapeId="0">
+    <comment ref="U74" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; no se evalúa una línea base no profunda frente al módulo de detección de anomalías. La propia decisión final del método propuesto es basada en reglas, pero ello no constituye una comparación experimental independiente.</t>
       </text>
     </comment>
-    <comment ref="E75" authorId="0" shapeId="0">
+    <comment ref="E75" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias GPS; secuencias de puntos geográficos con marcas temporales procedentes de taxis. El modelo utiliza ubicaciones transformadas a celdas de cuadrícula y representaciones de fechas, horas, minutos y segundos.</t>
       </text>
     </comment>
-    <comment ref="F75" authorId="0" shapeId="0">
+    <comment ref="F75" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ambos; datos de circulación de taxis en redes viales urbanas de Porto y Chengdu. Los autores contemplan rutas por diferentes regiones y tipos de carretera, pero no presentan resultados separados para autopistas frente a calles urbanas; la evidencia experimental corresponde principalmente a movilidad urbana.</t>
       </text>
     </comment>
-    <comment ref="H75" authorId="0" shapeId="0">
+    <comment ref="H75" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Inyectadas/sintéticas; ante la ausencia de etiquetas reales de anomalías, los autores modifican trayectorias reales desplazando una fracción continua α de sus puntos una distancia d expresada en celdas de cuadrícula. También alteran los intervalos temporales bajo el supuesto de velocidad constante, de manera que la perturbación espacial afecta las marcas temporales. La sección 7.1 (p. 7) describe tres configuraciones principales: α = 0,1 y d = 3; α = 0,2 y d = 2; α = 0,3 y d = 2. No se reporta validación externa de estas anomalías mediante registros de tránsito o anotadores humanos.</t>
       </text>
     </comment>
-    <comment ref="J75" authorId="0" shapeId="0">
+    <comment ref="J75" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado; el modelo generativo aprende distribuciones y patrones normales de trayectorias mediante reconstrucción y maximización de una cota inferior de verosimilitud, sin requerir etiquetas reales de anomalías para entrenar el detector. Las anomalías sintéticas se utilizan como referencia de evaluación. El modelo auxiliar de ranking aprende a predecir posiciones en distribuciones, pero no convierte la detección principal en clasificación supervisada de anomalías.</t>
       </text>
     </comment>
-    <comment ref="K75" authorId="0" shapeId="0">
+    <comment ref="K75" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM/GRU) y Atención/Transformer; utiliza RNN para inferencia de rutas y generación de secuencias, además de mecanismos de atención cruzada y atención entre segmentos a diferentes escalas. Incluye agregación espacial inspirada en GCN, pero el artículo no especifica una arquitectura GNN independiente claramente diferenciada. También emplea una representación generativa probabilística con mezcla de gaussianas, relacionada con modelos de autoencodificación variacional.</t>
       </text>
     </comment>
-    <comment ref="M75" authorId="0" shapeId="0">
+    <comment ref="M75" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; la arquitectura combina una familia recurrente RNN con mecanismos neuronales de atención cruzada y atención multiescala, tratadas como componentes de aprendizaje profundo distintos. No debe describirse como CNN + GNN ni como Transformer completo, porque el artículo no presenta esas arquitecturas completas como componentes separados del detector.</t>
       </text>
     </comment>
-    <comment ref="N75" authorId="0" shapeId="0">
+    <comment ref="N75" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectoria anómala; desviaciones espaciales respecto de rutas normales y desviaciones temporales respecto del tiempo habitual de recorrido. La Figura 1 (p. 2) ilustra rutas distintas y una trayectoria que sigue el mismo camino pero demora seis minutos en un segmento donde la normal demora dos. Las pruebas cuantitativas usan perturbaciones sintéticas de rutas y tiempos; no clasifican accidentes reales, congestión confirmada ni infracciones específicas.</t>
       </text>
     </comment>
-    <comment ref="S75" authorId="0" shapeId="0">
+    <comment ref="S75" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria y temporal parcial; sección 7.1 (pp. 6–7): para cada conjunto se selecciona aleatoriamente el 80 % de las trayectorias para entrenamiento y el 20 % para prueba. Para experimentos de actualización, los dos primeros meses de Porto y los tres primeros días de Chengdu se utilizan para evaluación inicial y entrenamiento del ranking; los periodos restantes se destinan a actualizar el conjunto de entrenamiento. La evaluación combina una partición aleatoria con una secuencia temporal de actualización, pero no documenta una separación estricta por vehículo o ruta ni un protocolo externo independiente de detección.</t>
       </text>
     </comment>
-    <comment ref="U75" authorId="0" shapeId="0">
+    <comment ref="U75" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; iBAT y TPRRO son comparadores de detección de anomalías no basados en redes neuronales profundas, incluidos explícitamente en la Tabla 2 (p. 8).</t>
       </text>
     </comment>
-    <comment ref="E76" authorId="0" shapeId="0">
+    <comment ref="E76" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal; sensores/detectores de tráfico PeMS combinados con metadatos geográficos, registros históricos de incidentes y datos meteorológicos obtenidos mediante API. Las variables de tráfico incluyen flujo, ocupación y velocidad; las meteorológicas incluyen temperatura, viento, precipitación y humedad.</t>
       </text>
     </comment>
-    <comment ref="F76" authorId="0" shapeId="0">
+    <comment ref="F76" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopista; datos de estaciones del sistema California Performance Measurement System (PeMS), con metadatos de freeway, dirección y características de estaciones. Aunque los autores plantean aplicaciones a tráfico urbano, el conjunto descrito procede de estaciones de carreteras de California y no se documenta una evaluación independiente en calles urbanas.</t>
       </text>
     </comment>
-    <comment ref="H76" authorId="0" shapeId="0">
+    <comment ref="H76" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Pseudo-etiquetas para anomalías y congestión; registros reales asociados mediante reglas para incidentes. Isolation Forest asigna etiquetas binarias normal/anómalo con contaminación del 1 %, contrastadas parcialmente mediante IQR, puntuaciones Z, informes históricos e inspección visual, sin protocolo documentado de validación manual independiente (p. 4). K-means genera tres clases de congestión a partir de flujo, velocidad y ocupación (p. 4). Los incidentes se etiquetan relacionando informes registrados con estaciones próximas dentro de 1,5 km y coincidencia temporal mediante cKDTree (p. 5).</t>
       </text>
     </comment>
-    <comment ref="J76" authorId="0" shapeId="0">
+    <comment ref="J76" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado con pseudoetiquetas; la red multi-head + LSTM se entrena con etiquetas generadas previamente mediante métodos no supervisados o reglas de asociación. El proceso de creación de etiquetas de anomalía es no supervisado, pero el entrenamiento del clasificador neuronal utiliza objetivos binarios y pérdida de entropía cruzada, por lo que no debe clasificarse al detector profundo completo como estrictamente no supervisado.</t>
       </text>
     </comment>
-    <comment ref="K76" authorId="0" shapeId="0">
+    <comment ref="K76" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM/GRU) y Atención/Transformer; combina capas LSTM con atención multi-head, normalización, capas densas, dropout y global average pooling. No se documenta un Transformer completo con sus bloques estándar ni una CNN como componente de la arquitectura propuesta.</t>
       </text>
     </comment>
-    <comment ref="M76" authorId="0" shapeId="0">
+    <comment ref="M76" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; combina explícitamente modelado recurrente profundo mediante LSTM y un mecanismo neuronal de atención multi-head, dos familias funcionales distintas dentro de una misma arquitectura. Además integra Isolation Forest y K-means, pero estos componentes de aprendizaje automático tradicional no son la razón para clasificarlo como híbrido de Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="N76" authorId="0" shapeId="0">
+    <comment ref="N76" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Congestión atípica y accidentes/incidentes; la primera etapa detecta desviaciones del flujo vehicular, como caídas bruscas de velocidad y aumentos inusuales de congestión. La segunda asigna nivel bajo, medio o alto de congestión. La tercera distingue anomalías asociadas a incidentes registrados, incluidos accidentes, averías y obras, mediante coincidencia espacial y temporal. No detecta trayectorias individuales anómalas ni comportamiento de conducción a partir de video.</t>
       </text>
     </comment>
-    <comment ref="S76" authorId="0" shapeId="0">
+    <comment ref="S76" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Temporal; entrenamiento con datos de 15 días y evaluación en el archivo CSV del día 16, no visto durante entrenamiento, declarado en p. 6 y reiterado en p. 7. Los autores afirman que SMOTE se aplica sin contaminar el conjunto de prueba. No se describen con suficiente detalle los identificadores de estaciones de cada partición, el proceso de ajuste del pseudoetiquetador respecto del día de prueba ni una separación espacial independiente.</t>
       </text>
     </comment>
-    <comment ref="U76" authorId="0" shapeId="0">
+    <comment ref="U76" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No como línea base experimental directa; las tablas incluyen modelos tradicionales como Network Lasso, sistemas de aprendizaje automático y SASYNO-RF-RSKNN, pero sus resultados provienen de estudios previos con datos y protocolos distintos. Isolation Forest y K-means se utilizan para generar etiquetas, no como detectores comparativos evaluados en las mismas condiciones frente a la red propuesta.</t>
       </text>
     </comment>
-    <comment ref="E77" authorId="0" shapeId="0">
+    <comment ref="E77" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias GPS; secuencias de posiciones de taxis DiDi transformadas mediante map-matching en secuencias de segmentos de una red vial. Se utilizan identificadores de segmentos, transiciones entre vías, características contextuales del tráfico, patrones históricos de rutas y representaciones de la red de OpenStreetMap.</t>
       </text>
     </comment>
-    <comment ref="F77" authorId="0" shapeId="0">
+    <comment ref="F77" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano; redes viales de Chengdu y Xi’an, China, con trayectorias de taxis y pares origen-destino. No se presenta una evaluación específica y separada en autopistas.</t>
       </text>
     </comment>
-    <comment ref="H77" authorId="0" shapeId="0">
+    <comment ref="H77" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación manual de anomalías para la evaluación; pseudoetiquetas heurísticas para inicialización del entrenamiento. Se seleccionan 200 pares origen-destino con suficientes trayectorias y se visualizan sus rutas sobre la red vial. Cinco participantes identifican rutas y subtrayectorias anómalas por inspección visual; otro grupo de cinco verificadores etiqueta independientemente una muestra aleatoria del 10 %, agregando sus decisiones por mayoría. Se reporta exactitud de concordancia de 98,7 % para Chengdu y 94,3 % para Xi’an (sección V-A). El entrenamiento de RSRNet comienza con etiquetas ruidosas calculadas por frecuencia histórica de transiciones, posteriormente refinadas mediante ASDNet; las anotaciones manuales constituyen referencia de evaluación y no supervisión directa principal.</t>
       </text>
     </comment>
-    <comment ref="J77" authorId="0" shapeId="0">
+    <comment ref="J77" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado mediante Deep Reinforcement Learning con inicialización débilmente supervisada; RSRNet se inicializa con etiquetas heurísticas ruidosas derivadas de transiciones históricas y ASDNet aprende una política de refinamiento de etiquetas por recompensas. El método no necesita las etiquetas manuales de anomalías usadas para medir rendimiento. No debe describirse como supervisado convencional con anotaciones humanas.</t>
       </text>
     </comment>
-    <comment ref="K77" authorId="0" shapeId="0">
+    <comment ref="K77" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM/GRU) y Otra: Deep Reinforcement Learning mediante una red de política neuronal. RSRNet utiliza LSTM para representar secuencias de segmentos viales; ASDNet emplea aprendizaje por refuerzo con gradiente de política REINFORCE. No se presenta una CNN, GNN o Transformer como arquitectura central de detección.</t>
       </text>
     </comment>
-    <comment ref="M77" authorId="0" shapeId="0">
+    <comment ref="M77" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; integra una arquitectura recurrente profunda LSTM para representación secuencial y una red neuronal de política entrenada por Deep Reinforcement Learning para decisiones de anomalía, con funciones diferenciadas y aprendizaje iterativo conjunto. No se considera híbrido por incorporar map-matching, heurísticas de transición o reglas sobre la red vial, que no constituyen familias profundas.</t>
       </text>
     </comment>
-    <comment ref="N77" authorId="0" shapeId="0">
+    <comment ref="N77" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectoria anómala; identificación y localización de segmentos o subtrayectorias que se desvían de los patrones habituales entre un mismo origen y destino. Se aplica a desvíos de ruta de taxis y potenciales comportamientos inusuales durante desplazamientos. El estudio no clasifica directamente accidentes, fallas de sensores ni congestión como eventos etiquetados.</t>
       </text>
     </comment>
-    <comment ref="S77" authorId="0" shapeId="0">
+    <comment ref="S77" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria; sección V-A: se seleccionan aleatoriamente 10000 trayectorias para entrenamiento y se utilizan las restantes para prueba. No se documenta separación temporal estricta ni partición independiente por ciudad o por pares origen-destino. Los conjuntos Chengdu y Xi’an se evalúan por separado. El protocolo de etiquetado manual utiliza 200 pares origen-destino seleccionados para contar con suficientes trayectorias, por lo que el alcance del conjunto evaluado debe distinguirse del conjunto bruto.</t>
       </text>
     </comment>
-    <comment ref="U77" authorId="0" shapeId="0">
+    <comment ref="U77" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; se comparan experimentalmente métodos no profundos como IBOAT, DBTOD y CTSS, además de modelos profundos de autoencoders y variantes de RL4OASD. Todos aparecen en la misma Tabla III con resultados sobre Chengdu y Xi’an, lo que permite comparación directa dentro del estudio.</t>
       </text>
     </comment>
-    <comment ref="E78" authorId="0" shapeId="0">
+    <comment ref="E78" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias extraídas de video de vigilancia; secuencias de coordenadas espaciales y tiempo de vehículos rastreados en imágenes. No son trayectorias GPS. Cada muestra se representa como una secuencia de estados (x, y, t), suavizada y normalizada mediante Least-squares Cubic Spline Curves Approximation, LCSCA, a longitud fija de 12 pasos, sección 3 y sección 4-B.</t>
       </text>
     </comment>
-    <comment ref="F78" authorId="0" shapeId="0">
+    <comment ref="F78" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano; vigilancia vehicular de una intersección vial en VMT y múltiples escenas de tráfico en DETRAC. El artículo no presenta un experimento específicamente identificado como autopista ni proporciona una clasificación vial detallada de las 31 escenas DETRAC.</t>
       </text>
     </comment>
-    <comment ref="H78" authorId="0" shapeId="0">
+    <comment ref="H78" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Etiquetas de anomalía preexistentes utilizadas como verdad de referencia para evaluar la detección, no para entrenar el autoencoder. En VMT, las anotaciones de 24 trayectorias anómalas provienen del trabajo citado como referencia [18]. En DETRAC, las anotaciones de anomalía también proceden de [18], combinadas con resultados de seguimiento de vehículos. El artículo no detalla el procedimiento original de anotación, número de anotadores ni acuerdo interevaluador. El entrenamiento propuesto utiliza todas las trayectorias sin etiquetas de normalidad.</t>
       </text>
     </comment>
-    <comment ref="J78" authorId="0" shapeId="0">
+    <comment ref="J78" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado; aprende regularidades de trayectorias a partir de datos sin etiquetas, incluidas posibles anomalías escasas. El codificador-decodificador reconstruye las secuencias y el error de reconstrucción sirve como puntuación de anomalía. Las etiquetas existentes se emplean únicamente para evaluar resultados, según secciones 3 y 4.</t>
       </text>
     </comment>
-    <comment ref="K78" authorId="0" shapeId="0">
+    <comment ref="K78" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM/GRU) y Autoencoder/VAE; arquitectura de autoencoder sequence-to-sequence cuyos componentes codificador y decodificador son redes recurrentes GRU. Ambas categorías describen la misma arquitectura integrada, no dos modelos profundos independientes.</t>
       </text>
     </comment>
-    <comment ref="M78" authorId="0" shapeId="0">
+    <comment ref="M78" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; el codificador y decodificador son ambos GRU y constituyen una única familia recurrente dentro de un autoencoder. Aunque el método combina reconstrucción neuronal y una regla estadística de tres sigmas, la regla estadística no representa una segunda familia de Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="N78" authorId="0" shapeId="0">
+    <comment ref="N78" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectoria anómala y comportamiento de conducción; rutas irregulares, trayectorias retorcidas, espera o detención inusual en la vía y paradas prolongadas. VMT incluye espera en la calzada, trayectorias retorcidas y rutas poco comunes, Figura 4, p. 1115. DETRAC incluye rutas irregulares y detenciones prolongadas, Figura 5, p. 1115. No se evalúa detección específica de accidentes.</t>
       </text>
     </comment>
-    <comment ref="S78" authorId="0" shapeId="0">
+    <comment ref="S78" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No reportada; el artículo indica entrenamiento del autoencoder con todas las muestras disponibles sin etiquetas y evaluación con anotaciones existentes, pero no especifica una partición aleatoria, temporal, por cámara, por escena o un conjunto de prueba independiente. Tampoco informa cómo se evita que una misma trayectoria contribuya al aprendizaje y a la evaluación. La sección 4-A indica expresamente que ninguno de los dos conjuntos proporciona datos de entrenamiento separados.</t>
       </text>
     </comment>
-    <comment ref="U78" authorId="0" shapeId="0">
+    <comment ref="U78" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; se incluyen comparadores no profundos HMM, OCSVM, Sparse y Dist-Euc, junto con el comparador profundo Dist-RNN y una ablación basada en MSE. Todos se evalúan en los mismos conjuntos VMT y DETRAC mediante Detection Rate, False Alarm Rate y AUC, Tablas 1–3.</t>
       </text>
     </comment>
-    <comment ref="E79" authorId="0" shapeId="0">
+    <comment ref="E79" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal; imágenes RGB del conductor obtenidas de cámaras para la CNN, complementadas con señales IoT de GPS, acelerómetro y sensor de alcohol. La evaluación cuantitativa del componente Deep Learning corresponde a clasificación de imágenes de distracción, no a fusión neuronal de todos los sensores.</t>
       </text>
     </comment>
-    <comment ref="F79" authorId="0" shapeId="0">
+    <comment ref="F79" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Tráfico vehicular terrestre en contexto de conducción; entorno urbano o autopista no especificado para las imágenes de entrenamiento y prueba. El sistema se plantea para seguridad vial en Ruanda, pero no se identifica una carretera, ciudad o trayecto concreto como escenario de validación de la CNN.</t>
       </text>
     </comment>
-    <comment ref="H79" authorId="0" shapeId="0">
+    <comment ref="H79" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación de imágenes por clase; phone_holding=1 y not_holding=0, sección 3.4.2, p. 279. La procedencia exacta y el procedimiento de validación de las etiquetas no se describen. No se documentan anotadores independientes, criterios de consenso ni revisión de errores. Los sensores de accidentes, velocidad y alcohol producen estados mediante sus propias lecturas, sin demostrarse que esas etiquetas se utilicen para entrenar la CNN.</t>
       </text>
     </comment>
-    <comment ref="J79" authorId="0" shapeId="0">
+    <comment ref="J79" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; CNN entrenada con imágenes etiquetadas de dos clases, conductor sosteniendo teléfono y conductor sin teléfono, sección 3.4.2–3.4.3, p. 279. El módulo IoT opera mediante lecturas y condiciones de sensores; no se describe entrenamiento profundo para detectar accidentes, exceso de velocidad o alcohol.</t>
       </text>
     </comment>
-    <comment ref="K79" authorId="0" shapeId="0">
+    <comment ref="K79" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN); red convolucional personalizada implementada con Keras y TensorFlow. No se presenta evidencia de uso de una arquitectura VGGNet, ResNetV2 o Transformer en el modelo propio, aunque algunos nombres aparecen en palabras clave o antecedentes.</t>
       </text>
     </comment>
-    <comment ref="M79" authorId="0" shapeId="0">
+    <comment ref="M79" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; el componente Deep Learning descrito utiliza una sola familia CNN. Su integración con GPS, acelerómetro, sensor de alcohol, Raspberry Pi y servicios de comunicación constituye un sistema híbrido de hardware y software, pero no una combinación de dos familias distintas de redes profundas.</t>
       </text>
     </comment>
-    <comment ref="N79" authorId="0" shapeId="0">
+    <comment ref="N79" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción anómalo; distracción del conductor por uso del teléfono móvil. El sistema adicionalmente identifica exceso de velocidad, consumo de alcohol y posibles accidentes mediante sensores, pero estas últimas funciones no cuentan con evaluación cuantitativa atribuible a la CNN.</t>
       </text>
     </comment>
-    <comment ref="S79" authorId="0" shapeId="0">
+    <comment ref="S79" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria o por imágenes, no verificable; la sección 3.4.3, p. 279, afirma que los datos se dividen en entrenamiento, validación y prueba, pero no informa porcentajes, procedimiento de aleatorización ni separación por conductor, vehículo, sesión, cámara o fecha. La sección 4.1 menciona que se utilizaron imágenes personales durante pruebas. No puede confirmarse una partición independiente por sujeto o escenario.</t>
       </text>
     </comment>
-    <comment ref="U79" authorId="0" shapeId="0">
+    <comment ref="U79" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; no se ejecuta una línea base no profunda para clasificar las mismas imágenes de phone_holding y not_holding. Las comparaciones de las Tablas 2 y 3 son entre propuestas o funcionalidades de estudios diferentes, sin un protocolo común de entrenamiento y prueba.</t>
       </text>
     </comment>
-    <comment ref="E80" authorId="0" shapeId="0">
+    <comment ref="E80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video; imágenes RGB estáticas de accidentes de tráfico utilizadas para entrenamiento y evaluación, complementadas con una secuencia de video CCTV procesada por fotogramas para demostración. No se emplean sensores de tráfico, trayectorias GPS ni datos de flujo vehicular.</t>
       </text>
     </comment>
-    <comment ref="F80" authorId="0" shapeId="0">
+    <comment ref="F80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ambos/no delimitado; escenas de accidentes en carreteras, vías urbanas y otros entornos viales terrestres, sin clasificación sistemática por tipo de carretera. Bangladesh es el contexto de aplicación y motivación, pero no se demuestra que todas las imágenes procedan de Bangladesh ni que exista una validación geográfica específica en Dhaka.</t>
       </text>
     </comment>
-    <comment ref="H80" authorId="0" shapeId="0">
+    <comment ref="H80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación manual de imágenes reales obtenidas de Internet; los autores indican que las imágenes fueron etiquetadas manualmente en Roboflow, incluyendo cuadros delimitadores de accidentes, sección 2 y Figura 1, p. 3. No se describen número de anotadores, verificación independiente, acuerdo interanotador ni criterios detallados para diferenciar accidente de escena sin accidente. La procedencia y validación de los 28 ejemplos negativos del conjunto de prueba tampoco se detallan.</t>
       </text>
     </comment>
-    <comment ref="J80" authorId="0" shapeId="0">
+    <comment ref="J80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; detección de objetos y escenas de accidente mediante anotaciones manuales con cuadros delimitadores. Los modelos utilizan transferencia de aprendizaje desde pesos preentrenados y ajuste fino sobre el conjunto etiquetado; sección 2, pp. 3–4.</t>
       </text>
     </comment>
-    <comment ref="K80" authorId="0" shapeId="0">
+    <comment ref="K80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN); familia de detectores profundos YOLO, específicamente YOLOv9c, YOLOv10 y YOLOv11. Aunque el texto introductorio menciona mecanismos de atención y otros avances de distintas versiones, no documenta una segunda familia profunda independiente integrada en el sistema propuesto.</t>
       </text>
     </comment>
-    <comment ref="M80" authorId="0" shapeId="0">
+    <comment ref="M80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; YOLOv9, YOLOv10 y YOLOv11 se entrenan y evalúan como alternativas separadas. Comparar varias generaciones de detectores CNN no constituye una arquitectura híbrida formada por dos familias distintas de Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="N80" authorId="0" shapeId="0">
+    <comment ref="N80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes; principalmente colisiones entre vehículos, motocicletas y otros siniestros viales, incluidos vuelcos y vehículos accidentados. No se evalúan específicamente congestión atípica, anomalías de trayectoria ni comportamientos de conducción previos al accidente.</t>
       </text>
     </comment>
-    <comment ref="S80" authorId="0" shapeId="0">
+    <comment ref="S80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria o convencional por imágenes, con procedimiento de asignación no reportado; sección 2, pp. 3–4, declara división de aproximadamente 70 % entrenamiento, 20 % prueba y 10 % validación, concretada en Tabla 1 como 6310/1800/890 imágenes. No se informa separación temporal, por accidente original, fuente web, cámara, carretera o ubicación. Tampoco se documenta comprobación de duplicados o imágenes casi idénticas entre conjuntos.</t>
       </text>
     </comment>
-    <comment ref="U80" authorId="0" shapeId="0">
+    <comment ref="U80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; la comparación experimental propia utiliza exclusivamente tres modelos profundos YOLO. La Tabla 5 incluye métodos tradicionales y combinaciones con SVM, Decision Tree, KNN, Naïve Bayes y Logistic Regression procedentes de otras publicaciones, sin reentrenamiento ni evaluación sobre las mismas 9000 imágenes. Por tanto, no existe una línea base no profunda directamente comparable dentro del experimento.</t>
       </text>
     </comment>
-    <comment ref="E81" authorId="0" shapeId="0">
+    <comment ref="E81" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video; imágenes RGB estáticas de tráfico vehicular para entrenamiento y validación, complementadas con grabaciones CCTV procesadas por fotogramas para demostraciones de detección. No se utilizan trayectorias GPS, sensores de flujo ni datos tabulares de movilidad.</t>
       </text>
     </comment>
-    <comment ref="F81" authorId="0" shapeId="0">
+    <comment ref="F81" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano y carreteras; las imágenes incluyen vehículos accidentados y circulación normal en diferentes escenarios viales, mientras que una demostración CCTV se realiza en una intersección. El texto también contextualiza el problema en carreteras y autopistas, pero no presenta una clasificación sistemática del conjunto por entorno urbano o autopista.</t>
       </text>
     </comment>
-    <comment ref="H81" authorId="0" shapeId="0">
+    <comment ref="H81" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación manual de imágenes obtenidas de fuentes abiertas de Internet mediante makesense.ai, con etiquetas Normal y Accident y cuadros delimitadores de vehículos o regiones relevantes; sección 3.2 y Figuras 2–3, p. 71. Los autores mencionan correcciones de anotaciones antes del entrenamiento. No informan número de anotadores, acuerdo interanotador, validación independiente ni criterios detallados de clasificación de accidentes.</t>
       </text>
     </comment>
-    <comment ref="J81" authorId="0" shapeId="0">
+    <comment ref="J81" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; aprendizaje mediante etiquetas manuales y bounding boxes de las clases Normal y Accident, con transferencia de aprendizaje desde pesos preentrenados de YOLOv8n, YOLOv8s y YOLOv8m, ajustados al conjunto propio.</t>
       </text>
     </comment>
-    <comment ref="K81" authorId="0" shapeId="0">
+    <comment ref="K81" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN); tres variantes de la familia YOLOv8: YOLOv8n, YOLOv8s y YOLOv8m. El artículo describe extracción convolucional de características, detección de objetos, fusión multiescala y predicción de clases y cuadros delimitadores.</t>
       </text>
     </comment>
-    <comment ref="M81" authorId="0" shapeId="0">
+    <comment ref="M81" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; YOLOv8n, YOLOv8s y YOLOv8m son variantes de una misma familia convolucional profunda evaluadas por separado. El artículo no implementa una combinación de dos familias distintas de Deep Learning dentro de una arquitectura híbrida.</t>
       </text>
     </comment>
-    <comment ref="N81" authorId="0" shapeId="0">
+    <comment ref="N81" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes; colisiones entre vehículos, vuelcos y choques contra postes u otros elementos de la vía. Se incluyen escenas de tráfico normal como clase de contraste. No se estudian anomalías de trayectoria, congestión atípica ni predicción de accidentes futuros.</t>
       </text>
     </comment>
-    <comment ref="S81" authorId="1" shapeId="0">
+    <comment ref="S81" authorId="0" shapeId="0">
       <text>
         <t>Antes: Prueba independiente
 Motivo: Sin procedimiento de selección ni conjunto de prueba.</t>
       </text>
     </comment>
-    <comment ref="U81" authorId="0" shapeId="0">
+    <comment ref="U81" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No; las comparaciones experimentales del estudio se limitan a tres variantes profundas YOLOv8. No se evalúan SVM, Random Forest, métodos basados en reglas ni otros modelos tradicionales sobre los mismos datos.</t>
       </text>
     </comment>
-    <comment ref="E82" authorId="0" shapeId="0">
+    <comment ref="E82" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal; señales temporales de sensores embarcados, radar milimétrico 4D, LiDAR, cámaras, sensores de infraestructura vial, información V2X y trayectorias vinculadas a mapas de alta precisión. Se derivan cinco variables temporales principales: velocidad longitudinal, velocidad lateral, aceleración, ángulo de orientación y distancia temporal al vehículo precedente. No es un estudio basado exclusivamente en video ni exclusivamente en GPS.</t>
       </text>
     </comment>
-    <comment ref="F82" authorId="0" shapeId="0">
+    <comment ref="F82" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ambos; el artículo considera conducción en vías urbanas y autopistas, incluyendo intersecciones, incorporaciones, adelantamientos y condiciones complejas de circulación. La sección 3, p. 3, contrasta explícitamente autopistas y calles urbanas congestionadas para la adaptación de umbrales. No se informa la proporción de muestras correspondiente a cada tipo de vía.</t>
       </text>
     </comment>
-    <comment ref="H82" authorId="0" shapeId="0">
+    <comment ref="H82" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales/registros y anotación manual, complementadas con anomalías inducidas y simuladas. La sección 4.1, p. 5, describe selección de eventos peligrosos en conducción natural según ISO 34502, reproducción controlada de seis maniobras por conductores profesionales y generación adversarial con simuladores. Diez expertos realizaron etiquetado cruzado de tres niveles siguiendo SAE J3016, exigiendo concordancia de al menos tres personas; se informa coeficiente Kappa de 0,87. También se verificaron muestras simuladas con un sistema de valores de referencia. Las etiquetas combinan evidencia real, experimental y sintética, por lo que no deben clasificarse como exclusivamente reales.</t>
       </text>
     </comment>
-    <comment ref="J82" authorId="0" shapeId="0">
+    <comment ref="J82" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado; el modelo utiliza muestras multimodales con etiquetas de anomalías revisadas por expertos y se evalúa mediante clasificación de seis tipos de comportamiento anómalo. La sección 4.1, p. 5, documenta partición de entrenamiento, validación y prueba. El artículo también describe aprendizaje federado como parte del procesamiento colaborativo y la protección de datos, pero no demuestra que el paradigma principal de detección sea auto-supervisado o no supervisado.</t>
       </text>
     </comment>
-    <comment ref="K82" authorId="0" shapeId="0">
+    <comment ref="K82" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Atención/Transformer, con componentes convolucionales residuales. ADID+ combina representación espectral de señales, atención de canal y atención espaciotemporal cruzada; la sección 3, pp. 3–4, describe una red convolucional residual del marco ADID original y la Figura 3, p. 4, muestra bloques de atención y transformación de características. Se clasifica principalmente como arquitectura profunda de atención tiempo-frecuencia, con componentes convolucionales.</t>
       </text>
     </comment>
-    <comment ref="M82" authorId="0" shapeId="0">
+    <comment ref="M82" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí; arquitectura de atención/Transformer combinada con procesamiento convolucional residual de características espectrales, según la descripción del ADID original y la extensión ADID+ en las pp. 3–4. La combinación se registra como atención más CNN residual, no como una simple suma de transformaciones estadísticas y aprendizaje profundo. No obstante, el artículo no ofrece una ablación aislada que cuantifique la contribución específica de cada familia profunda.</t>
       </text>
     </comment>
-    <comment ref="N82" authorId="0" shapeId="0">
+    <comment ref="N82" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción; seis tipos específicos: Malicious Cut-in (MCI, incorporación peligrosa), Illegal Overtaking (IOT, adelantamiento ilegal), S-shaped Maneuver (SSM, maniobra en zigzag), Emergency Braking (EMB, frenada de emergencia), Wrong-way Driving (WWD, circulación en sentido contrario) e Illegal Parking Occupation (IPO, estacionamiento ilegal u ocupación indebida). Se trata de detección de maniobras anómalas o peligrosas, no de predicción de accidentes ya ocurridos.</t>
       </text>
     </comment>
-    <comment ref="S82" authorId="0" shapeId="0">
+    <comment ref="S82" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Partición 70 % entrenamiento, 15 % validación y 15 % prueba; sección 4.1, p. 5. Los autores indican que entrenamiento contiene datos de carreteras de una sola ciudad, validación mezcla datos de distintas ciudades y prueba se reserva para condiciones extremas, como lluvia intensa e interferencia multitrayecto en pasos elevados. No se especifican ciudades, cantidades exactas por partición, fechas, vehículos compartidos ni control de dependencia entre muestras del mismo recorrido. Se trata de una separación declarada con evaluación de escenarios extremos, pero no de una validación geográfica independiente demostrada.</t>
       </text>
     </comment>
-    <comment ref="U82" authorId="0" shapeId="0">
+    <comment ref="U82" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí, con alcance limitado; en la p. 6 se comparan puntualmente resultados de métodos basados en reglas, como detección de luces de emergencia para IPO con 82,3 % de exactitud frente a 96,8 % de ADID+, y métodos monomodales de referencia. Sin embargo, los comparadores sistemáticos de la Tabla 1 son modelos profundos y no se presenta un protocolo completo de entrenamiento y evaluación de un modelo tradicional sobre las seis clases.</t>
       </text>
     </comment>
-    <comment ref="E84" authorId="0" shapeId="0">
+    <comment ref="E84" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias vehiculares derivadas de seguimiento visual; datos espaciotemporales de posición bidimensional de vehículos. El entrenamiento utiliza NGSIM, cuyos movimientos vehiculares fueron capturados mediante cámaras instaladas junto a las carreteras; se registran coordenadas, velocidad y aceleración. RETAD recibe posiciones locales transformadas a diferencias de primer orden y utiliza secuencias de subtrayectorias de longitud fija, pp. 4–5.</t>
       </text>
     </comment>
-    <comment ref="F84" authorId="1" shapeId="0">
+    <comment ref="F84" authorId="0" shapeId="0">
       <text>
         <t>Antes: Autopista
 Motivo: No indica qué escenas de NGSIM usa.</t>
       </text>
     </comment>
-    <comment ref="H84" authorId="0" shapeId="0">
+    <comment ref="H84" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Inyectadas/sintéticas — Las anomalías utilizadas para validación y prueba se generan mediante un algoritmo de simulación basado en datos, controlando parámetros para producir diferentes comportamientos anómalos. El artículo no presenta anotación humana independiente ni verificación de estas anomalías mediante registros de incidentes reales. La procedencia real de NGSIM corresponde al entrenamiento de patrones vehiculares, no a las etiquetas anómalas evaluadas; pp. 3–5.</t>
       </text>
     </comment>
-    <comment ref="J84" authorId="0" shapeId="0">
+    <comment ref="J84" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado — RETAD aprende representaciones y patrones de trayectorias mediante reconstrucción sin utilizar etiquetas normal/anómalo en la función de entrenamiento. El artículo indica que el entrenamiento puede contener una pequeña cantidad de trayectorias anómalas. Las etiquetas sintéticas se emplean para validación, ajuste del umbral y evaluación, pp. 3 y 5.</t>
       </text>
     </comment>
-    <comment ref="K84" authorId="0" shapeId="0">
+    <comment ref="K84" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autoencoder/VAE y Recurrente (RNN/LSTM/GRU) — Autoencoder recurrente cuyos módulos codificador y decodificador se implementan con unidades GRU. La arquitectura utiliza MLP y max pooling para incorporar interacciones vehiculares, pp. 5–8.</t>
       </text>
     </comment>
-    <comment ref="M84" authorId="0" shapeId="0">
+    <comment ref="M84" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí — Combina una arquitectura recurrente GRU con un autoencoder de reconstrucción, dos familias funcionales de Deep Learning empleadas conjuntamente para modelar secuencias y reconstruir trayectorias. El módulo global pooling incorpora interacción entre vehículos, pero no constituye por sí mismo una familia adicional como GNN o Transformer.</t>
       </text>
     </comment>
-    <comment ref="N84" authorId="0" shapeId="0">
+    <comment ref="N84" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectoria anómala y comportamiento de conducción — Cinco categorías representadas en la Figura 1, p. 4: aceleración repentina, detención prolongada, cambios frecuentes de dirección, oscilación lateral y conducción en sentido contrario. Las categorías se generan sintéticamente y la evaluación cuantitativa se presenta de forma agregada por conjunto Traj-1 a Traj-6, sin métricas independientes por cada una de las cinco clases de anomalía.</t>
       </text>
     </comment>
-    <comment ref="S84" authorId="0" shapeId="0">
+    <comment ref="S84" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Prueba independiente respecto al conjunto de entrenamiento: el modelo se entrena con trayectorias reales NGSIM y se evalúa en seis conjuntos sintéticos Traj-1 a Traj-6. El artículo menciona validación etiquetada para ajuste de parámetros, pero no documenta tamaños ni separación temporal/geográfica de validación y prueba, ni una evaluación sobre anomalías reales independientes. Se trata de separación por origen experimental, no de una validación temporal rigurosa demostrada; pp. 3–5 y 9–10.</t>
       </text>
     </comment>
-    <comment ref="U84" authorId="0" shapeId="0">
+    <comment ref="U84" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí — LCSS, TOP-EYE, Isolation Forest y XGBoost son comparadores no profundos implementados y evaluados cuantitativamente en la Tabla 2, p. 10. También se incluye ATD-RNN como baseline de Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="E85" authorId="0" shapeId="0">
+    <comment ref="E85" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video e imágenes RGB de vigilancia vial — El sistema recibe fotogramas de cámaras de tráfico a través de RabbitMQ y los procesa como imágenes individuales. El detector de accidentes CNN utiliza imágenes de 250 × 250 × 3 píxeles. El artículo no demuestra modelado temporal explícito para el detector CNN de accidentes; se describe transmisión continua de fotogramas, pp. 69–70.</t>
       </text>
     </comment>
-    <comment ref="F85" authorId="1" shapeId="0">
+    <comment ref="F85" authorId="0" shapeId="0">
       <text>
         <t>Antes: Autopista
 Motivo: Evaluado con autos de juguete en escenario controlado.</t>
       </text>
     </comment>
-    <comment ref="H85" authorId="0" shapeId="0">
+    <comment ref="H85" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación de clases accidente/no accidente y simulación propia — El artículo indica que las imágenes de entrenamiento corresponden a accidentes y no accidentes, pero no documenta quién asignó las etiquetas, cómo fueron verificadas ni la proporción por clase. La prueba descrita explícitamente utiliza accidentes simulados con automóviles de juguete. No se evidencia validación de las etiquetas de prueba mediante registros de accidentes reales; pp. 70–71.</t>
       </text>
     </comment>
-    <comment ref="J85" authorId="0" shapeId="0">
+    <comment ref="J85" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado — El módulo CNN realiza clasificación binaria de imágenes de accidente/no accidente mediante ejemplos etiquetados. El módulo complementario de violencia utiliza un modelo CLIP preentrenado con Vision Transformer. No se describe entrenamiento no supervisado, semisupervisado ni aprendizaje de anomalías exclusivamente con ejemplos normales; pp. 69–70.</t>
       </text>
     </comment>
-    <comment ref="K85" authorId="0" shapeId="0">
+    <comment ref="K85" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN) para detección de accidentes; Atención/Transformer (ViT) para detección de violencia. Ambas familias se emplean en módulos independientes del sistema y no constituyen una arquitectura fusionada de detección de accidentes; pp. 69–70.</t>
       </text>
     </comment>
-    <comment ref="M85" authorId="0" shapeId="0">
+    <comment ref="M85" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — Aunque RIDS contiene CNN y ViT, ambos se utilizan como clasificadores separados para tareas distintas: accidentes y violencia. No se documenta fusión CNN–Transformer ni combinación de sus representaciones para una misma decisión de anomalía vial. Bajo el criterio de modelo híbrido de la revisión, no corresponde clasificarlo como híbrido; pp. 69–70.</t>
       </text>
     </comment>
-    <comment ref="N85" authorId="0" shapeId="0">
+    <comment ref="N85" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes — Detección binaria de accidentes frente a no accidentes en imágenes de vigilancia vial. El sistema también identifica violencia mediante un módulo separado, pero esa tarea no se considera evidencia principal de detección de anomalías vehiculares. Los accidentes evaluados cuantitativamente se simulan con automóviles de juguete; pp. 70–71.</t>
       </text>
     </comment>
-    <comment ref="S85" authorId="0" shapeId="0">
+    <comment ref="S85" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No reportada — El artículo identifica conjuntos utilizados para entrenamiento y pruebas, pero no especifica proporciones train/validation/test, división aleatoria, temporal, por cámara, por ubicación o por video. El 93 % procede de pruebas controladas con automóviles de juguete; no se aclara si los ejemplos son independientes del conjunto de entrenamiento ni se informa el tamaño de prueba. No hay evidencia de evaluación externa rigurosa; pp. 70–71.</t>
       </text>
     </comment>
-    <comment ref="U85" authorId="0" shapeId="0">
+    <comment ref="U85" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — No se evalúa experimentalmente ningún comparador tradicional o de aprendizaje automático no profundo sobre el mismo conjunto de accidentes. Las técnicas de mejora visual como CLAHE y dehazing son componentes de preprocesamiento, no baselines de detección; pp. 69–71.</t>
       </text>
     </comment>
-    <comment ref="E86" authorId="0" shapeId="0">
+    <comment ref="E86" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal — Video RGB de cámaras de vigilancia vial, descripciones textuales de escenas normales y accidentes, y mapas de atención visual humana (eye-gaze) registrados mediante seguimiento ocular. Durante el entrenamiento utiliza secuencias de cinco fotogramas, textos generales y específicos, y mapas de mirada; durante la inferencia no requiere textos específicos ni mapas de mirada de los videos de prueba, sino imágenes y dos descripciones textuales generales. Secciones 3–4, pp. 5–11.</t>
       </text>
     </comment>
-    <comment ref="F86" authorId="0" shapeId="0">
+    <comment ref="F86" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano — Escenarios de vigilancia vial con intersecciones y carreteras observadas por cámaras externas. La Figura 1, p. 6, muestra colisiones entre automóviles y motocicletas en intersecciones; TADS contiene distintas situaciones de accidentes. El artículo no identifica explícitamente una evaluación separada en autopistas ni desglosa los resultados por entorno urbano/autopista.</t>
       </text>
     </comment>
-    <comment ref="H86" authorId="0" shapeId="0">
+    <comment ref="H86" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales/registros y anotación humana — Los videos proceden de escenas de vigilancia de accidentes viales; el estudio utiliza intervalos identificados como normales o anómalos, descripciones textuales añadidas por los investigadores y mapas de mirada registrados de múltiples observadores humanos mediante eye-tracking y procesamiento gaussiano. No se detalla en este artículo un procedimiento independiente de verificación de cada accidente contra registros oficiales, ni el acuerdo entre anotadores para las etiquetas temporales. Las anotaciones de texto son humanas y los mapas de mirada constituyen supervisión auxiliar, no sustituyen las etiquetas de anomalía. Secciones 3 y 4.3.4, pp. 5–6 y 10.</t>
       </text>
     </comment>
-    <comment ref="J86" authorId="0" shapeId="0">
+    <comment ref="J86" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado — Ajuste fino de un modelo CLIP preentrenado con correspondencias entre videos normales/anómalos y descripciones textuales generales y específicas; optimización de alineación multimodal y supervisión adicional mediante mapas reales de atención visual humana. No corresponde a detección no supervisada ni a zero-shot puro: CLIP zero-shot se evalúa solo como comparación y obtiene resultados inferiores. Secciones 4.3 y 5.5, pp. 9–11 y 18.</t>
       </text>
     </comment>
-    <comment ref="K86" authorId="0" shapeId="0">
+    <comment ref="K86" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Atención/Transformer — Modelo visual-lingüístico CLIP con codificadores de imagen y texto, fusión temporal basada en Transformer y atención cruzada texto-imagen para aprender mapas espaciales de atención. El artículo no especifica de manera inequívoca en el texto extraído el nombre exacto del backbone visual de CLIP; por tanto, no se debe atribuir adicionalmente una familia CNN concreta sin verificar su configuración. Secciones 4.1–4.2, pp. 7–8.</t>
       </text>
     </comment>
-    <comment ref="M86" authorId="0" shapeId="0">
+    <comment ref="M86" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — La arquitectura combina componentes de atención y Transformer dentro de una misma familia principal de Deep Learning, además de alineación multimodal y supervisión por mapas de mirada. No se verifica una integración explícita de dos familias profundas diferentes, como CNN + RNN o CNN + GNN, que cumpla el criterio operativo de modelo híbrido de esta revisión.</t>
       </text>
     </comment>
-    <comment ref="N86" authorId="0" shapeId="0">
+    <comment ref="N86" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes — Detección de intervalos anómalos asociados a accidentes viales, incluyendo colisiones entre vehículos y elementos de infraestructura. TADS distingue 12 categorías basadas en los objetos involucrados; la sección 5.3.3 menciona explícitamente colisiones de vehículos pequeños y grandes contra infraestructura. La salida principal es anomalía vial frente a normalidad, no clasificación multiclase de los 12 tipos. Secciones 1, 3 y 5.3.3, pp. 2, 5–6 y 14.</t>
       </text>
     </comment>
-    <comment ref="S86" authorId="0" shapeId="0">
+    <comment ref="S86" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Prueba independiente dentro del mismo dataset, con detalles de separación no reportados — Se utiliza un conjunto de entrenamiento y un conjunto de prueba de TADS y se presentan resultados en el TADS testing set, Tabla 1, p. 13. El artículo no describe en detalle si la separación fue aleatoria, temporal, por cámara, ubicación o evento; tampoco acredita ausencia de solapamiento entre escenas relacionadas. No existe una validación externa en otro dataset.</t>
       </text>
     </comment>
-    <comment ref="U86" authorId="0" shapeId="0">
+    <comment ref="U86" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — Los seis baselines principales son arquitecturas de aprendizaje profundo; CLIP zero-shot también es un modelo profundo preentrenado. No se presenta evaluación experimental propia de SVM, Random Forest u otro método no profundo en el mismo protocolo. Las referencias a esos métodos en Related Work no constituyen baselines del estudio.</t>
       </text>
     </comment>
-    <comment ref="E87" authorId="0" shapeId="0">
+    <comment ref="E87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias GPS — Registros de posicionamiento de taxis Didi con coordenadas de latitud/longitud, marcas temporales, identificadores de conductor y pedido; los recorridos se transforman en secuencias de regiones y enlaces de una red vial dirigida. No utiliza video como entrada principal. Sección 2, pp. 2–3.</t>
       </text>
     </comment>
-    <comment ref="F87" authorId="0" shapeId="0">
+    <comment ref="F87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano — Red de carreteras comprendida dentro del segundo anillo vial de Chengdu, China, dividida en 116 regiones de tráfico según la estructura de las vías y su densidad de circulación. La Figura 2, p. 3, representa la división espacial; no se documenta una evaluación independiente en autopistas.</t>
       </text>
     </comment>
-    <comment ref="H87" authorId="0" shapeId="0">
+    <comment ref="H87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No reportado con validación individual — Los autores definen trayectorias anómalas por distancia recorrida excesiva, tiempo de viaje excesivo o desvío/retorno significativo respecto de la ruta esperada. DeepWalk y Node2vec identifican rutas con baja correspondencia, mientras que SVDD delimita regiones anómalas. La sección 4.2, p. 7, indica verificación complementaria de resultados mediante anomalías publicadas por la Oficina de Tráfico de Chengdu y registros de redes sociales. No se especifica si cada trayectoria fue etiquetada manualmente, por registros oficiales o por el propio algoritmo, ni se proporciona acuerdo entre anotadores.</t>
       </text>
     </comment>
-    <comment ref="J87" authorId="0" shapeId="0">
+    <comment ref="J87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado — DeepWalk aprende representaciones mediante caminatas aleatorias y Skip-Gram sobre la red vial, sin necesidad de etiquetas de anomalía para la representación inicial; SVDD utiliza muestras normales para ajustar una hiperesfera de una clase. El artículo menciona búsqueda de parámetros de Node2vec en forma supervisada, pero no presenta un protocolo completo de clasificación supervisada con etiquetas de anomalía. Secciones 3.2 y 4.1, pp. 4–6.</t>
       </text>
     </comment>
-    <comment ref="K87" authorId="0" shapeId="0">
+    <comment ref="K87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Otra — Aprendizaje de representaciones de grafos mediante DeepWalk y Node2vec con red neuronal Skip-Gram y Hierarchical Softmax. No corresponde a una GNN moderna basada en paso de mensajes, GCN o GAT; tampoco se identifica una arquitectura CNN, LSTM, Transformer o autoencoder. Sección 3.2, p. 4.</t>
       </text>
     </comment>
-    <comment ref="M87" authorId="0" shapeId="0">
+    <comment ref="M87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — DeepWalk y Node2vec pertenecen a la misma familia de embeddings neuronales de grafos; SVDD es aprendizaje de una clase basado en vectores de soporte y Apriori es minería de reglas de asociación. La combinación constituye un sistema algorítmico mixto, pero no integra dos familias distintas de Deep Learning según el criterio operativo de esta revisión.</t>
       </text>
     </comment>
-    <comment ref="N87" authorId="0" shapeId="0">
+    <comment ref="N87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectoria anómala y congestión atípica — Se identifican recorridos de taxi excesivamente largos, lentos o con desvíos, utilizados como indicadores de anomalías en la red vial; posteriormente se localizan regiones de tráfico anormal y se estima la posible propagación de congestión. Los accidentes se consideran una causa potencial de las alteraciones, pero no se presenta una clasificación específica de tipos de accidente. Secciones 1, 3 y 4, pp. 1–7.</t>
       </text>
     </comment>
-    <comment ref="S87" authorId="0" shapeId="0">
+    <comment ref="S87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No reportada de manera suficiente — El artículo distingue datos de entrenamiento y prueba en el análisis de correlaciones de la Figura 12, p. 7, y utiliza una matriz de pesos obtenida de datos de entrenamiento, pero no informa proporciones, fechas de corte, aleatorización, separación por trayectorias o regiones, ni prevención de fuga temporal. Se clasifica como partición no reportada en detalle; no debe asumirse separación temporal independiente.</t>
       </text>
     </comment>
-    <comment ref="U87" authorId="0" shapeId="0">
+    <comment ref="U87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí — SDA es un método estadístico no profundo y se compara cuantitativamente con el sistema DeepWalk/Node2vec + SVDD + Apriori sobre el mismo caso de estudio, Tabla 4, p. 7.</t>
       </text>
     </comment>
-    <comment ref="E88" authorId="0" shapeId="0">
+    <comment ref="E88" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video — Cámaras externas de vigilancia vial; YOLOv4 detecta y sigue vehículos, ciclistas y peatones, y se extraen trayectorias mediante coordenadas normalizadas de bounding boxes. La entrada principal del clasificador es una secuencia temporal de posiciones de vehículos, no imágenes RGB completas. Secciones 4.4 y 4.6, pp. 8–9.</t>
       </text>
     </comment>
-    <comment ref="F88" authorId="0" shapeId="0">
+    <comment ref="F88" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ambos — Escenarios de intersecciones urbanas (42 %), autopistas (35 %) y carreteras suburbanas (23 %). Condiciones de iluminación: día 65 %, amanecer/atardecer 20 % y noche 15 %. Los porcentajes describen el corpus curado; no se presentan resultados independientes para cada entorno. Sección 3, p. 6.</t>
       </text>
     </comment>
-    <comment ref="H88" authorId="0" shapeId="0">
+    <comment ref="H88" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación manual — Tres anotadores humanos independientes utilizaron CVAT y asignaron etiquetas binarias Normal/Dangerous a cada segmento de trayectoria. Se consideró peligroso el zigzag sostenido, adelantamiento riesgoso con desplazamiento lateral próximo a otros agentes o exceso de velocidad sostenido al cruzar un paso peatonal. Los desacuerdos se resolvieron mediante mayoría y los casos persistentemente ambiguos se descartaron. Fleiss kappa = 0,82. Secciones 4.5 y protocolo de anotación, pp. 8–9.</t>
       </text>
     </comment>
-    <comment ref="J88" authorId="0" shapeId="0">
+    <comment ref="J88" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado — Clasificación binaria Normal/Dangerous a partir de segmentos etiquetados manualmente. Los hiperparámetros se seleccionan mediante validación interna de los folds de entrenamiento y maximización de macro-F1, vigilando el recall de la clase Dangerous. Secciones 4.1, 4.5 y 4.8, pp. 7–11.</t>
       </text>
     </comment>
-    <comment ref="K88" authorId="0" shapeId="0">
+    <comment ref="K88" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Atención/Transformer y Convolucional (CNN) — La arquitectura principal Multi-Speed Transformer combina ramas con convoluciones temporales 1D y mecanismos de atención/Transformer; YOLOv4 es un detector CNN utilizado en preprocesamiento. Se compara con TCN, arquitectura convolucional temporal. Secciones 4.4 y 4.8, pp. 8 y 10; Figura 2, p. 7.</t>
       </text>
     </comment>
-    <comment ref="M88" authorId="0" shapeId="0">
+    <comment ref="M88" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí — La arquitectura de detección principal integra convoluciones temporales 1D, pertenecientes a la familia CNN, con procesamiento mediante atención/Transformer, que constituye otra familia de Deep Learning. Además, YOLOv4 se emplea como extractor visual previo, pero no es necesario contarlo como segunda familia porque el propio clasificador integra convolución y atención.</t>
       </text>
     </comment>
-    <comment ref="N88" authorId="0" shapeId="0">
+    <comment ref="N88" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción y trayectoria anómala — Clasificación binaria de conducción normal frente a peligrosa; ejemplos de anomalías: zigzag, weaving, adelantamientos riesgosos y exceso de velocidad cerca de pasos peatonales. El modelo no clasifica separadamente cada subtipo ni detecta directamente accidentes ocurridos. Secciones 1 y 4.5, pp. 2 y 9.</t>
       </text>
     </comment>
-    <comment ref="S88" authorId="0" shapeId="0">
+    <comment ref="S88" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria/estratificada por segmento — Validación cruzada stratified k-fold y partición hold-out 70/30. El ajuste de hiperparámetros se realiza dentro de los folds de entrenamiento y el sobremuestreo no se aplica a prueba. La sección 4.7, pp. 9–10, especifica asignación por segmento de trayectoria y afirma disponer de identificadores de partición reproducibles, pero no documenta separación estricta por video, ubicación, conductor o tiempo. No se especifica el número k de folds.</t>
       </text>
     </comment>
-    <comment ref="U88" authorId="0" shapeId="0">
+    <comment ref="U88" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí — Random Forest es un algoritmo de aprendizaje automático no profundo y se utiliza como comparador experimental directo con el Multi-Speed Transformer y TCN, Tabla 1, p. 11.</t>
       </text>
     </comment>
-    <comment ref="E89" authorId="0" shapeId="0">
+    <comment ref="E89" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores/detectores — Series temporales de densidad vehicular, velocidad y volumen, captadas mediante dos sensores virtuales fijos de PTV Vissim, separados aproximadamente 1 km. Datos simulados a intervalos de 1 segundo y remuestreados a 5 y 20 segundos. Sección 2.1, pp. 4–5.</t>
       </text>
     </comment>
-    <comment ref="F89" authorId="0" shapeId="0">
+    <comment ref="F89" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopista/vía expresa — Corredor de cuatro carriles y límite de velocidad de 120 km/h, correspondiente a un tramo de 5 km de Shaikh Zayed bin Sultan Street en Abu Dabi, Emiratos Árabes Unidos. Se trata de un único corredor simulado, no de una evaluación multiciudad. Figura 2 y sección 2.1, p. 4.</t>
       </text>
     </comment>
-    <comment ref="H89" authorId="0" shapeId="0">
+    <comment ref="H89" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Inyectadas/sintéticas — Las etiquetas proceden directamente de los escenarios definidos en PTV Vissim: 0 corresponde a tráfico normal sin cierre y 1–4 al número de carriles cerrados. Los incidentes se implementan mediante señales virtuales que bloquean carriles durante 20 minutos. No existen etiquetas de accidentes reales ni anotación independiente de eventos observados. Secciones 2.1–2.3, pp. 4–6.</t>
       </text>
     </comment>
-    <comment ref="J89" authorId="0" shapeId="0">
+    <comment ref="J89" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado — Aprendizaje de secuencias etiquetadas con categorías de gravedad predefinidas. Se emplea Stratified Shuffle Split para conservar proporciones de clase y búsqueda aleatoria de hiperparámetros. Los modelos se evalúan con tres formulaciones: binaria, tres clases y cinco clases. Secciones 2.2–2.6, pp. 5–9.</t>
       </text>
     </comment>
-    <comment ref="K89" authorId="0" shapeId="0">
+    <comment ref="K89" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN) y Recurrente/reservorio — CNN-1D y Temporal Convolutional Network son modelos convolucionales profundos; Reservoir Computing utiliza estados recurrentes dinámicos con reservorio fijo y capa de lectura entrenable. El artículo compara las tres arquitecturas como alternativas, no como componentes de una misma red híbrida. Sección 2.4, pp. 6–8; Figuras 5–7.</t>
       </text>
     </comment>
-    <comment ref="M89" authorId="0" shapeId="0">
+    <comment ref="M89" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — CNN-1D, TCN y Reservoir Computing se entrenan y comparan como modelos independientes. No se presenta una arquitectura que fusione dos familias distintas de Deep Learning en un único detector. La comparación entre CNN y TCN tampoco constituye por sí misma hibridación.</t>
       </text>
     </comment>
-    <comment ref="N89" authorId="0" shapeId="0">
+    <comment ref="N89" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes y congestión no recurrente — Incidentes representados por cierres simulados de carriles. Clasificación binaria: Major, cierres de tres o cuatro carriles, frente a Not major, que incluye normalidad y cierres de uno o dos carriles. Tres clases: Normal, Minor y Major. Cinco clases: normal y cierres de uno, dos, tres o cuatro carriles. No se detectan colisiones reales ni trayectorias peligrosas individuales. Sección 2.3, pp. 5–6.</t>
       </text>
     </comment>
-    <comment ref="S89" authorId="0" shapeId="0">
+    <comment ref="S89" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria estratificada — Stratified Shuffle Split de secuencias etiquetadas, preservando la distribución de clases. Cada secuencia mantiene un identificador de escenario y orden cronológico interno; no se usan ventanas completas solapadas. El artículo no demuestra un conjunto externo independiente ni una partición por corredor o ubicación. La asignación estratificada no constituye por sí misma validación temporal independiente. Secciones 2.2 y 2.5, pp. 5 y 8–9.</t>
       </text>
     </comment>
-    <comment ref="U89" authorId="0" shapeId="0">
+    <comment ref="U89" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — Los dos baselines cuantitativos son CNN-1D y TCN, ambos de Deep Learning. Aunque el artículo revisa métodos tradicionales en la introducción, no presenta una comparación experimental directa con un algoritmo no profundo independiente.</t>
       </text>
     </comment>
-    <comment ref="E90" authorId="0" shapeId="0">
+    <comment ref="E90" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video — Clips RGB procedentes de cámaras de tráfico/vigilancia elevadas (Trafficam) y cámaras instaladas en vehículos (DashCam), complementados con un dataset externo de accidentes. Se extrae flujo óptico para representar movimiento y se combina con características RGB. Los videos se segmentan en clips no solapados de cinco segundos; los fotogramas se redimensionan a 224 × 224 píxeles. Sección IV, pp. 7–8; sección V.A, p. 9.</t>
       </text>
     </comment>
-    <comment ref="F90" authorId="0" shapeId="0">
+    <comment ref="F90" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano y otros entornos viales — El trabajo se orienta a transporte urbano y ciudades inteligentes, con cámaras de vigilancia y DashCam de distintas localizaciones. Los autores indican recopilación mundial, pero no desglosan de manera verificable cuántos clips corresponden a vías urbanas, autopistas o carreteras interurbanas. Sección IV.A, pp. 7–8.</t>
       </text>
     </comment>
-    <comment ref="H90" authorId="0" shapeId="0">
+    <comment ref="H90" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación manual — Cada clip de cinco segundos fue etiquetado con Labelbox. Inicialmente se consideraron categorías como vuelco, colisión frontal, colisión trasera, impacto lateral y tráfico normal; debido a la escasez de ejemplos por categoría, se agruparon en Accident y Normal Traffic. Las etiquetas se aplican a videos de eventos reales recopilados de fuentes públicas, pero el artículo no informa número de anotadores, acuerdo interanotador ni auditoría independiente. Sección IV.B, p. 8.</t>
       </text>
     </comment>
-    <comment ref="J90" authorId="0" shapeId="0">
+    <comment ref="J90" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado — Clasificación binaria Accident/No Accident mediante clips anotados manualmente, con conjuntos separados de entrenamiento, validación y prueba. Se utiliza aprendizaje por transferencia desde I3D preentrenado y ajuste fino de sus últimas 15 capas en la variante principal. Secciones IV.B, V.A y VI, pp. 8–12.</t>
       </text>
     </comment>
-    <comment ref="K90" authorId="0" shapeId="0">
+    <comment ref="K90" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN) y Recurrente (LSTM) — La arquitectura principal combina I3D, una red convolucional tridimensional, con capas ConvLSTM2D, que incorporan memoria recurrente LSTM y convoluciones espaciales. El comparador DenseNet-Transformer combina una CNN con mecanismos de atención. Figura 3, p. 9; secciones V.A y VI.E, pp. 9–12.</t>
       </text>
     </comment>
-    <comment ref="M90" authorId="0" shapeId="0">
+    <comment ref="M90" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí — La arquitectura principal combina dos familias de Deep Learning: extracción convolucional I3D y procesamiento recurrente ConvLSTM2D. Además, integra dos modalidades visuales, RGB y flujo óptico, mediante fusión de características. La clasificación como híbrida se fundamenta en CNN + LSTM, no únicamente en la combinación de dos flujos de entrada.</t>
       </text>
     </comment>
-    <comment ref="N90" authorId="0" shapeId="0">
+    <comment ref="N90" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes — Detección binaria de accidentes vehiculares frente a circulación normal. Los videos originales contienen categorías como colisiones frontales, traseras, laterales y vuelcos, pero el modelo final no clasifica tipos específicos de accidentes. No evalúa explícitamente congestión atípica, anomalías de trayectoria sin colisión ni fallos de sensores. Secciones III y IV.B, pp. 5–8.</t>
       </text>
     </comment>
-    <comment ref="S90" authorId="0" shapeId="0">
+    <comment ref="S90" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Partición de entrenamiento, validación y prueba — Tabla 1, p. 9: 3912/1054/725 clips, equivalentes aproximadamente a 68,7 %/18,5 %/12,7 %. Se muestran particiones por Trafficam, DashCam y datos externos. No se informa que los videos originales, escenas, cámaras, ciudades o eventos estén separados entre particiones; tampoco se documenta una división cronológica. Por ello no puede afirmarse independencia por ubicación o evento ni ausencia total de fuga de información entre clips de una misma grabación.</t>
       </text>
     </comment>
-    <comment ref="U90" authorId="0" shapeId="0">
+    <comment ref="U90" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — La evaluación experimental no incluye un baseline tradicional independiente como SVM, Random Forest, regresión logística, detector de cambio estadístico o método convencional de análisis de movimiento. La revisión de técnicas tradicionales en la sección II no constituye una comparación experimental propia.</t>
       </text>
     </comment>
-    <comment ref="E91" authorId="0" shapeId="0">
+    <comment ref="E91" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video — Imágenes individuales extraídas de cámaras montadas en vehículos de patrullaje y monitoreo de autopistas. El sistema de captura emplea dos cámaras de 30 fps; la evaluación de Deep Learning se realiza principalmente sobre fotogramas redimensionados a 418 × 418 píxeles. Aunque el sistema integra GPS para comunicar la ubicación del evento, el modelo visual no utiliza trayectorias GPS como entrada de aprendizaje. Secciones 3 y 5.1, pp. 5 y 10.</t>
       </text>
     </comment>
-    <comment ref="F91" authorId="0" shapeId="0">
+    <comment ref="F91" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopista — Datos de carreteras de alta velocidad de Corea del Sur supervisadas por Korea Expressway Corporation. Las escenas representan vehículos averiados o accidentados, tráfico, trabajadores y peatones, y objetos peligrosos sobre la calzada. No se documenta una evaluación específica en calles urbanas. Secciones 3 y 5.1–5.2, pp. 5 y 10–11.</t>
       </text>
     </comment>
-    <comment ref="H91" authorId="0" shapeId="0">
+    <comment ref="H91" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación manual de imágenes reales — La sección 4.2, pp. 7–8, describe etiquetas de clase de escena y cajas delimitadoras de objetos individuales o agrupados. Dataset A identifica objetos por separado; dataset B agrupa objetos relacionados con una situación peligrosa; dataset C utiliza etiquetas globales de escena. Las Figuras 4 y 5, pp. 7 y 9, muestran ejemplos visuales de anotación y detección. No se especifica el número de anotadores, su capacitación, acuerdo interanotador ni verificación independiente del ground truth.</t>
       </text>
     </comment>
-    <comment ref="J91" authorId="0" shapeId="0">
+    <comment ref="J91" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado — YOLOv5 se entrena con cajas delimitadoras y etiquetas de objetos; ResNet-34 modificada aprende directamente de imágenes con etiquetas de escena. Todos los enfoques emplean transferencia de aprendizaje desde parámetros preentrenados y ajuste fino sobre el dataset del estudio. Secciones 4.1–4.3, pp. 6–9.</t>
       </text>
     </comment>
-    <comment ref="K91" authorId="0" shapeId="0">
+    <comment ref="K91" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN) — YOLOv5 para detección de objetos y ResNet-34 modificada para clasificación de escenas. Ambas son arquitecturas convolucionales profundas; el clasificador probabilístico posterior a YOLOv5 no constituye una segunda familia de Deep Learning. Sección 4.1 y Figura 3, p. 6.</t>
       </text>
     </comment>
-    <comment ref="M91" authorId="0" shapeId="0">
+    <comment ref="M91" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — Los enfoques comparados utilizan una sola familia profunda, CNN, representada por YOLOv5 o ResNet-34. La combinación de YOLOv5 con un clasificador probabilístico basado en objetos constituye un sistema de dos etapas, pero no combina dos familias distintas de Deep Learning. La ResNet modificada tampoco incorpora una arquitectura recurrente o Transformer.</t>
       </text>
     </comment>
-    <comment ref="N91" authorId="0" shapeId="0">
+    <comment ref="N91" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes y Evento/otro — Identificación de vehículos detenidos por accidente o avería, obstáculos y residuos peligrosos, presencia inesperada de peatones, trabajadores o personal de control y escenas de congestión o circulación normal. Tabla 2, p. 8. La clase 2 no distingue congestión anómala de circulación normal; por tanto, el estudio no proporciona una métrica independiente de congestión atípica.</t>
       </text>
     </comment>
-    <comment ref="S91" authorId="0" shapeId="0">
+    <comment ref="S91" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Partición entrenamiento/prueba 4:1, equivalente a 80 %/20 %, declarada en sección 5.2, p. 10. El artículo menciona seguimiento de pérdida de entrenamiento y validación en sección 4.3, p. 9, pero no documenta claramente el tamaño de esa validación. No se especifica si la separación se realizó por secuencia original, vehículo, autopista, fecha o ubicación. La prueba contiene imágenes de secuencias de eventos, pero no se acredita independencia geográfica o temporal rigurosa.</t>
       </text>
     </comment>
-    <comment ref="U91" authorId="0" shapeId="0">
+    <comment ref="U91" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — No existe un experimento con un detector íntegramente no profundo. Los métodos A y B contienen YOLOv5, que es Deep Learning, aunque su etapa posterior sea probabilística. La presencia de un clasificador probabilístico no convierte al sistema completo en baseline tradicional.</t>
       </text>
     </comment>
-    <comment ref="E92" authorId="0" shapeId="0">
+    <comment ref="E92" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Trayectorias vehiculares 2D y representación estructural de carriles — Entradas basadas en desplazamientos relativos de coordenadas de vehículos, posiciones de otros vehículos próximos y nodos de carril permitidos hacia delante, izquierda y derecha. El modelo no procesa directamente imágenes ni video; la información de carriles se añade a las trayectorias simuladas MAAD mediante discretización del mapa. Secciones 3.1 y 4.1, pp. 3 y 5–6.</t>
       </text>
     </comment>
-    <comment ref="F92" authorId="0" shapeId="0">
+    <comment ref="F92" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopista — Entorno simulado de carretera recta con dos carriles por sentido y separador entre sentidos de circulación. Se estudian interacciones de dos vehículos y maniobras peligrosas, incluidas circulación en sentido contrario y salida de la carretera. Sección 4.1, pp. 5–6; Figura 1, p. 2.</t>
       </text>
     </comment>
-    <comment ref="H92" authorId="0" shapeId="0">
+    <comment ref="H92" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Inyectadas/sintéticas — Las etiquetas de normalidad y anomalía proceden de escenarios simulados MAAD. El entrenamiento contiene únicamente maniobras normales, como adelantamiento, seguimiento y circulación paralela; la prueba contiene comportamientos normales y 11 clases de maniobras anómalas. La Figura 3, p. 5, muestra etiquetas temporales de normal, ignorado y anómalo. No se documenta validación de estas etiquetas frente a incidentes reales de autopista.</t>
       </text>
     </comment>
-    <comment ref="J92" authorId="0" shapeId="0">
+    <comment ref="J92" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No supervisado — El entrenamiento utiliza exclusivamente trayectorias normales y minimiza pérdidas de reconstrucción y predicción de estados vehiculares. Las etiquetas de anomalía del conjunto de prueba se emplean para evaluación y selección de hiperparámetros, no como etiquetas de entrenamiento de la arquitectura principal. Secciones 3.3 y 4.1–4.4, pp. 5–7.</t>
       </text>
     </comment>
-    <comment ref="K92" authorId="0" shapeId="0">
+    <comment ref="K92" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autoencoder/VAE; Recurrente (GRU); Atención — Arquitectura variacional recurrente con atención multi-cabeza de producto punto escalado. La familia principal es Autoencoder/VAE, combinada con una red recurrente GRU y mecanismos de atención. No se utiliza una GNN con convoluciones de grafos como núcleo de SABeR-VAE, aunque el escenario se representa mediante relaciones entre vehículos y nodos de carril. Sección 3.2, pp. 3–5; Figura 2, p. 4.</t>
       </text>
     </comment>
-    <comment ref="M92" authorId="0" shapeId="0">
+    <comment ref="M92" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí — Integra dos familias de Deep Learning distintas: codificación recurrente mediante GRU y aprendizaje generativo mediante autoencoder variacional, junto con atención neuronal para modelar interacciones espaciales. El operador de Koopman es un mecanismo adicional de propagación latente, no una familia profunda independiente. La variante SABeR-AE conserva la estructura recurrente y la atención, pero elimina la regularización variacional.</t>
       </text>
     </comment>
-    <comment ref="N92" authorId="0" shapeId="0">
+    <comment ref="N92" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Comportamiento de conducción y Trayectoria anómala — El conjunto MAAD incorpora 11 clases de maniobras anómalas, entre ellas adelantamiento agresivo, desplazamiento lateral forzado, seguimiento excesivamente cercano, derrape, salida de carretera y circulación en sentido contrario. La Tabla 2, p. 7, presenta siete tipos específicos: reeving, pushing aside, right spreading, left spreading, off-road, skidding y wrong-way. No se evalúa detección directa de accidentes reales ni congestión vehicular.</t>
       </text>
     </comment>
-    <comment ref="S92" authorId="0" shapeId="0">
+    <comment ref="S92" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Prueba independiente parcialmente comprometida — MAAD contiene 80 trayectorias para entrenamiento y 66 para prueba; las ventanas de longitud 15 se generan dentro de estas trayectorias. Sin embargo, la sección 4.4, p. 6, declara que los hiperparámetros se seleccionan usando un 20 % del conjunto de prueba completo y que luego se evalúa el modelo sobre todo ese conjunto, incluyendo el subconjunto empleado para validación. No se documenta una separación adicional entre validación y prueba final. No existe evaluación temporal o geográfica externa.</t>
       </text>
     </comment>
-    <comment ref="U92" authorId="0" shapeId="0">
+    <comment ref="U92" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí — El Constant Velocity Model (CVM) constituye un baseline no profundo explícito, basado en extrapolar la velocidad del último paso temporal sin aprendizaje neuronal. La Tabla 1, p. 6, informa AUROC 83,1 %, AUPR-Abnormal 54,5 %, AUPR-Normal 96,0 % y FPR @ 95%-TPR 74,6 % para CVM.</t>
       </text>
     </comment>
-    <comment ref="E93" authorId="0" shapeId="0">
+    <comment ref="E93" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video — Videos RGB de vigilancia aérea del tráfico vehicular, procesados mediante extracción de fotogramas, mejora visual, detección de objetos, segmentación de superpíxeles, localización y estimación de movimiento. La información se obtiene de imágenes captadas desde una perspectiva aérea, no de sensores inductivos, GPS ni registros de flujo agregado. Secciones Proposed methodology y Dataset description, pp. 4–14.</t>
       </text>
     </comment>
-    <comment ref="F93" authorId="0" shapeId="0">
+    <comment ref="F93" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Urbano — El conjunto UIT-ADrone registra tráfico vial observado desde drones, con circulación vehicular y situaciones de tráfico urbano. El artículo no identifica una autopista como entorno exclusivo de evaluación. La metodología se plantea para carreteras y escenas de circulación densa, pero no presenta resultados separados por tipo de vía.</t>
       </text>
     </comment>
-    <comment ref="H93" authorId="0" shapeId="0">
+    <comment ref="H93" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación del conjunto de datos — El artículo utiliza categorías normal, vehículo detenido, accidente y actividad sospechosa para entrenar y evaluar clasificadores supervisados. Se trabaja con videos de vigilancia aérea y etiquetas por clase; sin embargo, no se describe detalladamente quién realizó las anotaciones, el protocolo de validación, el acuerdo entre anotadores ni la verificación independiente de cada evento. La procedencia específica de las etiquetas de cada clase no queda completamente documentada.</t>
       </text>
     </comment>
-    <comment ref="J93" authorId="0" shapeId="0">
+    <comment ref="J93" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado — Los dos clasificadores SBAF-CNN se entrenan para reconocer clases definidas, primero normal frente a anómalo y después vehículo detenido, accidente y actividad sospechosa. El entrenamiento utiliza entropía cruzada categórica y una salida softmax. El agrupamiento Kd-SLIC-K-means es una etapa auxiliar de segmentación y no convierte el entrenamiento de las CNN en no supervisado. Sección Implementation details, pp. 14–15.</t>
       </text>
     </comment>
-    <comment ref="K93" authorId="0" shapeId="0">
+    <comment ref="K93" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN) — La arquitectura de aprendizaje profundo se basa en clasificadores SBAF-CNN y un detector YOLO. Los módulos Kd-SLIC-K-means, RF-IDO, DistSurf-BM y THG-GF son procedimientos de procesamiento, segmentación, localización y movimiento, no familias adicionales de Deep Learning. La propuesta no integra una RNN, GNN o Transformer como segunda familia profunda propia.</t>
       </text>
     </comment>
-    <comment ref="M93" authorId="0" shapeId="0">
+    <comment ref="M93" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — Es un sistema híbrido en sentido amplio porque combina CNN con algoritmos tradicionales de procesamiento de imágenes, segmentación y optimización. Sin embargo, bajo el criterio de esta revisión, que exige combinar al menos dos familias distintas de Deep Learning, no se clasifica como híbrido profundo: los componentes neuronales identificados pertenecen fundamentalmente a la familia convolucional.</t>
       </text>
     </comment>
-    <comment ref="N93" authorId="0" shapeId="0">
+    <comment ref="N93" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes; Comportamiento de conducción; Evento/otro — La segunda etapa diferencia vehículos detenidos, vehículos accidentados y actividades sospechosas en escenas de circulación vial. No se informa una evaluación independiente de congestión atípica, trayectorias GPS anómalas o fallos de sensores. La Tabla 1, p. 13, identifica las clases finales y la Tabla 2, p. 14, presenta su distribución experimental.</t>
       </text>
     </comment>
-    <comment ref="S93" authorId="1" shapeId="0">
+    <comment ref="S93" authorId="0" shapeId="0">
       <text>
         <t>Antes: Prueba independiente
 Motivo: División 80/20 de videos sin otro criterio.</t>
       </text>
     </comment>
-    <comment ref="U93" authorId="0" shapeId="0">
+    <comment ref="U93" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí, parcialmente — Los componentes de segmentación y localización se contrastan con algoritmos tradicionales, como Kd-K-means, K-means, IDO, Daugman, Hough y Sobel, en tablas y figuras de evaluación de módulos. Sin embargo, para la tarea final de clasificación de anomalías, la Tabla 5 compara principalmente arquitecturas neuronales CNN, RNN, LSTM y ANN; no se presenta un clasificador tradicional no profundo evaluado de extremo a extremo con el mismo protocolo. Por tanto, existe comparación no profunda de componentes, pero no un baseline no-DL directamente equivalente para detección final.</t>
       </text>
     </comment>
-    <comment ref="E94" authorId="0" shapeId="0">
+    <comment ref="E94" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sensores/detectores — Datos de radares fijos de carretera que registran volumen, velocidad y ocupación vehicular cada 30 segundos; se transforman en diagramas espacio-temporales de ondas de choque para alimentar redes LSTM. El artículo también utiliza detectores de lazo inductivo para una tarea secundaria de predicción de eventos públicos, que debe diferenciarse de la detección de accidentes.</t>
       </text>
     </comment>
-    <comment ref="F94" authorId="0" shapeId="0">
+    <comment ref="F94" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopista — La evaluación de accidentes se desarrolla en un tramo de 18 millas de Interstate 24, dirección Nashville, Tennessee, Estados Unidos. La tarea secundaria de predicción de eventos se desarrolla en Interstate 5, Seattle, Washington. No se reporta evaluación de accidentes en vías urbanas.</t>
       </text>
     </comment>
-    <comment ref="H94" authorId="0" shapeId="0">
+    <comment ref="H94" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales/registros — Las etiquetas de accidentes provienen de 59 siniestros incluidos en informes oficiales del Nashville Traffic Management Center. Una secuencia recibe la etiqueta accidente cuando ocurre al menos un accidente en cualquiera de los tres segmentos consecutivos asociados durante su ventana temporal de 10 minutos; en caso contrario recibe la etiqueta no accidente. Sección 6.1.1, p. 16. No se documenta una auditoría independiente de los informes ni la correspondencia exacta entre cada incidente y todas las ventanas derivadas.</t>
       </text>
     </comment>
-    <comment ref="J94" authorId="0" shapeId="0">
+    <comment ref="J94" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado — Clasificación binaria accidente/no accidente mediante etiquetas procedentes de informes de siniestros. Los modelos LSTM y Sparse-LSTM aprenden con pérdida de entropía cruzada ponderada. Para la tarea de accidentes se aplica submuestreo aleatorio de muestras negativas y una partición aleatoria 70/30 de secuencias etiquetadas. Secciones 6.1.1–6.1.2, p. 16.</t>
       </text>
     </comment>
-    <comment ref="K94" authorId="0" shapeId="0">
+    <comment ref="K94" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Recurrente (RNN/LSTM/GRU) — Los modelos principales son Vanilla LSTM y Sparse-LSTM. La contribución Sparse-LSTM modifica la estructura de matrices entrenables de una LSTM mediante bloques diagonales y máscaras, preservando relaciones interpretables entre componentes de la codificación. No se utiliza CNN, GNN ni Transformer como segunda familia de aprendizaje profundo para la tarea de accidentes.</t>
       </text>
     </comment>
-    <comment ref="M94" authorId="0" shapeId="0">
+    <comment ref="M94" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — La arquitectura profunda pertenece a una sola familia, LSTM recurrente, aunque utiliza codificación físico-informada, matrices dispersas, máscaras y un procedimiento algorítmico de reconstrucción de ondas de choque. La combinación de procesamiento basado en teoría de tráfico con una LSTM no constituye una integración de dos familias diferentes de Deep Learning bajo los criterios de esta revisión.</t>
       </text>
     </comment>
-    <comment ref="N94" authorId="0" shapeId="0">
+    <comment ref="N94" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes — Detección binaria de accidentes viales a partir de sus efectos en el flujo, velocidad, ocupación y propagación de ondas de choque. El modelo identifica si una ventana de 10 minutos asociada a tres segmentos contiene un accidente. La predicción de eventos deportivos y de congestión recurrente es una tarea adicional, no la métrica principal de anomalías vehiculares para esta extracción.</t>
       </text>
     </comment>
-    <comment ref="S94" authorId="0" shapeId="0">
+    <comment ref="S94" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 División aleatoria — Para detección de accidentes, las secuencias etiquetadas se mezclan aleatoriamente y se dividen en 70 % entrenamiento y 30 % prueba; se aplica submuestreo aleatorio de secuencias sin accidente. Sección 6.1.1, p. 16. Las ventanas tienen 10 minutos y desplazamiento de 5 minutos, por lo que pueden compartir observaciones entre particiones; no se informa bloqueo por fecha, accidente, estación o segmento. Es importante no confundir esta partición con la división cronológica de mayo–agosto frente a agosto–septiembre utilizada exclusivamente para la tarea secundaria de eventos públicos en Seattle.</t>
       </text>
     </comment>
-    <comment ref="U94" authorId="0" shapeId="0">
+    <comment ref="U94" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No — Todos los baselines cuantitativos de detección de accidentes de la Tabla 4 utilizan modelos LSTM, con diferentes entradas y estructuras. No se evalúan Random Forest, SVM, regresión logística, métodos estadísticos de detección ni otros clasificadores no profundos sobre la misma tarea de accidentes. Los algoritmos físicos empleados para construir diagramas de ondas de choque son componentes de preprocesamiento, no clasificadores alternativos de accidentes.</t>
       </text>
     </comment>
-    <comment ref="E95" authorId="0" shapeId="0">
+    <comment ref="E95" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video — Secuencias RGB capturadas mediante cámaras instaladas en vehículos, denominadas dashcams o cámaras de tablero, desde perspectiva egocéntrica. Los videos muestran accidentes que involucran al vehículo portador de la cámara o a otros participantes de la vía. El modelo procesa características visuales de fotogramas y su evolución temporal; no utiliza sensores de tráfico, GPS ni registros de infraestructura vial como entrada.</t>
       </text>
     </comment>
-    <comment ref="F95" authorId="1" shapeId="0">
+    <comment ref="F95" authorId="0" shapeId="0">
       <text>
         <t>Antes: Ambos
 Motivo: DoTA/CCD sin clasificación por tipo de vía.</t>
       </text>
     </comment>
-    <comment ref="H95" authorId="0" shapeId="0">
+    <comment ref="H95" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anotación de benchmarks reales — DoTA proporciona etiquetas temporales de inicio y final del accidente, categorías de eventos y trayectorias delimitadoras de objetos anómalos; CCD contiene etiquetas de videos positivos y negativos, anotaciones temporales de accidentes y atributos ambientales. Estas etiquetas son heredadas de los conjuntos de referencia citados por los autores. El PDF no describe un nuevo procedimiento propio de anotación, número de anotadores, acuerdo interevaluador ni auditoría independiente de las etiquetas.</t>
       </text>
     </comment>
-    <comment ref="J95" authorId="0" shapeId="0">
+    <comment ref="J95" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado — El artículo declara explícitamente que TempoLearn es un método fully supervised. Aprende a partir de anotaciones temporales y categorías de accidentes, optimizando conjuntamente pérdida de clasificación binaria de propuestas, regresión de límites temporales y clasificación multiclase de accidentes. Las ecuaciones 20–23, p. 6, definen la pérdida combinada. No se trata de aprendizaje no supervisado ni débilmente supervisado, aunque algunos baselines comparados sí utilizan esos paradigmas.</t>
       </text>
     </comment>
-    <comment ref="K95" authorId="0" shapeId="0">
+    <comment ref="K95" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN) y Atención/Transformer — La arquitectura combina una ResNet-101 bidimensional para extraer características visuales, una TCN de convoluciones temporales dilatadas acausales para aprender contexto antes y después del accidente, un módulo convolucional de generación de propuestas y un Transformer con atención multi-cabeza para clasificar los accidentes. Es una integración de dos familias distintas de Deep Learning.</t>
       </text>
     </comment>
-    <comment ref="M95" authorId="0" shapeId="0">
+    <comment ref="M95" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí — Arquitectura híbrida CNN + Transformer. Integra ResNet-101 y TCN para representación visual y temporal, junto con un clasificador Transformer basado en atención multi-cabeza. Las dos familias se combinan funcionalmente en un mismo sistema entrenado para localización y clasificación de accidentes. No se clasifica como recurrente porque TempoLearn no incorpora LSTM o GRU en su arquitectura propuesta, aunque compara con modelos recurrentes.</t>
       </text>
     </comment>
-    <comment ref="N95" authorId="0" shapeId="0">
+    <comment ref="N95" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes — Localización temporal de accidentes de tránsito y clasificación de sus categorías. DoTA incluye colisiones entre vehículos estacionarios o en movimiento, choques laterales, choques con vehículos en sentido contrario, colisiones durante giros o cruces, atropellos, colisiones con obstáculos y pérdida de control o salida de la carretera; también distingue accidentes que involucran al vehículo observador y accidentes de terceros. Tabla 2, p. 8. No se evalúan como objetivo independiente la congestión atípica, fallos de sensores o anomalías de GPS.</t>
       </text>
     </comment>
-    <comment ref="S95" authorId="0" shapeId="0">
+    <comment ref="S95" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aleatoria o no especificada en su mecanismo — DoTA: 80 % entrenamiento y 20 % prueba, después de excluir videos de categoría desconocida, total 4585 videos; sección IV-B, p. 7. CCD: 80 % entrenamiento y 20 % prueba sobre los 1500 videos positivos empleados para localización; sección IV-B, p. 7. Los autores no especifican que la división sea cronológica, por ubicación o por conductor, ni detallan un procedimiento de prevención de solapamiento de escenas entre particiones. CCD constituye un segundo benchmark evaluado, pero el modelo se vuelve a entrenar en CCD con y sin inicialización desde DoTA; no es una prueba puramente externa sin reentrenamiento.</t>
       </text>
     </comment>
-    <comment ref="U95" authorId="0" shapeId="0">
+    <comment ref="U95" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí — Existe un comparador no profundo de tipo FC, red completamente conectada de tres capas, pero debe clasificarse como Deep Learning por ser una red neuronal multicapa; por tanto, no constituye baseline no-DL. En sentido estricto, No: las Tablas 3–5 comparan arquitecturas neuronales profundas y variantes de detección de anomalías basadas en redes; no se presenta un clasificador tradicional independiente, como SVM, Random Forest, regresión logística o un detector estadístico clásico, evaluado en las mismas condiciones.</t>
       </text>
     </comment>
-    <comment ref="E96" authorId="0" shapeId="0">
+    <comment ref="E96" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video: imágenes de vigilancia CCTV y representaciones derivadas de trayectorias de objetos; las entradas finales del clasificador son mapas de influencia.</t>
       </text>
     </comment>
-    <comment ref="F96" authorId="0" shapeId="0">
+    <comment ref="F96" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Ambos/no delimitado: escenas de tráfico vehicular terrestre captadas mediante CCTV; el artículo menciona diversos escenarios viales, pero no proporciona una clasificación cuantitativa separada entre vías urbanas y autopistas.</t>
       </text>
     </comment>
-    <comment ref="H96" authorId="0" shapeId="0">
+    <comment ref="H96" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales/registros con anotaciones del conjunto CADP: los videos representan accidentes y situaciones sin accidente captados mediante CCTV, con anotaciones espaciales y temporales existentes. Los autores asignan etiquetas binarias 0 = sin accidente y 1 = accidente; no describen una nueva validación independiente de las anotaciones. Sección 4.3, pp. 9–10.</t>
       </text>
     </comment>
-    <comment ref="J96" authorId="0" shapeId="0">
+    <comment ref="J96" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado: clasificación binaria de fotogramas mediante etiquetas de accidente y no accidente, con entrenamiento y validación del modelo CNN.</t>
       </text>
     </comment>
-    <comment ref="K96" authorId="0" shapeId="0">
+    <comment ref="K96" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Convolucional (CNN): YOLOv5 para detección visual de objetos y una CNN para clasificación de accidentes; Deep SORT realiza seguimiento de objetos y los mapas de influencia son una representación diseñada de las trayectorias.</t>
       </text>
     </comment>
-    <comment ref="M96" authorId="0" shapeId="0">
+    <comment ref="M96" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No: aunque integra YOLOv5, Deep SORT y una CNN, no combina dos familias distintas de arquitecturas de Deep Learning para la detección final; los componentes neuronales principales son convolucionales y el mapa de influencia es una transformación de características.</t>
       </text>
     </comment>
-    <comment ref="N96" authorId="0" shapeId="0">
+    <comment ref="N96" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes: identificación binaria de la presencia o ausencia de accidentes vehiculares en fotogramas CCTV; no se evalúan de forma independiente congestión atípica, severidad de accidentes ni otros tipos de anomalía.</t>
       </text>
     </comment>
-    <comment ref="S96" authorId="0" shapeId="0">
+    <comment ref="S96" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 División de validación 90 % entrenamiento (6750 mapas) y 10 % validación (750 mapas), Tabla 3, p. 9. No se especifica si la partición es aleatoria, temporal o por video; tampoco se documenta un conjunto de prueba independiente ni una separación por cámara, lugar o accidente.</t>
       </text>
     </comment>
-    <comment ref="U96" authorId="0" shapeId="0">
+    <comment ref="U96" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No: las comparaciones cuantitativas de detección corresponden a una CNN convencional y a alternativas de representación visual; no se documenta un clasificador tradicional no profundo evaluado directamente como línea base.</t>
       </text>
     </comment>
-    <comment ref="E97" authorId="0" shapeId="0">
+    <comment ref="E97" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Video: secuencias de imágenes de accidentes vehiculares, cajas delimitadoras de vehículos y peatones y máscaras de objetos obtenidas mediante sustracción del fondo.</t>
       </text>
     </comment>
-    <comment ref="F97" authorId="1" shapeId="0">
+    <comment ref="F97" authorId="0" shapeId="0">
       <text>
         <t>Antes: Autopista
 Motivo: No desagrega urbano/autopista.</t>
       </text>
     </comment>
-    <comment ref="H97" authorId="0" shapeId="0">
+    <comment ref="H97" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Reales/registros con anotaciones existentes: CCD incluye información anotada sobre ubicación de vehículos y peatones, tipo de accidente y momento del accidente. Los autores efectúan limpieza de etiquetas erróneas y videos de baja resolución, pero no describen concordancia entre anotadores ni una validación independiente de las etiquetas finales. Sección 4.2, pp. 9–10.</t>
       </text>
     </comment>
-    <comment ref="J97" authorId="0" shapeId="0">
+    <comment ref="J97" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado: aprendizaje de clasificación binaria accidente/no accidente con fotogramas etiquetados; entrenamiento y validación sobre subconjuntos del CCD.</t>
       </text>
     </comment>
-    <comment ref="K97" authorId="0" shapeId="0">
+    <comment ref="K97" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Híbrido de familias Convolucional (CNN) y Atención/Transformer; YOLOv5 también utiliza una arquitectura convolucional para localizar objetos.</t>
       </text>
     </comment>
-    <comment ref="M97" authorId="0" shapeId="0">
+    <comment ref="M97" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí: combina explícitamente dos familias distintas de Deep Learning, CNN y Transformer, dentro del detector espacio-temporal; YOLOv5 se utiliza adicionalmente para el preprocesamiento y localización de objetos.</t>
       </text>
     </comment>
-    <comment ref="N97" authorId="0" shapeId="0">
+    <comment ref="N97" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes/incidentes: detección binaria de accidentes de tránsito en fotogramas de video. No se cuantifica por separado la detección de congestión anómala, conducción peligrosa ni severidad del accidente.</t>
       </text>
     </comment>
-    <comment ref="S97" authorId="0" shapeId="0">
+    <comment ref="S97" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Partición 80 % entrenamiento y 20 % validación: 7160 y 1790 fotogramas respectivamente, Tabla 3, p. 9. El artículo no especifica si la partición fue temporal, aleatoria o agrupada por video, cámara o accidente; no reporta un conjunto de prueba independiente.</t>
       </text>
     </comment>
-    <comment ref="U97" authorId="0" shapeId="0">
+    <comment ref="U97" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No: las líneas base experimentales son modelos de Deep Learning y una ablación de la arquitectura propuesta; no se reporta un clasificador tradicional no profundo evaluado directamente sobre las mismas muestras.</t>
       </text>
     </comment>
-    <comment ref="E99" authorId="0" shapeId="0">
+    <comment ref="E99" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Multimodal: imágenes RGB de cámaras de vigilancia de autopistas y mapas espaciotemporales de trayectorias vehiculares. Los atributos originales de trayectoria se extraen mediante una plataforma con cámara RGB y radar FMCW de ondas milimétricas de 80 GHz; incluyen marcas temporales, posiciones iniciales y finales, velocidad media y tipo de vehículo. El modelo utiliza las imágenes y los mapas de trayectorias renderizados, no una rama de radar bruto. Sección 3.1, p. 4; Figura 2, p. 5.</t>
       </text>
     </comment>
-    <comment ref="F99" authorId="0" shapeId="0">
+    <comment ref="F99" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Autopistas y túneles de carretera en China; incluye dos túneles y múltiples escenarios de autopista convencional. No se presenta una evaluación independiente en vías urbanas o intersecciones. Secciones 3.2 y 5.1, pp. 5 y 8–9.</t>
       </text>
     </comment>
-    <comment ref="H99" authorId="0" shapeId="0">
+    <comment ref="H99" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Etiquetas reales con anotación manual: las imágenes de objetos caídos sobre la carretera fueron anotadas manualmente y asociadas con mapas de trayectorias generados por un script. La sección 3.1, p. 4, afirma que cinco integrantes verificaron conjuntamente la alineación de mapas y videos; sin embargo, el pie de la Figura 2, p. 5, menciona cuatro verificadores. No se documenta concordancia entre anotadores ni una validación externa de las cajas de referencia.</t>
       </text>
     </comment>
-    <comment ref="J99" authorId="0" shapeId="0">
+    <comment ref="J99" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Supervisado, con detección de objetos mediante cajas y etiquetas de referencia, complementado por aprendizaje contrastivo supervisado entre propuestas de región de la misma clase y clases distintas. La pérdida conjunta combina clasificación, regresión y contraste; ecuaciones 5–7, p. 8.</t>
       </text>
     </comment>
-    <comment ref="K99" authorId="0" shapeId="0">
+    <comment ref="K99" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CNN convolucional para ambas modalidades, mediante ResNet-101 y WideResNet-101; mecanismo de memoria enlazada LMTTM con direccionamiento por atención temporal; detector de dos etapas basado en Faster R-CNN, FPN, RPN y RoI; cabeza MLP de aprendizaje contrastivo. No se demuestra el uso de una GNN convencional con capas de paso de mensajes, pese al término grafos espaciotemporales del título.</t>
       </text>
     </comment>
-    <comment ref="M99" authorId="0" shapeId="0">
+    <comment ref="M99" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No según el criterio estricto de combinar dos familias distintas de Deep Learning: las ramas principales son CNN más CNN, con memoria temporal y atención como mecanismos auxiliares; no se documenta una arquitectura GNN, RNN/GRU/LSTM o Transformer independiente. Sí existe fusión multimodal de dos ramas profundas, pero multimodalidad no equivale automáticamente a hibridación entre familias.</t>
       </text>
     </comment>
-    <comment ref="N99" authorId="1" shapeId="0">
+    <comment ref="N99" authorId="0" shapeId="0">
       <text>
         <t>Antes: Trayectoria anómala
 Motivo: Objetos caídos sobre la calzada.</t>
       </text>
     </comment>
-    <comment ref="S99" authorId="1" shapeId="0">
+    <comment ref="S99" authorId="0" shapeId="0">
       <text>
         <t>Antes: Prueba independiente
 Motivo: Solo dice que entrena y valida 100 épocas.</t>
       </text>
     </comment>
-    <comment ref="U99" authorId="0" shapeId="0">
+    <comment ref="U99" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No: todos los comparadores cuantitativos principales corresponden a detectores o modelos profundos; las ablaciones también pertenecen al marco de Deep Learning. No se presenta una comparación directa con un detector tradicional basado exclusivamente en reglas, características manuales o métodos estadísticos no profundos.</t>
       </text>
     </comment>
-    <comment ref="E102" authorId="0" shapeId="0">
+    <comment ref="E102" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Series temporales de volumen de tráfico vehicular procedentes de sensores inductivos de la vía, originalmente muestreados cada 20 segundos y agregados a intervalos de 3 minutos. Se utiliza flujo unidireccional agregado de cuatro carriles, sin incorporar directamente velocidad, ocupación, trayectorias GPS, imágenes ni video. El método transforma la serie unidimensional en nueve características que representan variaciones instantáneas, desviaciones estadísticas multiescala y características del estado temporal del tráfico. Sección 3.1, p. 15; Tabla 1, p. 10.</t>
       </text>
     </comment>
-    <comment ref="F102" authorId="0" shapeId="0">
+    <comment ref="F102" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Vía rápida urbana, específicamente Whitemud Drive, Edmonton, Alberta, Canadá. El sensor VDS 1030 se sitúa en una sección de cuatro carriles; se selecciona para evitar interacciones complejas de rampas y zonas de entrecruzamiento. Se trata de un único punto de observación de una autopista urbana, no de una evaluación de toda una red de calles ni de múltiples corredores independientes. Sección 3.1 y Figura 5, p. 15.</t>
       </text>
     </comment>
-    <comment ref="H102" authorId="0" shapeId="0">
+    <comment ref="H102" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Etiquetas de evaluación sintéticas por inyección controlada. Primero se depura el tráfico real mediante descomposición STL, detección estadística local y global y verificación visual manual de candidatos; luego se generan secuencias normales y se inyectan anomalías puntuales y de forma temporal mediante perturbaciones basadas en reducciones de capacidad del Highway Capacity Manual. Las etiquetas finales corresponden a los intervalos artificialmente perturbados, no a accidentes confirmados por registros policiales u operativos. Secciones 3.2–3.5, pp. 16–21; Figuras 6 y 9.</t>
       </text>
     </comment>
-    <comment ref="J102" authorId="0" shapeId="0">
+    <comment ref="J102" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aprendizaje supervisado de clasificación binaria de anomalías por paso temporal. El modelo recibe etiquetas normales/anómalas de eventos inyectados y se entrena mediante Focal Loss, con ponderación de clase anómala α = 0.95 y parámetro γ = 2.0. Las etiquetas sintéticas se utilizan en entrenamiento y evaluación; no es un método puramente no supervisado ni de aprendizaje por reconstrucción. Secciones 2.2.3 y 4.1.4, pp. 13–14 y 22.</t>
       </text>
     </comment>
-    <comment ref="K102" authorId="0" shapeId="0">
+    <comment ref="K102" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Redes neuronales recurrentes GRU con atención temporal aditiva de tipo Bahdanau, combinadas con una rama neuronal feedforward o MLP y un mecanismo aprendido de fusión contextual mediante compuertas. El módulo MS-NaN de extracción de características utiliza información estadística y física del tráfico, pero no constituye por sí mismo una familia de Deep Learning. Figura 3 y sección 2.2.2, pp. 10–13.</t>
       </text>
     </comment>
-    <comment ref="M102" authorId="0" shapeId="0">
+    <comment ref="M102" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí, considerando la combinación explícita de una rama profunda feedforward/MLP y una rama recurrente GRU con mecanismo de atención, fusionadas mediante compuertas aprendidas. Debe codificarse con precisión como arquitectura de doble rama MLP–GRU con atención aditiva; no como CNN–Transformer, porque el modelo propuesto no emplea un Transformer completo ni una CNN en sus ramas principales.</t>
       </text>
     </comment>
-    <comment ref="N102" authorId="0" shapeId="0">
+    <comment ref="N102" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anomalías de volumen de tráfico: perturbaciones puntuales que simulan pérdida de datos o aumentos anómalos de lectura; anomalías temporales cortas, medianas y largas que representan caídas de flujo y congestión no recurrente asociada a reducciones hipotéticas de capacidad. Las reducciones siguen factores inspirados en el Highway Capacity Manual: cierres de arcén y de uno, dos o tres carriles. No se detectan ni clasifican accidentes reales individualizados. Sección 3.5 y Tabla 4, pp. 19–21.</t>
       </text>
     </comment>
-    <comment ref="S102" authorId="0" shapeId="0">
+    <comment ref="S102" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 División cronológica del conjunto completo de 91 días: 70% inicial, aproximadamente 64 días, para entrenamiento y 30% final, aproximadamente 27 días, para prueba independiente, según sección 4.1.1, p. 22. Los autores afirman utilizar estadísticas de normalización calculadas con entrenamiento y retener pesos según pérdida de validación. Se fijan semillas aleatorias. La separación temporal es positiva, pero debe señalarse que las secuencias sintéticas proceden de patrones construidos a partir del mismo origen de datos y que la optimización de umbrales por F1 no especifica claramente un conjunto de validación independiente.</t>
       </text>
     </comment>
-    <comment ref="U102" authorId="0" shapeId="0">
+    <comment ref="U102" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí. Si-TDD constituye un comparador externo basado en distancias de vecinos más cercanos y no requiere entrenamiento de una red profunda; obtiene F1 = 0.6061 y AUROC = 0.8235 frente a F1 = 0.7757 y AUROC = 0.9112 de DB-CGNet, Tabla 7, p. 26. Auto-RL utiliza LSTM-DQN, por lo que no debe clasificarse como comparador no profundo.</t>
       </text>
     </comment>
-    <comment ref="E103" authorId="0" shapeId="0">
+    <comment ref="E103" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Imágenes RGB estáticas de escenas de tráfico y vigilancia vial, almacenadas en formato JPG y procesadas a una resolución de 224 × 224 píxeles. Las imágenes proceden de los conjuntos Traffic-Net y Road Anomaly Dataset (RAD). No se utilizan secuencias temporales, trayectorias GPS, series de sensores de tráfico ni información de movimiento entre fotogramas. Página 4, secciones 3.2–3.4 y Figura 2.</t>
       </text>
     </comment>
-    <comment ref="F103" authorId="1" shapeId="0">
+    <comment ref="F103" authorId="0" shapeId="0">
       <text>
         <t>Antes: Autopista
 Motivo: No clasifica las imágenes por tipo de vía.</t>
       </text>
     </comment>
-    <comment ref="H103" authorId="0" shapeId="0">
+    <comment ref="H103" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Se emplean etiquetas categóricas preexistentes de los conjuntos públicos Traffic-Net y RAD, atribuidas a anotación de investigadores sobre imágenes procedentes de vigilancia. No se describe un nuevo proceso de anotación realizado por los autores, número de anotadores, concordancia interevaluador ni auditoría independiente de la validez de las etiquetas. Las etiquetas son clases visuales de escena, no marcas temporales de eventos. Página 4, sección 3.2 y Tabla 2.</t>
       </text>
     </comment>
-    <comment ref="J103" authorId="0" shapeId="0">
+    <comment ref="J103" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aprendizaje supervisado multiclase mediante transferencia de aprendizaje. Las tres redes se inicializan con pesos preentrenados en ImageNet y se ajustan con imágenes etiquetadas de Traffic-Net y RAD. La función de pérdida es entropía cruzada categórica, el optimizador es Adam y las predicciones se fusionan durante inferencia. No se describe entrenamiento no supervisado ni aprendizaje con muestras normales exclusivamente. Páginas 5–6, secciones 4.1–4.4.</t>
       </text>
     </comment>
-    <comment ref="K103" authorId="0" shapeId="0">
+    <comment ref="K103" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Familia CNN, específicamente redes residuales profundas ResNet50 y ResNet101, junto con EfficientNetB0. Las tres arquitecturas son variantes de redes neuronales convolucionales para clasificación de imágenes. La fusión es un ensamble de modelos CNN heterogéneos, no una combinación CNN–RNN, CNN–Transformer o CNN–autoencoder. Página 5, Figura 3 y sección 4.2.</t>
       </text>
     </comment>
-    <comment ref="M103" authorId="0" shapeId="0">
+    <comment ref="M103" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No, según el criterio de combinar al menos dos familias diferentes de Deep Learning. Aunque los autores lo denominan ensamble heterogéneo, ResNet50, ResNet101 y EfficientNetB0 pertenecen a la misma familia CNN. Se registra como ensamble de tres arquitecturas convolucionales, no como modelo híbrido entre familias profundas. Página 5, secciones 4.1–4.3.</t>
       </text>
     </comment>
-    <comment ref="N103" authorId="0" shapeId="0">
+    <comment ref="N103" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Clasificación visual de cuatro categorías por conjunto. Traffic-Net: Accident, Dense Traffic, Fire y Sparse Traffic. RAD: Accident, Car Fire, Fighting y Snatching at Gunpoint. Las clases de accidentes e incendios de vehículos corresponden directamente a incidentes viales; congestión densa puede representar una condición anómala dependiendo del contexto; tráfico escaso no implica necesariamente anomalía; peleas y robos son eventos de seguridad pública, no necesariamente anomalías del tránsito vehicular. No se realiza localización temporal ni detección de trayectorias anormales. Página 4, Tabla 2 y Figura 2.</t>
       </text>
     </comment>
-    <comment ref="S103" authorId="0" shapeId="0">
+    <comment ref="S103" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Se declara partición estratificada 70% entrenamiento, 15% validación y 15% prueba para ambos conjuntos. Traffic-Net: 3080/660/680; RAD: 2393/513/513. La aumentación se aplica exclusivamente al entrenamiento, mientras validación y prueba solo se normalizan. Los tres modelos utilizan las mismas particiones y configuraciones. No se especifica separación por cámara, ubicación, video original o evento, por lo que podrían existir imágenes muy similares entre particiones si proceden de una misma secuencia; este riesgo no está demostrado, pero tampoco descartado. Página 4, sección 3.5 y Tabla 2; página 6, sección 4.4.</t>
       </text>
     </comment>
-    <comment ref="U103" authorId="0" shapeId="0">
+    <comment ref="U103" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No se incluye un comparador no profundo evaluado directamente con las mismas particiones. Los tres baselines experimentales son CNN. Los métodos estadísticos, SVM, k-NN, K-means e Isolation Forest se mencionan en antecedentes, pero no se entrenan ni evalúan sobre Traffic-Net o RAD dentro de este estudio. Páginas 2–3, sección 2; páginas 7–9, Tablas 3, 4 y 6.</t>
       </text>
     </comment>
-    <comment ref="E104" authorId="0" shapeId="0">
+    <comment ref="E104" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Datos multimodales sincronizados a 30 Hz: señales telemétricas del vehículo procedentes del CAN-Bus; señales fisiológicas del conductor recogidas mediante sensores portables; y distancias espaciales a participantes cercanos del tráfico obtenidas mediante detección visual de objetos con tecnología Mobileye. El modelo utiliza las distancias derivadas de la cámara, no imágenes RGB crudas como entrada principal de la arquitectura. Cada observación se representa como una secuencia temporal y la decisión se realiza sobre segmentos de seis segundos. Página 6, sección IV-A.</t>
       </text>
     </comment>
-    <comment ref="F104" authorId="0" shapeId="0">
+    <comment ref="F104" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Principalmente conducción urbana real en una ciudad asiática no identificada. Incluye calles residenciales, zonas escolares y áreas céntricas; el artículo indica que existen muy pocos segmentos de autopista. Los ejemplos de la Figura 1, página 1, muestran un vehículo circulando en sentido incorrecto, peatones que cruzan inesperadamente, ciclistas que irrumpen en la vía y vehículos que invaden el carril. No se evalúan por separado carreteras urbanas y autopistas.</t>
       </text>
     </comment>
-    <comment ref="H104" authorId="0" shapeId="0">
+    <comment ref="H104" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 El conjunto DAD contiene anotaciones manuales de eventos y maniobras realizadas a partir de videos de la carretera siguiendo el protocolo del conjunto Honda Driving Dataset. Los autores construyen dos grupos de evaluación: normal, segmentos sin anotaciones superpuestas; y candidato, segmentos que coinciden con maniobras inducidas por estímulos, errores del conductor o infracciones. Las etiquetas candidato son indicadores indirectos y no equivalen necesariamente a anomalías confirmadas. Para una evaluación adicional se seleccionan 400 segmentos de seis segundos y tres evaluadores humanos los etiquetan directamente como normales o anómalos; la etiqueta final se obtiene por mayoría de al menos dos evaluadores. Se reporta Krippendorff α = 0.895 para normalidad/anomalía. Página 6, Tabla I; página 8, sección V-B y Figura 7.</t>
       </text>
     </comment>
-    <comment ref="J104" authorId="0" shapeId="0">
+    <comment ref="J104" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aprendizaje no supervisado y contrastivo. Cada GAN condicional aprende a predecir señales futuras a partir del historial temporal sin utilizar etiquetas de anomalía. Las representaciones latentes de los discriminadores se fusionan mediante atención y se entrenan con triplet loss utilizando como ancla la señal real, como positivo su predicción correspondiente y como negativo una predicción de un segmento no relacionado. Las etiquetas normal/candidato se utilizan para evaluación y para seleccionar el margen α sobre desarrollo, no para la pérdida principal de entrenamiento. Por tanto, la arquitectura es no supervisada, aunque la selección de hiperparámetros sí utiliza etiquetas de desarrollo. Páginas 4–7, secciones III y IV-B.</t>
       </text>
     </comment>
-    <comment ref="K104" authorId="0" shapeId="0">
+    <comment ref="K104" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Arquitectura híbrida con GAN condicionales, CNN, RNN-LSTM y atención multi-head de tipo Transformer. Las CNN extraen características locales de señales temporales, las LSTM modelan dependencias temporales, las GAN generan predicciones y representaciones discriminativas, y la atención combina información entre modalidades. Se utiliza aprendizaje contrastivo mediante triplet loss. No se emplean GNN, VAE ni difusión. Páginas 4–5, Figuras 3–5.</t>
       </text>
     </comment>
-    <comment ref="M104" authorId="0" shapeId="0">
+    <comment ref="M104" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí. El método integra al menos dos familias distintas de Deep Learning: CNN, LSTM y GAN condicionales, junto con atención multi-head para fusión multimodal. La combinación CNN-LSTM implementa modelado espaciotemporal de señales; las GAN permiten predicción adversarial; la atención aprende relaciones entre modalidades. Se clasifica como arquitectura híbrida profunda multimodal, no simplemente como ensamble de modelos de una sola familia. Páginas 4–5, Figuras 3 y 4.</t>
       </text>
     </comment>
-    <comment ref="N104" authorId="0" shapeId="0">
+    <comment ref="N104" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Anomalías de conducción y situaciones inesperadas o potencialmente peligrosas: evasión de peatones y ciclistas, interacción imprevista con otros vehículos, invasiones de carril, maniobras inducidas por estímulos, errores de conducción e infracciones de tránsito. La formulación final distingue comportamiento esperado frente a inesperado, sin identificar necesariamente una clase concreta de incidente. No se centra en detección de fallas de sensores, congestión macroscópica ni predicción de accidentes futuros. Página 1, Figura 1; página 6, Tabla I.</t>
       </text>
     </comment>
-    <comment ref="S104" authorId="1" shapeId="0">
+    <comment ref="S104" authorId="0" shapeId="0">
       <text>
         <t>Antes: No reportada
 Motivo: Separación por sesiones de conducción.</t>
       </text>
     </comment>
-    <comment ref="U104" authorId="0" shapeId="0">
+    <comment ref="U104" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No. Los comparadores experimentales principales son modelos de Deep Learning: CNN-LSTM GANs, BeatGAN y variantes de atención. No se presentan resultados propios de Isolation Forest, One-Class SVM, modelos estadísticos, métodos basados en reglas o clasificadores tradicionales sobre la misma partición de DAD. Los métodos clásicos se mencionan en la revisión de antecedentes, pero no son baselines cuantitativos del experimento. Páginas 2–3 y 7.</t>
       </text>
     </comment>
-    <comment ref="E105" authorId="0" shapeId="0">
+    <comment ref="E105" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Videos RGB de cámaras de vigilancia, procesados como secuencias de fotogramas mediante convoluciones tridimensionales. No utiliza señales GPS, trayectorias numéricas, sensores de flujo, CAN-Bus ni datos fisiológicos. La Figura 7, página 10, muestra escenas reales de calles, intersecciones, vehículos y accidentes; la Figura 11, página 14, representa imágenes y puntuaciones de anomalía a lo largo de los fotogramas.</t>
       </text>
     </comment>
-    <comment ref="F105" authorId="0" shapeId="0">
+    <comment ref="F105" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Entorno vial principalmente urbano, representado por intersecciones, calles y escenas de videovigilancia de accidentes. No se identifica una ciudad específica ni se documenta un subconjunto independiente de autopistas. El conjunto UCF-Crime incluye videos de contextos no viales; por tanto, el entorno urbano corresponde a las escenas vehiculares mostradas y no debe atribuirse a todo el corpus. Páginas 9–10, Tabla 2 y Figura 7.</t>
       </text>
     </comment>
-    <comment ref="H105" authorId="0" shapeId="0">
+    <comment ref="H105" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Etiquetas de categorías preexistentes de UCF-Crime, entre ellas Road accidents y Normal. El artículo emplea esas categorías para entrenar, validar y probar modelos de reconocimiento. No describe un procedimiento nuevo de anotación independiente de accidentes, acuerdo entre anotadores, verificación de etiquetas ni proporción de errores de etiquetado. La Figura 11 presenta localización visual de anomalías por fotograma, pero no especifica el origen ni la granularidad de anotaciones temporales utilizadas para evaluar esas curvas. Página 9, Tabla 2; página 14, Figura 11.</t>
       </text>
     </comment>
-    <comment ref="J105" authorId="0" shapeId="0">
+    <comment ref="J105" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Aprendizaje supervisado de clasificación de videos o secuencias etiquetadas. Los autores entrenan seis arquitecturas y calculan exactitud de clasificación usando verdaderos positivos, verdaderos negativos, falsos positivos y falsos negativos. Aunque la arquitectura incorpora una operación adaptativa de filtrado de características, no constituye aprendizaje no supervisado, auto-supervisado ni detección basada en reconstrucción. El texto no documenta una función de pérdida específica ni detalles suficientes para establecer si se empleó balanceo de clases. Páginas 9–11.</t>
       </text>
     </comment>
-    <comment ref="K105" authorId="0" shapeId="0">
+    <comment ref="K105" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CNN tridimensional residual R3D y Dense-R3D para extracción espaciotemporal; RNN de tipo Bi-LSTM para dependencias temporales bidireccionales; bloques densos inspirados en DenseNet; y umbralización suave adaptativa interpretada por los autores como un mecanismo especial de atención sobre características. No se emplean GNN, Transformer explícito, VAE, GAN ni modelos de difusión. Páginas 4–8, Figuras 2–6.</t>
       </text>
     </comment>
-    <comment ref="M105" authorId="0" shapeId="0">
+    <comment ref="M105" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Sí. Integra dos familias distintas de Deep Learning: convoluciones 3D de tipo CNN residual y denso, junto con redes recurrentes bidireccionales Bi-LSTM. La umbralización suave es un módulo adaptativo de selección y supresión de características, no una familia profunda independiente. El modelo se clasifica como híbrido CNN 3D + Bi-LSTM, con filtrado adaptativo de ruido. Páginas 5–8.</t>
       </text>
     </comment>
-    <comment ref="N105" authorId="0" shapeId="0">
+    <comment ref="N105" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 Accidentes de tráfico y comportamientos vehiculares anómalos visibles en videovigilancia, incluidos choques, incendios de vehículos y otros eventos peligrosos mencionados en la descripción del conjunto. El artículo también evalúa arrestos, incendios, robos, hurtos en tiendas y vandalismo, que no deben confundirse con anomalías de tráfico. La categoría específica pertinente para esta revisión es Road accidents. Página 9, Tabla 2; página 12, Tabla 5.</t>
       </text>
     </comment>
-    <comment ref="S105" authorId="1" shapeId="0">
+    <comment ref="S105" authorId="0" shapeId="0">
       <text>
         <t>Antes: Aleatoria
 Motivo: No informa proporciones ni criterio de división.</t>
       </text>
     </comment>
-    <comment ref="U105" authorId="0" shapeId="0">
+    <comment ref="U105" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No. Todas las arquitecturas comparadas experimentalmente pertenecen a Deep Learning: R3D, DRN, LSTM, Bi-LSTM, P3D, I3D y R(2+1)D. El apartado de trabajos relacionados menciona SVM y métodos tradicionales, pero no presenta una comparación experimental propia con un clasificador no profundo sobre los mismos datos. Páginas 3 y 11–13.</t>
@@ -4170,6 +4233,12 @@
       <text>
         <t>Antes: In the future, we plan to broaden this work in several challengable directions. (p. 10)
 Motivo: Coherente con la hoja 2.</t>
+      </text>
+    </comment>
+    <comment ref="M43" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: 0.5
+Motivo: Código con DOI (ETS) y datasets públicos (DAD, CCD, A3D): ambos públicos.</t>
       </text>
     </comment>
   </commentList>
@@ -4465,1565 +4534,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="130" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>LECTURA A TEXTO COMPLETO — un estudio por fila, el mismo ID en las tres hojas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Hoja 1_TextoCompleto: lee el PDF y decide Incluir o Excluir. Si excluyes: CRITERIO + EVIDENCIA con cita y página.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Orden de los criterios: CE-5 (survey, preprint, resumen extendido) → CE-2 (no es tráfico vehicular) →</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   CE-3 (solo pronóstico, no detecta anomalías) → CE-4 (el DL no es el método principal) →</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   CI-6 (no evalúa cuantitativamente la DETECCIÓN; solo otra tarea) → CE-6 (no describe modelo, datos o resultados).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Hoja 2_Extraccion: solo para los que quedan en Incluir. Usa las listas desplegables cuando las haya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Hoja 3_Calidad: solo para los incluidos. Cada ítem 1 / 0.5 / 0 y la frase con la página que lo justifica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   La calidad NO excluye estudios: solo se reporta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>La fila amarilla (fila 2) explica qué poner en cada columna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cuando termines, guarda el archivo en cribado\revision\ y súbelo con git (o pásalo por el chat).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D66"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="110" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Hoja</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Qué</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Motivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>R0032</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>REHACER</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>La hoja 1 tiene el texto de R0045 (copiado) y las hojas 2-3 dicen EXCLUIDO: rehacer con el PDF de R0032 (Driver Behavior Profiling on UAH-DriveSet).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>R0167</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>REHACER</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Paradigma no identificable («aprendizaje federado»): elegir una opción de la lista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>R0192</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>REHACER</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>La hoja 2 está desplazada (cada valor en la columna equivocada): volver a pegar el bloque de 20 valores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>R0389</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>REHACER</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Las tres hojas tienen los datos de otro artículo (R0380, DOI 10.3390/ijgi13100351): rehacer con el PDF de R0389 (DOI 10.1007/s43926-022-00025-y).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>R0403</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>REHACER</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Las tres hojas tienen los datos de R0380 (Traffic-ConvLSTM, Wuhan): rehacer con el PDF de R0403 (DOI 10.1016/j.commtr.2025.100214, anticipación de accidentes).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>R0025</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Partición «No reportada» en la hoja 2 pero QA2 = 1 en la hoja 3: revisa uno de los dos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>R0029</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Se excluyó por CE-3 (clasifica perfiles normal/somnoliento/agresivo), pero R0360, R0428 y R1029 se incluyeron con clasificación de conducción anómala. Decide con el mismo criterio para todos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>R0051</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Partición aleatoria (411/35/148) pero QA2 = 1: según la escala sería 0.5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>R0666</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Caso límite: el DL extrae y reconstruye trayectorias y la anomalía se decide con reglas. Se mantiene incluido (regla de híbridos de CI-5); va al anexo de casos límite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>R0986</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Revisar</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>El texto analizado corresponde a Systems and Soft Computing (DOI 10.1016/j.sasc.2025.200254), pero el registro tiene DOI 10.1002/spy2.70136: confirma que el PDF es el del registro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>R0024</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «QA8 Limitaciones» → 0</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>La hoja 2 dice «No reportadas»: la cita es trabajo futuro, no una limitación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>R0024</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «QA8 evidencia» → No reportado (solo trabajo futuro, p. 10)</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Coherente con la hoja 2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>R0052</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → Ambos</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Intersecciones y rampas/puentes de carretera.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>R0080</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Incidentes distintos en entrenamiento (23) y prueba (22).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>R0097</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → No reportado</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Ubicación y tipo de vía no reportados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>R0106</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>No recuperado</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Sin PDF: cuenta en PRISMA como «informe no recuperado», no como excluido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>R0119</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → Ambos</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Intersecciones y autopistas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>R0119</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Aleatoria</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Partición estratificada sin separación temporal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>R0121</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → Urbano</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Dos cruces peatonales de calle (35 mph) en Florida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>R0136</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>No recuperado</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sin PDF: cuenta en PRISMA como «informe no recuperado», no como excluido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>R0157</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>No recuperado</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Sin PDF: cuenta en PRISMA como «informe no recuperado», no como excluido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>R0167</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → No reportada</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>«No se detallan particiones».</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>R0175</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → No reportado</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>No especifica el tipo de vía.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>R0185</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → No reportada</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>No describe la partición.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>R0190</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «CRITERIO» → CE-3</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>R0244</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «DECISIÓN TC» → Incluir</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>«INCLUIDO» no es una opción de la lista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>R0249</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>R0337</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>No recuperado</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Sin PDF: cuenta en PRISMA como «informe no recuperado», no como excluido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>R0379</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>Evalúa en una grabación highD no vista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>R0471</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>No recuperado</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sin PDF: cuenta en PRISMA como «informe no recuperado», no como excluido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>R0501</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → Ambos</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Vías urbanas e interurbanas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>R0501</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Conjunto externo ECVD solo para prueba.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>R0526</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>No recuperado</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Sin PDF: cuenta en PRISMA como «informe no recuperado», no como excluido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>R0528</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>R0537</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → No reportada</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Sin proporciones ni protocolo de separación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>R0592</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>No recuperado</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Sin PDF: cuenta en PRISMA como «informe no recuperado», no como excluido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>R0596</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → No reportada</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>Partición insuficientemente reportada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>R0598</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → No reportado</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Pista de pruebas; no es urbano ni autopista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>R0601</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>Conjunto de prueba de AI City Challenge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>R0604</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>R0604</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «CRITERIO» → CE-2</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Monitoreo del conductor dentro de la cabina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>R0614</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «CRITERIO» → CE-3</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>R0623</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>No recuperado</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Sin PDF: cuenta en PRISMA como «informe no recuperado», no como excluido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>R0658</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>Particiones oficiales de los benchmarks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>R0664</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Videos de prueba separados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>R0666</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → No reportada</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>No detalla la partición.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>R0929</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>R0929</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «CRITERIO» → CE-2</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>Monitoreo del conductor dentro de la cabina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>R0943</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → No reportada</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Sin procedimiento de selección ni conjunto de prueba.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>R1000</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → No reportado</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>No indica qué escenas de NGSIM usa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>R1010</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → No reportado</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>Evaluado con autos de juguete en escenario controlado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>R1013</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>Conjunto de prueba oficial de TADS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>R1014</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Familia DL principal» → Otra</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>DeepWalk/Node2vec no es una GNN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>R1082</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Conjunto de prueba de MAAD (con ajuste de hiperparámetros en parte de él).</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>R1092</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Aleatoria</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>División 80/20 de videos sin otro criterio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>R1100</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → No reportado</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>DoTA/CCD sin clasificación por tipo de vía.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>R1138</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → No reportado</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>No desagrega urbano/autopista.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>R1140</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>No recuperado</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>Sin PDF: cuenta en PRISMA como «informe no recuperado», no como excluido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>R1148</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Categoría de anomalía» → Evento/otro</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>Objetos caídos sobre la calzada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>R1148</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → No reportada</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>Solo dice que entrena y valida 100 épocas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>R1149</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>No recuperado</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Sin PDF: cuenta en PRISMA como «informe no recuperado», no como excluido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>R1166</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>R1185</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Entorno» → No reportado</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>No clasifica las imágenes por tipo de vía.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>R1202</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>Separación por sesiones de conducción.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>R1214</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Corregido «Partición» → No reportada</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>No informa proporciones ni criterio de división.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
@@ -6224,40 +4734,40 @@
       </c>
     </row>
     <row r="6" ht="57.6" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>R0032</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>A Comparative Analysis of Machine Learning, Deep Learning, and Metaheuristic-Based Ensemble Learning for Driver Behavior Profiling on UAH-DriveSet</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>cribado\pdf\R0032.pdf</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Incluir</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>We develop an online real-time incident detection approach that leverages the model ensemble and the uncertainty quantification while detecting incidents. (p. 1); "Overall, the deep ensemble model with the 75% quantile of probability output achieved 0.90 DR and 0.08 FAR" (p. 10)</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>[Incluir] Investigación experimental de detección de incidentes vehiculares en autopistas mediante LSTM y deep ensemble con supervisión débil (Snorkel). Utiliza datos reales PeMS de velocidad y ocupación, evalúa 211 incidentes y reporta DR=0.90 y FAR=0.08 para el ensamble. Cumple el enfoque de Deep Learning, detección de anomalías y validación cuantitativa.</t>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Página 1: título, autores, conferencia ICIIT 2026, DOI y licencia CC BY 4.0. Página 3, sección 3.1: UAH-DriveSet, más de 500 minutos, seis conductores, carreteras y vías secundarias, tres comportamientos. Página 3, sección 3.2: partición estratificada 70% entrenamiento, 15% validación y 15% prueba. Página 4, Figura 1: flujo de preprocesamiento, modelos ML/DL y ensamble metaheurístico. Página 5, Tabla 1: comparación de nueve modelos, con accuracy de 0.9989 para PSO Ensemble, 0.9983 para Attention-LSTM y 0.9967 para TCN. Página 5, Figura 2: curvas ROC. Página 6: conclusiones y discusión del rendimiento.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Se incluye porque analiza comportamientos de conducción potencialmente anómalos mediante sensores de teléfonos inteligentes y arquitecturas profundas de clasificación temporal. Compara CatBoost, XGBoost, KNN y ExtraTrees con CNN 1D, BiLSTM, TCN y Attention-LSTM, y propone un ensamble de modelos optimizado mediante Particle Swarm Optimization. El mejor modelo alcanza accuracy global de 99.89% y recall de 95% para la clase minoritaria de somnolencia. No detecta accidentes ocurridos ni eventos anómalos desconocidos: reconoce tres clases previamente definidas de estilo de conducción. Se identifican riesgos metodológicos importantes: solo seis conductores; agrupación de sus datos antes de la partición; ausencia de evaluación independiente por conductor; aplicación de SMOTE y preprocesamiento sin precisar su ajuste exclusivo sobre entrenamiento; resultados prácticamente perfectos en varios modelos; y falta de experimentos repetidos o validación externa. El propio artículo advierte posibles problemas de particionamiento en modelos temporales. Estos factores deben considerarse al interpretar la precisión y al comparar el estudio con métodos de detección de anomalías en tráfico vial.</t>
         </is>
       </c>
     </row>
@@ -7584,78 +6094,82 @@
       </c>
     </row>
     <row r="42" ht="28.8" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>R0389</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Detection of road traffic anomalies based on computational data science</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>cribado\pdf\R0389.pdf</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Excluir</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>CI-6</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Página 1: resumen y DOI; declara detección de anomalías y uso de Deep Learning. Página 4, Figuras 1–3: comparación de velocidades y variaciones estadísticas ante condiciones anormales. Página 5, sección 3.2: umbral ilustrativo de reducción de velocidad de 30 km/h y pruebas de diferencias entre estaciones. Página 9, sección 4.11: red descrita genéricamente mediante entrada, capas ocultas y salida. Página 10, Figura 7: flujo CDS para detección, identificación de fuente y localización. Página 13, Figura 10: esquema genérico de neuronas, pesos y activación. Página 15, Tabla 4: estadísticas de regresión para condiciones con y sin ruido, no métricas de clasificación. Página 15, Figuras 13–14: visualización de anomalías de posicionamiento y comparación gráfica CDS frente a ML sin indicadores cuantitativos de detección. Página 16, conclusiones: se afirma una mejora de pronóstico, pero no se cuantifica la detección de anomalías.</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Se excluye de la síntesis principal de estudios de detección de anomalías vehiculares mediante Deep Learning por ausencia de evaluación cuantitativa específica del detector. Raiyn (2022) propone Computational Data Science para analizar datos de velocidad, posición GNSS y calidad de datos obtenidos mediante teléfonos inteligentes, sensores y dispositivos Ublox. Considera anomalías asociadas a accidentes, congestión, ruido, interferencia y pérdida de información. Define condiciones anormales mediante desviaciones de velocidad y diferencias espaciales y temporales; presenta una red neuronal conceptual y un procedimiento de entrenamiento y prueba. Sin embargo, no identifica con precisión el conjunto experimental, las etiquetas de referencia, la arquitectura profunda, el tamaño de entrenamiento y prueba ni los parámetros de aprendizaje. La Tabla 4 informa Multiple R, R², R² ajustado, desviación estándar y asimetría en presencia y ausencia de ruido, pero esos valores no son métricas de detección. Las Figuras 13 y 14 muestran resultados visuales sin tasas de aciertos o errores. Por tanto, no es posible extraer un rendimiento comparable con los estudios incluidos. Se conserva como antecedente conceptual sobre anomalías de velocidad, calidad de datos y posicionamiento vehicular, sin incorporarlo al análisis cuantitativo principal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28.8" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>R0403</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Domain-enhanced dual-branch model for efficient and interpretable accident anticipation</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>cribado\pdf\R0403.pdf</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Incluir</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>PDF completo de 14 páginas, publicado el 4 de octubre de 2024 en ISPRS International Journal of Geo-Information, volumen 13, artículo 351, DOI: 10.3390/ijgi13100351. El artículo presenta Traffic-ConvLSTM, una arquitectura profunda no supervisada que combina convoluciones multiescala y redes ConvLSTM para identificar desviaciones de patrones normales de tráfico urbano (sección 3.2, pp. 7–8; Figura 3, p. 8). Utiliza datos reales obtenidos mediante la API de Amap en Wuhan, China, entre el 20 de septiembre de 2021 y el 17 de junio de 2022, con aproximadamente 60 millones de registros y muestreo cada 30 minutos (sección 3.1, pp. 5–6). Compara su rendimiento con SAE, CNN-LSTM, Bi-LSTM, GAN y Transformer, obteniendo City-precision de 92.875%, City-accuracy de 83.871%, Road-precision de 88.889% y Road-accuracy de 92.035% (Tabla 2, p. 10). Incluye experimentos de ablación y análisis de anomalías relacionadas con festividades y eventos deportivos (pp. 9–12). El texto completo es Open Access bajo licencia CC BY 4.0.</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>Se incluye porque es un estudio original publicado en 2024 que desarrolla y evalúa un modelo de Deep Learning específicamente orientado a detectar anomalías en tráfico vehicular urbano. Traffic-ConvLSTM aprende patrones normales de circulación mediante datos reales y detecta desviaciones espaciotemporales usando diferencias del índice de similitud estructural SSIM. Su objetivo central es identificar anomalías, no únicamente predecir velocidades o flujo vehicular. Presenta resultados cuantitativos, comparación con cinco arquitecturas profundas y análisis experimental en escalas de ciudad y carretera. Cumple los criterios de temática, metodología, periodo de publicación y acceso gratuito al texto completo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28.8" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>R0403</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Domain-enhanced dual-branch model for efficient and interpretable accident anticipation</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>cribado\pdf\R0403.pdf</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Incluir</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>Artículo publicado en ISPRS International Journal of Geo-Information (2024), volumen 13, artículo 351, DOI 10.3390/ijgi13100351. Propone Traffic-ConvLSTM, un modelo profundo no supervisado para detectar anomalías espaciotemporales en el tráfico urbano mediante datos de monitoreo vehicular. Utiliza aproximadamente 60 millones de registros reales de Wuhan, China, recopilados entre septiembre de 2021 y junio de 2022 mediante Amap API (sección 3.1, pp. 5–6). La arquitectura integra convoluciones multiescala y ConvLSTM, y emplea diferencias del índice SSIM para identificar anomalías (sección 3.2, pp. 7–8). La Tabla 2, p. 10, presenta resultados cuantitativos de detección en escalas de ciudad y carretera frente a cinco modelos de referencia. El texto completo está disponible en acceso abierto.</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>Se incluye porque es una investigación original publicada dentro del periodo 2020–2026, centrada específicamente en la detección de anomalías del tráfico vehicular mediante Deep Learning. El modelo Traffic-ConvLSTM aprende patrones espaciotemporales normales y detecta desviaciones asociadas con congestión atípica y eventos urbanos. Presenta evaluación cuantitativa sobre datos reales, comparación con cinco modelos profundos y experimentos de ablación. Cumple los criterios temáticos, metodológicos, temporales y de acceso gratuito al texto completo. Se registran como limitaciones la documentación insuficiente de las particiones experimentales y las inconsistencias en la denominación de las métricas.</t>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Página 1: identificación bibliográfica, DOI, licencia abierta y resumen con la propuesta dual-branch. Página 3, Figura 2: arquitectura multimodal de extracción visual, representación textual, alineamiento y anticipación. Páginas 4–7: construcción de conocimiento de dominio, características y mecanismo de predicción. Página 8, sección 3.8 y Figura 6: umbral aprendible y comparación de decisiones. Página 8, sección 4.1: descripción y particiones de DAD, CCD y A3D. Página 9, Tablas 2–4: tamaños de datasets, AP y mTTA frente a múltiples métodos. Página 11, Tabla 7: ablación de atención, características textuales y umbral. Página 11, Figura 10: ejemplo de fallo por baja calidad visual. Página 13, sección Replication and data sharing: DOI del código en ETS.</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Se incluye en la revisión sistemática sobre detección de anomalías en tráfico vehicular mediante Deep Learning (2020–2026). Guan et al. (2025) presentan una arquitectura de dos ramas que integra representaciones visuales de videos dashcam, información textual estructurada a partir de informes de accidentes, conocimiento de dominio y mecanismos de atención para estimar anticipadamente el riesgo de colisión. El método utiliza VGG-16 y Long-CLIP para la representación, un umbral aprendible para generar alertas y GPT-4o para explicaciones y recomendaciones posteriores. Se evalúa en tres benchmarks reales: DAD, CCD y A3D. Obtiene AP de 87,7 %, 99,7 % y 95,4 %, respectivamente, con mTTA de 4,47 s, 3,70 s y 3,18 s. La comparación con diez métodos en DAD y las ablaciones permiten examinar su contribución. Como cautelas, las particiones se describen por videos pero no se demuestra separación por procedencia o evento; A3D crea negativos a partir de segmentos sin accidente; la Figura 6 menciona una búsqueda de mejor umbral F1 en prueba; y el modelo falla cuando la baja iluminación u oclusión impide reconocer comportamientos críticos. El código se declara disponible en ETS, DOI 10.26599/ETSD.2025.9190040. Se incorpora a la síntesis como anticipación de accidentes basada en video y aprendizaje profundo multimodal, distinguiendo AP de clasificación anticipada y mTTA de métricas de detección retrospectiva.</t>
         </is>
       </c>
     </row>
@@ -10050,7 +8564,1281 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Hoja</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Qué</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>R0167</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>REHACER</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Paradigma no identificable («aprendizaje federado»): elegir una opción de la lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>R0192</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>REHACER</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>La hoja 2 está desplazada (cada valor en la columna equivocada): volver a pegar el bloque de 20 valores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>R0025</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Partición «No reportada» en la hoja 2 pero QA2 = 1 en la hoja 3: revisa uno de los dos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>R0029</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Se excluyó por CE-3 (clasifica perfiles normal/somnoliento/agresivo), pero R0032 (UAH-DriveSet, mismas tres clases), R0360, R0428 y R1029 se incluyeron. Decide con el mismo criterio para todos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>R0051</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Partición aleatoria (411/35/148) pero QA2 = 1: según la escala sería 0.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>R0666</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Caso límite: el DL extrae y reconstruye trayectorias y la anomalía se decide con reglas. Se mantiene incluido (regla de híbridos de CI-5); va al anexo de casos límite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>R0986</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>El texto analizado corresponde a Systems and Soft Computing (DOI 10.1016/j.sasc.2025.200254), pero el registro tiene DOI 10.1002/spy2.70136: confirma que el PDF es el del registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>R0024</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «QA8 Limitaciones» → 0</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>La hoja 2 dice «No reportadas»: la cita es trabajo futuro, no una limitación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>R0024</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «QA8 evidencia» → No reportado (solo trabajo futuro, p. 10)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Coherente con la hoja 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>R0032</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Tipo de dato» → Multimodal</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Acelerómetro, giroscopio y GPS del teléfono (UAH-DriveSet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>R0052</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → Ambos</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Intersecciones y rampas/puentes de carretera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>R0080</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Incidentes distintos en entrenamiento (23) y prueba (22).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>R0097</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Ubicación y tipo de vía no reportados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>R0119</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → Ambos</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Intersecciones y autopistas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>R0119</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Aleatoria</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Partición estratificada sin separación temporal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>R0121</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → Urbano</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Dos cruces peatonales de calle (35 mph) en Florida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>R0167</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>«No se detallan particiones».</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>R0175</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>No especifica el tipo de vía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>R0185</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>No describe la partición.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>R0190</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CE-3</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>R0244</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «DECISIÓN TC» → Incluir</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>«INCLUIDO» no es una opción de la lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>R0249</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CI-6</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>R0379</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Evalúa en una grabación highD no vista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>R0389</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CI-6</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>R0403</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «QA5 Código y datos» → 1</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Código con DOI (ETS) y datasets públicos (DAD, CCD, A3D): ambos públicos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>R0403</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Particiones oficiales de DAD y CCD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>R0501</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → Ambos</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Vías urbanas e interurbanas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>R0501</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto externo ECVD solo para prueba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>R0528</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CI-6</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>R0537</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Sin proporciones ni protocolo de separación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>R0596</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Partición insuficientemente reportada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>R0598</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Pista de pruebas; no es urbano ni autopista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>R0601</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto de prueba de AI City Challenge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>R0604</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>R0604</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CE-2</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Monitoreo del conductor dentro de la cabina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>R0614</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CE-3</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>R0658</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Particiones oficiales de los benchmarks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>R0664</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Videos de prueba separados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>R0666</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>No detalla la partición.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>R0929</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>R0929</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CE-2</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Monitoreo del conductor dentro de la cabina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>R0943</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Sin procedimiento de selección ni conjunto de prueba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>R1000</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>No indica qué escenas de NGSIM usa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>R1010</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Evaluado con autos de juguete en escenario controlado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>R1013</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto de prueba oficial de TADS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>R1014</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Familia DL principal» → Otra</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>DeepWalk/Node2vec no es una GNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>R1082</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto de prueba de MAAD (con ajuste de hiperparámetros en parte de él).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>R1092</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Aleatoria</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>División 80/20 de videos sin otro criterio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>R1100</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>DoTA/CCD sin clasificación por tipo de vía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>R1138</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>No desagrega urbano/autopista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>R1148</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Categoría de anomalía» → Evento/otro</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Objetos caídos sobre la calzada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>R1148</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Solo dice que entrena y valida 100 épocas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>R1166</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CI-6</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>R1185</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>No clasifica las imágenes por tipo de vía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>R1202</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Separación por sesiones de conducción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>R1214</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>No informa proporciones ni criterio de división.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10596,46 +10384,126 @@
       <c r="X5" s="4" t="n"/>
     </row>
     <row r="6" ht="57.6" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>R0032</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>A Comparative Analysis of Machine Learning, Deep Learning, and Metaheuristic-Based Ensemble Learning for Driver Behavior Profiling on UAH-DriveSet</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>cribado\pdf\R0032.pdf</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="6" t="n"/>
-      <c r="Q6" s="6" t="n"/>
-      <c r="R6" s="6" t="n"/>
-      <c r="S6" s="6" t="n"/>
-      <c r="T6" s="6" t="n"/>
-      <c r="U6" s="6" t="n"/>
-      <c r="V6" s="6" t="n"/>
-      <c r="W6" s="6" t="n"/>
-      <c r="X6" s="6" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Multimodal</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Autopista</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>UAH-DriveSet, conjunto de conducción naturalista públicamente disponible, con más de 500 minutos de datos y videos asociados de seis participantes. Contiene tres estilos: normal, somnoliento y agresivo, en autopistas y carreteras secundarias. Los autores reúnen los datos de los seis conductores en una base común. La referencia 20, página 7, proporciona la dirección http://www.robesafe.uah.es/personal/eduardo.romera/uah-driveset/. No se especifica el número de filas, ventanas temporales, muestras por conductor, frecuencia de muestreo utilizada, duración de ventanas ni distribución exacta de las clases en el conjunto procesado.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Reales/registros</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>No se reporta el número original ni el porcentaje exacto de observaciones por clase. Los autores identifican la somnolencia como clase minoritaria y aplican SMOTE para compensar el desbalance. No se comunica cuántas muestras originales o sintéticas corresponden a normal, agresiva o somnolienta, ni el denominador de la evaluación específica de somnolencia. El recall de 95% de esa clase no permite inferir su prevalencia. Páginas 1, 3 y 4.</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Supervisado</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Convolucional (CNN)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>El procedimiento comienza reuniendo datos de seis conductores y aplicando limpieza de valores atípicos, imputación KNN de valores ausentes, SMOTE, selección de características por información mutua, codificación de variables categóricas y estandarización mediante StandardScaler. Se realiza una división estratificada 70/15/15. Se entrenan cuatro modelos ML: CatBoost, XGBoost, KNN y ExtraTrees; y cuatro DL: CNN 1D, BiLSTM, TCN y Attention-LSTM. Los autores seleccionan modelos de mejor rendimiento y utilizan PSO para optimizar sus pesos de fusión. La sección 4.3 atribuye la complementariedad a CatBoost, CNN 1D y TCN, aunque no publica la fórmula completa del ensamble ni los pesos numéricos finales. No se detallan número de capas, unidades, kernels, épocas, batch size, funciones de pérdida ni hiperparámetros de PSO. Páginas 3–4, Figura 1 y sección 4.3.</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Comportamiento de conducción</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy, precision, recall, F1-score, ROC-AUC y matrices de confusión para clasificación supervisada de estilos de conducción. La Tabla 1 muestra métricas globales de los nueve modelos; la Figura 2 presenta curvas ROC y valores AUC; el resumen y la sección 4.3 comunican recall específico de somnolencia. No se reportan falsas alarmas por kilómetro, tiempo de anticipación de accidentes, detección de eventos no vistos ni resultados de anomalía binaria normal/anómalo. Páginas 1, 3–5.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>PSO Ensemble: accuracy 99.89%, precision 1.00, recall global 1.00 y F1 global 1.00, con redondeo a dos decimales en Tabla 1; recall específico de somnolencia 95% en resumen y sección 4.3. Attention-LSTM: accuracy 99.83%, precision, recall y F1 redondeados a 1.00. TCN: accuracy 99.67%, precision, recall y F1 redondeados a 1.00. CatBoost: accuracy 94.47%, precision 0.95, recall 0.94 y F1 0.94. CNN 1D: accuracy 94.02%. BiLSTM: accuracy 11.13% y F1 0.02. La Figura 2 informa AUC 1.00 para TCN, Attention-LSTM y PSO Ensemble; aproximadamente 0.98 para CatBoost y CNN 1D; 0.87 ExtraTrees; 0.82 XGBoost; 0.70 KNN; y 0.55 BiLSTM. Son métricas de clasificación de comportamiento, no detección de accidentes.</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>Unidad exacta de evaluación: observación o instancia de características de conducción obtenida del conjunto procesado. El artículo no especifica si cada instancia corresponde a una muestra instantánea, una ventana de longitud fija o una secuencia temporal de duración determinada. La evaluación no se presenta por conductor completo, recorrido completo, evento de riesgo o accidente. La naturaleza secuencial de CNN 1D, TCN y LSTM no permite inferir una longitud concreta de ventana. Páginas 3–5.</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>La regla de salida es clasificación supervisada en una de tres categorías: normal, somnolienta o agresiva. El ensamble fusiona predicciones mediante pesos optimizados por PSO. No se publican los pesos finales, la fórmula precisa de combinación ni el criterio numérico para convertir probabilidades en etiquetas. Tampoco se establece un umbral binario de anomalía o una regla de alerta para conducción peligrosa. Las curvas ROC varían umbrales estadísticos de clasificación, pero no identifican un umbral operativo seleccionado. Páginas 3–5, Figura 1 y Figura 2.</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>Aleatoria</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>Ocho comparadores individuales: cuatro tradicionales, CatBoost, XGBoost, KNN y ExtraTrees; y cuatro profundos, CNN 1D, BiLSTM, TCN y Attention-LSTM. La Tabla 1 presenta accuracy, precision, recall y F1 para todos, y la Figura 2 muestra comparación ROC. El ensamble PSO se contrasta con los ocho modelos. No se incluye una ablación formal con pesos uniformes, pesos aleatorios u otro optimizador metaheurístico, ni resultados de variabilidad estadística entre ejecuciones. Páginas 4–5.</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>El ensamble PSO obtiene accuracy 99.89% frente a Attention-LSTM 99.83%, diferencia absoluta de +0.06 puntos porcentuales y mejora relativa aproximada de 0.060%; frente a TCN 99.67%, +0.22 puntos y 0.221% relativo; frente a CatBoost 94.47%, +5.42 puntos y 5.74% relativo; y frente a CNN 1D 94.02%, +5.87 puntos y 6.24% relativo. El recall de somnolencia del ensamble es 95% frente a 75% comunicado para CatBoost, diferencia de +20 puntos porcentuales y 26.67% relativo; no obstante, el PDF no proporciona denominadores ni matrices de confusión completas para verificar esas cifras. Las mejoras de accuracy son muy pequeñas respecto de los mejores modelos profundos y no se acompañan de pruebas de significación. Página 4, secciones 4.1–4.3; página 5, Tabla 1.</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>Los autores reconocen explícitamente problemas de desbalance, ruido, valores ausentes, sobreajuste y dificultades de ajuste de hiperparámetros en datos de conducción. En la sección 4.2 advierten que los resultados casi perfectos de TCN y Attention-LSTM deben interpretarse con cautela debido a posibles problemas de particionamiento relacionados con la clase minoritaria. En la sección 4.4 señalan mayor complejidad computacional y tiempo de procesamiento del ensamble, y sensibilidad de los modelos profundos a hiperparámetros. No desarrollan una sección formal de limitaciones ni cuantifican esos riesgos mediante pruebas adicionales. Páginas 2–5.</t>
+        </is>
+      </c>
+      <c r="X6" s="5" t="inlineStr">
+        <is>
+          <t>Datos: UAH-DriveSet identificado explícitamente como conjunto público y citado con URL http://www.robesafe.uah.es/personal/eduardo.romera/uah-driveset/ en referencia 20, página 7. Código: no se proporciona repositorio público, archivos de implementación, pesos entrenados ni scripts reproducibles de PSO. No se publican las particiones exactas, transformaciones ajustadas ni hiperparámetros suficientes para reproducir los resultados. Se registra dataset público identificado y código público no reportado; la disponibilidad del dataset no implica reproducibilidad íntegra del experimento.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="28.8" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -12106,118 +11974,118 @@
       <c r="X20" s="4" t="n"/>
     </row>
     <row r="21" ht="43.2" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>R0167</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>A Personalized Federated Learning Framework for Post-Event Forensic Traffic Analysis in Autonomous Vehicle Systems</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>cribado\pdf\R0167.pdf</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Trayectorias GPS</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>Urbano</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>No especificado; se utilizan datos simulados CARLA y subconjuntos Comma.ai distribuidos en 3 clientes federados; no se reportan cantidades de vehículos, trayectorias, registros ni instancias de anomalías</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Inyectadas/sintéticas</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>Aprendizaje federado personalizado con entrenamiento local y agregación global; detección de anomalías mediante comportamientos anormales introducidos en los escenarios; no se especifica completamente el procedimiento de etiquetado ni el protocolo de partición</t>
         </is>
       </c>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="inlineStr">
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>Grafos (GNN)</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>Personalized Lightweight Federated Learning (PLFL) con arquitectura MGTGCN; aprendizaje de trayectorias y detección de anomalías mediante fusión temporal y espacial; agregación federada personalizada según divergencia de modelos; Dynamic Model Pruning para reducir comunicación</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>Comportamiento de conducción</t>
         </is>
       </c>
-      <c r="O21" s="6" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>Precision, Recall y ROC-AUC para detección de anomalías; Average Displacement Error (ADE) y Final Displacement Error (FDE) para reconstrucción de trayectorias; tamaño de actualizaciones en MB para comunicación</t>
         </is>
       </c>
-      <c r="P21" s="6" t="inlineStr">
+      <c r="P21" s="9" t="inlineStr">
         <is>
           <t>Precision=89.3%, Recall=84.7%, ROC-AUC=0.921; PLFL ADE=1.98 m y FDE=4.55 m; FedAvg ADE=2.35 m y FDE=5.70 m; reducción de comunicación aproximada del 28%</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="9" t="inlineStr">
         <is>
           <t>Datos simulados CARLA con comportamientos de conducción, colisiones y anomalías de ruta; subconjuntos reales Comma.ai; tres clientes: urbano, intersecciones y autopista/suburbano; tamaño exacto del conjunto de datos no especificado</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="9" t="inlineStr">
         <is>
           <t>Construcción de grafos espaciotemporales con nodos correspondientes a ubicaciones o segmentos viales y aristas de conectividad; extracción de características de telemetría; proyección a 64 dimensiones; fusión TCN-GCN-GAT; agregación personalizada; poda dinámica de parámetros de baja magnitud</t>
         </is>
       </c>
-      <c r="S21" s="6" t="inlineStr">
+      <c r="S21" s="9" t="inlineStr">
         <is>
           <t>No reportada</t>
         </is>
       </c>
-      <c r="T21" s="6" t="inlineStr">
+      <c r="T21" s="9" t="inlineStr">
         <is>
           <t>Centralized MGTGCN; Federated Learning FedAvg; Personalized FL/PLFL; comparación con y sin Dynamic Model Pruning; no se presenta tabla cuantitativa de Precision, Recall y ROC-AUC por cada baseline</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
+      <c r="U21" s="9" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="V21" s="6" t="inlineStr">
+      <c r="V21" s="9" t="inlineStr">
         <is>
           <t>PLFL mejora ADE frente a FedAvg de 2.35 m a 1.98 m y FDE de 5.70 m a 4.55 m; alcanza Precision=89.3%, Recall=84.7% y ROC-AUC=0.921 en anomalías; reduce tamaño de actualización de 22.5 MB a 16.1 MB; mejora adaptación a distribuciones heterogéneas entre clientes</t>
         </is>
       </c>
-      <c r="W21" s="6" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>Enfoque forense posterior al evento sin evaluación en tiempo real; no se reportan tamaños exactos ni particiones de datasets; simulación CARLA con brecha respecto al mundo real; escasa representación de anomalías extremas; falta validación operacional a gran escala; no se evalúa resistencia a clientes maliciosos; inconsistencias entre tabla y figura de comunicación; no se proporciona código ni configuración experimental completa</t>
         </is>
       </c>
-      <c r="X21" s="6" t="inlineStr">
+      <c r="X21" s="9" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
@@ -12590,94 +12458,94 @@
       </c>
     </row>
     <row r="25" ht="28.8" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>R0192</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>A Self-Imputing Deep Multitask Sequence Model for Traffic Disruption Detection in Extreme Conditions</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>cribado\pdf\R0192.pdf</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>SI-DMSeq (Self-Imputing Deep Multitask Sequence)</t>
         </is>
       </c>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>Encoder LSTM compartido y dos decodificadores LSTM con atención para reconstrucción y predicción</t>
         </is>
       </c>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>Manhattan, Nueva York, Estados Unidos</t>
         </is>
       </c>
-      <c r="M25" s="6" t="n"/>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="9" t="inlineStr">
         <is>
           <t>Evento/otro</t>
         </is>
       </c>
-      <c r="O25" s="6" t="inlineStr">
+      <c r="O25" s="9" t="inlineStr">
         <is>
           <t>Detección no supervisada basada en aprendizaje de patrones normales</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
+      <c r="P25" s="9" t="inlineStr">
         <is>
           <t>Errores de reconstrucción MSE, gráficos de control estadístico SPC y soft-thresholding por zona</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="9" t="inlineStr">
         <is>
           <t>Detección a nivel de red y localización de zonas afectadas por eventos extremos</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="9" t="inlineStr">
         <is>
           <t>RMSE para imputación; estadístico MSE y límites de control para detección; validación visual de anomalías</t>
         </is>
       </c>
-      <c r="S25" s="6" t="inlineStr">
+      <c r="S25" s="9" t="inlineStr">
         <is>
           <t>Aleatoria</t>
         </is>
       </c>
-      <c r="T25" s="6" t="inlineStr">
+      <c r="T25" s="9" t="inlineStr">
         <is>
           <t>Comparación de imputación con Temporal Mean, RTRC y PARATUCK2</t>
         </is>
       </c>
-      <c r="U25" s="6" t="n"/>
-      <c r="V25" s="6" t="inlineStr">
+      <c r="U25" s="9" t="n"/>
+      <c r="V25" s="9" t="inlineStr">
         <is>
           <t>Detección de anomalías a dos escalas, imputación integrada y procesamiento apto para monitoreo casi en tiempo real</t>
         </is>
       </c>
-      <c r="W25" s="6" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>Evaluación limitada a Manhattan y eventos meteorológicos; validación de detección principalmente visual; sin precisión, recall, F1-score ni AUC reportados</t>
         </is>
       </c>
-      <c r="X25" s="6" t="inlineStr">
+      <c r="X25" s="9" t="inlineStr">
         <is>
           <t>https://doi.org/10.1109/ACCESS.2025.3612407 ; https://github.com/minanouri/SI-DMSeq</t>
         </is>
@@ -14556,246 +14424,246 @@
       </c>
     </row>
     <row r="42" ht="28.8" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>R0389</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Detection of road traffic anomalies based on computational data science</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>cribado\pdf\R0389.pdf</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Movilidad agregada</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Datos numéricos y series temporales de velocidad de tráfico, tiempo de viaje, sección vial y posicionamiento GNSS. El artículo describe adquisición mediante servicios móviles y teléfonos inteligentes, sensores magnéticos y dispositivos Ublox. Las Tablas 2 y 3 contienen ejemplos de mensajes GNSS y datos estructurados con tiempo UTC, longitud, latitud, velocidad sobre el suelo y rumbo. Las Figuras 1, 2, 5, 13 y 14 presentan observaciones de velocidad. No se utiliza video como entrada experimental demostrada del detector. Páginas 4, 6, 11, 14 y 15.</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Principalmente carreteras urbanas divididas en tramos de 300 metros, con análisis de tráfico vehicular, congestión y anomalías de posicionamiento. El artículo también menciona vehículos autónomos y comunicación V2V, V2I y V2X, pero no proporciona una evaluación separada en autopistas frente a calles urbanas. No debe atribuirse una ciudad específica al conjunto completo de datos sin documentación adicional. Páginas 6, 9 y 12.</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Datos de viaje recogidos mediante servicios de telefonía móvil y teléfonos inteligentes en intervalos de 2,5 minutos; datos de posicionamiento obtenidos con dispositivos Ublox y teléfonos inteligentes. Las vías se subdividen en secciones de 300 metros. Las Figuras 1 y 14 muestran ejes de observaciones de hasta aproximadamente 1600 y 2500 registros respectivamente, pero no permiten establecer el tamaño exacto de una única base experimental. Las Tablas 2 y 3 muestran ejemplos GNSS; no se reportan nombre oficial del dataset, período completo de captura, cantidad total de recorridos, vehículos, conductores, anomalías ni particiones. La sección de disponibilidad indica que la mayoría de los conjuntos son públicos y algunos privados pueden solicitarse, sin identificadores individuales. Páginas 4, 9, 11, 14–16.</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>No se documenta un protocolo de anotación de anomalías ni un conjunto de etiquetas independientes de referencia. Se propone considerar anormal una reducción de velocidad de al menos 30 km/h respecto del promedio comparable y utilizar diferencias espaciales y temporales entre estaciones. Se menciona un conjunto de accidentes cuya información identifica la hora, pero no el minuto del evento, sin detallar su procedencia o cantidad. La sección 5.11 menciona una trayectoria de referencia para ensayos de posicionamiento GNSS, pero no publica etiquetas evaluables de anomalía. Por tanto, las anomalías se caracterizan principalmente mediante reglas estadísticas y observaciones, no mediante una validación documentada de etiquetas. Páginas 4–5 y 15.</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>No reportada. No se informa número ni porcentaje de incidentes, episodios de congestión anormal, errores GNSS o registros incompletos sobre el total de observaciones. Las caídas de velocidad visibles en las Figuras 1, 4, 13 y 14 no constituyen un conteo validado de anomalías. Tampoco se cuantifica la proporción de datos faltantes o contaminados por ruido.</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>El artículo declara aprendizaje supervisado y división de datos en entrenamiento y prueba, y propone identificar patrones anormales respecto del tráfico normal. No especifica etiquetas de entrenamiento, función objetivo, procedimiento de optimización ni mecanismo para construir los ejemplos supervisados. El enfoque CDS combina limpieza, análisis estadístico, reglas de detección, regresión y un componente neuronal descrito como Deep Learning. No hay evidencia suficiente para clasificarlo como aprendizaje no supervisado o auto-supervisado. Páginas 7–9, 12–13 y 16.</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Red neuronal profunda genérica declarada por el autor, sin familia específica verificable. Se describen capa de entrada, capa oculta y capa de salida, con pesos y función de activación, y se presenta un esquema de conexiones neuronales en la Figura 10. No se identifica CNN, LSTM, GRU, GNN, Transformer, autoencoder, VAE ni otra arquitectura concreta. Tampoco se documenta el número real de capas ocultas o una implementación que permita confirmar la profundidad de la red. Páginas 7–9 y 12–13.</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Propuesta CDS: adquisición de velocidad y posicionamiento mediante dispositivos móviles y GNSS; estructuración y limpieza de datos; extracción de características; clasificación y entrenamiento/prueba; identificación de anomalías mediante cambios de velocidad y medidas estadísticas; localización de su origen; actualización de información vial y búsqueda de rutas alternativas. La sección 4.11 indica como atributos de entrada tiempo, sección vial y velocidad, con observaciones cada 2,5 minutos y tramos de 300 metros. La sección 5.8 expresa la salida neuronal como suma ponderada de señales más error, seguida de activación. La Figura 10 representa un esquema neuronal conceptual, no una arquitectura detallada con capas, hiperparámetros, función de pérdida, optimizador, épocas o configuración reproducible. Páginas 9–13, Figuras 6, 7 y 10.</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>No demostrado. El estudio combina procedimientos estadísticos, regresión, reglas de velocidad y un componente denominado DL, pero no demuestra la combinación de dos familias diferentes de Deep Learning. La Figura 10 presenta una red genérica; no hay evidencia de arquitectura híbrida CNN–LSTM, CNN–Transformer, GNN–RNN u otra combinación multfamilia. CDS debe registrarse como enfoque integrado de análisis de datos y no como arquitectura híbrida DL confirmada.</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>Anomalías de flujo vehicular caracterizadas por caídas inusuales de velocidad y congestión; posibles efectos de accidentes, mal tiempo, obras y cambios de carril fallidos; datos incompletos, ruido e interferencias; errores de posicionamiento GNSS. La contribución experimental visible se concentra en cambios de velocidad, calidad de datos y posicionamiento. No se demuestra una clasificación separada y validada de cada causa, ni detección visual de accidentes o maniobras peligrosas. Páginas 2, 4–6, 8–9 y 12–15.</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>No se reportan métricas cuantitativas específicas de detección de anomalías, tales como precision, recall, F1, AUROC, AUPRC, sensibilidad, especificidad, tasa de falsas alarmas, tiempo de detección o mAP. La Tabla 4 presenta Multiple R, R², R² ajustado, desviación estándar y skewness de un análisis estadístico con y sin ruido. Esas métricas no deben confundirse con la capacidad de detección del modelo DL. Las Figuras 13 y 14 son comparaciones visuales de velocidades sin evaluación mediante etiquetas de referencia. Página 15.</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>No se informa un mejor resultado numérico de detección de anomalías. La Tabla 4 reporta, sin ruido: Multiple R 0.323891, R² 0.104905, R² ajustado 0.100452, desviación estándar 0.032198 y skewness 0.610392862; con ruido: Multiple R 0.950014086, R² 0.902526764, R² ajustado 0.901693659, desviación estándar 10.25998381 y skewness 0.934485831. Estos valores describen análisis de regresión y ruido, no accuracy o AUC de anomalías. La Figura 14 afirma visualmente una ventaja CDS frente a ML, pero no cuantifica mejora de detección. Página 15, Tabla 4 y Figura 14.</t>
+        </is>
+      </c>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>La observación básica de tráfico se registra aproximadamente cada 2,5 minutos y está asociada a secciones viales de 300 metros; el posicionamiento GNSS se representa mediante registros individuales con tiempo, coordenadas y velocidad. No se establece si la evaluación del detector se realizó por observación, tramo, secuencia, incidente o episodio de congestión. Las figuras muestran series de observaciones, pero no un protocolo explícito de correspondencia entre predicción y evento verdadero. Páginas 4, 9, 11 y 14–15.</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>Se declara un umbral ilustrativo de caída de velocidad de al menos 30 km/h respecto del promedio correspondiente al mismo horario y día de la semana. La sección 3.2 introduce pruebas espaciales y temporales con umbrales K1, K2 y K3 para diferencias entre estaciones y cambios de velocidad. No se publican valores operativos completos de K1, K2 y K3 ni un umbral de salida de la red neuronal. El umbral de 30 km/h es descrito por el propio autor como simbólico, por lo que no debe asumirse como un punto de operación validado experimentalmente. Páginas 4–5, ecuaciones 1–3.</t>
+        </is>
+      </c>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>El artículo describe fases de entrenamiento y prueba, y la conclusión afirma que el conjunto procesado se dividió en subconjuntos para aprendizaje supervisado. No se especifican porcentajes, número de muestras, selección temporal, separación por tramos, vehículos o días, ni procedimiento para impedir que observaciones correlacionadas aparezcan en ambas particiones. Tampoco se documenta un conjunto de validación independiente. Por ello no puede verificarse independencia de prueba ni ausencia de fuga de información durante limpieza y reconstrucción de datos faltantes. Páginas 7, 9 y 16.</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>Se presenta una comparación conceptual y gráfica entre CDS y ML en la Figura 14. También se emplea regresión lineal y correlación de Pearson para analizar ruido en los datos. No se identifican modelos de referencia de detección implementados con configuración verificable, ni una comparación cuantitativa mediante métricas comunes y etiquetas de anomalías. Los trabajos de otros autores citados en antecedentes no deben contarse como baselines experimentales del estudio. Páginas 12–15.</t>
+        </is>
+      </c>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>Sí, parcialmente: se utiliza regresión lineal y correlación de Pearson para el análisis estadístico, y la Figura 14 contrasta CDS frente a una curva etiquetada ML. Sin embargo, el artículo no especifica qué algoritmo de Machine Learning produjo esa curva ni ofrece métricas de detección comparables. La regresión estadística no constituye por sí sola un detector no profundo evaluado con precision o recall. Páginas 12–15, Tabla 4 y Figura 14.</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>No calculable. No se dispone de métricas de detección del método CDS y del comparador ML sobre un mismo conjunto etiquetado, por lo que no corresponde informar diferencias en puntos porcentuales ni mejoras relativas. Las curvas de velocidad de la Figura 14 no permiten inferir un porcentaje de mejora válido. Los cambios de R² entre condiciones con y sin ruido de la Tabla 4 no representan una mejora de detección y no deben utilizarse para comparar modelos.</t>
+        </is>
+      </c>
+      <c r="W42" s="5" t="inlineStr">
+        <is>
+          <t>Los autores describen como desafíos la pérdida de datos, el ruido, las interferencias de comunicaciones, los errores de posicionamiento GNSS y las dificultades de procesar datos heterogéneos. En la sección 4.4 advierten de forma general que pocas neuronas reducen la capacidad de aprendizaje y demasiadas pueden producir sobreajuste. La sección 4.8 declara que la ciberseguridad queda fuera del alcance. En la conclusión reconocen que ciertas interferencias solo se compensan parcialmente. No presentan una discusión explícita y sistemática de las limitaciones de la evaluación de DL, ausencia de métricas de detección, generalización o validez de etiquetas; estas últimas son observaciones del revisor y no deben atribuirse a los autores. Páginas 7–8 y 16.</t>
+        </is>
+      </c>
+      <c r="X42" s="5" t="inlineStr">
+        <is>
+          <t>Código: no se identifica repositorio público, implementación descargable, pesos entrenados ni scripts de experimentación. Datos: la sección Data availability, página 16, afirma que la mayoría de los datasets utilizados son públicamente accesibles y que los privados pueden proporcionarse bajo solicitud, pero no identifica enlaces concretos ni los subconjuntos experimentales exactos. Los ejemplos de GNSS de las Tablas 2 y 3 no equivalen a publicar el dataset completo. En consecuencia, la disponibilidad pública exacta de los datos utilizados no puede verificarse a partir del PDF y la reproducibilidad integral del estudio no está demostrada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28.8" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>R0403</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Domain-enhanced dual-branch model for efficient and interpretable accident anticipation</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>cribado\pdf\R0403.pdf</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Urbano</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>Dataset real de monitoreo de tráfico de Wuhan obtenido mediante Amap API entre el 20 de septiembre de 2021 y el 17 de junio de 2022. Contiene aproximadamente 60 millones de registros, alrededor de 60000 observaciones por muestreo y frecuencia de 30 minutos. Las variables incluyen velocidad, localización y tiempo. El conjunto se transforma en imágenes espaciotemporales para alimentar Traffic-ConvLSTM (sección 3.1, pp. 5–6).</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>Sin etiquetas</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>No se reporta una proporción global de observaciones normales y anómalas ni un porcentaje de desbalance del dataset. El artículo describe eventos anómalos menos frecuentes que los patrones normales y establece una relación de muestreo temporal de 16:3:1 para las escalas horaria, diaria y semanal (p. 6), pero esta relación no representa una distribución entre clases normales y anómalas.</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>No supervisado</t>
-        </is>
-      </c>
-      <c r="K42" s="6" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>DAD: 1750 videos, 620 con accidente y 1130 sin accidente; entrenamiento 1284 videos, 455 positivos y 829 negativos; prueba 466 videos, 165 positivos y 301 negativos; duración 5 s, 100 fotogramas a 20 FPS, accidente alineado con fotograma 90. CCD: 4500 videos, 1500 positivos de YouTube y 3000 negativos de BDD100K; entrenamiento 3600, 1200 positivos y 2400 negativos; prueba 900, 300 positivos y 600 negativos; duración 5 s, 50 fotogramas a 10 FPS; accidente situado aleatoriamente en los últimos 2 s. A3D: 1500 clips de accidentes, 100 fotogramas a 20 FPS, partición 80/20; los ejemplos negativos se generan a partir de segmentos anteriores al accidente. Se usan además informes de accidentes de vehículos autónomos del DMV de California y 500 descripciones sintéticas de conducción segura para la rama textual. Páginas 4–5 y 8–9, Tablas 1 y 2.</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Anotación manual</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>DAD: 620/1750 videos positivos, equivalentes a 35,43 %; prueba 165/466, 35,41 %. CCD: 1500/4500 positivos, 33,33 %; prueba 300/900, 33,33 %. A3D: 1500/1500 clips originales contienen accidentes, 100 % del conjunto original; el estudio genera segmentos negativos, pero no informa aquí una prevalencia final equivalente de videos independientes después de construir esos negativos. Las proporciones corresponden a videos con accidente y no a porcentajes de fotogramas anormales. Página 8, sección 4.1 y Tabla 2.</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Supervisado</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>Convolucional (CNN)</t>
         </is>
       </c>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>Traffic-ConvLSTM; arquitectura generativa no supervisada de tipo encoder-forecasting que utiliza tres tamaños de kernel convolucional, 7×7, 5×5 y 3×3, para capturar características espaciales en distintas escalas. Integra secuencias temporales horarias, diarias y semanales y genera imágenes predictivas de condiciones de tráfico. Las diferencias entre las imágenes previstas y observadas se evalúan mediante SSIM para identificar anomalías (sección 3.2, pp. 7–8; Figura 3, p. 8).</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>El sistema procesa fotogramas dashcam mediante VGG-16, cuya representación se ajusta a 512 dimensiones; la rama textual utiliza Long-CLIP-L preentrenado con embeddings originales de 768 dimensiones reducidos linealmente a 512. Los textos se derivan de informes de accidentes reales y escenarios seguros sintéticos, estructurados con conocimiento del dominio. El modelo relaciona características de video y texto mediante similitud y atención multi-head, estima la probabilidad de accidente por instante y optimiza una función de pérdida con componentes ponderados inicialmente 1:1:1, cuyos pesos son aprendibles. El umbral τ se aprende junto con el predictor para decidir alertas. GPT-4o recibe fotogramas, predicciones y conocimiento contextual para producir aviso, descripción de escena, tipo de riesgo y consejo. Entrenamiento: PyTorch, GPU RTX 4090, Adam, 30 épocas, batch 10, learning rate inicial 0,001; para el umbral 0,1; weight decay 0,0001; ReduceLROnPlateau factor 0,5 y paciencia 3. Páginas 3–9, Figuras 2 y 6.</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="N42" s="6" t="inlineStr">
-        <is>
-          <t>Congestión atípica</t>
-        </is>
-      </c>
-      <c r="O42" s="6" t="inlineStr">
-        <is>
-          <t>Dos métricas denominadas Accuracy y Precision por los autores, calculadas mediante las ecuaciones 6 y 7 de la p. 8. Debe advertirse que sus fórmulas no corresponden a las definiciones convencionales: Accuracy=Fp/Ft, equivalente a precisión positiva habitual, y Precision=Fp/Fr, equivalente a sensibilidad o recall habitual, según las definiciones de Fp, Ft y Fr del artículo. No se reportan F1-score, ROC-AUC ni Average Precision.</t>
-        </is>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>La Tabla 2, p. 10, informa para Traffic-ConvLSTM: City-precision 92.875%, City-accuracy 83.871%, Road-precision 88.889% y Road-accuracy 92.035%, respetando literalmente las denominaciones originales. El tiempo de ejecución reportado es 4.88, sin unidad explícita en la tabla. Los resultados proceden de datos reales de Wuhan y muestran rendimiento favorable frente a los modelos comparados en varias métricas, aunque no domina todas las métricas individuales.</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>Unidad principal de detección: imagen de condiciones de tráfico correspondiente a un instante de muestreo y área espacial; se analizan anomalías de segmentos viales y de ciudad. Los datos se muestrean cada 30 minutos, generando 48 resultados diarios (sección 4, p. 8). No se evalúa la clasificación individual de conductores o vehículos como unidad principal.</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>Se calcula la similitud estructural SSIM entre las condiciones de tráfico y el patrón de referencia. El modelo construye índices SSIM estándar para 48 intervalos diarios durante siete días de la semana, obteniendo 7×48 valores de referencia. Una diferencia superior a un umbral indica una anomalía (sección 3.2, p. 8). El artículo no especifica claramente un valor numérico universal del umbral ni un procedimiento exhaustivo de calibración.</t>
-        </is>
-      </c>
-      <c r="S42" s="6" t="inlineStr">
-        <is>
-          <t>No reportada</t>
-        </is>
-      </c>
-      <c r="T42" s="6" t="inlineStr">
-        <is>
-          <t>Stacked Autoencoder (SAE), CNN-LSTM, Bidirectional LSTM (Bi-LSTM), Generative Adversarial Network (GAN) y Transformer. Aunque el texto introductorio de la sección 4.1 menciona tres modelos de referencia, la Tabla 2, p. 10, presenta resultados para cinco baselines además de Traffic-ConvLSTM.</t>
-        </is>
-      </c>
-      <c r="U42" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V42" s="6" t="inlineStr">
-        <is>
-          <t>En City-precision, Traffic-ConvLSTM obtiene 92.875% frente a 90.124% de GAN, una mejora absoluta de 2.751 puntos porcentuales respecto al mejor baseline en esa métrica. En City-accuracy obtiene 83.871% frente a 80.154% de Transformer, mejora de 3.717 puntos. En Road-accuracy alcanza 92.035% frente a 91.715% de Transformer, mejora de 0.320 puntos. Sin embargo, en Road-precision obtiene 88.889%, por debajo de Transformer (94.582%) y GAN (92.236%). Valores de Tabla 2, p. 10.</t>
-        </is>
-      </c>
-      <c r="W42" s="6" t="inlineStr">
-        <is>
-          <t>Las fórmulas y denominaciones de Accuracy y Precision no coinciden con las convenciones habituales, lo que dificulta la comparación directa con otros estudios (p. 8). No se documenta suficientemente la partición entrenamiento-prueba ni el procedimiento de etiquetado independiente. La validación se limita a una ciudad y un periodo histórico; no se incluyen intervalos de confianza ni pruebas de significancia. Los resultados de ablación muestran sensibilidad a la profundidad y al orden de características espaciales (Tablas 3–4, p. 10).</t>
-        </is>
-      </c>
-      <c r="X42" s="6" t="inlineStr">
-        <is>
-          <t>Disponibilidad parcial; el artículo declara en la p. 13 que los datos pueden proporcionarse previa solicitud a los autores. No se identifica un repositorio público del dataset procesado ni un enlace de código fuente del modelo. Se mencionan Keras y TensorFlow como herramientas de implementación (sección 4, p. 8), pero no se publican scripts completos ni configuraciones suficientes para garantizar reproducción independiente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28.8" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>R0403</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>Domain-enhanced dual-branch model for efficient and interpretable accident anticipation</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>cribado\pdf\R0403.pdf</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Movilidad agregada</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>Urbano</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>Dataset real de monitoreo de tráfico de Wuhan recopilado mediante Amap API desde el 20 de septiembre de 2021 hasta el 17 de junio de 2022. Contiene aproximadamente 60 millones de registros y observaciones cada 30 minutos. Las variables principales incluyen velocidad del tráfico, localización y tiempo. Se generan imágenes espaciotemporales para el entrenamiento y evaluación del modelo (sección 3.1, pp. 5–6).</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>Reales/registros</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>No reportada; el artículo no proporciona el porcentaje global de registros anómalos respecto del total de observaciones. La proporción temporal 16:3:1 corresponde a la configuración de características horarias, diarias y semanales, no a la distribución de clases normales y anómalas.</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>No supervisado</t>
-        </is>
-      </c>
-      <c r="K43" s="6" t="inlineStr">
-        <is>
-          <t>Convolucional (CNN)</t>
-        </is>
-      </c>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>Traffic-ConvLSTM; arquitectura encoder-forecasting que combina convoluciones de tamaños 7×7, 5×5 y 3×3 con unidades ConvLSTM. Integra características temporales horarias, diarias y semanales para generar imágenes predictivas de condiciones de tráfico. Las diferencias SSIM entre las imágenes observadas y las estimadas permiten identificar anomalías espaciotemporales (sección 3.2, pp. 7–8; Figura 3, p. 8).</t>
-        </is>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="N43" s="6" t="inlineStr">
-        <is>
-          <t>Congestión atípica</t>
-        </is>
-      </c>
-      <c r="O43" s="6" t="inlineStr">
-        <is>
-          <t>Accuracy y Precision según la terminología original del artículo (ecuaciones 6 y 7, p. 8). Existe una inconsistencia metodológica: las fórmulas presentadas intercambian las denominaciones convencionales de precisión y sensibilidad o recall. No se reportan F1-score, ROC-AUC ni Average Precision.</t>
-        </is>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>Traffic-ConvLSTM obtiene City-precision de 92.875%, City-accuracy de 83.871%, Road-precision de 88.889% y Road-accuracy de 92.035%, según la Tabla 2, p. 10. Estos valores mantienen las denominaciones originales del artículo y no deben reinterpretarse automáticamente como métricas convencionales.</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>Imágenes de condiciones de tráfico correspondientes a intervalos temporales de 30 minutos y unidades espaciales de carretera, región o ciudad. Se producen 48 intervalos diarios; no se realiza detección individual de conductores como unidad principal.</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>Se calcula SSIM entre condiciones de tráfico observadas y estimadas. El modelo construye referencias para siete días de la semana y 48 intervalos diarios, generando 336 valores de referencia. Una diferencia superior al umbral establecido indica anomalía. No se reporta claramente un valor numérico universal del umbral ni un procedimiento completo de calibración (sección 3.2, p. 8).</t>
-        </is>
-      </c>
-      <c r="S43" s="6" t="inlineStr">
-        <is>
-          <t>No reportada</t>
-        </is>
-      </c>
-      <c r="T43" s="6" t="inlineStr">
-        <is>
-          <t>Stacked Autoencoder (SAE), CNN-LSTM, Bidirectional LSTM (Bi-LSTM), Generative Adversarial Network (GAN) y Transformer. Los resultados comparativos se presentan en la Tabla 2, p. 10.</t>
-        </is>
-      </c>
-      <c r="U43" s="6" t="inlineStr">
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>Accidentes/incidentes</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>Average Precision, AP, calculada mediante la curva precisión-recall para anticipación de accidentes; mean Time-to-Accident, mTTA, en segundos, que mide cuánto antes del accidente se genera una predicción positiva. También se presentan curvas de precisión y recall frente a umbrales, análisis de tiempo de anticipación por condiciones, ablaciones de AP/mTTA y medidas de complejidad computacional. No se publican como métricas principales AUROC, AUPRC separada, F1 final global ni mAP de detección de objetos. Página 8, sección 4.2; página 9, Tablas 3–4; página 11, Tabla 7.</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>DAD: AP 87,7 % y mTTA 4,47 s. CCD: AP 99,7 % y mTTA 3,70 s. A3D: AP 95,4 % y mTTA 3,18 s. Tabla 3, página 9. En DAD, la ablación sin atención multi-head obtiene AP 49,6 % y mTTA 3,73 s; sin características textuales, AP 74,3 % y mTTA 4,46 s; sin umbral aprendible, AP 61,2 % y mTTA 4,46 s; modelo completo, AP 87,7 % y mTTA 4,47 s. Tabla 7, página 11. Los resultados corresponden a anticipación de accidentes y no a clasificación del tipo de accidente.</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>El modelo produce probabilidades por fotograma o instante de video, mientras AP se resume a nivel de la tarea de anticipación de accidentes en videos positivos y negativos. mTTA se calcula a partir de la diferencia entre el fotograma en que se anticipa el accidente y el fotograma del evento real, expresada en segundos. Los conjuntos contienen clips de 5 s y diferentes FPS; el análisis de rendimiento se informa por dataset, no por cada objeto o trayectoria individual. Páginas 8–9, ecuación 16 y Tabla 2.</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>El predictor produce logits de dos clases y ajusta la clase positiva restando un parámetro aprendible τ. Se emite una predicción positiva cuando la probabilidad softmax ajustada supera 0,5, equivalente a una comparación de logits tras la corrección. τ se inicializa en 0 y se optimiza durante entrenamiento, con learning rate inicial 0,1. La Figura 6 contrasta el umbral aprendible, el fijo de 0,5 y un umbral óptimo obtenido mediante búsqueda exhaustiva del F1 en el conjunto de prueba; este último aparece como referencia experimental y debe diferenciarse del umbral operativo aprendido. Páginas 8–9, ecuaciones 13–15 y Figura 6.</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>Prueba independiente</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>Tabla 3, página 9: DSA, ACRA, AdaLEA, UString, DSTA, GSC, AccNet, WWW, CCAF-Net y THAT-NET, con resultados disponibles según dataset. Tabla 4: comparación adicional en DAD con ACRA, DSA, UniFormerV2, VideoSwin, MViTv2, UString, GSC, WWW, AccNet, CCAF-Net, DSTA y THAT-NET. Tabla 7: ablaciones internas sin atención multi-head, sin características textuales y sin umbral aprendible. Los baselines se comparan principalmente mediante AP y mTTA, aunque no todos tienen resultados en todos los datasets.</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V43" s="6" t="inlineStr">
-        <is>
-          <t>En City-precision, Traffic-ConvLSTM obtiene 92.875% frente a 90.124% de GAN, mejora de 2.751 puntos porcentuales. En City-accuracy alcanza 83.871% frente a 80.154% de Transformer, mejora de 3.717 puntos. En Road-accuracy obtiene 92.035% frente a 91.715% de Transformer, mejora de 0.320 puntos. En Road-precision, Transformer supera al modelo propuesto con 94.582% frente a 88.889% (Tabla 2, p. 10).</t>
-        </is>
-      </c>
-      <c r="W43" s="6" t="inlineStr">
-        <is>
-          <t>Los resultados de ablación evidencian sensibilidad a la profundidad de la arquitectura y al orden de integración de características espaciotemporales (Tablas 3–4, p. 10). El artículo aborda los costes computacionales y el posible sobreajuste asociado al aumento de profundidad. No desarrolla suficientemente las amenazas relacionadas con generalización geográfica, verificación de etiquetas, independencia de particiones o incertidumbre estadística; estas últimas son limitaciones identificadas durante la evaluación crítica, no necesariamente reconocidas expresamente por los autores.</t>
-        </is>
-      </c>
-      <c r="X43" s="6" t="inlineStr">
-        <is>
-          <t>No; el artículo no proporciona una URL pública del código fuente de Traffic-ConvLSTM. La declaración de disponibilidad indica que los datos pueden solicitarse a los autores, pero no identifica un repositorio público del dataset procesado (p. 13).</t>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>En DAD, frente a THAT-NET, mejor AP de la Tabla 3 con 77,8 %, el modelo alcanza 87,7 %, mejora absoluta de 9,9 puntos porcentuales y relativa de 12,72 %. En mTTA, frente a WWW 4,26 s, alcanza 4,47 s, mejora absoluta de 0,21 s y relativa de 4,93 %; los dos referentes son distintos y no deben fusionarse como si fueran un mismo baseline. En CCD, el AP 99,7 % empata con WWW, mientras su mTTA 3,70 s es inferior a WWW 3,93 s, DSTA 3,87 s y CCAF-Net 4,94 s; no hay superioridad universal. En A3D, AP 95,4 % supera a AccNet 95,1 % por 0,3 puntos porcentuales, pero queda por debajo de WWW 96,4 % por 1 punto porcentual; mTTA 3,18 s también es inferior a WWW 3,48 s. Por tanto, la ventaja más clara está en DAD, no en todas las métricas de los tres conjuntos. Tabla 3, página 9.</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="inlineStr">
+        <is>
+          <t>Los autores reconocen explícitamente la dependencia de la calidad visual: en un caso de fallo, la iluminación extremadamente deficiente u oclusiones impiden observar comportamientos críticos y el riesgo estimado no alcanza el umbral para emitir alerta. También discuten dificultades de los umbrales fijos ante desequilibrios de clases y de los umbrales seleccionados por búsqueda exhaustiva. En la generación de textos señalan el riesgo de alucinaciones del LLM y aplican restricciones de contexto y conocimiento de dominio para mitigarlo. Estas limitaciones son explícitas; la falta de separación por eventos, la posible confusión de dominios en CCD y la referencia al umbral óptimo de prueba son observaciones adicionales del revisor. Páginas 5–8 y 11, Figura 10.</t>
+        </is>
+      </c>
+      <c r="X43" s="5" t="inlineStr">
+        <is>
+          <t>El artículo declara expresamente que el código propuesto está disponible en la plataforma ETS mediante DOI https://doi.org/10.26599/ETSD.2025.9190040, sección Replication and data sharing, página 13. Los conjuntos DAD, CCD y A3D son benchmarks publicados y nombrados, con sus fuentes bibliográficas, pero el PDF no ofrece una declaración igualmente explícita de que todos los archivos de video y las particiones exactas del estudio puedan descargarse libremente sin restricciones. Por ello se documenta código declarado disponible y datasets identificables, distinguiendo disponibilidad bibliográfica de verificación de acceso público integral.</t>
         </is>
       </c>
     </row>
@@ -21916,7 +21784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22365,47 +22233,91 @@
       </c>
     </row>
     <row r="6" ht="57.6" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>R0032</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>A Comparative Analysis of Machine Learning, Deep Learning, and Metaheuristic-Based Ensemble Learning for Driver Behavior Profiling on UAH-DriveSet</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>cribado\pdf\R0032.pdf</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>EXCLUIDO</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="6" t="n"/>
-      <c r="Q6" s="6" t="n"/>
-      <c r="R6" s="6" t="n"/>
-      <c r="S6" s="6" t="n"/>
-      <c r="T6" s="6" t="n"/>
-      <c r="U6" s="6">
+      <c r="E6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>QA1 — Validez de etiquetas: el estudio utiliza las tres categorías preexistentes de UAH-DriveSet, normal, somnolienta y agresiva, obtenidas en conducción real. No se trata de anomalías simuladas, pero el PDF no documenta criterios originales de etiquetado, validación por expertos, concordancia interevaluador ni comprobación de etiquetas después del procesamiento. La aplicación de SMOTE genera instancias sintéticas de entrenamiento, sin añadir validación de etiquetas reales. Puntuación parcial por etiquetas de referencia sin validación específica documentada. Página 3, sección 3.1.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>QA2 — Separación: se declara división estratificada 70/15/15 en entrenamiento, validación y prueba. Sin embargo, se reúnen previamente datos de seis conductores y no se demuestra separación por conductor, recorrido o tiempo. El orden de descripción de SMOTE y otras transformaciones tampoco permite confirmar que se hayan ajustado exclusivamente en entrenamiento. Los propios autores advierten posibles problemas de particionamiento. Se asigna crédito parcial por la existencia de particiones, sin acreditar independencia fuerte ni ausencia de fuga. Páginas 3–4, secciones 3.1, 3.2 y 4.2.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>QA3 — Baselines: el ensamble se compara con ocho modelos individuales, incluidos cuatro algoritmos clásicos y cuatro arquitecturas profundas. La Tabla 1 presenta métricas comparables de clasificación y la Figura 2 incluye curvas ROC. Se cumple el requisito de al menos dos baselines relevantes. No obstante, no se evalúa un ensamble de pesos uniformes que permita aislar el efecto de PSO; esta observación no invalida la existencia de baselines. Páginas 4–5.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>QA4 — Robustez estadística: no se reportan entrenamientos repetidos con diferentes semillas, desviaciones estándar, intervalos de confianza, pruebas de significación, validación cruzada ni análisis cuantitativo de sensibilidad a hiperparámetros. Las curvas ROC y las comparaciones de modelos son resultados puntuales, no evidencia de estabilidad estadística. La mención de posibles problemas de particionamiento no constituye una prueba de robustez. Páginas 4–6.</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>QA5 — Reproducibilidad: el conjunto UAH-DriveSet está identificado como público y el artículo incluye una URL específica en la referencia 20. No se proporciona código fuente del ensamble, implementación de PSO, pesos de fusión, semillas, hiperparámetros completos ni archivos de partición. Se cumple solamente uno de los dos requisitos principales, disponibilidad pública de datos de origen, por lo que corresponde puntuación parcial. Página 7, referencia 20.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>QA6 — Generalización: UAH-DriveSet contiene seis conductores y recorridos en autopistas y carreteras secundarias, lo que introduce variedad de sujetos y condiciones dentro de un único corpus. Sin embargo, no se presenta evaluación leave-one-driver-out, transferencia a conductores no vistos, otro dataset independiente ni validación externa. Se concede puntuación parcial por diversidad interna de participantes y vías, sin demostrar generalización fuera del corpus. Página 3, sección 3.1.</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>QA7 — Protocolo: se identifican tres clases, una división estratificada y métricas de clasificación; también se presenta el flujo general de selección y fusión de modelos. Sin embargo, no se define la unidad temporal exacta de cada instancia, ni la fórmula y los pesos finales de fusión, ni un umbral operativo para alertar sobre conducción peligrosa. La evaluación es interpretable como clasificación supervisada, pero la regla de decisión no es completamente reproducible. Páginas 3–5, Figura 1 y Tabla 1.</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>QA8 — Limitaciones: los autores reconocen desbalance de clases, ruido, datos ausentes, sensibilidad a hiperparámetros, costo computacional y posibles problemas de particionamiento que podrían afectar los resultados casi perfectos. Son observaciones pertinentes, pero se distribuyen en la introducción y discusión y no se acompañan de una sección formal de limitaciones, análisis correctivos o cuantificación de sus efectos. Se concede puntuación parcial por reconocimiento explícito, aunque limitado. Páginas 2–5.</t>
+        </is>
+      </c>
+      <c r="U6" s="5">
         <f>IF(COUNT(E6,G6,I6,K6,M6,O6,Q6,S6)=0,"",SUM(E6,G6,I6,K6,M6,O6,Q6,S6))</f>
         <v/>
       </c>
@@ -25374,181 +25286,181 @@
       </c>
     </row>
     <row r="42" ht="28.8" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>R0389</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Detection of road traffic anomalies based on computational data science</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>cribado\pdf\R0389.pdf</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>El estudio define conceptualmente las anomalías como desviaciones de patrones normales de circulación (pp. 1–2) y describe la recopilación de información sobre eventos mediante noticias, plataformas digitales y fuentes oficiales de tráfico (p. 6). Sin embargo, no especifica un protocolo completo de anotación independiente, concordancia entre evaluadores ni etiquetas verificables para cada observación. Las festividades y eventos deportivos aportan referencias contextuales, pero no equivalen a un ground truth exhaustivo.</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="n">
+      <c r="E42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>El artículo documenta nueve meses de datos históricos reales y una evaluación experimental, pero no informa con suficiente precisión los periodos asignados a entrenamiento, validación y prueba ni una partición temporal estricta. Tampoco describe validación cruzada temporal o controles explícitos de fuga de información. La existencia de datos históricos no demuestra por sí sola independencia entre entrenamiento y evaluación (secciones 3.1 y 4.1, pp. 5–10).</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>La sección 4.1, pp. 8–10, compara Traffic-ConvLSTM con cinco modelos: SAE, CNN-LSTM, Bi-LSTM, GAN y Transformer. La Tabla 2 presenta métricas comparativas en escala urbana y de carretera. Las Tablas 3 y 4 incluyen experimentos de ablación sobre cantidad de capas ConvLSTM y orden de características espaciotemporales, proporcionando evidencia adicional del diseño propuesto.</t>
-        </is>
-      </c>
-      <c r="K42" s="6" t="n">
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>QA1 — Validez de etiquetas: no se proporciona un conjunto verificable de etiquetas reales de anomalías, protocolo de anotación, validación manual o comparación contra eventos confirmados. Se utiliza una regla estadística de reducción de velocidad y se mencionan accidentes y errores GNSS, pero no se documentan casos etiquetados con verdad de referencia para evaluar el detector. La trayectoria de referencia citada en la sección 5.11 corresponde a ensayos de posicionamiento y no demuestra validación de todas las anomalías de tráfico. Páginas 4–5 y 15.</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>Las Tablas 2–4, p. 10, muestran resultados puntuales, pero no incluyen desviaciones estándar, intervalos de confianza, pruebas de significancia estadística ni repetición documentada de experimentos con diferentes semillas. Los experimentos de ablación permiten analizar componentes arquitectónicos, pero no cuantifican incertidumbre estadística ni variabilidad entre ejecuciones.</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N42" s="6" t="inlineStr">
-        <is>
-          <t>El artículo identifica la procedencia de los datos, periodo de recopilación, frecuencia de muestreo, variables y herramientas de implementación Keras/TensorFlow (pp. 5–8). La declaración de disponibilidad, p. 13, indica que los datos pueden solicitarse a los autores. No se proporciona acceso directo al dataset procesado, código fuente o particiones experimentales completas. Por ello, la reproducibilidad es parcial.</t>
-        </is>
-      </c>
-      <c r="O42" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>El modelo se evalúa sobre aproximadamente 60 millones de registros reales de monitoreo urbano de Wuhan durante nueve meses (sección 3.1, pp. 5–6). Incluye escenarios viales, urbanos, festividades y eventos deportivos, pero todos proceden de una misma ciudad y fuente principal de datos. No existe validación externa documentada en otras ciudades, redes viales independientes o periodos posteriores.</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>La unidad de análisis está definida mediante imágenes de condiciones de tráfico, intervalos de 30 minutos y escalas espaciales de carretera, región y ciudad (pp. 5–8). La sección 3.2 establece que las diferencias SSIM superiores a un umbral indican anomalías. Sin embargo, no se informa claramente el valor numérico del umbral ni su procedimiento de selección. Además, las fórmulas de Accuracy y Precision de la p. 8 presentan denominaciones intercambiadas respecto a las métricas convencionales, limitando la claridad de la evaluación.</t>
-        </is>
-      </c>
-      <c r="S42" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T42" s="6" t="inlineStr">
-        <is>
-          <t>El estudio examina la sensibilidad arquitectónica mediante experimentos de ablación con distintas cantidades de capas ConvLSTM y diferentes órdenes de integración espaciotemporal (Tablas 3–4, p. 10). También discute los costes computacionales y posibles efectos de sobreajuste al aumentar la profundidad. Sin embargo, no desarrolla una sección sistemática de amenazas a la validez ni analiza suficientemente sesgos de selección de eventos, generalización geográfica, incertidumbre estadística o posibles fugas temporales.</t>
-        </is>
-      </c>
-      <c r="U42" s="6">
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>QA2 — Separación: el artículo menciona entrenamiento y prueba, pero no informa proporciones, tamaños, partición temporal, separación por vehículos o secciones ni independencia de los datos evaluados. Tampoco queda claro si el preprocesamiento se ajustó antes o después de dividir los registros. La mera declaración de dos fases no permite verificar un protocolo de prueba independiente. Páginas 7, 9 y 16.</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>QA3 — Baselines: la Figura 14 presenta una comparación gráfica CDS frente a ML, por lo que existe al menos un comparador nominal. Sin embargo, no se identifica el algoritmo ML concreto, su configuración ni métricas cuantitativas de detección. La regresión lineal y Pearson se usan como análisis estadístico, no como dos detectores competitivos documentados. Se concede puntuación parcial por una comparación limitada, sin otorgar el máximo correspondiente a dos baselines verificables. Páginas 12–15.</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>QA4 — Robustez estadística: no se reportan ejecuciones repetidas, semillas, intervalos de confianza, desviaciones de rendimiento de detección, pruebas de significación ni análisis cuantitativo de sensibilidad del detector. La Tabla 4 muestra desviaciones estándar y estadísticas de regresión de los datos, no variabilidad del rendimiento del modelo entre experimentos. Páginas 12–15.</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>QA5 — Reproducibilidad: no se publica código fuente y, aunque la sección de disponibilidad declara que la mayoría de los datos son públicos, no ofrece identificadores o enlaces que permitan recuperar inequívocamente los conjuntos utilizados en los experimentos. Los datos privados se ofrecen solo bajo solicitud, lo cual no equivale a acceso público. No se cumplen de forma verificable los requisitos de código y datos públicos identificables. Página 16, Data availability.</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>QA6 — Generalización: se presentan diferentes escenarios y ejemplos de datos de velocidad y posicionamiento, pero no se documentan dos datasets independientes, evaluaciones en distintas ciudades con resultados cuantitativos de detección, transferencia entre redes viales ni validación por tramos separados. Tampoco se ofrecen métricas por escenario que permitan otorgar crédito parcial de generalización. Páginas 4–6 y 14–15.</t>
+        </is>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>QA7 — Protocolo: el artículo identifica entradas de tiempo, sección y velocidad, observaciones cada 2,5 minutos y tramos de 300 metros, y describe una regla estadística de caída de velocidad de 30 km/h. Sin embargo, no se establece la unidad exacta de evaluación del detector, los valores operativos completos de los umbrales K1–K3 ni el criterio de decisión de la red neuronal. Se concede puntuación parcial por reglas y variables explícitas, aunque no exista un protocolo de detección completamente reproducible. Páginas 4–5 y 9.</t>
+        </is>
+      </c>
+      <c r="S42" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>QA8 — Limitaciones: se reconocen dificultades asociadas con ruido, información incompleta, interferencia, errores GNSS, complejidad de datos y posible sobreajuste por número de neuronas. También se excluye expresamente la ciberseguridad del alcance del estudio. Sin embargo, estas observaciones son generales y no se presenta una discusión profunda de limitaciones experimentales, incertidumbre de resultados o ausencia de validación cuantitativa del detector. Páginas 7–8 y 16.</t>
+        </is>
+      </c>
+      <c r="U42" s="5">
         <f>IF(COUNT(E42,G42,I42,K42,M42,O42,Q42,S42)=0,"",SUM(E42,G42,I42,K42,M42,O42,Q42,S42))</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="28.8" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>R0403</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Domain-enhanced dual-branch model for efficient and interpretable accident anticipation</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>cribado\pdf\R0403.pdf</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>El estudio utiliza información contextual de eventos procedente de noticias, plataformas digitales y autoridades de tráfico de Wuhan para identificar situaciones anómalas (sección 3.1, p. 6). Sin embargo, no documenta un protocolo exhaustivo de anotación independiente, verificación sistemática de etiquetas ni concordancia entre evaluadores. Las referencias contextuales constituyen evidencia parcial, pero no un ground truth completamente validado.</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>El artículo presenta nueve meses de datos reales y evaluación experimental, pero no especifica claramente los periodos de entrenamiento, validación y prueba ni una estrategia de partición temporal independiente. Tampoco documenta validación cruzada temporal o controles explícitos contra fuga de información (secciones 3.1 y 4.1, pp. 5–10).</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="n">
+      <c r="E43" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>La sección 4.1 y la Tabla 2, p. 10, comparan Traffic-ConvLSTM con cinco modelos profundos: SAE, CNN-LSTM, Bi-LSTM, GAN y Transformer. Las Tablas 3 y 4 presentan experimentos de ablación sobre la profundidad de ConvLSTM y la integración de características espaciotemporales. Existen múltiples referencias cuantitativas pertinentes para evaluar la propuesta.</t>
-        </is>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>Las Tablas 2–4 presentan resultados puntuales sin desviaciones estándar, intervalos de confianza, pruebas de significancia estadística ni experimentos repetidos con diferentes semillas. Los estudios de ablación no proporcionan por sí mismos evidencia de robustez estadística.</t>
-        </is>
-      </c>
-      <c r="M43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="6" t="inlineStr">
-        <is>
-          <t>El artículo identifica la procedencia, el periodo y la frecuencia de los datos, así como las herramientas Keras y TensorFlow. Sin embargo, no publica código fuente ni ofrece descarga pública directa del dataset procesado; la disponibilidad de datos queda condicionada a una solicitud a los autores (p. 13). Según la rúbrica de acceso público efectivo a código y datos, no se cumple ninguno de los dos requisitos.</t>
-        </is>
-      </c>
-      <c r="O43" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>El modelo se evalúa sobre diferentes escalas espaciales y escenarios de una misma red urbana de Wuhan, incluyendo carreteras, ciudad, festividades y eventos deportivos (secciones 3.1 y 4.2). No se presenta validación cuantitativa en otras ciudades, redes independientes o fuentes externas de datos. La diversidad interna de escenarios permite una puntuación parcial.</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>El estudio define las unidades espaciales y temporales de detección mediante imágenes de condiciones de tráfico y observaciones cada 30 minutos (pp. 5–8). La sección 3.2 establece una regla basada en diferencias SSIM superiores a un umbral, pero no especifica claramente su valor numérico ni un procedimiento reproducible de calibración. Por ello, el protocolo de decisión queda parcialmente documentado.</t>
-        </is>
-      </c>
-      <c r="S43" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T43" s="6" t="inlineStr">
-        <is>
-          <t>El artículo analiza el efecto de diferentes configuraciones arquitectónicas mediante experimentos de ablación (Tablas 3–4, p. 10) y menciona aspectos relacionados con profundidad, costes computacionales y posible sobreajuste. No presenta una discusión sistemática de amenazas a la validez, generalización geográfica, incertidumbre estadística o sesgos en las referencias de anomalías.</t>
-        </is>
-      </c>
-      <c r="U43" s="6">
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>QA1 — Validez de etiquetas: los conjuntos DAD, CCD y A3D proceden de benchmarks reales de videos de accidentes con identificación de episodios positivos y referencia temporal del evento. DAD y CCD incluyen negativos sin accidente y particiones definidas. A3D genera negativos desde segmentos anteriores a la colisión, circunstancia que debe documentarse, pero la condición positiva se fundamenta en accidentes reales y no únicamente en colisiones sintéticas. Página 8, sección 4.1 y Tabla 2.</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>QA2 — Separación: se reportan particiones independientes por video para DAD y CCD, y 80/20 para A3D, pero no se demuestra separación temporal, por evento, vehículo o fuente de captura. La Figura 6 presenta un umbral óptimo F1 obtenido mediante búsqueda en el conjunto de prueba como referencia, sin aclarar por completo la independencia de todas las decisiones experimentales. Se concede crédito parcial por particiones documentadas, no el máximo reservado para independencia robusta. Páginas 8–9.</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>QA3 — Baselines: las Tablas 3 y 4 comparan el método con múltiples modelos relevantes de anticipación de accidentes, incluidos DSTA, AccNet, WWW, CCAF-Net y THAT-NET, utilizando AP y mTTA cuando están disponibles. También se ofrecen ablaciones de tres componentes. Se cumple ampliamente el requisito de al menos dos baselines competitivos. Páginas 9–11.</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>QA4 — Robustez: el artículo presenta ablaciones cuantitativas de atención multi-head, características textuales y umbral aprendible, y analiza el tiempo de anticipación por escenarios de accidente y condiciones visuales. Sin embargo, no reporta de manera verificable medias y desviaciones entre múltiples semillas, intervalos de confianza o pruebas de significación de las diferencias de AP. Se concede crédito parcial por sensibilidad estructural, no por robustez estadística completa. Páginas 10–11, Figuras 8–10 y Tabla 7.</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>QA5 — Reproducibilidad: los autores declaran código disponible mediante DOI de ETS 10.26599/ETSD.2025.9190040 y proporcionan detalles de optimizador, épocas, batch, tasas de aprendizaje y arquitectura. Aunque DAD, CCD y A3D son conjuntos de referencia identificados, el PDF no permite confirmar acceso público irrestricto a los tres datasets completos y a las particiones exactas empleadas. Se otorga 0,5 por el código expresamente publicado, sin asumir disponibilidad íntegra y verificada de todos los datos. Páginas 8–9 y 13.</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>QA6 — Generalización: se realizan evaluaciones cuantitativas separadas en tres benchmarks distintos, DAD, CCD y A3D, con procedencias y composiciones diferentes. La Tabla 3 presenta AP y mTTA para cada uno, lo que satisface el requisito de validación en al menos dos datasets independientes. Debe precisarse que no se demuestra necesariamente transferencia entre dominios sin reentrenamiento, sino evaluación en múltiples benchmarks. Páginas 8–9, Tablas 2 y 3.</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>QA7 — Protocolo: la sección 4.2 define AP mediante la curva precisión-recall y mTTA mediante la anticipación temporal respecto del accidente. Las ecuaciones 13–15 especifican el ajuste del logit positivo mediante τ y la regla de decisión con softmax superior a 0,5. Se conocen FPS, duración de clips y particiones. Aunque la Figura 6 introduce una referencia de umbral óptimo en prueba, la unidad temporal y la regla operativa del predictor están suficientemente definidas. Páginas 8–9.</t>
+        </is>
+      </c>
+      <c r="S43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>QA8 — Limitaciones: los autores documentan un caso de fallo concreto en la Figura 10, atribuido a mala visibilidad y pérdida de pistas de comportamiento vehicular, además de discutir riesgos de alucinación del LLM y dificultades de umbrales fijos o buscados exhaustivamente. Se trata de limitaciones explícitas y técnicamente relevantes para despliegues de seguridad vial, acompañadas de evidencia cualitativa. Páginas 5–8 y 11.</t>
+        </is>
+      </c>
+      <c r="U43" s="5">
         <f>IF(COUNT(E43,G43,I43,K43,M43,O43,Q43,S43)=0,"",SUM(E43,G43,I43,K43,M43,O43,Q43,S43))</f>
         <v/>
       </c>

--- a/RSL/cribado/revision/REVISION_TEXTO_COMPLETO.xlsx
+++ b/RSL/cribado/revision/REVISION_TEXTO_COMPLETO.xlsx
@@ -230,10 +230,28 @@
 Motivo: Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
       </text>
     </comment>
+    <comment ref="E25" authorId="1" shapeId="0">
+      <text>
+        <t>Antes: Incluir
+Motivo: Releído el PDF: la detección solo se valida de forma visual (face validation); la única métrica cuantitativa (RMSE, Tabla 1) es de imputación.</t>
+      </text>
+    </comment>
     <comment ref="F25" authorId="0" shapeId="0">
       <text>
         <t>Texto original:
 NO APLICA</t>
+      </text>
+    </comment>
+    <comment ref="G25" authorId="1" shapeId="0">
+      <text>
+        <t>Antes: El estudio propone SI-DMSeq, un modelo de Deep Learning multitarea basado en encoder-decoder LSTM con atención, para detectar anomalías de tráfico a nivel de red y de zonas (pp. 2-4, secciones I y III-A). La detección utiliza errores de reconstrucción, gráficos de control estadístico y puntuaciones locales mediante soft-thresholding (p. 7, sección III-F). Se valida con datos reales de Manhattan procedentes de aproximadamente 700 millones de viajes de taxi, agregados en 46 zonas (p. 8, sección IV
+Motivo: Cita del PDF.</t>
+      </text>
+    </comment>
+    <comment ref="H25" authorId="1" shapeId="0">
+      <text>
+        <t>Antes: [Incluir] Investigación original publicada en IEEE Access (2025), con texto completo Open Access. Presenta SI-DMSeq, arquitectura LSTM multitarea con atención que integra reconstrucción de secuencias, detección de anomalías e imputación de datos faltantes. Evalúa alteraciones del tráfico urbano a nivel global y local utilizando datos reales de Manhattan y dos eventos meteorológicos extremos. La detección se fundamenta en errores de reconstrucción y límites de control estadístico; la localización
+Motivo: Motivo.</t>
       </text>
     </comment>
     <comment ref="F30" authorId="0" shapeId="0">
@@ -5468,20 +5486,24 @@
           <t>cribado\pdf\R0192.pdf</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Incluir</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>El estudio propone SI-DMSeq, un modelo de Deep Learning multitarea basado en encoder-decoder LSTM con atención, para detectar anomalías de tráfico a nivel de red y de zonas (pp. 2-4, secciones I y III-A). La detección utiliza errores de reconstrucción, gráficos de control estadístico y puntuaciones locales mediante soft-thresholding (p. 7, sección III-F). Se valida con datos reales de Manhattan procedentes de aproximadamente 700 millones de viajes de taxi, agregados en 46 zonas (p. 8, sección IV-A). Identifica interrupciones durante el huracán Sandy y la tormenta de nieve de diciembre de 2010 (pp. 9-12). El modelo también realiza imputación de datos faltantes y presenta un tiempo medio de inferencia de 55 ms por secuencia (p. 12). Cumple los criterios de detección explícita de anomalías vehiculares mediante Deep Learning, validación empírica, periodo 2020-2026 y acceso abierto al texto completo.</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>[Incluir] Investigación original publicada en IEEE Access (2025), con texto completo Open Access. Presenta SI-DMSeq, arquitectura LSTM multitarea con atención que integra reconstrucción de secuencias, detección de anomalías e imputación de datos faltantes. Evalúa alteraciones del tráfico urbano a nivel global y local utilizando datos reales de Manhattan y dos eventos meteorológicos extremos. La detección se fundamenta en errores de reconstrucción y límites de control estadístico; la localización emplea puntuaciones de anomalía por zona. Los resultados respaldan la detección de interrupciones asociadas a eventos históricos. Limitaciones: evaluación restringida a Manhattan y eventos meteorológicos, validación principalmente gráfica de la detección y ausencia de métricas convencionales de clasificación como F1-score, precisión, recall y AUC. Cumple el objetivo de la revisión sistemática y pasa a extracción de datos y evaluación de calidad.</t>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Excluir</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>CI-6</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>"we employ a face validation approach. In this approach, we visually examine the pace time series of various zones" (p. 10, sección IV-E); "Table 1 presents the mean and standard deviation of RMSE across 10 trials of inference-phase imputation" (p. 9, sección IV-C).</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CI-6] SI-DMSeq (encoder-decoder LSTM con atención, Manhattan, huracán Sandy y tormenta de 2010) detecta disrupciones con una carta de control sobre el error de reconstrucción, pero no las evalúa contra etiquetas: no hay precision, recall, F1, AUC ni tasa de detección; la única métrica numérica (RMSE) es de imputación.</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8619,36 +8641,36 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Paradigma no identificable («aprendizaje federado»): elegir una opción de la lista.</t>
+          <t>Paradigma no identificable («aprendizaje federado»): elegir una opción de la lista con el PDF (https://jcbi.org/index.php/Main/article/download/1147/825). Si el PDF ya no se puede obtener, poner DECISIÓN TC = «No recuperado».</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>R0192</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>REHACER</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>La hoja 2 está desplazada (cada valor en la columna equivocada): volver a pegar el bloque de 20 valores.</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>R0025</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Partición «No reportada» en la hoja 2 pero QA2 = 1 en la hoja 3: revisa uno de los dos.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>R0025</t>
+          <t>R0029</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -8663,14 +8685,14 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Partición «No reportada» en la hoja 2 pero QA2 = 1 en la hoja 3: revisa uno de los dos.</t>
+          <t>Se excluyó por CE-3 (clasifica perfiles normal/somnoliento/agresivo), pero R0032 (UAH-DriveSet, mismas tres clases), R0360, R0428 y R1029 se incluyeron. Decide con el mismo criterio para todos.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>R0029</t>
+          <t>R0051</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -8685,14 +8707,14 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Se excluyó por CE-3 (clasifica perfiles normal/somnoliento/agresivo), pero R0032 (UAH-DriveSet, mismas tres clases), R0360, R0428 y R1029 se incluyeron. Decide con el mismo criterio para todos.</t>
+          <t>Partición aleatoria (411/35/148) pero QA2 = 1: según la escala sería 0.5.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>R0051</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -8707,14 +8729,14 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Partición aleatoria (411/35/148) pero QA2 = 1: según la escala sería 0.5.</t>
+          <t>Caso límite: el DL extrae y reconstruye trayectorias y la anomalía se decide con reglas. Se mantiene incluido (regla de híbridos de CI-5); va al anexo de casos límite.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0986</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -8729,29 +8751,29 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Caso límite: el DL extrae y reconstruye trayectorias y la anomalía se decide con reglas. Se mantiene incluido (regla de híbridos de CI-5); va al anexo de casos límite.</t>
+          <t>El texto analizado corresponde a Systems and Soft Computing (DOI 10.1016/j.sasc.2025.200254), pero el registro tiene DOI 10.1002/spy2.70136: confirma que el PDF es el del registro.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>R0986</t>
+          <t>R0024</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Corregido «QA8 Limitaciones» → 0</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>El texto analizado corresponde a Systems and Soft Computing (DOI 10.1016/j.sasc.2025.200254), pero el registro tiene DOI 10.1002/spy2.70136: confirma que el PDF es el del registro.</t>
+          <t>La hoja 2 dice «No reportadas»: la cita es trabajo futuro, no una limitación.</t>
         </is>
       </c>
     </row>
@@ -8768,41 +8790,41 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Corregido «QA8 Limitaciones» → 0</t>
+          <t>Corregido «QA8 evidencia» → No reportado (solo trabajo futuro, p. 10)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>La hoja 2 dice «No reportadas»: la cita es trabajo futuro, no una limitación.</t>
+          <t>Coherente con la hoja 2.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>R0024</t>
+          <t>R0032</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Corregido «QA8 evidencia» → No reportado (solo trabajo futuro, p. 10)</t>
+          <t>Corregido «Tipo de dato» → Multimodal</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Coherente con la hoja 2.</t>
+          <t>Acelerómetro, giroscopio y GPS del teléfono (UAH-DriveSet).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>R0032</t>
+          <t>R0052</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -8812,19 +8834,19 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Tipo de dato» → Multimodal</t>
+          <t>Corregido «Entorno» → Ambos</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Acelerómetro, giroscopio y GPS del teléfono (UAH-DriveSet).</t>
+          <t>Intersecciones y rampas/puentes de carretera.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>R0052</t>
+          <t>R0080</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -8834,19 +8856,19 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Ambos</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Intersecciones y rampas/puentes de carretera.</t>
+          <t>Incidentes distintos en entrenamiento (23) y prueba (22).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>R0080</t>
+          <t>R0097</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -8856,19 +8878,19 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Incidentes distintos en entrenamiento (23) y prueba (22).</t>
+          <t>Ubicación y tipo de vía no reportados.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>R0097</t>
+          <t>R0119</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -8878,12 +8900,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Entorno» → Ambos</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Ubicación y tipo de vía no reportados.</t>
+          <t>Intersecciones y autopistas.</t>
         </is>
       </c>
     </row>
@@ -8900,19 +8922,19 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Ambos</t>
+          <t>Corregido «Partición» → Aleatoria</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Intersecciones y autopistas.</t>
+          <t>Partición estratificada sin separación temporal.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>R0119</t>
+          <t>R0121</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -8922,19 +8944,19 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Aleatoria</t>
+          <t>Corregido «Entorno» → Urbano</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Partición estratificada sin separación temporal.</t>
+          <t>Dos cruces peatonales de calle (35 mph) en Florida.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>R0121</t>
+          <t>R0167</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -8944,19 +8966,19 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Urbano</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Dos cruces peatonales de calle (35 mph) en Florida.</t>
+          <t>«No se detallan particiones».</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>R0167</t>
+          <t>R0175</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -8966,19 +8988,19 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>«No se detallan particiones».</t>
+          <t>No especifica el tipo de vía.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>R0175</t>
+          <t>R0185</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -8988,41 +9010,41 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>No especifica el tipo de vía.</t>
+          <t>No describe la partición.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>R0185</t>
+          <t>R0190</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «CRITERIO» → CE-3</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>No describe la partición.</t>
+          <t>Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>R0190</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -9032,19 +9054,19 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-3</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
+          <t>Releído el PDF: la detección solo se valida de forma visual (face validation); la única métrica cuantitativa (RMSE, Tabla 1) es de imputación.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>R0244</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -9054,19 +9076,19 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Incluir</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>«INCLUIDO» no es una opción de la lista.</t>
+          <t>Sin evaluación cuantitativa de la detección (igual que R0249 y R0389).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>R0249</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -9076,41 +9098,41 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «EVIDENCIA (cita y página)» → "we employ a face validation approach. In this approach, we visually examine the pace time series of various zones" (p. 10, sección IV-E); "Table 1 presents the mean and standard deviation of RMSE across 10 trials of inference-phase imputation" (p. 9, sección IV-C).</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
+          <t>Cita del PDF.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>R0379</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Comentario» → [Excluir CI-6] SI-DMSeq (encoder-decoder LSTM con atención, Manhattan, huracán Sandy y tormenta de 2010) detecta disrupciones con una carta de control sobre el error de reconstrucción, pero no las evalúa contra etiquetas: no hay precision, recall, F1, AUC ni tasa de detección; la única métrica numérica (RMSE) es de imputación.</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Evalúa en una grabación highD no vista.</t>
+          <t>Motivo.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>R0389</t>
+          <t>R0244</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -9120,41 +9142,41 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «DECISIÓN TC» → Incluir</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
+          <t>«INCLUIDO» no es una opción de la lista.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>R0403</t>
+          <t>R0249</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Corregido «QA5 Código y datos» → 1</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Código con DOI (ETS) y datasets públicos (DAD, CCD, A3D): ambos públicos.</t>
+          <t>Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>R0403</t>
+          <t>R0379</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -9169,80 +9191,80 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Particiones oficiales de DAD y CCD.</t>
+          <t>Evalúa en una grabación highD no vista.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>R0501</t>
+          <t>R0389</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Ambos</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Vías urbanas e interurbanas.</t>
+          <t>Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>R0501</t>
+          <t>R0403</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «QA5 Código y datos» → 1</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Conjunto externo ECVD solo para prueba.</t>
+          <t>Código con DOI (ETS) y datasets públicos (DAD, CCD, A3D): ambos públicos.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>R0528</t>
+          <t>R0403</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
+          <t>Particiones oficiales de DAD y CCD.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>R0537</t>
+          <t>R0501</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -9252,19 +9274,19 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Entorno» → Ambos</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Sin proporciones ni protocolo de separación.</t>
+          <t>Vías urbanas e interurbanas.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>R0596</t>
+          <t>R0501</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -9274,41 +9296,41 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Partición insuficientemente reportada.</t>
+          <t>Conjunto externo ECVD solo para prueba.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>R0598</t>
+          <t>R0528</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Pista de pruebas; no es urbano ni autopista.</t>
+          <t>Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>R0601</t>
+          <t>R0537</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -9318,195 +9340,195 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba de AI City Challenge.</t>
+          <t>Sin proporciones ni protocolo de separación.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>R0604</t>
+          <t>R0596</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
+          <t>Partición insuficientemente reportada.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>R0604</t>
+          <t>R0598</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-2</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina.</t>
+          <t>Pista de pruebas; no es urbano ni autopista.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>R0614</t>
+          <t>R0601</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-3</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
+          <t>Conjunto de prueba de AI City Challenge.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>R0658</t>
+          <t>R0604</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Particiones oficiales de los benchmarks.</t>
+          <t>Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>R0664</t>
+          <t>R0604</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «CRITERIO» → CE-2</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Videos de prueba separados.</t>
+          <t>Monitoreo del conductor dentro de la cabina.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0614</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «CRITERIO» → CE-3</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>No detalla la partición.</t>
+          <t>Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>R0929</t>
+          <t>R0658</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
+          <t>Particiones oficiales de los benchmarks.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>R0929</t>
+          <t>R0664</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-2</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina.</t>
+          <t>Videos de prueba separados.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>R0943</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -9521,58 +9543,58 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Sin procedimiento de selección ni conjunto de prueba.</t>
+          <t>No detalla la partición.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>R1000</t>
+          <t>R0929</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>No indica qué escenas de NGSIM usa.</t>
+          <t>La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>R1010</t>
+          <t>R0929</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «CRITERIO» → CE-2</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Evaluado con autos de juguete en escenario controlado.</t>
+          <t>Monitoreo del conductor dentro de la cabina.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>R1013</t>
+          <t>R0943</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -9582,19 +9604,19 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba oficial de TADS.</t>
+          <t>Sin procedimiento de selección ni conjunto de prueba.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>R1014</t>
+          <t>R1000</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -9604,19 +9626,19 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Familia DL principal» → Otra</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>DeepWalk/Node2vec no es una GNN.</t>
+          <t>No indica qué escenas de NGSIM usa.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>R1082</t>
+          <t>R1010</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -9626,19 +9648,19 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba de MAAD (con ajuste de hiperparámetros en parte de él).</t>
+          <t>Evaluado con autos de juguete en escenario controlado.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>R1092</t>
+          <t>R1013</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -9648,19 +9670,19 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Aleatoria</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>División 80/20 de videos sin otro criterio.</t>
+          <t>Conjunto de prueba oficial de TADS.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>R1100</t>
+          <t>R1014</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -9670,19 +9692,19 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Familia DL principal» → Otra</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>DoTA/CCD sin clasificación por tipo de vía.</t>
+          <t>DeepWalk/Node2vec no es una GNN.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>R1138</t>
+          <t>R1082</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -9692,19 +9714,19 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>No desagrega urbano/autopista.</t>
+          <t>Conjunto de prueba de MAAD (con ajuste de hiperparámetros en parte de él).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>R1148</t>
+          <t>R1092</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -9714,19 +9736,19 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Categoría de anomalía» → Evento/otro</t>
+          <t>Corregido «Partición» → Aleatoria</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Objetos caídos sobre la calzada.</t>
+          <t>División 80/20 de videos sin otro criterio.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>R1148</t>
+          <t>R1100</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -9736,41 +9758,41 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Solo dice que entrena y valida 100 épocas.</t>
+          <t>DoTA/CCD sin clasificación por tipo de vía.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>R1166</t>
+          <t>R1138</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
+          <t>No desagrega urbano/autopista.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>R1185</t>
+          <t>R1148</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -9780,19 +9802,19 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Categoría de anomalía» → Evento/otro</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>No clasifica las imágenes por tipo de vía.</t>
+          <t>Objetos caídos sobre la calzada.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>R1202</t>
+          <t>R1148</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -9802,32 +9824,98 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Separación por sesiones de conducción.</t>
+          <t>Solo dice que entrena y valida 100 épocas.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t>R1166</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CI-6</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>R1185</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>No clasifica las imágenes por tipo de vía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>R1202</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Separación por sesiones de conducción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
           <t>R1214</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>No informa proporciones ni criterio de división.</t>
         </is>
@@ -12458,94 +12546,94 @@
       </c>
     </row>
     <row r="25" ht="28.8" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>R0192</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>A Self-Imputing Deep Multitask Sequence Model for Traffic Disruption Detection in Extreme Conditions</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>cribado\pdf\R0192.pdf</t>
         </is>
       </c>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>SI-DMSeq (Self-Imputing Deep Multitask Sequence)</t>
         </is>
       </c>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Encoder LSTM compartido y dos decodificadores LSTM con atención para reconstrucción y predicción</t>
         </is>
       </c>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Manhattan, Nueva York, Estados Unidos</t>
         </is>
       </c>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="inlineStr">
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>Evento/otro</t>
         </is>
       </c>
-      <c r="O25" s="9" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>Detección no supervisada basada en aprendizaje de patrones normales</t>
         </is>
       </c>
-      <c r="P25" s="9" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>Errores de reconstrucción MSE, gráficos de control estadístico SPC y soft-thresholding por zona</t>
         </is>
       </c>
-      <c r="Q25" s="9" t="inlineStr">
+      <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>Detección a nivel de red y localización de zonas afectadas por eventos extremos</t>
         </is>
       </c>
-      <c r="R25" s="9" t="inlineStr">
+      <c r="R25" s="5" t="inlineStr">
         <is>
           <t>RMSE para imputación; estadístico MSE y límites de control para detección; validación visual de anomalías</t>
         </is>
       </c>
-      <c r="S25" s="9" t="inlineStr">
+      <c r="S25" s="5" t="inlineStr">
         <is>
           <t>Aleatoria</t>
         </is>
       </c>
-      <c r="T25" s="9" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>Comparación de imputación con Temporal Mean, RTRC y PARATUCK2</t>
         </is>
       </c>
-      <c r="U25" s="9" t="n"/>
-      <c r="V25" s="9" t="inlineStr">
+      <c r="U25" s="5" t="n"/>
+      <c r="V25" s="5" t="inlineStr">
         <is>
           <t>Detección de anomalías a dos escalas, imputación integrada y procesamiento apto para monitoreo casi en tiempo real</t>
         </is>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="5" t="inlineStr">
         <is>
           <t>Evaluación limitada a Manhattan y eventos meteorológicos; validación de detección principalmente visual; sin precisión, recall, F1-score ni AUC reportados</t>
         </is>
       </c>
-      <c r="X25" s="9" t="inlineStr">
+      <c r="X25" s="5" t="inlineStr">
         <is>
           <t>https://doi.org/10.1109/ACCESS.2025.3612407 ; https://github.com/minanouri/SI-DMSeq</t>
         </is>

--- a/RSL/cribado/revision/REVISION_TEXTO_COMPLETO.xlsx
+++ b/RSL/cribado/revision/REVISION_TEXTO_COMPLETO.xlsx
@@ -42,7 +42,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -81,11 +81,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0000467F"/>
       </patternFill>
     </fill>
@@ -102,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -125,10 +120,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -208,473 +200,491 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>Revisión</author>
     <author>Normalización</author>
-    <author>Revisión</author>
   </authors>
   <commentList>
-    <comment ref="F6" authorId="0" shapeId="0">
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Excluir
+Motivo: El autor verificó que no hay texto completo en acceso abierto (la copia de SSRN no está disponible).</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: CE-3
+Motivo: No recuperado no lleva criterio.</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: [Excluir CE-3] Estudio comparativo de clasificación de perfiles de conducción mediante ML, DL y ensamble PSO; no presenta una tarea específica de detección o anticipación de anomalías vehiculares.
+Motivo: Coherente con las demás no recuperadas.</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica: cumple los criterios de inclusión por ser un artículo original de conferencia ACM publicado en 2026, con texto completo disponible, aplicación a conducción vehicular real, modelos de Deep Learning y evaluación cuantitativa de comportamientos de riesgo. Se incluye como clasificación supervisada de conducción normal, agresiva y somnolienta, no como detección no supervisada de anomalías desconocidas.</t>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
+    <comment ref="F7" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 —</t>
       </text>
     </comment>
-    <comment ref="F24" authorId="1" shapeId="0">
+    <comment ref="F24" authorId="0" shapeId="0">
       <text>
         <t>Antes: CE-2
 Motivo: Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
       </text>
     </comment>
-    <comment ref="E25" authorId="1" shapeId="0">
+    <comment ref="E25" authorId="0" shapeId="0">
       <text>
         <t>Antes: Incluir
 Motivo: Releído el PDF: la detección solo se valida de forma visual (face validation); la única métrica cuantitativa (RMSE, Tabla 1) es de imputación.</t>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F25" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 NO APLICA</t>
       </text>
     </comment>
-    <comment ref="G25" authorId="1" shapeId="0">
+    <comment ref="G25" authorId="0" shapeId="0">
       <text>
         <t>Antes: El estudio propone SI-DMSeq, un modelo de Deep Learning multitarea basado en encoder-decoder LSTM con atención, para detectar anomalías de tráfico a nivel de red y de zonas (pp. 2-4, secciones I y III-A). La detección utiliza errores de reconstrucción, gráficos de control estadístico y puntuaciones locales mediante soft-thresholding (p. 7, sección III-F). Se valida con datos reales de Manhattan procedentes de aproximadamente 700 millones de viajes de taxi, agregados en 46 zonas (p. 8, sección IV
 Motivo: Cita del PDF.</t>
       </text>
     </comment>
-    <comment ref="H25" authorId="1" shapeId="0">
+    <comment ref="H25" authorId="0" shapeId="0">
       <text>
         <t>Antes: [Incluir] Investigación original publicada en IEEE Access (2025), con texto completo Open Access. Presenta SI-DMSeq, arquitectura LSTM multitarea con atención que integra reconstrucción de secuencias, detección de anomalías e imputación de datos faltantes. Evalúa alteraciones del tráfico urbano a nivel global y local utilizando datos reales de Manhattan y dos eventos meteorológicos extremos. La detección se fundamenta en errores de reconstrucción y límites de control estadístico; la localización
 Motivo: Motivo.</t>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 NO APLICA</t>
       </text>
     </comment>
-    <comment ref="F31" authorId="1" shapeId="0">
+    <comment ref="F31" authorId="0" shapeId="0">
       <text>
         <t>Antes: CE-3
 Motivo: Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
       </text>
     </comment>
-    <comment ref="F32" authorId="0" shapeId="0">
+    <comment ref="F32" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F33" authorId="0" shapeId="0">
+    <comment ref="F33" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; cumple los criterios de inclusión</t>
       </text>
     </comment>
-    <comment ref="F34" authorId="0" shapeId="0">
+    <comment ref="F34" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; cumple los criterios de inclusión</t>
       </text>
     </comment>
-    <comment ref="F36" authorId="0" shapeId="0">
+    <comment ref="F36" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F37" authorId="0" shapeId="0">
+    <comment ref="F37" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F38" authorId="0" shapeId="0">
+    <comment ref="F38" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F39" authorId="0" shapeId="0">
+    <comment ref="F39" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F40" authorId="0" shapeId="0">
+    <comment ref="F40" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F41" authorId="0" shapeId="0">
+    <comment ref="F41" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F42" authorId="1" shapeId="0">
+    <comment ref="F42" authorId="0" shapeId="0">
       <text>
         <t>Antes: CE-3
 Motivo: Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
       </text>
     </comment>
-    <comment ref="F43" authorId="0" shapeId="0">
+    <comment ref="F43" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica: cumple los criterios de inclusión por ser un artículo original revisado por pares, publicado en 2025 y disponible en acceso abierto, que desarrolla y evalúa cuantitativamente un modelo de Deep Learning para anticipación de accidentes vehiculares. La tarea se considera detección anticipada de situaciones anormales de riesgo, no detección retrospectiva de accidentes.</t>
       </text>
     </comment>
-    <comment ref="F44" authorId="0" shapeId="0">
+    <comment ref="F44" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F45" authorId="0" shapeId="0">
+    <comment ref="F45" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F46" authorId="0" shapeId="0">
+    <comment ref="F46" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F47" authorId="0" shapeId="0">
+    <comment ref="F47" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F49" authorId="0" shapeId="0">
+    <comment ref="F49" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F51" authorId="1" shapeId="0">
+    <comment ref="F51" authorId="0" shapeId="0">
       <text>
         <t>Antes: CE-3
 Motivo: Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
       </text>
     </comment>
-    <comment ref="F52" authorId="0" shapeId="0">
+    <comment ref="F52" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F53" authorId="0" shapeId="0">
+    <comment ref="F53" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F54" authorId="0" shapeId="0">
+    <comment ref="F54" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F55" authorId="0" shapeId="0">
+    <comment ref="F55" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F56" authorId="0" shapeId="0">
+    <comment ref="F56" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F57" authorId="0" shapeId="0">
+    <comment ref="F57" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CE-5: Tipo de publicación no elegible; tesis de maestría, sin evidencia de publicación de este documento como artículo revisado por pares.</t>
       </text>
     </comment>
-    <comment ref="F59" authorId="0" shapeId="0">
+    <comment ref="F59" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; cumple los criterios de inclusión.</t>
       </text>
     </comment>
-    <comment ref="F60" authorId="0" shapeId="0">
+    <comment ref="F60" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; cumple los criterios de inclusión.</t>
       </text>
     </comment>
-    <comment ref="F61" authorId="0" shapeId="0">
+    <comment ref="F61" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; cumple los criterios temáticos y de acceso, aunque presenta reservas importantes sobre la validez de los resultados.</t>
       </text>
     </comment>
-    <comment ref="F62" authorId="0" shapeId="0">
+    <comment ref="F62" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="E63" authorId="1" shapeId="0">
+    <comment ref="E63" authorId="0" shapeId="0">
       <text>
         <t>Antes: Incluir
 Motivo: Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
       </text>
     </comment>
-    <comment ref="F63" authorId="0" shapeId="0">
+    <comment ref="F63" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica</t>
       </text>
     </comment>
-    <comment ref="F64" authorId="1" shapeId="0">
+    <comment ref="F64" authorId="0" shapeId="0">
       <text>
         <t>Antes: CE-4
 Motivo: Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
       </text>
     </comment>
-    <comment ref="F65" authorId="0" shapeId="0">
+    <comment ref="F65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica. Cumple los criterios de inclusión: artículo original de revista publicado en 2025; tráfico vehicular terrestre en carreteras montañosas; utilización de una red neuronal profunda LSTM; detección explícita de incidentes mediante clasificación binaria; evaluación cuantitativa con DR, FAR, F1, accuracy y AUC; texto completo accesible.</t>
       </text>
     </comment>
-    <comment ref="F66" authorId="0" shapeId="0">
+    <comment ref="F66" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CE-5: documento disponible como prepublicación arXiv, sin evidencia de publicación arbitrada en revista o congreso dentro del PDF. El manuscrito se identifica como arXiv:2505.02613v1, fechado el 5 de mayo de 2025, y no presenta DOI editorial, nombre de congreso, revista ni datos de aceptación. La exclusión se refiere al estado de publicación verificable de esta versión; no implica que el trabajo carezca de calidad científica ni descarta una eventual versión publicada posteriormente.</t>
       </text>
     </comment>
-    <comment ref="F67" authorId="0" shapeId="0">
+    <comment ref="F67" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CE-5: prepublicación arXiv sin acreditación de revisión por pares en la versión PDF examinada. El documento figura como arXiv:2303.05000v1 [cs.LG], fechado el 9 de marzo de 2023, sin nombre de revista, congreso, volumen, páginas editoriales ni DOI de publicación. La decisión corresponde exclusivamente a esta versión documental y deberá reconsiderarse si se identifica una publicación arbitrada equivalente.</t>
       </text>
     </comment>
-    <comment ref="F69" authorId="0" shapeId="0">
+    <comment ref="F69" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CE-3: El estudio se centra en predicción de riesgo de colisión y no demuestra un sistema de detección explícita de anomalías vehiculares en tráfico general. Aunque clasifica muestras peligrosas y presenta métricas de clasificación, los escenarios peligrosos se preseleccionan mediante TTC &lt; 3 s; el propio artículo reconoce que todavía es necesario identificar esos periodos en aplicaciones reales.</t>
       </text>
     </comment>
-    <comment ref="F70" authorId="0" shapeId="0">
+    <comment ref="F70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; cumple los criterios de inclusión. Artículo original de revista publicado en 2020, dentro del intervalo 2020–2026, centrado en la identificación explícita de comportamientos anómalos de conducción vehicular mediante una arquitectura híbrida de Deep Learning LSTM-CNN, con datos reales y evaluación cuantitativa.</t>
       </text>
     </comment>
-    <comment ref="F71" authorId="0" shapeId="0">
+    <comment ref="F71" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CE-3: el estudio no evalúa cuantitativamente la detección de anomalías en tráfico vehicular. Aunque propone un modelo Deep Learning para analizar conducción peligrosa, su tarea experimental es la predicción de series temporales y del nivel macroscópico de riesgo generado mediante reglas difusas, sin contrastar decisiones de anomalía contra etiquetas de referencia independientes.</t>
       </text>
     </comment>
-    <comment ref="F72" authorId="0" shapeId="0">
+    <comment ref="F72" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; cumple los criterios de inclusión por tratarse de un artículo original de revista científica publicado en 2025, con texto completo disponible, uso de Deep Learning y evaluación cuantitativa de detección de anomalías en tráfico vehicular mediante UIT-ADrone.</t>
       </text>
     </comment>
-    <comment ref="F73" authorId="0" shapeId="0">
+    <comment ref="F73" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; cumple los criterios de inclusión por ser un artículo original de revista científica de 2025, con acceso abierto al texto completo, modelo basado en Deep Learning y evaluación cuantitativa de incidentes de tráfico vehicular.</t>
       </text>
     </comment>
-    <comment ref="F74" authorId="0" shapeId="0">
+    <comment ref="F74" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; artículo original de revista científica, publicado en 2024, con texto completo abierto y evaluación cuantitativa de comportamientos anómalos en autopistas mediante un sistema que incorpora redes profundas. La inclusión es condicionada a que el protocolo acepte Deep Learning para obtener y reconstruir trayectorias, aunque la decisión final de anomalía se base en reglas.</t>
       </text>
     </comment>
-    <comment ref="F75" authorId="0" shapeId="0">
+    <comment ref="F75" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; estudio original publicado en una conferencia científica ACM KDD 2024, dentro del periodo 2020–2026, con texto completo disponible, aplicación explícita de Deep Learning y evaluación cuantitativa de detección de trayectorias vehiculares anómalas.</t>
       </text>
     </comment>
-    <comment ref="F76" authorId="0" shapeId="0">
+    <comment ref="F76" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; artículo original publicado en Scientific Reports, volumen 16, artículo 1516, año 2026, con texto completo Open Access. Aborda tráfico vehicular terrestre, utiliza aprendizaje profundo mediante atención multi-head y LSTM, y presenta evaluación cuantitativa de detección de anomalías e identificación de incidentes.</t>
       </text>
     </comment>
-    <comment ref="F77" authorId="0" shapeId="0">
+    <comment ref="F77" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; estudio original de conferencia científica IEEE ICDE 2023, dentro del periodo 2020–2026, con texto completo disponible. Analiza trayectorias reales de taxis sobre redes viales y propone un modelo de Deep Reinforcement Learning para detectar y localizar subtrayectorias anómalas en línea, con evaluación cuantitativa mediante F1 y TF1.</t>
       </text>
     </comment>
-    <comment ref="F78" authorId="0" shapeId="0">
+    <comment ref="F78" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; artículo científico original publicado en 2023, dentro del periodo 2020–2026, con texto completo accesible. Aborda detección explícita de trayectorias anómalas de vehículos terrestres mediante aprendizaje profundo recurrente y reporta resultados cuantitativos de detección sobre dos conjuntos de datos reales.</t>
       </text>
     </comment>
-    <comment ref="E79" authorId="1" shapeId="0">
+    <comment ref="E79" authorId="0" shapeId="0">
       <text>
         <t>Antes: Incluir
 Motivo: La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
       </text>
     </comment>
-    <comment ref="F79" authorId="0" shapeId="0">
+    <comment ref="F79" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; estudio original publicado en una conferencia ACM de 2024, con texto completo disponible. Desarrolla y evalúa una CNN para reconocer una conducta anómala de conducción, específicamente el uso del teléfono móvil, y la integra en un sistema de seguridad vehicular.</t>
       </text>
     </comment>
-    <comment ref="F80" authorId="0" shapeId="0">
+    <comment ref="F80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; artículo original de investigación publicado en Heliyon en 2025, dentro del periodo 2020–2026, con texto completo Open Access. Estudia explícitamente la detección de accidentes en tráfico vehicular terrestre mediante modelos de Deep Learning y presenta métricas cuantitativas de detección.</t>
       </text>
     </comment>
-    <comment ref="F81" authorId="0" shapeId="0">
+    <comment ref="F81" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; estudio original publicado en Transportation Research Procedia, volumen 85, páginas 68–75, en 2025, con revisión por pares y texto completo Open Access. Investiga explícitamente la detección de accidentes vehiculares terrestres mediante Deep Learning y presenta métricas cuantitativas de detección.</t>
       </text>
     </comment>
-    <comment ref="F82" authorId="0" shapeId="0">
+    <comment ref="F82" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; artículo original de revista científica publicado en Chinese Journal of Mechanical Engineering, volumen 39 (2026), artículo 100169, DOI 10.1016/j.cjme.2025.100169, con texto completo Open Access bajo licencia CC BY 4.0. Se encuentra dentro del periodo 2020–2026, estudia tráfico vehicular terrestre, desarrolla un modelo de Deep Learning y evalúa cuantitativamente la detección de comportamientos de conducción anómalos.</t>
       </text>
     </comment>
-    <comment ref="F83" authorId="0" shapeId="0">
+    <comment ref="F83" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CE-3 — El estudio no desarrolla ni evalúa cuantitativamente un método de detección de anomalías en tráfico vehicular. Su objetivo principal es la predicción no lineal del flujo de tráfico mediante una red LSTM de dos capas y una infraestructura IoT. Aunque menciona incidentes, condiciones anormales, valores atípicos y fallos de sensores, no presenta etiquetas de anomalías viales, una regla de clasificación de eventos anómalos ni métricas específicas de detección.</t>
       </text>
     </comment>
-    <comment ref="F84" authorId="0" shapeId="0">
+    <comment ref="F84" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — El estudio cumple los criterios de inclusión: artículo científico original de revista, publicado dentro del periodo 2020–2026, texto completo Open Access, tráfico vehicular terrestre, modelo basado en Deep Learning y evaluación cuantitativa explícita de detección de anomalías.</t>
       </text>
     </comment>
-    <comment ref="F85" authorId="0" shapeId="0">
+    <comment ref="F85" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Artículo original de conferencia ACM publicado en 2025, con texto completo Open Access; aborda incidentes de tráfico vehicular mediante Deep Learning y presenta evaluación cuantitativa de detección de accidentes.</t>
       </text>
     </comment>
-    <comment ref="F86" authorId="0" shapeId="0">
+    <comment ref="F86" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Estudio original publicado en Sensors en 2026, con revisión por pares y texto completo Open Access; desarrolla y evalúa cuantitativamente un modelo de Deep Learning para detectar accidentes y anomalías del tráfico vehicular mediante videos de vigilancia.</t>
       </text>
     </comment>
-    <comment ref="F87" authorId="0" shapeId="0">
+    <comment ref="F87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Artículo original de investigación publicado en revista científica, dentro del periodo 2020–2026, con texto completo Open Access; aborda explícitamente la detección de trayectorias anómalas y regiones de tráfico vehicular anormal mediante aprendizaje neuronal de representaciones de grafos.</t>
       </text>
     </comment>
-    <comment ref="F88" authorId="0" shapeId="0">
+    <comment ref="F88" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Estudio original publicado en revista científica revisada por pares en 2026, con texto completo Open Access, que aborda explícitamente la detección de comportamiento anómalo de conducción mediante redes neuronales profundas y reporta métricas cuantitativas de clasificación.</t>
       </text>
     </comment>
-    <comment ref="F89" authorId="0" shapeId="0">
+    <comment ref="F89" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Artículo original publicado en revista científica en 2026, con acceso abierto y aplicación explícita de Deep Learning a la detección y clasificación de incidentes de tráfico vehicular.</t>
       </text>
     </comment>
-    <comment ref="F90" authorId="0" shapeId="0">
+    <comment ref="F90" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Estudio original revisado por pares, publicado en IEEE Access en 2024, con texto completo accesible; desarrolla y evalúa un modelo de Deep Learning para detectar accidentes vehiculares mediante video.</t>
       </text>
     </comment>
-    <comment ref="F91" authorId="0" shapeId="0">
+    <comment ref="F91" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Artículo científico original publicado en Sensors en 2023, dentro del periodo 2020–2026, revisado por pares y disponible en acceso abierto. Aborda directamente la identificación de eventos extraordinarios del tráfico vehicular mediante redes neuronales profundas y presenta evaluación cuantitativa sobre imágenes reales de autopistas.</t>
       </text>
     </comment>
-    <comment ref="F92" authorId="0" shapeId="0">
+    <comment ref="F92" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Estudio original publicado en las actas de AAMAS 2023, dentro del periodo 2020–2026, con texto completo accesible gratuitamente. Investiga directamente la detección de anomalías en tráfico vehicular de autopista mediante Deep Learning y reporta resultados cuantitativos de detección.</t>
       </text>
     </comment>
-    <comment ref="F93" authorId="0" shapeId="0">
+    <comment ref="F93" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Artículo original publicado en Scientific Reports en 2026, dentro del periodo 2020–2026, con texto completo de acceso abierto. Presenta una arquitectura basada en redes neuronales convolucionales para detectar y clasificar anomalías en tráfico vehicular mediante videos de vigilancia aérea y ofrece evaluación cuantitativa.</t>
       </text>
     </comment>
-    <comment ref="F94" authorId="0" shapeId="0">
+    <comment ref="F94" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Artículo original de revista científica publicado en 2026, dentro del periodo de la revisión. Emplea Deep Learning y presenta una tarea explícita de detección de accidentes de tráfico con evaluación cuantitativa. El PDF completo está disponible para análisis.</t>
       </text>
     </comment>
-    <comment ref="F95" authorId="0" shapeId="0">
+    <comment ref="F95" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Estudio original publicado en IEEE Access en diciembre de 2023, dentro del periodo 2020–2026; artículo revisado por pares, con texto completo de acceso abierto, modelo de Deep Learning y evaluación cuantitativa explícita de detección de accidentes de tráfico.</t>
       </text>
     </comment>
-    <comment ref="F96" authorId="0" shapeId="0">
+    <comment ref="F96" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica: cumple los criterios de elegibilidad; es un artículo científico original publicado en Mathematics en 2023, con texto completo de acceso abierto, aplicación explícita de Deep Learning al tráfico vehicular terrestre y evaluación cuantitativa de la detección de accidentes.</t>
       </text>
     </comment>
-    <comment ref="F97" authorId="0" shapeId="0">
+    <comment ref="F97" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica: artículo original revisado por pares, publicado en Mathematics en 2023, con texto completo de acceso abierto, aplicación explícita de Deep Learning al tráfico vehicular terrestre y evaluación cuantitativa de detección de accidentes.</t>
       </text>
     </comment>
-    <comment ref="F99" authorId="0" shapeId="0">
+    <comment ref="F99" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica: cumple los criterios de inclusión. Es un artículo original de revista científica revisada por pares, aceptado en 2025 y publicado bajo copyright de 2026, con texto completo Open Access; estudia anomalías de tráfico vehicular en autopistas mediante Deep Learning y proporciona resultados cuantitativos de detección y localización.</t>
       </text>
     </comment>
-    <comment ref="F101" authorId="1" shapeId="0">
+    <comment ref="F101" authorId="0" shapeId="0">
       <text>
         <t>Antes: CE-3
 Motivo: Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
       </text>
     </comment>
-    <comment ref="F102" authorId="0" shapeId="0">
+    <comment ref="F102" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica: el estudio cumple los criterios de inclusión por tratarse de un artículo original revisado por pares, publicado en 2026, con texto completo Open Access, contexto de tráfico vehicular urbano, arquitectura de Deep Learning y evaluación cuantitativa de detección de anomalías.</t>
       </text>
     </comment>
-    <comment ref="F103" authorId="0" shapeId="0">
+    <comment ref="F103" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica: cumple los criterios de inclusión por ser un artículo científico original publicado en 2026, con texto completo Open Access, aplicación a anomalías visuales del tráfico vehicular, uso de redes neuronales profundas y evaluación cuantitativa.</t>
       </text>
     </comment>
-    <comment ref="F104" authorId="0" shapeId="0">
+    <comment ref="F104" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica: el estudio cumple los criterios de inclusión. Es un artículo científico original de IEEE Transactions on Intelligent Vehicles, publicado en 2023, con texto completo accesible gratuitamente, datos reales de tráfico vehicular, arquitectura de Deep Learning y evaluación explícita de detección de anomalías.</t>
       </text>
     </comment>
-    <comment ref="F105" authorId="0" shapeId="0">
+    <comment ref="F105" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica: cumple los criterios de inclusión por año (2024), publicación científica original, texto completo abierto, uso de Deep Learning y evaluación cuantitativa de accidentes de tráfico. Se incluye con advertencia de que UCF-Crime es un conjunto general de anomalías en videovigilancia y no exclusivamente de tráfico vehicular.</t>
@@ -4730,24 +4740,20 @@
           <t>cribado\pdf\R0029.pdf</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Excluir</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>CE-3</t>
-        </is>
-      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>No recuperado</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>three driving behaviors (normal, sleepy, and aggressive) on both highways and secondary roads (p. 3); "This section provides a comprehensive study of the proposed classification system for driving behavior." (p. 3)</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>[Excluir CE-3] Estudio comparativo de clasificación de perfiles de conducción mediante ML, DL y ensamble PSO; no presenta una tarea específica de detección o anticipación de anomalías vehiculares.</t>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>[No recuperado] Sin texto completo de acceso abierto.</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8624,31 +8630,31 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>R0167</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>REHACER</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>Paradigma no identificable («aprendizaje federado»): elegir una opción de la lista con el PDF (https://jcbi.org/index.php/Main/article/download/1147/825). Si el PDF ya no se puede obtener, poner DECISIÓN TC = «No recuperado».</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>R0025</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Partición «No reportada» en la hoja 2 pero QA2 = 1 en la hoja 3: revisa uno de los dos.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>R0025</t>
+          <t>R0051</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -8663,14 +8669,14 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Partición «No reportada» en la hoja 2 pero QA2 = 1 en la hoja 3: revisa uno de los dos.</t>
+          <t>Partición aleatoria (411/35/148) pero QA2 = 1: según la escala sería 0.5.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>R0029</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -8685,14 +8691,14 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Se excluyó por CE-3 (clasifica perfiles normal/somnoliento/agresivo), pero R0032 (UAH-DriveSet, mismas tres clases), R0360, R0428 y R1029 se incluyeron. Decide con el mismo criterio para todos.</t>
+          <t>Caso límite: el DL extrae y reconstruye trayectorias y la anomalía se decide con reglas. Se mantiene incluido (regla de híbridos de CI-5); va al anexo de casos límite.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>R0051</t>
+          <t>R0986</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -8707,124 +8713,124 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Partición aleatoria (411/35/148) pero QA2 = 1: según la escala sería 0.5.</t>
+          <t>El texto analizado corresponde a Systems and Soft Computing (DOI 10.1016/j.sasc.2025.200254), pero el registro tiene DOI 10.1002/spy2.70136: confirma que el PDF es el del registro.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0024</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Corregido «QA8 Limitaciones» → 0</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Caso límite: el DL extrae y reconstruye trayectorias y la anomalía se decide con reglas. Se mantiene incluido (regla de híbridos de CI-5); va al anexo de casos límite.</t>
+          <t>La hoja 2 dice «No reportadas»: la cita es trabajo futuro, no una limitación.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>R0986</t>
+          <t>R0024</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Corregido «QA8 evidencia» → No reportado (solo trabajo futuro, p. 10)</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>El texto analizado corresponde a Systems and Soft Computing (DOI 10.1016/j.sasc.2025.200254), pero el registro tiene DOI 10.1002/spy2.70136: confirma que el PDF es el del registro.</t>
+          <t>Coherente con la hoja 2.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>R0024</t>
+          <t>R0029</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Corregido «QA8 Limitaciones» → 0</t>
+          <t>Corregido «DECISIÓN TC» → No recuperado</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>La hoja 2 dice «No reportadas»: la cita es trabajo futuro, no una limitación.</t>
+          <t>El autor verificó que no hay texto completo en acceso abierto (la copia de SSRN no está disponible).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>R0024</t>
+          <t>R0029</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Corregido «QA8 evidencia» → No reportado (solo trabajo futuro, p. 10)</t>
+          <t>Corregido «CRITERIO» → None</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Coherente con la hoja 2.</t>
+          <t>No recuperado no lleva criterio.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>R0032</t>
+          <t>R0029</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Tipo de dato» → Multimodal</t>
+          <t>Corregido «Comentario» → [No recuperado] Sin texto completo de acceso abierto.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Acelerómetro, giroscopio y GPS del teléfono (UAH-DriveSet).</t>
+          <t>Coherente con las demás no recuperadas.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>R0052</t>
+          <t>R0032</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -8834,19 +8840,19 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Ambos</t>
+          <t>Corregido «Tipo de dato» → Multimodal</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Intersecciones y rampas/puentes de carretera.</t>
+          <t>Acelerómetro, giroscopio y GPS del teléfono (UAH-DriveSet).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>R0080</t>
+          <t>R0052</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -8856,19 +8862,19 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Entorno» → Ambos</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Incidentes distintos en entrenamiento (23) y prueba (22).</t>
+          <t>Intersecciones y rampas/puentes de carretera.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>R0097</t>
+          <t>R0080</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -8878,19 +8884,19 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Ubicación y tipo de vía no reportados.</t>
+          <t>Incidentes distintos en entrenamiento (23) y prueba (22).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>R0119</t>
+          <t>R0097</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -8900,12 +8906,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Ambos</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Intersecciones y autopistas.</t>
+          <t>Ubicación y tipo de vía no reportados.</t>
         </is>
       </c>
     </row>
@@ -8922,19 +8928,19 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Aleatoria</t>
+          <t>Corregido «Entorno» → Ambos</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Partición estratificada sin separación temporal.</t>
+          <t>Intersecciones y autopistas.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>R0121</t>
+          <t>R0119</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -8944,19 +8950,19 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Urbano</t>
+          <t>Corregido «Partición» → Aleatoria</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Dos cruces peatonales de calle (35 mph) en Florida.</t>
+          <t>Partición estratificada sin separación temporal.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>R0167</t>
+          <t>R0121</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -8966,19 +8972,19 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Entorno» → Urbano</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>«No se detallan particiones».</t>
+          <t>Dos cruces peatonales de calle (35 mph) en Florida.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>R0175</t>
+          <t>R0167</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -8988,19 +8994,19 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Paradigma» → No supervisado</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>No especifica el tipo de vía.</t>
+          <t>Releído el PDF: MGTGCN se entrena para predecir y reconstruir trayectorias (ADE/FDE, Tabla 1, p. 12), sin etiquetas de anomalía; las conductas anómalas se añaden después para evaluar: «adding a set of disruptive driving behaviors» (p. 12).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>R0185</t>
+          <t>R0167</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -9015,58 +9021,58 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>No describe la partición.</t>
+          <t>«No se detallan particiones».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>R0190</t>
+          <t>R0175</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-3</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
+          <t>No especifica el tipo de vía.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>R0192</t>
+          <t>R0185</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Releído el PDF: la detección solo se valida de forma visual (face validation); la única métrica cuantitativa (RMSE, Tabla 1) es de imputación.</t>
+          <t>No describe la partición.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>R0192</t>
+          <t>R0190</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -9076,12 +9082,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «CRITERIO» → CE-3</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Sin evaluación cuantitativa de la detección (igual que R0249 y R0389).</t>
+          <t>Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
         </is>
       </c>
     </row>
@@ -9098,12 +9104,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Corregido «EVIDENCIA (cita y página)» → "we employ a face validation approach. In this approach, we visually examine the pace time series of various zones" (p. 10, sección IV-E); "Table 1 presents the mean and standard deviation of RMSE across 10 trials of inference-phase imputation" (p. 9, sección IV-C).</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Cita del PDF.</t>
+          <t>Releído el PDF: la detección solo se valida de forma visual (face validation); la única métrica cuantitativa (RMSE, Tabla 1) es de imputación.</t>
         </is>
       </c>
     </row>
@@ -9120,19 +9126,19 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Comentario» → [Excluir CI-6] SI-DMSeq (encoder-decoder LSTM con atención, Manhattan, huracán Sandy y tormenta de 2010) detecta disrupciones con una carta de control sobre el error de reconstrucción, pero no las evalúa contra etiquetas: no hay precision, recall, F1, AUC ni tasa de detección; la única métrica numérica (RMSE) es de imputación.</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Motivo.</t>
+          <t>Sin evaluación cuantitativa de la detección (igual que R0249 y R0389).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>R0244</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -9142,19 +9148,19 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Incluir</t>
+          <t>Corregido «EVIDENCIA (cita y página)» → "we employ a face validation approach. In this approach, we visually examine the pace time series of various zones" (p. 10, sección IV-E); "Table 1 presents the mean and standard deviation of RMSE across 10 trials of inference-phase imputation" (p. 9, sección IV-C).</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>«INCLUIDO» no es una opción de la lista.</t>
+          <t>Cita del PDF.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>R0249</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -9164,41 +9170,41 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «Comentario» → [Excluir CI-6] SI-DMSeq (encoder-decoder LSTM con atención, Manhattan, huracán Sandy y tormenta de 2010) detecta disrupciones con una carta de control sobre el error de reconstrucción, pero no las evalúa contra etiquetas: no hay precision, recall, F1, AUC ni tasa de detección; la única métrica numérica (RMSE) es de imputación.</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
+          <t>Motivo.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>R0379</t>
+          <t>R0244</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «DECISIÓN TC» → Incluir</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Evalúa en una grabación highD no vista.</t>
+          <t>«INCLUIDO» no es una opción de la lista.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>R0389</t>
+          <t>R0249</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -9213,80 +9219,80 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
+          <t>Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>R0403</t>
+          <t>R0379</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Corregido «QA5 Código y datos» → 1</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Código con DOI (ETS) y datasets públicos (DAD, CCD, A3D): ambos públicos.</t>
+          <t>Evalúa en una grabación highD no vista.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>R0403</t>
+          <t>R0389</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Particiones oficiales de DAD y CCD.</t>
+          <t>Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>R0501</t>
+          <t>R0403</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Ambos</t>
+          <t>Corregido «QA5 Código y datos» → 1</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Vías urbanas e interurbanas.</t>
+          <t>Código con DOI (ETS) y datasets públicos (DAD, CCD, A3D): ambos públicos.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>R0501</t>
+          <t>R0403</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -9301,36 +9307,36 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Conjunto externo ECVD solo para prueba.</t>
+          <t>Particiones oficiales de DAD y CCD.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>R0528</t>
+          <t>R0501</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «Entorno» → Ambos</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
+          <t>Vías urbanas e interurbanas.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>R0537</t>
+          <t>R0501</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -9340,41 +9346,41 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Sin proporciones ni protocolo de separación.</t>
+          <t>Conjunto externo ECVD solo para prueba.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>R0596</t>
+          <t>R0528</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Partición insuficientemente reportada.</t>
+          <t>Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>R0598</t>
+          <t>R0537</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -9384,19 +9390,19 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Pista de pruebas; no es urbano ni autopista.</t>
+          <t>Sin proporciones ni protocolo de separación.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>R0601</t>
+          <t>R0596</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -9406,63 +9412,63 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba de AI City Challenge.</t>
+          <t>Partición insuficientemente reportada.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>R0604</t>
+          <t>R0598</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
+          <t>Pista de pruebas; no es urbano ni autopista.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>R0604</t>
+          <t>R0601</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-2</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina.</t>
+          <t>Conjunto de prueba de AI City Challenge.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>R0614</t>
+          <t>R0604</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -9472,63 +9478,63 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-3</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
+          <t>Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>R0658</t>
+          <t>R0604</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «CRITERIO» → CE-2</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Particiones oficiales de los benchmarks.</t>
+          <t>Monitoreo del conductor dentro de la cabina.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>R0664</t>
+          <t>R0614</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «CRITERIO» → CE-3</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Videos de prueba separados.</t>
+          <t>Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0658</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -9538,107 +9544,107 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>No detalla la partición.</t>
+          <t>Particiones oficiales de los benchmarks.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>R0929</t>
+          <t>R0664</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
+          <t>Videos de prueba separados.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>R0929</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-2</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina.</t>
+          <t>No detalla la partición.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>R0943</t>
+          <t>R0929</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Sin procedimiento de selección ni conjunto de prueba.</t>
+          <t>La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>R1000</t>
+          <t>R0929</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «CRITERIO» → CE-2</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>No indica qué escenas de NGSIM usa.</t>
+          <t>Monitoreo del conductor dentro de la cabina.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>R1010</t>
+          <t>R0943</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -9648,19 +9654,19 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Evaluado con autos de juguete en escenario controlado.</t>
+          <t>Sin procedimiento de selección ni conjunto de prueba.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>R1013</t>
+          <t>R1000</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -9670,19 +9676,19 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba oficial de TADS.</t>
+          <t>No indica qué escenas de NGSIM usa.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>R1014</t>
+          <t>R1010</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -9692,19 +9698,19 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Familia DL principal» → Otra</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>DeepWalk/Node2vec no es una GNN.</t>
+          <t>Evaluado con autos de juguete en escenario controlado.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>R1082</t>
+          <t>R1013</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -9719,14 +9725,14 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba de MAAD (con ajuste de hiperparámetros en parte de él).</t>
+          <t>Conjunto de prueba oficial de TADS.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>R1092</t>
+          <t>R1014</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -9736,19 +9742,19 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Aleatoria</t>
+          <t>Corregido «Familia DL principal» → Otra</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>División 80/20 de videos sin otro criterio.</t>
+          <t>DeepWalk/Node2vec no es una GNN.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>R1100</t>
+          <t>R1082</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -9758,19 +9764,19 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>DoTA/CCD sin clasificación por tipo de vía.</t>
+          <t>Conjunto de prueba de MAAD (con ajuste de hiperparámetros en parte de él).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>R1138</t>
+          <t>R1092</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -9780,19 +9786,19 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → Aleatoria</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>No desagrega urbano/autopista.</t>
+          <t>División 80/20 de videos sin otro criterio.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>R1148</t>
+          <t>R1100</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -9802,19 +9808,19 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Categoría de anomalía» → Evento/otro</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Objetos caídos sobre la calzada.</t>
+          <t>DoTA/CCD sin clasificación por tipo de vía.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>R1148</t>
+          <t>R1138</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -9824,41 +9830,41 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Solo dice que entrena y valida 100 épocas.</t>
+          <t>No desagrega urbano/autopista.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>R1166</t>
+          <t>R1148</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «Categoría de anomalía» → Evento/otro</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
+          <t>Objetos caídos sobre la calzada.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>R1185</t>
+          <t>R1148</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -9868,54 +9874,98 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>No clasifica las imágenes por tipo de vía.</t>
+          <t>Solo dice que entrena y valida 100 épocas.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>R1202</t>
+          <t>R1166</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Separación por sesiones de conducción.</t>
+          <t>Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
+          <t>R1185</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>No clasifica las imágenes por tipo de vía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>R1202</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Separación por sesiones de conducción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
           <t>R1214</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>No informa proporciones ni criterio de división.</t>
         </is>
@@ -12062,118 +12112,122 @@
       <c r="X20" s="4" t="n"/>
     </row>
     <row r="21" ht="43.2" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>R0167</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>A Personalized Federated Learning Framework for Post-Event Forensic Traffic Analysis in Autonomous Vehicle Systems</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>cribado\pdf\R0167.pdf</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Trayectorias GPS</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Urbano</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>No especificado; se utilizan datos simulados CARLA y subconjuntos Comma.ai distribuidos en 3 clientes federados; no se reportan cantidades de vehículos, trayectorias, registros ni instancias de anomalías</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Inyectadas/sintéticas</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Aprendizaje federado personalizado con entrenamiento local y agregación global; detección de anomalías mediante comportamientos anormales introducidos en los escenarios; no se especifica completamente el procedimiento de etiquetado ni el protocolo de partición</t>
         </is>
       </c>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>No supervisado</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Grafos (GNN)</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Personalized Lightweight Federated Learning (PLFL) con arquitectura MGTGCN; aprendizaje de trayectorias y detección de anomalías mediante fusión temporal y espacial; agregación federada personalizada según divergencia de modelos; Dynamic Model Pruning para reducir comunicación</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Comportamiento de conducción</t>
         </is>
       </c>
-      <c r="O21" s="9" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>Precision, Recall y ROC-AUC para detección de anomalías; Average Displacement Error (ADE) y Final Displacement Error (FDE) para reconstrucción de trayectorias; tamaño de actualizaciones en MB para comunicación</t>
         </is>
       </c>
-      <c r="P21" s="9" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>Precision=89.3%, Recall=84.7%, ROC-AUC=0.921; PLFL ADE=1.98 m y FDE=4.55 m; FedAvg ADE=2.35 m y FDE=5.70 m; reducción de comunicación aproximada del 28%</t>
         </is>
       </c>
-      <c r="Q21" s="9" t="inlineStr">
+      <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>Datos simulados CARLA con comportamientos de conducción, colisiones y anomalías de ruta; subconjuntos reales Comma.ai; tres clientes: urbano, intersecciones y autopista/suburbano; tamaño exacto del conjunto de datos no especificado</t>
         </is>
       </c>
-      <c r="R21" s="9" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>Construcción de grafos espaciotemporales con nodos correspondientes a ubicaciones o segmentos viales y aristas de conectividad; extracción de características de telemetría; proyección a 64 dimensiones; fusión TCN-GCN-GAT; agregación personalizada; poda dinámica de parámetros de baja magnitud</t>
         </is>
       </c>
-      <c r="S21" s="9" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>No reportada</t>
         </is>
       </c>
-      <c r="T21" s="9" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>Centralized MGTGCN; Federated Learning FedAvg; Personalized FL/PLFL; comparación con y sin Dynamic Model Pruning; no se presenta tabla cuantitativa de Precision, Recall y ROC-AUC por cada baseline</t>
         </is>
       </c>
-      <c r="U21" s="9" t="inlineStr">
+      <c r="U21" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="V21" s="9" t="inlineStr">
+      <c r="V21" s="5" t="inlineStr">
         <is>
           <t>PLFL mejora ADE frente a FedAvg de 2.35 m a 1.98 m y FDE de 5.70 m a 4.55 m; alcanza Precision=89.3%, Recall=84.7% y ROC-AUC=0.921 en anomalías; reduce tamaño de actualización de 22.5 MB a 16.1 MB; mejora adaptación a distribuciones heterogéneas entre clientes</t>
         </is>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="5" t="inlineStr">
         <is>
           <t>Enfoque forense posterior al evento sin evaluación en tiempo real; no se reportan tamaños exactos ni particiones de datasets; simulación CARLA con brecha respecto al mundo real; escasa representación de anomalías extremas; falta validación operacional a gran escala; no se evalúa resistencia a clientes maliciosos; inconsistencias entre tabla y figura de comunicación; no se proporciona código ni configuración experimental completa</t>
         </is>
       </c>
-      <c r="X21" s="9" t="inlineStr">
+      <c r="X21" s="5" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>

--- a/RSL/cribado/revision/REVISION_TEXTO_COMPLETO.xlsx
+++ b/RSL/cribado/revision/REVISION_TEXTO_COMPLETO.xlsx
@@ -222,16 +222,70 @@
 Motivo: Coherente con las demás no recuperadas.</t>
       </text>
     </comment>
+    <comment ref="E6" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Incluir
+Motivo: Perfilado del conductor por viaje (igual que R0321, R0660 y R1046, CE-3).</t>
+      </text>
+    </comment>
     <comment ref="F6" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica: cumple los criterios de inclusión por ser un artículo original de conferencia ACM publicado en 2026, con texto completo disponible, aplicación a conducción vehicular real, modelos de Deep Learning y evaluación cuantitativa de comportamientos de riesgo. Se incluye como clasificación supervisada de conducción normal, agresiva y somnolienta, no como detección no supervisada de anomalías desconocidas.</t>
       </text>
     </comment>
+    <comment ref="G6" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Página 1: título, autores, conferencia ICIIT 2026, DOI y licencia CC BY 4.0. Página 3, sección 3.1: UAH-DriveSet, más de 500 minutos, seis conductores, carreteras y vías secundarias, tres comportamientos. Página 3, sección 3.2: partición estratificada 70% entrenamiento, 15% validación y 15% prueba. Página 4, Figura 1: flujo de preprocesamiento, modelos ML/DL y ensamble metaheurístico. Página 5, Tabla 1: comparación de nueve modelos, con accuracy de 0.9989 para PSO Ensemble, 0.9983 para Attention
+Motivo: Hoja 1 y 2 del autor.</t>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Se incluye porque analiza comportamientos de conducción potencialmente anómalos mediante sensores de teléfonos inteligentes y arquitecturas profundas de clasificación temporal. Compara CatBoost, XGBoost, KNN y ExtraTrees con CNN 1D, BiLSTM, TCN y Attention-LSTM, y propone un ensamble de modelos optimizado mediante Particle Swarm Optimization. El mejor modelo alcanza accuracy global de 99.89% y recall de 95% para la clase minoritaria de somnolencia. No detecta accidentes ocurridos ni eventos anóm
+Motivo: Motivo.</t>
+      </text>
+    </comment>
     <comment ref="F7" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 —</t>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Incluir
+Motivo: Mismo modelo (MHGNN-CPLE), mismos autores y mismos datos que R0102; se conserva R0102 (Scientific Reports, versión más completa).</t>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: MHGNN-CPLE: detección estática Accuracy=0.980, F1=0.967, AUC=0.985 (p. 21, Tabla 5); detección dinámica de accidentes Accuracy=0.950, F1=0.945, AUC=0.970 (p. 22, Tabla 7); predicción dinámica de accidentes Accuracy=0.940, F1=0.935, AUC=0.965 (p. 23, Tabla 8); generalización METR-LA→PEMS-BAY Accuracy=0.945, F1=0.940 (p. 24, Tabla 9).
+Motivo: Hojas 1 y 2 del autor.</t>
+      </text>
+    </comment>
+    <comment ref="H12" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: [Incluir] Investigación original de 2025 sobre detección y predicción de anomalías vehiculares en autopistas mediante Deep Learning. Propone MHGNN-CPLE, integrando fusión multimodal, redes neuronales de grafos heterogéneos y optimización CPLE. Utiliza METR-LA y PEMS-BAY, con información de velocidad, flujo y densidad vehicular; también describe integración de imágenes y variables ambientales. Evalúa accidentes, congestión, tráfico normal y alteraciones meteorológicas. Compara con AGC-LSTM y Atte
+Motivo: Motivo.</t>
+      </text>
+    </comment>
+    <comment ref="E23" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Incluir
+Motivo: Clasifica niveles de riesgo de interacción, no eventos anómalos (igual que R0635, excluido por CE-3).</t>
+      </text>
+    </comment>
+    <comment ref="G23" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Seguimiento vehicular: Accuracy=83%, Precision=0.83, Recall=0.83, F1=0.83 (p. 6, Tabla 3). Cambio de carril: Accuracy=76%, Precision=0.75, Recall=0.76, F1=0.76 (p. 6, Tabla 4). Comparación: CNN=77%/67%, Bi-LSTM=80%/70%, GNN=61%/63% y CNN-LSTM-Attention=83%/76% de Accuracy en seguimiento/cambio de carril. Pruebas t pareadas y Wilcoxon con 10 ejecuciones independientes: p&lt;0.01 (p. 7). Evaluación de seguimiento con 3656 muestras de prueba (p. 7, Tabla 5). F1 de alto riesgo=0.87 en seguimiento y 0.7
+Motivo: Hoja 1 del autor.</t>
+      </text>
+    </comment>
+    <comment ref="H23" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: [Incluir] Investigación experimental original sobre identificación y predicción de estados anómalos de riesgo en conducción vehicular mediante Deep Learning. Propone CNN-LSTM-Attention con cuadrícula espacial 3×3 centrada en el vehículo, integración de Time-to-Collision (TTC) e Interaction Strength (IS), y clasificación dinámica de riesgo bajo, moderado y alto. Validación con trayectorias reales recolectadas en seis túneles de montaña de Chongqing, China. Obtiene Accuracy=83% en seguimiento vehi
+Motivo: Motivo.</t>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
@@ -504,10 +558,28 @@
 No aplica; cumple los criterios de inclusión por ser un artículo original de revista científica de 2025, con acceso abierto al texto completo, modelo basado en Deep Learning y evaluación cuantitativa de incidentes de tráfico vehicular.</t>
       </text>
     </comment>
+    <comment ref="E74" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Incluir
+Motivo: YOLOv5s/DeepSORT solo siguen vehículos; la anomalía se decide con umbrales manuales (igual que R0037, R0235 y R1213, excluidos por CE-4).</t>
+      </text>
+    </comment>
     <comment ref="F74" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica; artículo original de revista científica, publicado en 2024, con texto completo abierto y evaluación cuantitativa de comportamientos anómalos en autopistas mediante un sistema que incorpora redes profundas. La inclusión es condicionada a que el protocolo acepte Deep Learning para obtener y reconstruir trayectorias, aunque la decisión final de anomalía se base en reglas.</t>
+      </text>
+    </comment>
+    <comment ref="G74" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: El artículo presenta un sistema de vigilancia multicámara compuesto por YOLOv5s y DeepSORT para detección y seguimiento, una red de reidentificación vehicular con atributos y atención, y una BiLSTM para reconstruir trayectorias en zonas ciegas (secciones 3.1–3.3, pp. 5–11). La detección de anomalías utiliza reglas sobre dirección, velocidad, desplazamiento y pendiente de trayectoria, definidas en la Tabla 1 (p. 8) y sección 3.3.5 (pp. 10–11). Se evalúan conducción en sentido contrario, exceso de
+Motivo: Hoja 2 del autor.</t>
+      </text>
+    </comment>
+    <comment ref="H74" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: El estudio resulta pertinente para la revisión porque detecta anomalías de conducción vehicular en escenarios reales y utiliza Deep Learning como componente fundamental de la adquisición, asociación y reconstrucción de trayectorias. No obstante, la detección final se determina mediante umbrales manuales, por lo que sus resultados no demuestran el rendimiento de un clasificador profundo de anomalías. Las comparaciones con StRDAN, VAnet, PRND, SAVER y HPGN corresponden a reidentificación de vehícu
+Motivo: Motivo.</t>
       </text>
     </comment>
     <comment ref="F75" authorId="1" shapeId="0">
@@ -588,10 +660,28 @@
 No aplica — Estudio original publicado en Sensors en 2026, con revisión por pares y texto completo Open Access; desarrolla y evalúa cuantitativamente un modelo de Deep Learning para detectar accidentes y anomalías del tráfico vehicular mediante videos de vigilancia.</t>
       </text>
     </comment>
+    <comment ref="E87" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Incluir
+Motivo: DeepWalk/Node2vec no es Deep Learning; la anomalía la deciden SVDD y reglas.</t>
+      </text>
+    </comment>
     <comment ref="F87" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 No aplica — Artículo original de investigación publicado en revista científica, dentro del periodo 2020–2026, con texto completo Open Access; aborda explícitamente la detección de trayectorias anómalas y regiones de tráfico vehicular anormal mediante aprendizaje neuronal de representaciones de grafos.</t>
+      </text>
+    </comment>
+    <comment ref="G87" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Evidencia: Wang, Ye y Tang, Road traffic anomaly monitoring and warning based on DeepWalk algorithm, Transportation Safety and Environment, 2023, 5:tdac049, DOI 10.1093/tse/tdac049. La sección 2, p. 2, describe aproximadamente mil millones de puntos GPS correspondientes a 6083400 pedidos de taxis Didi en Chengdu durante noviembre de 2016. La sección 4.1, p. 6, informa una base procesada de aproximadamente 4160000 trayectorias, de las cuales 2 % son anómalas. La sección 3.2, pp. 4–5, describe Dee
+Motivo: Hoja 2 del autor.</t>
+      </text>
+    </comment>
+    <comment ref="H87" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Se incluye por su pertinencia directa para la detección de anomalías en tráfico vehicular mediante Deep Learning. El modelo aprende representaciones de la red vial a partir de trayectorias GPS reales y las utiliza en un sistema de detección y alerta de anomalías regionales. La contribución principal es combinar DeepWalk/Node2vec con SVDD y Apriori para identificar trayectorias anómalas, localizar regiones afectadas y estimar su propagación. La evaluación utiliza datos reales de Chengdu y un comp
+Motivo: Motivo.</t>
       </text>
     </comment>
     <comment ref="F88" authorId="1" shapeId="0">
@@ -4778,20 +4868,24 @@
           <t>cribado\pdf\R0032.pdf</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Incluir</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Página 1: título, autores, conferencia ICIIT 2026, DOI y licencia CC BY 4.0. Página 3, sección 3.1: UAH-DriveSet, más de 500 minutos, seis conductores, carreteras y vías secundarias, tres comportamientos. Página 3, sección 3.2: partición estratificada 70% entrenamiento, 15% validación y 15% prueba. Página 4, Figura 1: flujo de preprocesamiento, modelos ML/DL y ensamble metaheurístico. Página 5, Tabla 1: comparación de nueve modelos, con accuracy de 0.9989 para PSO Ensemble, 0.9983 para Attention-LSTM y 0.9967 para TCN. Página 5, Figura 2: curvas ROC. Página 6: conclusiones y discusión del rendimiento.</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>Se incluye porque analiza comportamientos de conducción potencialmente anómalos mediante sensores de teléfonos inteligentes y arquitecturas profundas de clasificación temporal. Compara CatBoost, XGBoost, KNN y ExtraTrees con CNN 1D, BiLSTM, TCN y Attention-LSTM, y propone un ensamble de modelos optimizado mediante Particle Swarm Optimization. El mejor modelo alcanza accuracy global de 99.89% y recall de 95% para la clase minoritaria de somnolencia. No detecta accidentes ocurridos ni eventos anómalos desconocidos: reconoce tres clases previamente definidas de estilo de conducción. Se identifican riesgos metodológicos importantes: solo seis conductores; agrupación de sus datos antes de la partición; ausencia de evaluación independiente por conductor; aplicación de SMOTE y preprocesamiento sin precisar su ajuste exclusivo sobre entrenamiento; resultados prácticamente perfectos en varios modelos; y falta de experimentos repetidos o validación externa. El propio artículo advierte posibles problemas de particionamiento en modelos temporales. Estos factores deben considerarse al interpretar la precisión y al comparar el estudio con métodos de detección de anomalías en tráfico vial.</t>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Excluir</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>CE-3</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>UAH-DriveSet, seis conductores, tres comportamientos (normal, somnoliento y agresivo); clasificación supervisada en una de las tres categorías (p. 3, secciones 3.1-3.2).</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-3] Compara ML, DL y un ensamble PSO para perfilar al conductor (normal/somnoliento/agresivo); no detecta eventos anómalos del tráfico.</t>
         </is>
       </c>
     </row>
@@ -5006,20 +5100,24 @@
           <t>cribado\pdf\R0072.pdf</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Incluir</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>MHGNN-CPLE: detección estática Accuracy=0.980, F1=0.967, AUC=0.985 (p. 21, Tabla 5); detección dinámica de accidentes Accuracy=0.950, F1=0.945, AUC=0.970 (p. 22, Tabla 7); predicción dinámica de accidentes Accuracy=0.940, F1=0.935, AUC=0.965 (p. 23, Tabla 8); generalización METR-LA→PEMS-BAY Accuracy=0.945, F1=0.940 (p. 24, Tabla 9).</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>[Incluir] Investigación original de 2025 sobre detección y predicción de anomalías vehiculares en autopistas mediante Deep Learning. Propone MHGNN-CPLE, integrando fusión multimodal, redes neuronales de grafos heterogéneos y optimización CPLE. Utiliza METR-LA y PEMS-BAY, con información de velocidad, flujo y densidad vehicular; también describe integración de imágenes y variables ambientales. Evalúa accidentes, congestión, tráfico normal y alteraciones meteorológicas. Compara con AGC-LSTM y AttentionDeepST; incluye pruebas de robustez, ablación y generalización entre conjuntos de datos. Limitaciones: documentación insuficiente sobre el origen de todas las modalidades, inconsistencias en la descripción de las particiones y falta de validación de despliegue en tiempo real.</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Excluir</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>CE-1</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Propone MHGNN-CPLE evaluado en METR-LA y PEMS-BAY con generalización METR-LA→PEMS-BAY (pp. 21-23, Tablas 5, 7 y 8); R0102 (Duan, Sun y Liu, 2025) presenta el mismo marco con las mismas bases.</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-1] Publicación paralela de R0102 (Sun y Liu, 2025); se incluye R0102 para no contar dos veces el mismo modelo.</t>
         </is>
       </c>
     </row>
@@ -5412,20 +5510,24 @@
           <t>cribado\pdf\R0185.pdf</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Incluir</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Seguimiento vehicular: Accuracy=83%, Precision=0.83, Recall=0.83, F1=0.83 (p. 6, Tabla 3). Cambio de carril: Accuracy=76%, Precision=0.75, Recall=0.76, F1=0.76 (p. 6, Tabla 4). Comparación: CNN=77%/67%, Bi-LSTM=80%/70%, GNN=61%/63% y CNN-LSTM-Attention=83%/76% de Accuracy en seguimiento/cambio de carril. Pruebas t pareadas y Wilcoxon con 10 ejecuciones independientes: p&lt;0.01 (p. 7). Evaluación de seguimiento con 3656 muestras de prueba (p. 7, Tabla 5). F1 de alto riesgo=0.87 en seguimiento y 0.79 en cambio de carril (pp. 7-8, Tablas 5-6).</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>[Incluir] Investigación experimental original sobre identificación y predicción de estados anómalos de riesgo en conducción vehicular mediante Deep Learning. Propone CNN-LSTM-Attention con cuadrícula espacial 3×3 centrada en el vehículo, integración de Time-to-Collision (TTC) e Interaction Strength (IS), y clasificación dinámica de riesgo bajo, moderado y alto. Validación con trayectorias reales recolectadas en seis túneles de montaña de Chongqing, China. Obtiene Accuracy=83% en seguimiento vehicular y 76% en cambio de carril, superando CNN, Bi-LSTM y GNN. PDF completo disponible con licencia CC BY 4.0. Limitaciones: datos restringidos a túneles de Chongqing, partición de entrenamiento/prueba insuficientemente documentada, ausencia de evaluación externa y falta de disponibilidad pública explícita del dataset. Predice estados de riesgo, no accidentes observados.</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Excluir</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>CE-3</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Clasificación del riesgo de seguimiento y cambio de carril en niveles bajo, moderado y alto: Accuracy 83 % y 76 % (p. 6, Tablas 3 y 4).</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-3] CNN-LSTM-Attention estima el nivel de riesgo de las interacciones en túneles; no detecta ni anticipa eventos anómalos.</t>
         </is>
       </c>
     </row>
@@ -7378,20 +7480,24 @@
           <t>cribado\pdf\R0666.pdf</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>Incluir</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>El artículo presenta un sistema de vigilancia multicámara compuesto por YOLOv5s y DeepSORT para detección y seguimiento, una red de reidentificación vehicular con atributos y atención, y una BiLSTM para reconstruir trayectorias en zonas ciegas (secciones 3.1–3.3, pp. 5–11). La detección de anomalías utiliza reglas sobre dirección, velocidad, desplazamiento y pendiente de trayectoria, definidas en la Tabla 1 (p. 8) y sección 3.3.5 (pp. 10–11). Se evalúan conducción en sentido contrario, exceso de velocidad, velocidad baja, estacionamiento y cambios peligrosos de carril mediante conteos de aciertos, omisiones y falsas detecciones en las Tablas 3–7 (pp. 16–17). El conjunto de reidentificación incluye 100 vehículos registrados en la autopista de circunvalación de Xi’an (p. 14).</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>El estudio resulta pertinente para la revisión porque detecta anomalías de conducción vehicular en escenarios reales y utiliza Deep Learning como componente fundamental de la adquisición, asociación y reconstrucción de trayectorias. No obstante, la detección final se determina mediante umbrales manuales, por lo que sus resultados no demuestran el rendimiento de un clasificador profundo de anomalías. Las comparaciones con StRDAN, VAnet, PRND, SAVER y HPGN corresponden a reidentificación de vehículos y no a detección de comportamientos anómalos. La evaluación de anomalías presenta conteos cuantitativos, pero no un contraste directo con detectores alternativos ni validación independiente de las etiquetas. Se recomienda incluirlo como arquitectura híbrida de procesamiento profundo y decisión basada en reglas, señalando expresamente esta característica en la síntesis metodológica.</t>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Excluir</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>CE-4</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Reglas explícitas: sentido contrario si Num/f ≥ 0,2; velocidad anómala si la media de 10 fotogramas supera n o baja de m; estacionamiento si la posición no cambia en cinco fotogramas (sección 3.3.5, pp. 10-11; Tabla 1, p. 8).</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-4] El DL detecta, sigue y reidentifica vehículos; los comportamientos peligrosos se deciden con umbrales manuales.</t>
         </is>
       </c>
     </row>
@@ -7880,20 +7986,24 @@
           <t>cribado\pdf\R1014.pdf</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>Incluir</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="n"/>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>Evidencia: Wang, Ye y Tang, Road traffic anomaly monitoring and warning based on DeepWalk algorithm, Transportation Safety and Environment, 2023, 5:tdac049, DOI 10.1093/tse/tdac049. La sección 2, p. 2, describe aproximadamente mil millones de puntos GPS correspondientes a 6083400 pedidos de taxis Didi en Chengdu durante noviembre de 2016. La sección 4.1, p. 6, informa una base procesada de aproximadamente 4160000 trayectorias, de las cuales 2 % son anómalas. La sección 3.2, pp. 4–5, describe DeepWalk con caminatas aleatorias y aprendizaje neuronal Skip-Gram, su extensión mediante Node2vec, la delimitación de regiones anómalas con SVDD y la predicción de propagación mediante Apriori. La Tabla 4, p. 7, reporta TAD 89,18 % y TAP 24,97 % frente al baseline SDA de 77,86 % y 22,25 %, respectivamente.</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>Se incluye por su pertinencia directa para la detección de anomalías en tráfico vehicular mediante Deep Learning. El modelo aprende representaciones de la red vial a partir de trayectorias GPS reales y las utiliza en un sistema de detección y alerta de anomalías regionales. La contribución principal es combinar DeepWalk/Node2vec con SVDD y Apriori para identificar trayectorias anómalas, localizar regiones afectadas y estimar su propagación. La evaluación utiliza datos reales de Chengdu y un comparador estadístico no profundo. Como limitaciones metodológicas para la revisión, la decisión final de región anómala se apoya en SVDD, la procedencia de las etiquetas no se documenta exhaustivamente, la partición entrenamiento/prueba no está suficientemente especificada y las métricas TAD/TAP presentan definiciones poco transparentes respecto de los indicadores estándar de clasificación. Se recomienda incluirlo, pero interpretar sus porcentajes como métricas propias del artículo y no como precision, recall o F1.</t>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>Excluir</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>CE-4</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>DeepWalk genera caminatas aleatorias y aprende embeddings con Skip-Gram; SVDD determina las regiones anómalas (sección 3, pp. 3-5); umbral de coincidencia de trayectorias anómalas 0,463 (sección 4.2, p. 6).</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-4] El detector es DeepWalk/Node2vec (embedding superficial, no DL) más SVDD, Apriori y umbrales.</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8676,7 +8786,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0986</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -8691,29 +8801,29 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Caso límite: el DL extrae y reconstruye trayectorias y la anomalía se decide con reglas. Se mantiene incluido (regla de híbridos de CI-5); va al anexo de casos límite.</t>
+          <t>El texto analizado corresponde a Systems and Soft Computing (DOI 10.1016/j.sasc.2025.200254), pero el registro tiene DOI 10.1002/spy2.70136: confirma que el PDF es el del registro.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>R0986</t>
+          <t>R0024</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Corregido «QA8 Limitaciones» → 0</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>El texto analizado corresponde a Systems and Soft Computing (DOI 10.1016/j.sasc.2025.200254), pero el registro tiene DOI 10.1002/spy2.70136: confirma que el PDF es el del registro.</t>
+          <t>La hoja 2 dice «No reportadas»: la cita es trabajo futuro, no una limitación.</t>
         </is>
       </c>
     </row>
@@ -8730,34 +8840,34 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Corregido «QA8 Limitaciones» → 0</t>
+          <t>Corregido «QA8 evidencia» → No reportado (solo trabajo futuro, p. 10)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>La hoja 2 dice «No reportadas»: la cita es trabajo futuro, no una limitación.</t>
+          <t>Coherente con la hoja 2.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>R0024</t>
+          <t>R0029</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Corregido «QA8 evidencia» → No reportado (solo trabajo futuro, p. 10)</t>
+          <t>Corregido «DECISIÓN TC» → No recuperado</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Coherente con la hoja 2.</t>
+          <t>El autor verificó que no hay texto completo en acceso abierto (la copia de SSRN no está disponible).</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8884,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → No recuperado</t>
+          <t>Corregido «CRITERIO» → None</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>El autor verificó que no hay texto completo en acceso abierto (la copia de SSRN no está disponible).</t>
+          <t>No recuperado no lleva criterio.</t>
         </is>
       </c>
     </row>
@@ -8796,34 +8906,34 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → None</t>
+          <t>Corregido «Comentario» → [No recuperado] Sin texto completo de acceso abierto.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>No recuperado no lleva criterio.</t>
+          <t>Coherente con las demás no recuperadas.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>R0029</t>
+          <t>R0032</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Comentario» → [No recuperado] Sin texto completo de acceso abierto.</t>
+          <t>Corregido «Tipo de dato» → Multimodal</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Coherente con las demás no recuperadas.</t>
+          <t>Acelerómetro, giroscopio y GPS del teléfono (UAH-DriveSet).</t>
         </is>
       </c>
     </row>
@@ -8835,90 +8945,90 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Tipo de dato» → Multimodal</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Acelerómetro, giroscopio y GPS del teléfono (UAH-DriveSet).</t>
+          <t>Perfilado del conductor por viaje (igual que R0321, R0660 y R1046, CE-3).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>R0052</t>
+          <t>R0032</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Ambos</t>
+          <t>Corregido «CRITERIO» → CE-3</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Intersecciones y rampas/puentes de carretera.</t>
+          <t>Clasifica estilos/perfiles de conducción, no anomalías del tráfico.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>R0080</t>
+          <t>R0032</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «EVIDENCIA (cita y página)» → UAH-DriveSet, seis conductores, tres comportamientos (normal, somnoliento y agresivo); clasificación supervisada en una de las tres categorías (p. 3, secciones 3.1-3.2).</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Incidentes distintos en entrenamiento (23) y prueba (22).</t>
+          <t>Hoja 1 y 2 del autor.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>R0097</t>
+          <t>R0032</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Comentario» → [Excluir CE-3] Compara ML, DL y un ensamble PSO para perfilar al conductor (normal/somnoliento/agresivo); no detecta eventos anómalos del tráfico.</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Ubicación y tipo de vía no reportados.</t>
+          <t>Motivo.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>R0119</t>
+          <t>R0052</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -8933,102 +9043,102 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Intersecciones y autopistas.</t>
+          <t>Intersecciones y rampas/puentes de carretera.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>R0119</t>
+          <t>R0072</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Aleatoria</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Partición estratificada sin separación temporal.</t>
+          <t>Mismo modelo (MHGNN-CPLE), mismos autores y mismos datos que R0102; se conserva R0102 (Scientific Reports, versión más completa).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>R0121</t>
+          <t>R0072</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Urbano</t>
+          <t>Corregido «CRITERIO» → CE-1</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Dos cruces peatonales de calle (35 mph) en Florida.</t>
+          <t>Versión menos completa del mismo estudio.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>R0167</t>
+          <t>R0072</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Paradigma» → No supervisado</t>
+          <t>Corregido «EVIDENCIA (cita y página)» → Propone MHGNN-CPLE evaluado en METR-LA y PEMS-BAY con generalización METR-LA→PEMS-BAY (pp. 21-23, Tablas 5, 7 y 8); R0102 (Duan, Sun y Liu, 2025) presenta el mismo marco con las mismas bases.</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Releído el PDF: MGTGCN se entrena para predecir y reconstruir trayectorias (ADE/FDE, Tabla 1, p. 12), sin etiquetas de anomalía; las conductas anómalas se añaden después para evaluar: «adding a set of disruptive driving behaviors» (p. 12).</t>
+          <t>Hojas 1 y 2 del autor.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>R0167</t>
+          <t>R0072</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Comentario» → [Excluir CE-1] Publicación paralela de R0102 (Sun y Liu, 2025); se incluye R0102 para no contar dos veces el mismo modelo.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>«No se detallan particiones».</t>
+          <t>Motivo.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>R0175</t>
+          <t>R0080</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -9038,19 +9148,19 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>No especifica el tipo de vía.</t>
+          <t>Incidentes distintos en entrenamiento (23) y prueba (22).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>R0185</t>
+          <t>R0097</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -9060,151 +9170,151 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>No describe la partición.</t>
+          <t>Ubicación y tipo de vía no reportados.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>R0190</t>
+          <t>R0119</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-3</t>
+          <t>Corregido «Entorno» → Ambos</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
+          <t>Intersecciones y autopistas.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>R0192</t>
+          <t>R0119</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «Partición» → Aleatoria</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Releído el PDF: la detección solo se valida de forma visual (face validation); la única métrica cuantitativa (RMSE, Tabla 1) es de imputación.</t>
+          <t>Partición estratificada sin separación temporal.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>R0192</t>
+          <t>R0121</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «Entorno» → Urbano</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Sin evaluación cuantitativa de la detección (igual que R0249 y R0389).</t>
+          <t>Dos cruces peatonales de calle (35 mph) en Florida.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>R0192</t>
+          <t>R0167</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Corregido «EVIDENCIA (cita y página)» → "we employ a face validation approach. In this approach, we visually examine the pace time series of various zones" (p. 10, sección IV-E); "Table 1 presents the mean and standard deviation of RMSE across 10 trials of inference-phase imputation" (p. 9, sección IV-C).</t>
+          <t>Corregido «Paradigma» → No supervisado</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Cita del PDF.</t>
+          <t>Releído el PDF: MGTGCN se entrena para predecir y reconstruir trayectorias (ADE/FDE, Tabla 1, p. 12), sin etiquetas de anomalía; las conductas anómalas se añaden después para evaluar: «adding a set of disruptive driving behaviors» (p. 12).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>R0192</t>
+          <t>R0167</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Comentario» → [Excluir CI-6] SI-DMSeq (encoder-decoder LSTM con atención, Manhattan, huracán Sandy y tormenta de 2010) detecta disrupciones con una carta de control sobre el error de reconstrucción, pero no las evalúa contra etiquetas: no hay precision, recall, F1, AUC ni tasa de detección; la única métrica numérica (RMSE) es de imputación.</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Motivo.</t>
+          <t>«No se detallan particiones».</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>R0244</t>
+          <t>R0175</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Incluir</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>«INCLUIDO» no es una opción de la lista.</t>
+          <t>No especifica el tipo de vía.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>R0249</t>
+          <t>R0185</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -9214,41 +9324,41 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
+          <t>Clasifica niveles de riesgo de interacción, no eventos anómalos (igual que R0635, excluido por CE-3).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>R0379</t>
+          <t>R0185</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «CRITERIO» → CE-3</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Evalúa en una grabación highD no vista.</t>
+          <t>Estimación de riesgo, sin detección de anomalías.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>R0389</t>
+          <t>R0185</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -9258,41 +9368,41 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «EVIDENCIA (cita y página)» → Clasificación del riesgo de seguimiento y cambio de carril en niveles bajo, moderado y alto: Accuracy 83 % y 76 % (p. 6, Tablas 3 y 4).</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
+          <t>Hoja 1 del autor.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>R0403</t>
+          <t>R0185</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Corregido «QA5 Código y datos» → 1</t>
+          <t>Corregido «Comentario» → [Excluir CE-3] CNN-LSTM-Attention estima el nivel de riesgo de las interacciones en túneles; no detecta ni anticipa eventos anómalos.</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Código con DOI (ETS) y datasets públicos (DAD, CCD, A3D): ambos públicos.</t>
+          <t>Motivo.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>R0403</t>
+          <t>R0185</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -9302,63 +9412,63 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Particiones oficiales de DAD y CCD.</t>
+          <t>No describe la partición.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>R0501</t>
+          <t>R0190</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Ambos</t>
+          <t>Corregido «CRITERIO» → CE-3</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Vías urbanas e interurbanas.</t>
+          <t>Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>R0501</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Conjunto externo ECVD solo para prueba.</t>
+          <t>Releído el PDF: la detección solo se valida de forma visual (face validation); la única métrica cuantitativa (RMSE, Tabla 1) es de imputación.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>R0528</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -9373,124 +9483,124 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
+          <t>Sin evaluación cuantitativa de la detección (igual que R0249 y R0389).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>R0537</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «EVIDENCIA (cita y página)» → "we employ a face validation approach. In this approach, we visually examine the pace time series of various zones" (p. 10, sección IV-E); "Table 1 presents the mean and standard deviation of RMSE across 10 trials of inference-phase imputation" (p. 9, sección IV-C).</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Sin proporciones ni protocolo de separación.</t>
+          <t>Cita del PDF.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>R0596</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Comentario» → [Excluir CI-6] SI-DMSeq (encoder-decoder LSTM con atención, Manhattan, huracán Sandy y tormenta de 2010) detecta disrupciones con una carta de control sobre el error de reconstrucción, pero no las evalúa contra etiquetas: no hay precision, recall, F1, AUC ni tasa de detección; la única métrica numérica (RMSE) es de imputación.</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Partición insuficientemente reportada.</t>
+          <t>Motivo.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>R0598</t>
+          <t>R0244</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «DECISIÓN TC» → Incluir</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Pista de pruebas; no es urbano ni autopista.</t>
+          <t>«INCLUIDO» no es una opción de la lista.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>R0601</t>
+          <t>R0249</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba de AI City Challenge.</t>
+          <t>Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>R0604</t>
+          <t>R0379</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
+          <t>Evalúa en una grabación highD no vista.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>R0604</t>
+          <t>R0389</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -9500,41 +9610,41 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-2</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina.</t>
+          <t>Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>R0614</t>
+          <t>R0403</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-3</t>
+          <t>Corregido «QA5 Código y datos» → 1</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
+          <t>Código con DOI (ETS) y datasets públicos (DAD, CCD, A3D): ambos públicos.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>R0658</t>
+          <t>R0403</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -9549,14 +9659,14 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Particiones oficiales de los benchmarks.</t>
+          <t>Particiones oficiales de DAD y CCD.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>R0664</t>
+          <t>R0501</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -9566,19 +9676,19 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Entorno» → Ambos</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Videos de prueba separados.</t>
+          <t>Vías urbanas e interurbanas.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0501</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -9588,19 +9698,19 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>No detalla la partición.</t>
+          <t>Conjunto externo ECVD solo para prueba.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>R0929</t>
+          <t>R0528</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -9610,41 +9720,41 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
+          <t>Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>R0929</t>
+          <t>R0537</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-2</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina.</t>
+          <t>Sin proporciones ni protocolo de separación.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>R0943</t>
+          <t>R0596</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -9659,14 +9769,14 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Sin procedimiento de selección ni conjunto de prueba.</t>
+          <t>Partición insuficientemente reportada.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>R1000</t>
+          <t>R0598</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -9681,14 +9791,14 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>No indica qué escenas de NGSIM usa.</t>
+          <t>Pista de pruebas; no es urbano ni autopista.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>R1010</t>
+          <t>R0601</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -9698,85 +9808,85 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Evaluado con autos de juguete en escenario controlado.</t>
+          <t>Conjunto de prueba de AI City Challenge.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>R1013</t>
+          <t>R0604</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba oficial de TADS.</t>
+          <t>Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>R1014</t>
+          <t>R0604</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Familia DL principal» → Otra</t>
+          <t>Corregido «CRITERIO» → CE-2</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>DeepWalk/Node2vec no es una GNN.</t>
+          <t>Monitoreo del conductor dentro de la cabina.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>R1082</t>
+          <t>R0614</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «CRITERIO» → CE-3</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba de MAAD (con ajuste de hiperparámetros en parte de él).</t>
+          <t>Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>R1092</t>
+          <t>R0658</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -9786,19 +9896,19 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Aleatoria</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>División 80/20 de videos sin otro criterio.</t>
+          <t>Particiones oficiales de los benchmarks.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>R1100</t>
+          <t>R0664</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -9808,85 +9918,85 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>DoTA/CCD sin clasificación por tipo de vía.</t>
+          <t>Videos de prueba separados.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>R1138</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>No desagrega urbano/autopista.</t>
+          <t>YOLOv5s/DeepSORT solo siguen vehículos; la anomalía se decide con umbrales manuales (igual que R0037, R0235 y R1213, excluidos por CE-4).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>R1148</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Categoría de anomalía» → Evento/otro</t>
+          <t>Corregido «CRITERIO» → CE-4</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Objetos caídos sobre la calzada.</t>
+          <t>La decisión de anomalía no la toma una red profunda.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>R1148</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «EVIDENCIA (cita y página)» → Reglas explícitas: sentido contrario si Num/f ≥ 0,2; velocidad anómala si la media de 10 fotogramas supera n o baja de m; estacionamiento si la posición no cambia en cinco fotogramas (sección 3.3.5, pp. 10-11; Tabla 1, p. 8).</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Solo dice que entrena y valida 100 épocas.</t>
+          <t>Hoja 2 del autor.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>R1166</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -9896,19 +10006,19 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «Comentario» → [Excluir CE-4] El DL detecta, sigue y reidentifica vehículos; los comportamientos peligrosos se deciden con umbrales manuales.</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
+          <t>Motivo.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>R1185</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -9918,54 +10028,472 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>No clasifica las imágenes por tipo de vía.</t>
+          <t>No detalla la partición.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>R1202</t>
+          <t>R0929</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Separación por sesiones de conducción.</t>
+          <t>La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
+          <t>R0929</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CE-2</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Monitoreo del conductor dentro de la cabina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>R0943</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Sin procedimiento de selección ni conjunto de prueba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>R1000</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>No indica qué escenas de NGSIM usa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>R1010</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Evaluado con autos de juguete en escenario controlado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>R1013</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto de prueba oficial de TADS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>R1014</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>DeepWalk/Node2vec no es Deep Learning; la anomalía la deciden SVDD y reglas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>R1014</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CE-4</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Sin componente profunda entrenada que decida la anomalía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>R1014</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «EVIDENCIA (cita y página)» → DeepWalk genera caminatas aleatorias y aprende embeddings con Skip-Gram; SVDD determina las regiones anómalas (sección 3, pp. 3-5); umbral de coincidencia de trayectorias anómalas 0,463 (sección 4.2, p. 6).</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Hoja 2 del autor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>R1014</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Comentario» → [Excluir CE-4] El detector es DeepWalk/Node2vec (embedding superficial, no DL) más SVDD, Apriori y umbrales.</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Motivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>R1014</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Familia DL principal» → Otra</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>DeepWalk/Node2vec no es una GNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>R1082</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto de prueba de MAAD (con ajuste de hiperparámetros en parte de él).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>R1092</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Aleatoria</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>División 80/20 de videos sin otro criterio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>R1100</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>DoTA/CCD sin clasificación por tipo de vía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>R1138</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>No desagrega urbano/autopista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>R1148</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Categoría de anomalía» → Evento/otro</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Objetos caídos sobre la calzada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>R1148</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Solo dice que entrena y valida 100 épocas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>R1166</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CI-6</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>R1185</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>No clasifica las imágenes por tipo de vía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>R1202</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Separación por sesiones de conducción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
           <t>R1214</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>No informa proporciones ni criterio de división.</t>
         </is>

--- a/RSL/cribado/revision/REVISION_TEXTO_COMPLETO.xlsx
+++ b/RSL/cribado/revision/REVISION_TEXTO_COMPLETO.xlsx
@@ -266,7 +266,7 @@
     </comment>
     <comment ref="H12" authorId="0" shapeId="0">
       <text>
-        <t>Antes: [Incluir] Investigación original de 2025 sobre detección y predicción de anomalías vehiculares en autopistas mediante Deep Learning. Propone MHGNN-CPLE, integrando fusión multimodal, redes neuronales de grafos heterogéneos y optimización CPLE. Utiliza METR-LA y PEMS-BAY, con información de velocidad, flujo y densidad vehicular; también describe integración de imágenes y variables ambientales. Evalúa accidentes, congestión, tráfico normal y alteraciones meteorológicas. Compara con AGC-LSTM y Atte
+        <t>Antes: [Excluir CE-1] Publicación paralela de R0102 (Sun y Liu, 2025); se incluye R0102 para no contar dos veces el mismo modelo.
 Motivo: Motivo.</t>
       </text>
     </comment>
@@ -294,6 +294,12 @@
 Motivo: Es tráfico vehicular (no CE-2): solo pronostica el flujo con MAE, no detecta anomalías.</t>
       </text>
     </comment>
+    <comment ref="H24" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: [Excluir - CE-2] El artículo aborda predicción de flujo vehicular mediante Deep LSTM y Mixture Deep LSTM utilizando datos simulados de tráfico y meteorología. Aunque incorpora escenarios posteriores a accidentes y condiciones de tráfico no habituales, los accidentes se consideran condiciones conocidas para pronosticar el flujo posterior, no eventos que el modelo deba detectar o clasificar. La variable de salida es el flujo vehicular previsto y la evaluación principal utiliza MAE. No se desarroll
+Motivo: Coherente con CE-3.</t>
+      </text>
+    </comment>
     <comment ref="E25" authorId="0" shapeId="0">
       <text>
         <t>Antes: Incluir
@@ -330,6 +336,12 @@
 Motivo: Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
       </text>
     </comment>
+    <comment ref="H31" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: [Excluir] Estudio original de 2020 sobre tráfico vehicular que utiliza un Variational Autoencoder (VAE) con datos reales de California (EE. UU.) e Inglaterra (Reino Unido). Aunque incluye una aplicación exploratoria a la detección de anomalías, no presenta evaluación cuantitativa específica de detección, como precisión, recall, F1 o AUROC, ni validación con etiquetas de anomalías. Las métricas numéricas principales evalúan predicción e imputación. Incumple CI-6; se registra CE-3 como motivo prin
+Motivo: Coherente con CI-6.</t>
+      </text>
+    </comment>
     <comment ref="F32" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
@@ -390,6 +402,12 @@
 Motivo: Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
       </text>
     </comment>
+    <comment ref="H42" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Se excluye de la síntesis principal de estudios de detección de anomalías vehiculares mediante Deep Learning por ausencia de evaluación cuantitativa específica del detector. Raiyn (2022) propone Computational Data Science para analizar datos de velocidad, posición GNSS y calidad de datos obtenidos mediante teléfonos inteligentes, sensores y dispositivos Ublox. Considera anomalías asociadas a accidentes, congestión, ruido, interferencia y pérdida de información. Define condiciones anormales media
+Motivo: Comentario conciso para el anexo.</t>
+      </text>
+    </comment>
     <comment ref="F43" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
@@ -432,6 +450,12 @@
 Motivo: Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
       </text>
     </comment>
+    <comment ref="H51" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Se excluye por CE-3 porque, aunque desarrolla un método de Deep Learning directamente relacionado con la detección de accidentes vehiculares, no aporta resultados cuantitativos verificables y comparables de detección de anomalías. Las curvas de entrenamiento y los gráficos de puntuaciones de anomalía no equivalen a una evaluación de clasificación frente a etiquetas de referencia. Tampoco se documentan claramente el tamaño final del conjunto de prueba, el número de accidentes evaluados, los falso
+Motivo: Coherente con CI-6.</t>
+      </text>
+    </comment>
     <comment ref="F52" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
@@ -466,6 +490,12 @@
       <text>
         <t>Texto original:
 CE-5: Tipo de publicación no elegible; tesis de maestría, sin evidencia de publicación de este documento como artículo revisado por pares.</t>
+      </text>
+    </comment>
+    <comment ref="H57" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Se excluye exclusivamente por CE-5, dado que el texto completo disponible es una tesis de maestría y el protocolo exige estudios originales publicados en revistas o congresos con revisión por pares. El estudio sí satisface los requisitos temáticos, temporales y metodológicos: aborda detección de incidentes vehiculares, utiliza una arquitectura profunda TabNet entrenada de forma supervisada y proporciona métricas cuantitativas de detección. Sus resultados proceden de incidentes simulados, no de u
+Motivo: Comentario conciso para el anexo.</t>
       </text>
     </comment>
     <comment ref="F59" authorId="1" shapeId="0">
@@ -504,12 +534,24 @@
 No aplica</t>
       </text>
     </comment>
+    <comment ref="H63" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Se incluye por abordar detección explícita de comportamientos de conducción peligrosos en transporte vehicular terrestre mediante un modelo Deep Learning entrenado y evaluado cuantitativamente. La detección de fatiga y distracción del conductor se considera una subcategoría de anomalías de comportamiento vehicular. Es necesario diferenciar estos resultados de la detección de accidentes o anomalías de flujo de tráfico, que el estudio no evalúa cuantitativamente. Presenta limitaciones de reproduci
+Motivo: Comentario conciso para el anexo.</t>
+      </text>
+    </comment>
     <comment ref="F64" authorId="0" shapeId="0">
       <text>
         <t>Antes: CE-4
 Motivo: Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
       </text>
     </comment>
+    <comment ref="H64" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Se excluye del corpus principal de la revisión sistemática porque no cumple el requisito metodológico obligatorio de emplear un modelo Deep Learning para detectar anomalías del tráfico vehicular. La contribución consiste en comparar clasificadores convencionales y métodos de boosting basados en árboles para estimar la severidad de accidentes conocidos, utilizando atributos meteorológicos, temporales y contextuales. LightGBM alcanza ROC-AUC de 0.866 en la Tabla 3, pero este resultado evalúa clasi
+Motivo: Coherente con CE-3.</t>
+      </text>
+    </comment>
     <comment ref="F65" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
@@ -522,18 +564,36 @@
 CE-5: documento disponible como prepublicación arXiv, sin evidencia de publicación arbitrada en revista o congreso dentro del PDF. El manuscrito se identifica como arXiv:2505.02613v1, fechado el 5 de mayo de 2025, y no presenta DOI editorial, nombre de congreso, revista ni datos de aceptación. La exclusión se refiere al estado de publicación verificable de esta versión; no implica que el trabajo carezca de calidad científica ni descarta una eventual versión publicada posteriormente.</t>
       </text>
     </comment>
+    <comment ref="H66" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Excluir por CE-5 conforme al requisito de incluir exclusivamente investigaciones originales publicadas en revistas o congresos con revisión por pares. El contenido técnico sí corresponde al tema de la revisión: detección de anomalías reales en tráfico vehicular mediante Deep Learning, con evaluación cuantitativa y etiquetas verificadas por expertos. La exclusión no se debe a falta de pertinencia temática, ausencia de aprendizaje profundo ni indisponibilidad del texto completo. Se conserva la ext
+Motivo: Comentario conciso para el anexo.</t>
+      </text>
+    </comment>
     <comment ref="F67" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CE-5: prepublicación arXiv sin acreditación de revisión por pares en la versión PDF examinada. El documento figura como arXiv:2303.05000v1 [cs.LG], fechado el 9 de marzo de 2023, sin nombre de revista, congreso, volumen, páginas editoriales ni DOI de publicación. La decisión corresponde exclusivamente a esta versión documental y deberá reconsiderarse si se identifica una publicación arbitrada equivalente.</t>
       </text>
     </comment>
+    <comment ref="H67" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Excluir por CE-5 de acuerdo con el protocolo de la revisión sistemática, que exige estudios originales publicados en revistas o congresos revisados por pares. El manuscrito aborda directamente la detección de trayectorias anómalas de vehículos mediante Deep Learning y aporta experimentos comparativos en dos datasets públicos. Es importante registrar que las anomalías son ataques adversariales generados artificialmente, no accidentes, congestiones o conductas anómalas reales anotadas por expertos
+Motivo: Comentario conciso para el anexo.</t>
+      </text>
+    </comment>
     <comment ref="F69" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
 CE-3: El estudio se centra en predicción de riesgo de colisión y no demuestra un sistema de detección explícita de anomalías vehiculares en tráfico general. Aunque clasifica muestras peligrosas y presenta métricas de clasificación, los escenarios peligrosos se preseleccionan mediante TTC &lt; 3 s; el propio artículo reconoce que todavía es necesario identificar esos periodos en aplicaciones reales.</t>
       </text>
     </comment>
+    <comment ref="H69" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Excluir por CE-3. Li et al. (2026) presentan LLMG + ST, una arquitectura híbrida de GPT-2-LoRA, GAT y LSTM para predecir riesgo de colisión en seguimiento vehicular a partir de trayectorias highD. Aunque la investigación es original, utiliza Deep Learning y obtiene resultados cuantitativos, no evalúa la detección autónoma de anomalías sobre tráfico no preseleccionado. Sus 240 eventos de riesgo se identifican previamente mediante un criterio TTC &lt; 3 s, y el modelo pronostica la peligrosidad de ve
+Motivo: Comentario conciso para el anexo.</t>
+      </text>
+    </comment>
     <comment ref="F70" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
@@ -544,6 +604,12 @@
       <text>
         <t>Texto original:
 CE-3: el estudio no evalúa cuantitativamente la detección de anomalías en tráfico vehicular. Aunque propone un modelo Deep Learning para analizar conducción peligrosa, su tarea experimental es la predicción de series temporales y del nivel macroscópico de riesgo generado mediante reglas difusas, sin contrastar decisiones de anomalía contra etiquetas de referencia independientes.</t>
+      </text>
+    </comment>
+    <comment ref="H71" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Se excluye Li, Lin y Chou (2022), DOI 10.1109/ACCESS.2022.3171247, por CE-3. El artículo es pertinente al análisis de conducción peligrosa y emplea una red recurrente profunda fuzzy-macro LSTM con datos reales de diez conductores, pero su evaluación se concentra en pronosticar variables vehiculares y una puntuación agregada de riesgo calculada mediante un sistema de inferencia difusa. El mejor modelo obtiene MAE 0,613, RMSE 0,733 y MSE 0,521 para la predicción del nivel de riesgo, resultados que
+Motivo: Comentario conciso para el anexo.</t>
       </text>
     </comment>
     <comment ref="F72" authorId="1" shapeId="0">
@@ -618,6 +684,12 @@
 No aplica; estudio original publicado en una conferencia ACM de 2024, con texto completo disponible. Desarrolla y evalúa una CNN para reconocer una conducta anómala de conducción, específicamente el uso del teléfono móvil, y la integra en un sistema de seguridad vehicular.</t>
       </text>
     </comment>
+    <comment ref="H79" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Se incluye exclusivamente por la detección supervisada mediante CNN de una conducta vehicular anómala observable en imágenes del conductor: uso del teléfono durante la conducción. No debe clasificarse como estudio que demuestra detección de accidentes mediante Deep Learning, porque el módulo de accidentes depende del acelerómetro y no se presenta una evaluación independiente de accidentes con CNN. La matriz de confusión contiene únicamente 32 imágenes y no se documenta la independencia entre suj
+Motivo: Comentario conciso para el anexo.</t>
+      </text>
+    </comment>
     <comment ref="F80" authorId="1" shapeId="0">
       <text>
         <t>Texto original:
@@ -640,6 +712,12 @@
       <text>
         <t>Texto original:
 CE-3 — El estudio no desarrolla ni evalúa cuantitativamente un método de detección de anomalías en tráfico vehicular. Su objetivo principal es la predicción no lineal del flujo de tráfico mediante una red LSTM de dos capas y una infraestructura IoT. Aunque menciona incidentes, condiciones anormales, valores atípicos y fallos de sensores, no presenta etiquetas de anomalías viales, una regla de clasificación de eventos anómalos ni métricas específicas de detección.</t>
+      </text>
+    </comment>
+    <comment ref="H83" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Excluir por CE-3. Aunque el artículo cumple los criterios de año, publicación científica, acceso al texto completo, contexto vehicular y uso de Deep Learning, no satisface el criterio central de la revisión: detección explícita y cuantitativamente evaluada de anomalías del tráfico vehicular. La LSTM predice conteos y velocidades, y los resultados MSE, MAE, RMSE y R² miden error de pronóstico, no capacidad para detectar accidentes, congestión atípica o comportamientos anómalos. El filtrado de out
+Motivo: Comentario conciso para el anexo.</t>
       </text>
     </comment>
     <comment ref="F84" authorId="1" shapeId="0">
@@ -754,6 +832,12 @@
       <text>
         <t>Antes: CE-3
 Motivo: Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
+      </text>
+    </comment>
+    <comment ref="H101" authorId="0" shapeId="0">
+      <text>
+        <t>Antes: Se excluye durante la revisión de texto completo porque la contribución principal es el diseño e implementación de una plataforma de videovigilancia vehicular con detección, seguimiento, calibración y análisis de trayectorias. El uso de Deep Learning está documentado, y la Figura 9 demuestra que el sistema contempla incidentes viales, pero no existe un experimento reproducible que cuantifique su capacidad para distinguir incidentes reales de situaciones normales. No se informa tamaño del conjunt
+Motivo: Coherente con CI-6.</t>
       </text>
     </comment>
     <comment ref="F102" authorId="1" shapeId="0">
@@ -5117,7 +5201,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>[Excluir CE-1] Publicación paralela de R0102 (Sun y Liu, 2025); se incluye R0102 para no contar dos veces el mismo modelo.</t>
+          <t>[Excluir CE-1] Publicación paralela de R0102 (Duan et al., 2025); se incluye R0102 para no contar dos veces el mismo modelo.</t>
         </is>
       </c>
     </row>
@@ -5567,9 +5651,9 @@
           <t>El estudio propone Deep LSTM y Mixture Deep LSTM para pronóstico del flujo vehicular en horas punta y escenarios posteriores a accidentes (p. 3, sección 3.1). Utiliza datos simulados inspirados en tráfico y meteorología de Los Ángeles (p. 3, sección 3.2). Reporta MAE=4 vehículos/minuto en horas punta y MAE=6 vehículos/minuto durante los primeros 30 minutos posteriores a accidentes (p. 4, secciones 4.3-4.4). La Figura 2 (p. 5) compara SimpleCNN=76.99%, CNN_LSTM=60% y BERT_CNN/FullIntegration=46.5%, pero estas métricas no corresponden a una evaluación explícita de detección de anomalías. No presenta etiquetas de anomalía, detección de incidentes ni métricas específicas de identificación de eventos anómalos.</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>[Excluir - CE-2] El artículo aborda predicción de flujo vehicular mediante Deep LSTM y Mixture Deep LSTM utilizando datos simulados de tráfico y meteorología. Aunque incorpora escenarios posteriores a accidentes y condiciones de tráfico no habituales, los accidentes se consideran condiciones conocidas para pronosticar el flujo posterior, no eventos que el modelo deba detectar o clasificar. La variable de salida es el flujo vehicular previsto y la evaluación principal utiliza MAE. No se desarrolla ni valida un método específico de detección de anomalías en tráfico vehicular. Se excluye por falta de correspondencia con el objetivo central de la revisión sistemática, no por ausencia de Deep Learning ni de texto completo.</t>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-3] Pronostica el flujo con Deep LSTM y Mixture Deep LSTM (MAE) en horas punta y tras accidentes; los accidentes son una condición de entrada, no eventos que se detecten.</t>
         </is>
       </c>
     </row>
@@ -5841,9 +5925,9 @@
           <t>Sección 7.2, pp. 13–16: exploración de anomalías mediante el espacio latente del VAE; p. 15: la metodología de detección automática y su precisión se dejan como trabajo futuro.</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>[Excluir] Estudio original de 2020 sobre tráfico vehicular que utiliza un Variational Autoencoder (VAE) con datos reales de California (EE. UU.) e Inglaterra (Reino Unido). Aunque incluye una aplicación exploratoria a la detección de anomalías, no presenta evaluación cuantitativa específica de detección, como precisión, recall, F1 o AUROC, ni validación con etiquetas de anomalías. Las métricas numéricas principales evalúan predicción e imputación. Incumple CI-6; se registra CE-3 como motivo principal.</t>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CI-6] VAE para imputación, reducción de dimensión y pronóstico; la detección de anomalías es exploratoria (espacio latente) y no se evalúa con etiquetas ni métricas de detección.</t>
         </is>
       </c>
     </row>
@@ -6259,9 +6343,9 @@
           <t>Página 1: resumen y DOI; declara detección de anomalías y uso de Deep Learning. Página 4, Figuras 1–3: comparación de velocidades y variaciones estadísticas ante condiciones anormales. Página 5, sección 3.2: umbral ilustrativo de reducción de velocidad de 30 km/h y pruebas de diferencias entre estaciones. Página 9, sección 4.11: red descrita genéricamente mediante entrada, capas ocultas y salida. Página 10, Figura 7: flujo CDS para detección, identificación de fuente y localización. Página 13, Figura 10: esquema genérico de neuronas, pesos y activación. Página 15, Tabla 4: estadísticas de regresión para condiciones con y sin ruido, no métricas de clasificación. Página 15, Figuras 13–14: visualización de anomalías de posicionamiento y comparación gráfica CDS frente a ML sin indicadores cuantitativos de detección. Página 16, conclusiones: se afirma una mejora de pronóstico, pero no se cuantifica la detección de anomalías.</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>Se excluye de la síntesis principal de estudios de detección de anomalías vehiculares mediante Deep Learning por ausencia de evaluación cuantitativa específica del detector. Raiyn (2022) propone Computational Data Science para analizar datos de velocidad, posición GNSS y calidad de datos obtenidos mediante teléfonos inteligentes, sensores y dispositivos Ublox. Considera anomalías asociadas a accidentes, congestión, ruido, interferencia y pérdida de información. Define condiciones anormales mediante desviaciones de velocidad y diferencias espaciales y temporales; presenta una red neuronal conceptual y un procedimiento de entrenamiento y prueba. Sin embargo, no identifica con precisión el conjunto experimental, las etiquetas de referencia, la arquitectura profunda, el tamaño de entrenamiento y prueba ni los parámetros de aprendizaje. La Tabla 4 informa Multiple R, R², R² ajustado, desviación estándar y asimetría en presencia y ausencia de ruido, pero esos valores no son métricas de detección. Las Figuras 13 y 14 muestran resultados visuales sin tasas de aciertos o errores. Por tanto, no es posible extraer un rendimiento comparable con los estudios incluidos. Se conserva como antecedente conceptual sobre anomalías de velocidad, calidad de datos y posicionamiento vehicular, sin incorporarlo al análisis cuantitativo principal.</t>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CI-6] Propone un enfoque de ciencia de datos con DL para anomalías de velocidad, pero no reporta métricas de detección (precision, recall, F1 o AUC) ni etiquetas de referencia.</t>
         </is>
       </c>
     </row>
@@ -6597,9 +6681,9 @@
           <t>Artículo de conferencia publicado en Electronic Imaging 2023, DOI 10.2352/EI.2023.35.3.MOBMU-364, con texto completo accesible de 12 páginas. Propone un sistema de detección de accidentes vehiculares que integra eliminación de fondo mediante U²-Net, detección y seguimiento de objetos mediante YOLO-R y DeepSORT, y redes generativas adversarias para identificar anomalías en escenas de vigilancia. Compara variantes GAN sin conexiones de salto, GAN con conexiones de salto y GAN con conexiones de salto y atención (secciones Methodology y Results, pp. 3-8). Utiliza imágenes procedentes de videos de vigilancia y describe conjuntos públicos de referencia como UCFCrime, Street Scene y ShanghaiTech (Tabla 1, p. 5). Las Figuras 10 y 13 (pp. 10-11) muestran señales de distancia de Mahalanobis y error adversarial, mientras que las Figuras 11 y 12 (p. 10) presentan curvas de entrenamiento. No se proporciona una tabla de resultados de detección con precision, recall, F1-score, AUC, tasa de falsos positivos o matriz de confusión, ni un protocolo cuantitativo suficientemente documentado que permita verificar el desempeño sobre accidentes etiquetados.</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>Se excluye por CE-3 porque, aunque desarrolla un método de Deep Learning directamente relacionado con la detección de accidentes vehiculares, no aporta resultados cuantitativos verificables y comparables de detección de anomalías. Las curvas de entrenamiento y los gráficos de puntuaciones de anomalía no equivalen a una evaluación de clasificación frente a etiquetas de referencia. Tampoco se documentan claramente el tamaño final del conjunto de prueba, el número de accidentes evaluados, los falsos positivos y negativos ni una comparación numérica completa entre las variantes propuestas. No se excluye por CE-2 ni CE-4, puesto que el dominio es tráfico vehicular y sí se utilizan redes profundas. El estudio puede citarse como antecedente metodológico, pero no debe incorporarse a la síntesis cuantitativa principal bajo los criterios establecidos.</t>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CI-6] YOLO-R, DeepSORT y GAN para detectar accidentes en video, sin tabla de resultados de detección (precision, recall, F1 o AUC) frente a accidentes etiquetados.</t>
         </is>
       </c>
     </row>
@@ -6829,9 +6913,9 @@
           <t>La portada identifica explícitamente el documento como "A Thesis Presented in Partial Fulfillment of the Requirements for the Degree Master of Science", presentada en Arizona State University y aprobada en mayo de 2024 (PDF, p. 1). El documento tiene estructura de tesis, con capítulos de introducción, trabajos relacionados, metodología, experimentos, resultados y conclusión, y no presenta datos editoriales que acrediten su publicación como artículo de revista o congreso revisado por pares. En cuanto al contenido científico, propone IncidentNet, basado en tres modelos TabNet para detección, localización y estimación de gravedad de incidentes de tráfico mediante sensores dispersos. Emplea datos microscópicos generados con SUMO y calibrados con conteos vehiculares reales de Tempe, Arizona. Reporta en el escenario urbano DR de 98 %, FAR de 6,26 %, MTTD de 197,44 segundos y F1 de 92,70 % (Tabla 5.1, PDF p. 25). También presenta resultados en autopistas, con DR de 99 %, FAR de 4,17 % y MTTD de 70 segundos (Tabla 5.2, PDF p. 28).</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>Se excluye exclusivamente por CE-5, dado que el texto completo disponible es una tesis de maestría y el protocolo exige estudios originales publicados en revistas o congresos con revisión por pares. El estudio sí satisface los requisitos temáticos, temporales y metodológicos: aborda detección de incidentes vehiculares, utiliza una arquitectura profunda TabNet entrenada de forma supervisada y proporciona métricas cuantitativas de detección. Sus resultados proceden de incidentes simulados, no de una validación operacional con accidentes reales, lo que constituye una limitación adicional, pero no el motivo principal de exclusión. Se recomienda conservar este registro como literatura relacionada y comprobar por separado si existe un artículo revisado por pares derivado de la tesis, evitando incluir automáticamente la tesis como si fuera dicho artículo.</t>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-5] El texto completo disponible es una tesis de maestría; no se encontró una versión revisada por pares de acceso abierto.</t>
         </is>
       </c>
     </row>
@@ -7057,9 +7141,9 @@
           <t>Artículo original de conferencia publicado en ACM CMNM 2026 (pp. 284–290), con texto completo disponible bajo licencia Creative Commons Attribution 4.0. Desarrolla un sistema de asistencia para la seguridad de camiones que integra un modelo YOLOv8n entrenado para reconocer comportamientos peligrosos del conductor, incluyendo bostezos, uso del teléfono y tabaquismo, así como estados de apertura y cierre de ojos. En la sección 3 (p. 289) se informa un conjunto propio de 6000 imágenes etiquetadas, dividido en entrenamiento y prueba con proporción 10:1 y utilizado para entrenar el modelo durante 120 épocas. La Tabla 1 (p. 286) presenta el mAP@0.5 de seis clases y la Tabla 2 (p. 289) proporciona precisión, recall, mAP@0.5 y mAP@0.5:0.95 para cuatro comportamientos. El mAP@0.5 global declarado es 95.8 %.</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>Se incluye por abordar detección explícita de comportamientos de conducción peligrosos en transporte vehicular terrestre mediante un modelo Deep Learning entrenado y evaluado cuantitativamente. La detección de fatiga y distracción del conductor se considera una subcategoría de anomalías de comportamiento vehicular. Es necesario diferenciar estos resultados de la detección de accidentes o anomalías de flujo de tráfico, que el estudio no evalúa cuantitativamente. Presenta limitaciones de reproducibilidad, ausencia de modelos comparativos y escasa documentación del dataset y de la generalización.</t>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-2] YOLOv8n reconoce fatiga, bostezos, uso del teléfono y tabaquismo del conductor de camión en imágenes de cabina: es monitoreo del conductor.</t>
         </is>
       </c>
     </row>
@@ -7099,9 +7183,9 @@
           <t>Artículo original publicado en AICCC 2023 (ACM, pp. 179–188), con texto completo disponible. La sección 4, Proposed Solution (p. 183), establece que la propuesta utiliza exclusivamente Random Forest, XGBoost y LightGBM para clasificación multiclase de la gravedad de accidentes. La sección 4.1 (p. 183) describe el Countrywide Traffic Accident Dataset, con aproximadamente 2.8 millones de accidentes estadounidenses entre febrero de 2016 y diciembre de 2021. La sección 5 y la Tabla 3 (pp. 186–187) presentan resultados únicamente de esos tres algoritmos. Las referencias a CNN, GAN y otras redes profundas en las secciones 3.1–3.3 y Tabla 1 (pp. 181–185) corresponden a antecedentes bibliográficos y no a experimentos propios.</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>Se excluye del corpus principal de la revisión sistemática porque no cumple el requisito metodológico obligatorio de emplear un modelo Deep Learning para detectar anomalías del tráfico vehicular. La contribución consiste en comparar clasificadores convencionales y métodos de boosting basados en árboles para estimar la severidad de accidentes conocidos, utilizando atributos meteorológicos, temporales y contextuales. LightGBM alcanza ROC-AUC de 0.866 en la Tabla 3, pero este resultado evalúa clasificación de severidad y no detección de accidentes. El estudio puede servir como antecedente contextual sobre predicción de severidad y tratamiento del desbalance de clases, sin incorporarse a la síntesis de modelos profundos de detección de anomalías.</t>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-3] Clasifica la gravedad de accidentes ya registrados (Random Forest, XGBoost, LightGBM); no detecta incidentes y tampoco usa DL.</t>
         </is>
       </c>
     </row>
@@ -7179,9 +7263,9 @@
           <t>El trabajo presenta un sistema de detección de anomalías de tráfico por carril en autopistas de Indiana, Estados Unidos, mediante datos extraídos de cámaras de vigilancia. Emplea YOLOv5x-CBAM y Deep SORT para detectar y seguir vehículos; genera series temporales de conteo, ocupación y porcentaje de camiones; utiliza un VQ-VAE sobre espectrogramas de transformada wavelet continua, reglas de congestión e Isolation Forest. El conjunto procede de 8746 videos de 15 minutos captados por cinco cámaras durante seis meses; se reportan 46 clips anómalos validados por expertos, 73139 muestras normales por carril y 341 muestras anómalas etiquetadas (sección III, pp. 2–4). La Tabla III (p. 6) reporta para el sistema completo accuracy 0,9787, precisión 0,8431, recall 1,0 y F1 0,9149. La Tabla II presenta comparaciones con Isolation Forest, OWAM, TimeVQVAE-AD y TranAD. La portada identifica el documento como arXiv:2505.02613v1, sin indicar publicación revisada por pares.</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>Excluir por CE-5 conforme al requisito de incluir exclusivamente investigaciones originales publicadas en revistas o congresos con revisión por pares. El contenido técnico sí corresponde al tema de la revisión: detección de anomalías reales en tráfico vehicular mediante Deep Learning, con evaluación cuantitativa y etiquetas verificadas por expertos. La exclusión no se debe a falta de pertinencia temática, ausencia de aprendizaje profundo ni indisponibilidad del texto completo. Se conserva la extracción metodológica porque el estudio aporta un conjunto de datos de autopistas con resolución por carril y un sistema modular VQ-VAE, reglas e Isolation Forest. Si se identifica posteriormente una versión arbitrada del mismo trabajo, debe verificarse su equivalencia y reevaluarse el registro sin duplicarlo en Parsifal.</t>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-5] Preprint de arXiv (2505.02613) sin versión revisada por pares verificable.</t>
         </is>
       </c>
     </row>
@@ -7221,9 +7305,9 @@
           <t>El estudio propone dos métodos de detección de trayectorias vehiculares anómalas: aprendizaje contrastivo supervisado y reconstrucción no supervisada mediante un adversarial autoencoder con espacio latente semántico. Ambos utilizan un extractor profundo que combina convoluciones unidimensionales para trayectorias y redes neuronales de grafos para mapas e interacciones entre agentes (sección III, pp. 3–5; Figuras 2–3, pp. 4–5). Se evalúan sobre Argoverse 1 y Argoverse 2, con anomalías adversariales sintéticas de tipo aleatorio y direccional lateral generadas mediante perturbaciones de trayectorias históricas (secciones II.A y IV.A, pp. 2 y 5). Las Tablas I–IV (p. 6) reportan F1, ROC-AUC y PR-AUC; el mejor resultado supervisado es F1 0,99, ROC-AUC 0,98 y PR-AUC 0,99 en anomalías laterales de Argoverse 2. La pertinencia temática y la evaluación cuantitativa están acreditadas, pero no la publicación arbitrada.</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>Excluir por CE-5 de acuerdo con el protocolo de la revisión sistemática, que exige estudios originales publicados en revistas o congresos revisados por pares. El manuscrito aborda directamente la detección de trayectorias anómalas de vehículos mediante Deep Learning y aporta experimentos comparativos en dos datasets públicos. Es importante registrar que las anomalías son ataques adversariales generados artificialmente, no accidentes, congestiones o conductas anómalas reales anotadas por expertos. La exclusión se fundamenta en el estado editorial de la versión suministrada, no en falta de relevancia, ausencia de DL o falta de texto completo. Si se localiza una versión revisada por pares, deberá comprobarse su identidad bibliográfica y reevaluarse este mismo registro sin duplicarlo en Parsifal.</t>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-5] Preprint de arXiv (2303.05000) sin versión revisada por pares verificable.</t>
         </is>
       </c>
     </row>
@@ -7297,9 +7381,9 @@
           <t>Evidencia: sección 3.1, página 3, Figura 1: el flujo comienza con la selección de eventos peligrosos del conjunto highD mediante TTC &lt; 3 s y termina en predicción de riesgo. Sección 4.1, página 6: se identifican 240 eventos peligrosos y se indica expresamente que el caso verifica el método sobre eventos de alto riesgo predefinidos. Sección 4.3.1, página 6: las primeras 70 tramas sirven para predecir riesgo en las 30 posteriores. Tabla 3, página 10: Accuracy 0.956, F1 0.872 y AUC 0.985 corresponden a predicción/clasificación de riesgo. Conclusiones, página 11: los autores reconocen que el método aún no identifica automáticamente periodos peligrosos en conducción real.</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>Excluir por CE-3. Li et al. (2026) presentan LLMG + ST, una arquitectura híbrida de GPT-2-LoRA, GAT y LSTM para predecir riesgo de colisión en seguimiento vehicular a partir de trayectorias highD. Aunque la investigación es original, utiliza Deep Learning y obtiene resultados cuantitativos, no evalúa la detección autónoma de anomalías sobre tráfico no preseleccionado. Sus 240 eventos de riesgo se identifican previamente mediante un criterio TTC &lt; 3 s, y el modelo pronostica la peligrosidad de ventanas futuras. Los autores reconocen explícitamente que la aplicación real requerirá identificar primero los periodos peligrosos e incorporar datos de conducción segura. Se conserva como antecedente metodológico relacionado, pero no cumple el objetivo específico de detección de anomalías de esta revisión.</t>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-3] GPT-2-LoRA, GAT y LSTM predicen el riesgo de colisión en eventos peligrosos preseleccionados (TTC &lt; 3 s) de highD; no detecta anomalías sobre tráfico no preseleccionado.</t>
         </is>
       </c>
     </row>
@@ -7377,9 +7461,9 @@
           <t>Evidencia del PDF: sección II.A, página 47882, define la salida como grado macroscópico de conducción riesgosa calculado a partir de aceleraciones bruscas, frenadas bruscas y velocidad media por 100 km. Sección II.C y Tabla 1, páginas 47883–47884, presentan 27 reglas difusas para asignar riesgo bajo, medio o alto. Sección III.A, página 47886, describe datos reales OBD-II de diez participantes durante nueve meses. Sección III.B, página 47887, establece exclusivamente MAE, MSE y RMSE como métricas experimentales. Tablas 2 y 3, página 47888, y Tabla 4, página 47891, comparan errores de predicción frente a cinco redes neuronales. Figuras 22–24, página 47892, comparan valores reales y pronosticados de velocidad, frenadas y aceleraciones; no presentan evaluación de identificación de eventos anómalos.</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>Se excluye Li, Lin y Chou (2022), DOI 10.1109/ACCESS.2022.3171247, por CE-3. El artículo es pertinente al análisis de conducción peligrosa y emplea una red recurrente profunda fuzzy-macro LSTM con datos reales de diez conductores, pero su evaluación se concentra en pronosticar variables vehiculares y una puntuación agregada de riesgo calculada mediante un sistema de inferencia difusa. El mejor modelo obtiene MAE 0,613, RMSE 0,733 y MSE 0,521 para la predicción del nivel de riesgo, resultados que no constituyen métricas de detección de anomalías. No se informa validación de eventos peligrosos detectados mediante etiquetas independientes, ni métricas de clasificación normal/anómalo, sensibilidad, precisión, F1 o AUC. La existencia de reglas de riesgo alto no basta para demostrar capacidad de detección. El artículo puede conservarse como referencia contextual sobre predicción del riesgo de conducción, pero no debe incorporarse a la síntesis cuantitativa de detección de anomalías.</t>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-3] LSTM difusa que pronostica variables de conducción y un nivel de riesgo calculado con reglas difusas; solo reporta MAE, MSE y RMSE.</t>
         </is>
       </c>
     </row>
@@ -7689,9 +7773,9 @@
           <t>La sección 3.4, pp. 279–280, describe una CNN personalizada entrenada con imágenes etiquetadas como phone_holding y not_holding. Se declara un conjunto de 11745 imágenes procedentes de How drive 3d driver distraction y fotografías propias, sección 3.4.1, p. 279. La Figura 2, p. 280, presenta tres capas convolucionales seguidas de capas densas. La Figura 7, p. 282, presenta una matriz de confusión de 32 imágenes: TN=9, FP=0, FN=0 y TP=23, equivalente a exactitud, precisión, sensibilidad y F1 del 100 % en esa muestra. La sección 4.1, p. 280, informa exactitud de entrenamiento del 100 %. La detección de accidentes se realiza mediante el acelerómetro ADXL335, mientras que velocidad y alcohol se supervisan mediante GPS y sensor MQ3, secciones 3.3 y 4.3, pp. 278 y 282. La Tabla 3, p. 286, declara 90 % de detección y reducción de accidentes, sin presentar denominadores, matriz de confusión ni protocolo de evaluación que respalden ese porcentaje.</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>Se incluye exclusivamente por la detección supervisada mediante CNN de una conducta vehicular anómala observable en imágenes del conductor: uso del teléfono durante la conducción. No debe clasificarse como estudio que demuestra detección de accidentes mediante Deep Learning, porque el módulo de accidentes depende del acelerómetro y no se presenta una evaluación independiente de accidentes con CNN. La matriz de confusión contiene únicamente 32 imágenes y no se documenta la independencia entre sujetos o sesiones de entrenamiento y prueba. Tampoco se presentan comparaciones cuantitativas entre modelos profundos bajo el mismo conjunto de prueba, intervalos de confianza ni evidencia de generalización externa. El 90 % de la Tabla 3 no debe utilizarse como métrica validada de detección de anomalías por Deep Learning. Es pertinente para la revisión en la subcategoría de comportamiento de conducción, con calidad experimental limitada.</t>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-2] La CNN clasifica si el conductor sostiene el teléfono en imágenes de cabina; el módulo de accidentes depende del acelerómetro y no se evalúa con DL.</t>
         </is>
       </c>
     </row>
@@ -7845,9 +7929,9 @@
           <t>El artículo es una investigación original publicada en 2025 en Systems and Soft Computing, volumen 7, artículo 200254, DOI 10.1016/j.sasc.2025.200254, con texto completo Open Access. La sección 3.2, p. 3, describe aproximadamente 9,1 millones de observaciones recogidas entre enero y junio de 2024 mediante 35 sensores IoT en 12 intersecciones y 23 segmentos de autopista. La sección 3.3, pp. 3–5, presenta una arquitectura LSTM de dos capas con 64 y 32 unidades, destinada a predecir variables del tráfico. La Tabla 6, p. 6, informa MSE de prueba 0,0953, MAE 0,0728, R² 0,8976 y RMSE 0,3087. La Tabla 7, p. 7, compara errores de predicción con media móvil, regresión lineal, Auto ARIMA y LSTM de una capa. La sección 4.3, p. 10, menciona adaptación a incidentes y bloqueos inesperados, pero únicamente como estudios de caso de predicción, sin matriz de confusión ni métricas de detección de anomalías. La sección 4.2, p. 10, informa 99,9 % de detección de condiciones anómalas del sistema de monitoreo en 30 segundos; este resultado corresponde a supervisión operativa de la infraestructura, no a la detección de anomalías vehiculares mediante la LSTM.</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>Excluir por CE-3. Aunque el artículo cumple los criterios de año, publicación científica, acceso al texto completo, contexto vehicular y uso de Deep Learning, no satisface el criterio central de la revisión: detección explícita y cuantitativamente evaluada de anomalías del tráfico vehicular. La LSTM predice conteos y velocidades, y los resultados MSE, MAE, RMSE y R² miden error de pronóstico, no capacidad para detectar accidentes, congestión atípica o comportamientos anómalos. El filtrado de outliers mediante IQR es una operación estadística de limpieza de datos y no constituye el método profundo de detección. Las alertas por incertidumbre, los fallos de sensores y las condiciones anómalas del sistema tampoco demuestran detección vial. No corresponde CE-4 porque sí emplea LSTM; tampoco CE-6 porque el PDF completo está disponible. Registrar CE-3 como motivo principal de exclusión en Parsifal.</t>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CE-3] LSTM con IoT para pronosticar el flujo de autopista; menciona eventos anormales, pero no los etiqueta ni evalúa su detección.</t>
         </is>
       </c>
     </row>
@@ -8529,9 +8613,9 @@
           <t>Página 1, resumen: se describe un sistema de procesamiento de video, compresión de redes neuronales, detección nocturna, seguimiento de vehículos y análisis de comportamiento; se afirma que funciona en distintas localidades de China, pero sin cifras de desempeño. Página 2, Figura 1: arquitectura modular de vigilancia. Página 4, Figuras 5 y 6: ejemplos visuales de detección y seguimiento de vehículos. Página 5, sección 5.2 y Figura 9: demostración de un incidente de circulación en sentido contrario, sin comparación con etiquetas de referencia ni resultados cuantitativos. Página 5, conclusión: se reiteran beneficios operativos y despliegue parcial en Zhejiang, sin métricas de anomalías.</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>Se excluye durante la revisión de texto completo porque la contribución principal es el diseño e implementación de una plataforma de videovigilancia vehicular con detección, seguimiento, calibración y análisis de trayectorias. El uso de Deep Learning está documentado, y la Figura 9 demuestra que el sistema contempla incidentes viales, pero no existe un experimento reproducible que cuantifique su capacidad para distinguir incidentes reales de situaciones normales. No se informa tamaño del conjunto de prueba, número de incidentes, falsos positivos, falsos negativos, precision, recall, F1, AUROC ni tiempo de detección. El estudio puede citarse como antecedente de arquitectura de sistemas de vigilancia, pero no debe incorporarse a la síntesis de efectividad de métodos de detección de anomalías. Criterio principal: CE-3; no corresponde excluirlo por ausencia de Deep Learning.</t>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>[Excluir CI-6] Plataforma de videovigilancia con detección y seguimiento de vehículos; muestra ejemplos de incidentes, pero no reporta métricas de detección.</t>
         </is>
       </c>
     </row>
@@ -8708,7 +8792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9126,7 +9210,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Comentario» → [Excluir CE-1] Publicación paralela de R0102 (Sun y Liu, 2025); se incluye R0102 para no contar dos veces el mismo modelo.</t>
+          <t>Corregido «Comentario» → [Excluir CE-1] Publicación paralela de R0102 (Duan et al., 2025); se incluye R0102 para no contar dos veces el mismo modelo.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -9446,7 +9530,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>R0192</t>
+          <t>R0190</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -9456,12 +9540,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «Comentario» → [Excluir CE-3] Pronostica el flujo con Deep LSTM y Mixture Deep LSTM (MAE) en horas punta y tras accidentes; los accidentes son una condición de entrada, no eventos que se detecten.</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Releído el PDF: la detección solo se valida de forma visual (face validation); la única métrica cuantitativa (RMSE, Tabla 1) es de imputación.</t>
+          <t>Coherente con CE-3.</t>
         </is>
       </c>
     </row>
@@ -9478,12 +9562,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Sin evaluación cuantitativa de la detección (igual que R0249 y R0389).</t>
+          <t>Releído el PDF: la detección solo se valida de forma visual (face validation); la única métrica cuantitativa (RMSE, Tabla 1) es de imputación.</t>
         </is>
       </c>
     </row>
@@ -9500,12 +9584,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Corregido «EVIDENCIA (cita y página)» → "we employ a face validation approach. In this approach, we visually examine the pace time series of various zones" (p. 10, sección IV-E); "Table 1 presents the mean and standard deviation of RMSE across 10 trials of inference-phase imputation" (p. 9, sección IV-C).</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Cita del PDF.</t>
+          <t>Sin evaluación cuantitativa de la detección (igual que R0249 y R0389).</t>
         </is>
       </c>
     </row>
@@ -9522,19 +9606,19 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Comentario» → [Excluir CI-6] SI-DMSeq (encoder-decoder LSTM con atención, Manhattan, huracán Sandy y tormenta de 2010) detecta disrupciones con una carta de control sobre el error de reconstrucción, pero no las evalúa contra etiquetas: no hay precision, recall, F1, AUC ni tasa de detección; la única métrica numérica (RMSE) es de imputación.</t>
+          <t>Corregido «EVIDENCIA (cita y página)» → "we employ a face validation approach. In this approach, we visually examine the pace time series of various zones" (p. 10, sección IV-E); "Table 1 presents the mean and standard deviation of RMSE across 10 trials of inference-phase imputation" (p. 9, sección IV-C).</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Motivo.</t>
+          <t>Cita del PDF.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>R0244</t>
+          <t>R0192</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -9544,19 +9628,19 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Incluir</t>
+          <t>Corregido «Comentario» → [Excluir CI-6] SI-DMSeq (encoder-decoder LSTM con atención, Manhattan, huracán Sandy y tormenta de 2010) detecta disrupciones con una carta de control sobre el error de reconstrucción, pero no las evalúa contra etiquetas: no hay precision, recall, F1, AUC ni tasa de detección; la única métrica numérica (RMSE) es de imputación.</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>«INCLUIDO» no es una opción de la lista.</t>
+          <t>Motivo.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>R0249</t>
+          <t>R0244</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -9566,41 +9650,41 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «DECISIÓN TC» → Incluir</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
+          <t>«INCLUIDO» no es una opción de la lista.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>R0379</t>
+          <t>R0249</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Evalúa en una grabación highD no vista.</t>
+          <t>Sí trata la detección de anomalías, pero solo de forma exploratoria y sin métricas de detección: es CI-6, no CE-3.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>R0389</t>
+          <t>R0249</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -9610,129 +9694,129 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «Comentario» → [Excluir CI-6] VAE para imputación, reducción de dimensión y pronóstico; la detección de anomalías es exploratoria (espacio latente) y no se evalúa con etiquetas ni métricas de detección.</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
+          <t>Coherente con CI-6.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>R0403</t>
+          <t>R0379</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Corregido «QA5 Código y datos» → 1</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Código con DOI (ETS) y datasets públicos (DAD, CCD, A3D): ambos públicos.</t>
+          <t>Evalúa en una grabación highD no vista.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>R0403</t>
+          <t>R0389</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Particiones oficiales de DAD y CCD.</t>
+          <t>Trata anomalías de tráfico pero no reporta métricas de detección: es CI-6 (igual que R0249, R0528 y R1166).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>R0501</t>
+          <t>R0389</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → Ambos</t>
+          <t>Corregido «Comentario» → [Excluir CI-6] Propone un enfoque de ciencia de datos con DL para anomalías de velocidad, pero no reporta métricas de detección (precision, recall, F1 o AUC) ni etiquetas de referencia.</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Vías urbanas e interurbanas.</t>
+          <t>Comentario conciso para el anexo.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>R0501</t>
+          <t>R0403</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «QA5 Código y datos» → 1</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Conjunto externo ECVD solo para prueba.</t>
+          <t>Código con DOI (ETS) y datasets públicos (DAD, CCD, A3D): ambos públicos.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>R0528</t>
+          <t>R0403</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
+          <t>Particiones oficiales de DAD y CCD.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>R0537</t>
+          <t>R0501</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -9742,19 +9826,19 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Entorno» → Ambos</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Sin proporciones ni protocolo de separación.</t>
+          <t>Vías urbanas e interurbanas.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>R0596</t>
+          <t>R0501</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -9764,85 +9848,85 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Partición insuficientemente reportada.</t>
+          <t>Conjunto externo ECVD solo para prueba.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>R0598</t>
+          <t>R0528</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «CRITERIO» → CI-6</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Pista de pruebas; no es urbano ni autopista.</t>
+          <t>Detecta accidentes con DL, pero no reporta métricas de detección: es CI-6, no CE-3.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>R0601</t>
+          <t>R0528</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Comentario» → [Excluir CI-6] YOLO-R, DeepSORT y GAN para detectar accidentes en video, sin tabla de resultados de detección (precision, recall, F1 o AUC) frente a accidentes etiquetados.</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba de AI City Challenge.</t>
+          <t>Coherente con CI-6.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>R0604</t>
+          <t>R0537</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
+          <t>Sin proporciones ni protocolo de separación.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>R0604</t>
+          <t>R0585</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -9852,41 +9936,41 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-2</t>
+          <t>Corregido «Comentario» → [Excluir CE-5] El texto completo disponible es una tesis de maestría; no se encontró una versión revisada por pares de acceso abierto.</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina.</t>
+          <t>Comentario conciso para el anexo.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>R0614</t>
+          <t>R0596</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-3</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
+          <t>Partición insuficientemente reportada.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>R0658</t>
+          <t>R0598</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -9896,19 +9980,19 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Particiones oficiales de los benchmarks.</t>
+          <t>Pista de pruebas; no es urbano ni autopista.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>R0664</t>
+          <t>R0601</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -9923,14 +10007,14 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Videos de prueba separados.</t>
+          <t>Conjunto de prueba de AI City Challenge.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0604</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -9945,14 +10029,14 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>YOLOv5s/DeepSORT solo siguen vehículos; la anomalía se decide con umbrales manuales (igual que R0037, R0235 y R1213, excluidos por CE-4).</t>
+          <t>Monitoreo del conductor dentro de la cabina (fatiga, bostezos, teléfono): CE-2 lo excluye expresamente.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0604</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -9962,19 +10046,19 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-4</t>
+          <t>Corregido «CRITERIO» → CE-2</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>La decisión de anomalía no la toma una red profunda.</t>
+          <t>Monitoreo del conductor dentro de la cabina.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0604</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -9984,19 +10068,19 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Corregido «EVIDENCIA (cita y página)» → Reglas explícitas: sentido contrario si Num/f ≥ 0,2; velocidad anómala si la media de 10 fotogramas supera n o baja de m; estacionamiento si la posición no cambia en cinco fotogramas (sección 3.3.5, pp. 10-11; Tabla 1, p. 8).</t>
+          <t>Corregido «Comentario» → [Excluir CE-2] YOLOv8n reconoce fatiga, bostezos, uso del teléfono y tabaquismo del conductor de camión en imágenes de cabina: es monitoreo del conductor.</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Hoja 2 del autor.</t>
+          <t>Comentario conciso para el anexo.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0614</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -10006,41 +10090,41 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Comentario» → [Excluir CE-4] El DL detecta, sigue y reidentifica vehículos; los comportamientos peligrosos se deciden con umbrales manuales.</t>
+          <t>Corregido «CRITERIO» → CE-3</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Motivo.</t>
+          <t>Predice la gravedad de accidentes ya registrados; CE-3 va antes que CE-4 en el orden fijo.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>R0666</t>
+          <t>R0614</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Comentario» → [Excluir CE-3] Clasifica la gravedad de accidentes ya registrados (Random Forest, XGBoost, LightGBM); no detecta incidentes y tampoco usa DL.</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>No detalla la partición.</t>
+          <t>Coherente con CE-3.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>R0929</t>
+          <t>R0618</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -10050,19 +10134,19 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Corregido «DECISIÓN TC» → Excluir</t>
+          <t>Corregido «Comentario» → [Excluir CE-5] Preprint de arXiv (2505.02613) sin versión revisada por pares verificable.</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
+          <t>Comentario conciso para el anexo.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>R0929</t>
+          <t>R0622</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -10072,63 +10156,63 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CE-2</t>
+          <t>Corregido «Comentario» → [Excluir CE-5] Preprint de arXiv (2303.05000) sin versión revisada por pares verificable.</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Monitoreo del conductor dentro de la cabina.</t>
+          <t>Comentario conciso para el anexo.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>R0943</t>
+          <t>R0635</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Comentario» → [Excluir CE-3] GPT-2-LoRA, GAT y LSTM predicen el riesgo de colisión en eventos peligrosos preseleccionados (TTC &lt; 3 s) de highD; no detecta anomalías sobre tráfico no preseleccionado.</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Sin procedimiento de selección ni conjunto de prueba.</t>
+          <t>Comentario conciso para el anexo.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>R1000</t>
+          <t>R0646</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Comentario» → [Excluir CE-3] LSTM difusa que pronostica variables de conducción y un nivel de riesgo calculado con reglas difusas; solo reporta MAE, MSE y RMSE.</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>No indica qué escenas de NGSIM usa.</t>
+          <t>Comentario conciso para el anexo.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>R1010</t>
+          <t>R0658</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -10138,19 +10222,19 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Evaluado con autos de juguete en escenario controlado.</t>
+          <t>Particiones oficiales de los benchmarks.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>R1013</t>
+          <t>R0664</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -10165,14 +10249,14 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba oficial de TADS.</t>
+          <t>Videos de prueba separados.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>R1014</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -10187,14 +10271,14 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>DeepWalk/Node2vec no es Deep Learning; la anomalía la deciden SVDD y reglas.</t>
+          <t>YOLOv5s/DeepSORT solo siguen vehículos; la anomalía se decide con umbrales manuales (igual que R0037, R0235 y R1213, excluidos por CE-4).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>R1014</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -10209,14 +10293,14 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Sin componente profunda entrenada que decida la anomalía.</t>
+          <t>La decisión de anomalía no la toma una red profunda.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>R1014</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -10226,7 +10310,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Corregido «EVIDENCIA (cita y página)» → DeepWalk genera caminatas aleatorias y aprende embeddings con Skip-Gram; SVDD determina las regiones anómalas (sección 3, pp. 3-5); umbral de coincidencia de trayectorias anómalas 0,463 (sección 4.2, p. 6).</t>
+          <t>Corregido «EVIDENCIA (cita y página)» → Reglas explícitas: sentido contrario si Num/f ≥ 0,2; velocidad anómala si la media de 10 fotogramas supera n o baja de m; estacionamiento si la posición no cambia en cinco fotogramas (sección 3.3.5, pp. 10-11; Tabla 1, p. 8).</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -10238,7 +10322,7 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>R1014</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -10248,7 +10332,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Comentario» → [Excluir CE-4] El detector es DeepWalk/Node2vec (embedding superficial, no DL) más SVDD, Apriori y umbrales.</t>
+          <t>Corregido «Comentario» → [Excluir CE-4] El DL detecta, sigue y reidentifica vehículos; los comportamientos peligrosos se deciden con umbrales manuales.</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -10260,7 +10344,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>R1014</t>
+          <t>R0666</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -10270,85 +10354,85 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Familia DL principal» → Otra</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>DeepWalk/Node2vec no es una GNN.</t>
+          <t>No detalla la partición.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>R1082</t>
+          <t>R0929</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Conjunto de prueba de MAAD (con ajuste de hiperparámetros en parte de él).</t>
+          <t>La CNN solo reconoce si el conductor sostiene el teléfono (imagen de cabina): CE-2 lo excluye expresamente.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>R1092</t>
+          <t>R0929</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Aleatoria</t>
+          <t>Corregido «CRITERIO» → CE-2</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>División 80/20 de videos sin otro criterio.</t>
+          <t>Monitoreo del conductor dentro de la cabina.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>R1100</t>
+          <t>R0929</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Comentario» → [Excluir CE-2] La CNN clasifica si el conductor sostiene el teléfono en imágenes de cabina; el módulo de accidentes depende del acelerómetro y no se evalúa con DL.</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>DoTA/CCD sin clasificación por tipo de vía.</t>
+          <t>Comentario conciso para el anexo.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>R1138</t>
+          <t>R0943</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -10358,41 +10442,41 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>No desagrega urbano/autopista.</t>
+          <t>Sin procedimiento de selección ni conjunto de prueba.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>R1148</t>
+          <t>R0986</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Categoría de anomalía» → Evento/otro</t>
+          <t>Corregido «Comentario» → [Excluir CE-3] LSTM con IoT para pronosticar el flujo de autopista; menciona eventos anormales, pero no los etiqueta ni evalúa su detección.</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Objetos caídos sobre la calzada.</t>
+          <t>Comentario conciso para el anexo.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>R1148</t>
+          <t>R1000</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -10402,41 +10486,41 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → No reportada</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Solo dice que entrena y valida 100 épocas.</t>
+          <t>No indica qué escenas de NGSIM usa.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>R1166</t>
+          <t>R1010</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Corregido «CRITERIO» → CI-6</t>
+          <t>Corregido «Entorno» → No reportado</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
+          <t>Evaluado con autos de juguete en escenario controlado.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>R1185</t>
+          <t>R1013</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -10446,54 +10530,362 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Entorno» → No reportado</t>
+          <t>Corregido «Partición» → Prueba independiente</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>No clasifica las imágenes por tipo de vía.</t>
+          <t>Conjunto de prueba oficial de TADS.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>R1202</t>
+          <t>R1014</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Corregido «Partición» → Prueba independiente</t>
+          <t>Corregido «DECISIÓN TC» → Excluir</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Separación por sesiones de conducción.</t>
+          <t>DeepWalk/Node2vec no es Deep Learning; la anomalía la deciden SVDD y reglas.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
+          <t>R1014</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CE-4</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Sin componente profunda entrenada que decida la anomalía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>R1014</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «EVIDENCIA (cita y página)» → DeepWalk genera caminatas aleatorias y aprende embeddings con Skip-Gram; SVDD determina las regiones anómalas (sección 3, pp. 3-5); umbral de coincidencia de trayectorias anómalas 0,463 (sección 4.2, p. 6).</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Hoja 2 del autor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>R1014</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Comentario» → [Excluir CE-4] El detector es DeepWalk/Node2vec (embedding superficial, no DL) más SVDD, Apriori y umbrales.</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Motivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>R1014</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Familia DL principal» → Otra</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>DeepWalk/Node2vec no es una GNN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>R1082</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Conjunto de prueba de MAAD (con ajuste de hiperparámetros en parte de él).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>R1092</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Aleatoria</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>División 80/20 de videos sin otro criterio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>R1100</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>DoTA/CCD sin clasificación por tipo de vía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>R1138</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>No desagrega urbano/autopista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>R1148</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Categoría de anomalía» → Evento/otro</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Objetos caídos sobre la calzada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>R1148</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → No reportada</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Solo dice que entrena y valida 100 épocas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>R1166</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «CRITERIO» → CI-6</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>Es un sistema de detección de incidentes sin métricas de detección: es CI-6, no CE-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>R1166</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Comentario» → [Excluir CI-6] Plataforma de videovigilancia con detección y seguimiento de vehículos; muestra ejemplos de incidentes, pero no reporta métricas de detección.</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Coherente con CI-6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>R1185</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Entorno» → No reportado</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>No clasifica las imágenes por tipo de vía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>R1202</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Corregido «Partición» → Prueba independiente</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Separación por sesiones de conducción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
           <t>R1214</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>Corregido «Partición» → No reportada</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>No informa proporciones ni criterio de división.</t>
         </is>
